--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="305">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 10/04/2026 15:09:21</t>
+    <t xml:space="preserve">Emitido em: 14/04/2026 11:16:21</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -376,18 +376,6 @@
     <t xml:space="preserve">42260424546165000393550040000970501740544286</t>
   </si>
   <si>
-    <t xml:space="preserve">606.146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.800,37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006061461393273729</t>
-  </si>
-  <si>
     <t xml:space="preserve">605.229</t>
   </si>
   <si>
@@ -707,6 +695,189 @@
   </si>
   <si>
     <t xml:space="preserve">52260405104359000122550010000045981527339360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260430228132000136550010000087911857568506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260430228132000136550010000087901687286834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">862.382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.210,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008623821213560250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.925 - MOHAWK REVESTIMENTOS COCAL DO SUL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.378.595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.039,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260486532538003005550010013785951001161991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 - TRAMONTINA PLANALTO S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.224,34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260400142240000120550010007046171954588381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.386,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260417781412000109550010000119631000316094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.224 - RFN ACABAMENTOS COMERCIO DE MATERIAIS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.750,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260427440377000118550010000568731093817604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.957.630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.293,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260460561719009503550210019576301529415683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.008,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260430228132000136550010000088161997156414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.582 - GRUPO MARMO E HIME COMERCIO, IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.865,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260420587017000285550010000389281318138378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.462,51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260409306858000153550010000707721210311252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">862.414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.426,27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008624141130085348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.425,55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260410691158000370550010002907811035993548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.660 - DEXCO S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181005963550010000422981834106576</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -16952,7 +17123,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM57"/>
+  <dimension ref="A1:BM70"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -19043,7 +19214,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>304420</v>
+        <v>304445</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>81</v>
@@ -19064,43 +19235,43 @@
         <v>114</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>5800.37</v>
+        <v>6479.22</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>5800.37</v>
+        <v>6479.22</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.014226</v>
+        <v>0.002592</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>6.28</v>
+        <v>4.23</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
@@ -19112,10 +19283,10 @@
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>5800.37</v>
+        <v>6479.22</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>406.02</v>
+        <v>453.55</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19220,7 +19391,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19234,7 +19405,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>304445</v>
+        <v>304446</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>81</v>
@@ -19243,7 +19414,7 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>83</v>
@@ -19261,7 +19432,7 @@
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6479.22</v>
+        <v>1594.98</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19270,22 +19441,22 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6479.22</v>
+        <v>1594.98</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.002592</v>
+        <v>0.024948</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>4.23</v>
+        <v>0.86</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
@@ -19303,10 +19474,10 @@
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>6479.22</v>
+        <v>1594.98</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>453.55</v>
+        <v>111.65</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19411,7 +19582,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19425,7 +19596,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>304446</v>
+        <v>304447</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>81</v>
@@ -19434,25 +19605,25 @@
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>114</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>1594.98</v>
+        <v>3738.51</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19461,16 +19632,16 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>1594.98</v>
+        <v>3738.51</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.024948</v>
+        <v>0.007419</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0.86</v>
+        <v>2.29</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
@@ -19482,7 +19653,7 @@
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
@@ -19494,10 +19665,10 @@
         <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>1594.98</v>
+        <v>3738.51</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>111.65</v>
+        <v>261.7</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19616,64 +19787,64 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>304447</v>
+        <v>304507</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>114</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>3738.51</v>
+        <v>1062.84</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>3738.51</v>
+        <v>1062.84</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.007419</v>
+        <v>0.0491</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>2.29</v>
+        <v>8.27</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
@@ -19685,10 +19856,10 @@
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>3738.51</v>
+        <v>1062.84</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>261.7</v>
+        <v>74.39</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19754,7 +19925,7 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AX17" s="10" t="s">
         <v>77</v>
@@ -19793,7 +19964,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19807,52 +19978,52 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>304507</v>
+        <v>304509</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>114</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1062.84</v>
+        <v>6091.08</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>1062.84</v>
+        <v>6091.08</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.0491</v>
+        <v>0.016644</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>8.27</v>
+        <v>2.94</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
@@ -19864,7 +20035,7 @@
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
@@ -19876,10 +20047,10 @@
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>1062.84</v>
+        <v>6091.08</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>74.39</v>
+        <v>426.38</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19945,10 +20116,10 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX18" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="AX18" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -19998,7 +20169,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>304509</v>
+        <v>304535</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>81</v>
@@ -20013,19 +20184,19 @@
         <v>83</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>6091.08</v>
+        <v>2252.84</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20034,43 +20205,43 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>6091.08</v>
+        <v>2252.84</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.016644</v>
+        <v>0.017952</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>2.94</v>
+        <v>0.31</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>6091.08</v>
+        <v>2252.84</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>426.38</v>
+        <v>157.7</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20136,10 +20307,10 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20175,7 +20346,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20189,79 +20360,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>304535</v>
+        <v>304539</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2252.84</v>
+        <v>8164.47</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>2252.84</v>
+        <v>7361.7</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.017952</v>
+        <v>0.039555</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0.31</v>
+        <v>7.25</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>28</v>
+        <v>55.71</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>717.77</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>2252.84</v>
+        <v>7446.7</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>157.7</v>
+        <v>297.87</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20327,7 +20498,7 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX20" s="10" t="s">
         <v>77</v>
@@ -20366,7 +20537,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20380,10 +20551,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>304539</v>
+        <v>304625</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -20392,67 +20563,67 @@
         <v>149</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>8164.47</v>
+        <v>5607.1</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>7361.7</v>
+        <v>5264.88</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.039555</v>
+        <v>0.0582</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>7.25</v>
+        <v>12.69</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>55.71</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>717.77</v>
+        <v>342.22</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>7446.7</v>
+        <v>5264.88</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>297.87</v>
+        <v>368.54</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20518,10 +20689,10 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX21" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="AX21" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20557,7 +20728,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20571,7 +20742,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>304625</v>
+        <v>304627</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>81</v>
@@ -20580,43 +20751,43 @@
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>5607.1</v>
+        <v>2276.64</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>5264.88</v>
+        <v>2276.64</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.0582</v>
+        <v>0.014952</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>12.69</v>
+        <v>3.42</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
@@ -20628,22 +20799,22 @@
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>342.22</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>5264.88</v>
+        <v>2276.64</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>368.54</v>
+        <v>159.36</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20712,7 +20883,7 @@
         <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20762,7 +20933,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>304627</v>
+        <v>304628</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>81</v>
@@ -20777,10 +20948,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>157</v>
@@ -20789,7 +20960,7 @@
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>2276.64</v>
+        <v>927.64</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20798,16 +20969,16 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>2276.64</v>
+        <v>927.64</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.014952</v>
+        <v>0.007392</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>3.42</v>
+        <v>0.13</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
@@ -20819,22 +20990,22 @@
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>2276.64</v>
+        <v>927.64</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>159.36</v>
+        <v>64.93</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20953,34 +21124,34 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>304628</v>
+        <v>304650</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>927.64</v>
+        <v>885.6</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -20989,16 +21160,16 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>927.64</v>
+        <v>885.6</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.007392</v>
+        <v>0.0126</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0.13</v>
+        <v>2.52</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
@@ -21010,22 +21181,22 @@
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>927.64</v>
+        <v>885.6</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>64.93</v>
+        <v>35.42</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21091,10 +21262,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21144,7 +21315,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>304650</v>
+        <v>304655</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>164</v>
@@ -21156,67 +21327,67 @@
         <v>165</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>885.6</v>
+        <v>2761.93</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>885.6</v>
+        <v>2761.93</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.0126</v>
+        <v>0</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>885.6</v>
+        <v>2761.93</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>35.42</v>
+        <v>193.34</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21282,10 +21453,10 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21321,7 +21492,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21335,79 +21506,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>304655</v>
+        <v>304660</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>114</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2761.93</v>
+        <v>8059.31</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>2761.93</v>
+        <v>8059.31</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.157707</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0</v>
+        <v>179.53</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>2761.93</v>
+        <v>8059.31</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>193.34</v>
+        <v>564.16</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21473,7 +21644,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>77</v>
@@ -21512,7 +21683,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21526,52 +21697,52 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>304660</v>
+        <v>304662</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>114</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>8059.31</v>
+        <v>8337.39</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>8059.31</v>
+        <v>7596.72</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.157707</v>
+        <v>0</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>179.53</v>
+        <v>0</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
@@ -21583,22 +21754,22 @@
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>740.67</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>8059.31</v>
+        <v>7596.72</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>564.16</v>
+        <v>303.88</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21664,7 +21835,7 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX27" s="10" t="s">
         <v>77</v>
@@ -21717,7 +21888,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>304662</v>
+        <v>304664</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>179</v>
@@ -21735,25 +21906,25 @@
         <v>114</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>8337.39</v>
+        <v>1075.33</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>7596.72</v>
+        <v>979.8</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
@@ -21774,22 +21945,22 @@
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>740.67</v>
+        <v>95.53</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>7596.72</v>
+        <v>979.8</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>303.88</v>
+        <v>39.19</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21855,7 +22026,7 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX28" s="10" t="s">
         <v>77</v>
@@ -21908,7 +22079,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>304664</v>
+        <v>304667</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>183</v>
@@ -21920,67 +22091,67 @@
         <v>184</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>114</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1075.33</v>
+        <v>863.58</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>979.8</v>
+        <v>836.4</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0</v>
+        <v>0.00476</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>95.53</v>
+        <v>27.18</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>979.8</v>
+        <v>836.4</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>39.19</v>
+        <v>58.55</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22046,7 +22217,7 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX29" s="10" t="s">
         <v>77</v>
@@ -22085,7 +22256,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22099,34 +22270,34 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>304667</v>
+        <v>304671</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>863.58</v>
+        <v>1129.81</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22135,43 +22306,43 @@
         <v>2</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>836.4</v>
+        <v>1029.44</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.00476</v>
+        <v>0.014256</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>27.18</v>
+        <v>100.37</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>836.4</v>
+        <v>1029.44</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>58.55</v>
+        <v>72.06</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22237,7 +22408,7 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AX30" s="10" t="s">
         <v>77</v>
@@ -22276,7 +22447,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22290,10 +22461,10 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>304671</v>
+        <v>304692</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -22302,67 +22473,67 @@
         <v>193</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>144</v>
-      </c>
       <c r="I31" s="9" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1129.81</v>
+        <v>323.73</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>1029.44</v>
+        <v>323.73</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.014256</v>
+        <v>0.003838</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>100.37</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>1029.44</v>
+        <v>323.73</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>72.06</v>
+        <v>22.66</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22428,10 +22599,10 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22467,7 +22638,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22481,52 +22652,52 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>304692</v>
+        <v>304722</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="I32" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>323.73</v>
+        <v>16301.36</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>323.73</v>
+        <v>16082.24</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.003838</v>
+        <v>0.898646</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>1.08</v>
+        <v>113.2</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
@@ -22538,22 +22709,22 @@
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>0</v>
+        <v>219.12</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>323.73</v>
+        <v>16082.24</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>22.66</v>
+        <v>993.95</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22619,10 +22790,10 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AX32" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY32" s="14" t="s">
         <v>75</v>
@@ -22672,10 +22843,10 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>304722</v>
+        <v>304768</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -22684,40 +22855,40 @@
         <v>202</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>16301.36</v>
+        <v>2575.16</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>16082.24</v>
+        <v>2575.16</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.898646</v>
+        <v>0.01105</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>113.2</v>
+        <v>5.74</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
@@ -22729,22 +22900,22 @@
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>219.12</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>16082.24</v>
+        <v>2575.16</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>993.95</v>
+        <v>180.26</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22810,7 +22981,7 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AX33" s="10" t="s">
         <v>77</v>
@@ -22863,10 +23034,10 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>304768</v>
+        <v>304799</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -22875,22 +23046,22 @@
         <v>206</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I34" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>171</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>2575.16</v>
+        <v>2905.86</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -22899,16 +23070,16 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>2575.16</v>
+        <v>2905.86</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.01105</v>
+        <v>0.013842</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>5.74</v>
+        <v>11.95</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
@@ -22920,22 +23091,22 @@
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Y34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>2575.16</v>
+        <v>2905.86</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>180.26</v>
+        <v>203.41</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23001,7 +23172,7 @@
         <v>74</v>
       </c>
       <c r="AW34" s="14" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AX34" s="10" t="s">
         <v>77</v>
@@ -23054,10 +23225,10 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>304799</v>
+        <v>304828</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -23066,22 +23237,22 @@
         <v>210</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>2905.86</v>
+        <v>189.4</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23090,16 +23261,16 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>2905.86</v>
+        <v>177.84</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.013842</v>
+        <v>0.003626</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>11.95</v>
+        <v>0.83</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
@@ -23111,22 +23282,22 @@
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>0</v>
+        <v>11.56</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>2905.86</v>
+        <v>177.84</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>203.41</v>
+        <v>12.45</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23192,7 +23363,7 @@
         <v>74</v>
       </c>
       <c r="AW35" s="14" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AX35" s="10" t="s">
         <v>77</v>
@@ -23245,7 +23416,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>304828</v>
+        <v>304829</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>64</v>
@@ -23260,19 +23431,19 @@
         <v>66</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I36" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>215</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>171</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>189.4</v>
+        <v>10076.2</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -23281,16 +23452,16 @@
         <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>177.84</v>
+        <v>10076.2</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.003626</v>
+        <v>0.04</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>0.83</v>
+        <v>53.59</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
@@ -23302,22 +23473,22 @@
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>11.56</v>
+        <v>0</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>177.84</v>
+        <v>10076.2</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>12.45</v>
+        <v>705.33</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23436,7 +23607,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>304829</v>
+        <v>304844</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>64</v>
@@ -23451,19 +23622,19 @@
         <v>66</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>10076.2</v>
+        <v>738.32</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -23472,43 +23643,43 @@
         <v>1</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>10076.2</v>
+        <v>693.26</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.04</v>
+        <v>0.011556</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>53.59</v>
+        <v>1.23</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>0</v>
+        <v>45.06</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>10076.2</v>
+        <v>693.26</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>705.33</v>
+        <v>48.53</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23613,7 +23784,7 @@
         <v>78</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23627,10 +23798,10 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>304844</v>
+        <v>304868</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -23642,37 +23813,37 @@
         <v>66</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>738.32</v>
+        <v>6336.03</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>693.26</v>
+        <v>6336.03</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.011556</v>
+        <v>0.004185</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>1.23</v>
+        <v>3.07</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
@@ -23684,22 +23855,22 @@
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>28</v>
+        <v>60.67</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>45.06</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>693.26</v>
+        <v>6336.03</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>48.53</v>
+        <v>253.44</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23818,7 +23989,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>304868</v>
+        <v>304897</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>225</v>
@@ -23833,37 +24004,37 @@
         <v>66</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6336.03</v>
+        <v>39.92</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>6336.03</v>
+        <v>36.37</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.004185</v>
+        <v>0.00483</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
@@ -23875,22 +24046,22 @@
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>6336.03</v>
+        <v>36.37</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>253.44</v>
+        <v>2.55</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -23959,7 +24130,7 @@
         <v>76</v>
       </c>
       <c r="AX39" s="10" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AY39" s="14" t="s">
         <v>75</v>
@@ -24008,1016 +24179,3499 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4"/>
+      <c r="A40" s="8" t="n">
+        <v>304900</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>934.7</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" s="12" t="n">
+        <v>851.66</v>
+      </c>
+      <c r="P40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="13" t="n">
+        <v>0.03381</v>
+      </c>
+      <c r="R40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="U40" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V40" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="W40" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X40" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y40" s="12" t="n">
+        <v>83.04</v>
+      </c>
+      <c r="Z40" s="12" t="n">
+        <v>851.66</v>
+      </c>
+      <c r="AA40" s="12" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="AB40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW40" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX40" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG40" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI40" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ40" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="BK40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM40" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
+    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="n">
+        <v>304904</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>3210.71</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="O41" s="12" t="n">
+        <v>3150.8</v>
+      </c>
+      <c r="P41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="13" t="n">
+        <v>0.275443</v>
+      </c>
+      <c r="R41" s="12" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="S41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="U41" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V41" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="W41" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X41" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y41" s="12" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="Z41" s="12" t="n">
+        <v>3150.8</v>
+      </c>
+      <c r="AA41" s="12" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="AB41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW41" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX41" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG41" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI41" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ41" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="BK41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM41" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="42" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="J42" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K42" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M42" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="N42" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O42" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P42" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q42" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R42" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S42" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="T42" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="U42" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V42" s="18" t="s">
-        <v>37</v>
+    <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="n">
+        <v>304909</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>1039.92</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="12" t="n">
+        <v>1033.2</v>
+      </c>
+      <c r="P42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="13" t="n">
+        <v>0.00222</v>
+      </c>
+      <c r="R42" s="12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="U42" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V42" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="W42" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X42" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y42" s="12" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="Z42" s="12" t="n">
+        <v>1033.2</v>
+      </c>
+      <c r="AA42" s="12" t="n">
+        <v>72.32</v>
+      </c>
+      <c r="AB42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW42" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX42" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG42" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI42" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ42" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="BK42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM42" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="n">
-        <v>35</v>
-      </c>
-      <c r="B43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="19" t="n">
-        <v>85</v>
-      </c>
-      <c r="D43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="19" t="n">
-        <v>2653.22</v>
-      </c>
-      <c r="F43" s="19" t="n">
-        <v>120571.27</v>
-      </c>
-      <c r="G43" s="19" t="n">
-        <v>7598.75</v>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="19" t="n">
-        <v>123224.49</v>
-      </c>
-      <c r="L43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="20" t="n">
-        <v>1.621779</v>
-      </c>
-      <c r="S43" s="19" t="n">
-        <v>120486.27</v>
-      </c>
-      <c r="T43" s="19" t="n">
-        <v>123224.49</v>
-      </c>
-      <c r="U43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="19" t="n">
-        <v>0</v>
+      <c r="A43" s="8" t="n">
+        <v>304926</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>10224.34</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="12" t="n">
+        <v>10224.34</v>
+      </c>
+      <c r="P43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="13" t="n">
+        <v>0.114114</v>
+      </c>
+      <c r="R43" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="U43" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="W43" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X43" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="12" t="n">
+        <v>10224.34</v>
+      </c>
+      <c r="AA43" s="12" t="n">
+        <v>1226.92</v>
+      </c>
+      <c r="AB43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW43" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX43" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ43" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="BK43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM43" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I44" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K44" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="L44" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="M44" s="18" t="s">
-        <v>238</v>
+    <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="n">
+        <v>304944</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>8386</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O44" s="12" t="n">
+        <v>7641</v>
+      </c>
+      <c r="P44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="U44" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V44" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="W44" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X44" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y44" s="12" t="n">
+        <v>745</v>
+      </c>
+      <c r="Z44" s="12" t="n">
+        <v>7641</v>
+      </c>
+      <c r="AA44" s="12" t="n">
+        <v>305.64</v>
+      </c>
+      <c r="AB44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW44" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX44" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ44" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="BK44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM44" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="n">
-        <v>525.49</v>
-      </c>
-      <c r="B45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="19" t="n">
-        <v>41.81</v>
-      </c>
-      <c r="E45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="19" t="n">
-        <v>0</v>
+      <c r="A45" s="8" t="n">
+        <v>304970</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>9750.72</v>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O45" s="12" t="n">
+        <v>9750.72</v>
+      </c>
+      <c r="P45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="U45" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X45" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="12" t="n">
+        <v>9750.72</v>
+      </c>
+      <c r="AA45" s="12" t="n">
+        <v>390.03</v>
+      </c>
+      <c r="AB45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW45" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX45" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="AY45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ45" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="BK45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM45" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4"/>
+      <c r="A46" s="8" t="n">
+        <v>304984</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>70293.33</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="O46" s="12" t="n">
+        <v>70085.31</v>
+      </c>
+      <c r="P46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="13" t="n">
+        <v>36.524292</v>
+      </c>
+      <c r="R46" s="12" t="n">
+        <v>3660.57</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="U46" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="W46" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X46" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y46" s="12" t="n">
+        <v>208.02</v>
+      </c>
+      <c r="Z46" s="12" t="n">
+        <v>70085.31</v>
+      </c>
+      <c r="AA46" s="12" t="n">
+        <v>4667.44</v>
+      </c>
+      <c r="AB46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW46" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX46" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG46" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI46" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ46" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="BK46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM46" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="47" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="21"/>
-      <c r="N47" s="21"/>
-      <c r="O47" s="21"/>
-      <c r="P47" s="21"/>
-      <c r="Q47" s="21"/>
-      <c r="R47" s="21"/>
-      <c r="S47" s="21"/>
-      <c r="T47" s="21"/>
-      <c r="U47" s="21"/>
-      <c r="V47" s="21"/>
-      <c r="W47" s="21"/>
-      <c r="X47" s="21"/>
-      <c r="Y47" s="21"/>
-      <c r="Z47" s="21"/>
-      <c r="AA47" s="21"/>
-      <c r="AB47" s="21"/>
-      <c r="AC47" s="21"/>
-      <c r="AD47" s="21"/>
-      <c r="AE47" s="21"/>
-      <c r="AF47" s="21"/>
-      <c r="AG47" s="21"/>
-      <c r="AH47" s="21"/>
-      <c r="AI47" s="21"/>
-      <c r="AJ47" s="21"/>
-      <c r="AK47" s="21"/>
-      <c r="AL47" s="21"/>
-      <c r="AM47" s="21"/>
-      <c r="AN47" s="21"/>
-      <c r="AO47" s="21"/>
-      <c r="AP47" s="21"/>
-      <c r="AQ47" s="21"/>
-      <c r="AR47" s="21"/>
-      <c r="AS47" s="21"/>
-      <c r="AT47" s="21"/>
-      <c r="AU47" s="21"/>
-      <c r="AV47" s="21"/>
-      <c r="AW47" s="21"/>
-      <c r="AX47" s="21"/>
-      <c r="AY47" s="21"/>
-      <c r="AZ47" s="21"/>
-      <c r="BA47" s="21"/>
-      <c r="BB47" s="21"/>
-      <c r="BC47" s="21"/>
-      <c r="BD47" s="21"/>
-      <c r="BE47" s="21"/>
-      <c r="BF47" s="21"/>
-      <c r="BG47" s="21"/>
-      <c r="BH47" s="21"/>
-      <c r="BI47" s="21"/>
-      <c r="BJ47" s="21"/>
-      <c r="BK47" s="21"/>
-      <c r="BL47" s="21"/>
-      <c r="BM47" s="21"/>
+    <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="n">
+        <v>304986</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L47" s="12" t="n">
+        <v>1008.04</v>
+      </c>
+      <c r="M47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O47" s="12" t="n">
+        <v>918.49</v>
+      </c>
+      <c r="P47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="13" t="n">
+        <v>0.302016</v>
+      </c>
+      <c r="R47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="U47" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V47" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="W47" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X47" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y47" s="12" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="Z47" s="12" t="n">
+        <v>918.49</v>
+      </c>
+      <c r="AA47" s="12" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AB47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW47" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX47" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF47" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG47" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI47" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ47" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="BK47" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL47" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM47" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
-      <c r="AB48" s="4"/>
-      <c r="AC48" s="4"/>
-      <c r="AD48" s="4"/>
-      <c r="AE48" s="4"/>
-      <c r="AF48" s="4"/>
-      <c r="AG48" s="4"/>
-      <c r="AH48" s="4"/>
-      <c r="AI48" s="4"/>
-      <c r="AJ48" s="4"/>
-      <c r="AK48" s="4"/>
-      <c r="AL48" s="4"/>
-      <c r="AM48" s="4"/>
-      <c r="AN48" s="4"/>
-      <c r="AO48" s="4"/>
-      <c r="AP48" s="4"/>
-      <c r="AQ48" s="4"/>
-      <c r="AR48" s="4"/>
-      <c r="AS48" s="4"/>
-      <c r="AT48" s="4"/>
-      <c r="AU48" s="4"/>
-      <c r="AV48" s="4"/>
-      <c r="AW48" s="4"/>
-      <c r="AX48" s="4"/>
-      <c r="AY48" s="4"/>
-      <c r="AZ48" s="4"/>
-      <c r="BA48" s="4"/>
-      <c r="BB48" s="4"/>
-      <c r="BC48" s="4"/>
-      <c r="BD48" s="4"/>
-      <c r="BE48" s="4"/>
-      <c r="BF48" s="4"/>
-      <c r="BG48" s="4"/>
-      <c r="BH48" s="4"/>
-      <c r="BI48" s="4"/>
-      <c r="BJ48" s="4"/>
-      <c r="BK48" s="4"/>
-      <c r="BL48" s="4"/>
-      <c r="BM48" s="4"/>
+      <c r="A48" s="8" t="n">
+        <v>304994</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L48" s="12" t="n">
+        <v>1865.26</v>
+      </c>
+      <c r="M48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" s="12" t="n">
+        <v>1661</v>
+      </c>
+      <c r="P48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="U48" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V48" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="W48" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X48" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y48" s="12" t="n">
+        <v>204.26</v>
+      </c>
+      <c r="Z48" s="12" t="n">
+        <v>1661</v>
+      </c>
+      <c r="AA48" s="12" t="n">
+        <v>66.44</v>
+      </c>
+      <c r="AB48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW48" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX48" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG48" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI48" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ48" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="BK48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM48" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
-      <c r="AB49" s="4"/>
-      <c r="AC49" s="4"/>
-      <c r="AD49" s="4"/>
-      <c r="AE49" s="4"/>
-      <c r="AF49" s="4"/>
-      <c r="AG49" s="4"/>
-      <c r="AH49" s="4"/>
-      <c r="AI49" s="4"/>
-      <c r="AJ49" s="4"/>
-      <c r="AK49" s="4"/>
-      <c r="AL49" s="4"/>
-      <c r="AM49" s="4"/>
-      <c r="AN49" s="4"/>
-      <c r="AO49" s="4"/>
-      <c r="AP49" s="4"/>
-      <c r="AQ49" s="4"/>
-      <c r="AR49" s="4"/>
-      <c r="AS49" s="4"/>
-      <c r="AT49" s="4"/>
-      <c r="AU49" s="4"/>
-      <c r="AV49" s="4"/>
-      <c r="AW49" s="4"/>
-      <c r="AX49" s="4"/>
-      <c r="AY49" s="4"/>
-      <c r="AZ49" s="4"/>
-      <c r="BA49" s="4"/>
-      <c r="BB49" s="4"/>
-      <c r="BC49" s="4"/>
-      <c r="BD49" s="4"/>
-      <c r="BE49" s="4"/>
-      <c r="BF49" s="4"/>
-      <c r="BG49" s="4"/>
-      <c r="BH49" s="4"/>
-      <c r="BI49" s="4"/>
-      <c r="BJ49" s="4"/>
-      <c r="BK49" s="4"/>
-      <c r="BL49" s="4"/>
-      <c r="BM49" s="4"/>
+      <c r="A49" s="8" t="n">
+        <v>304995</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <v>12462.51</v>
+      </c>
+      <c r="M49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O49" s="12" t="n">
+        <v>11355.36</v>
+      </c>
+      <c r="P49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="13" t="n">
+        <v>0.11544</v>
+      </c>
+      <c r="R49" s="12" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="S49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="U49" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V49" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="W49" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X49" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y49" s="12" t="n">
+        <v>1107.15</v>
+      </c>
+      <c r="Z49" s="12" t="n">
+        <v>11355.36</v>
+      </c>
+      <c r="AA49" s="12" t="n">
+        <v>794.87</v>
+      </c>
+      <c r="AB49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW49" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX49" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG49" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI49" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ49" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="BK49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM49" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="4"/>
-      <c r="AD50" s="4"/>
-      <c r="AE50" s="4"/>
-      <c r="AF50" s="4"/>
-      <c r="AG50" s="4"/>
-      <c r="AH50" s="4"/>
-      <c r="AI50" s="4"/>
-      <c r="AJ50" s="4"/>
-      <c r="AK50" s="4"/>
-      <c r="AL50" s="4"/>
-      <c r="AM50" s="4"/>
-      <c r="AN50" s="4"/>
-      <c r="AO50" s="4"/>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="4"/>
-      <c r="AR50" s="4"/>
-      <c r="AS50" s="4"/>
-      <c r="AT50" s="4"/>
-      <c r="AU50" s="4"/>
-      <c r="AV50" s="4"/>
-      <c r="AW50" s="4"/>
-      <c r="AX50" s="4"/>
-      <c r="AY50" s="4"/>
-      <c r="AZ50" s="4"/>
-      <c r="BA50" s="4"/>
-      <c r="BB50" s="4"/>
-      <c r="BC50" s="4"/>
-      <c r="BD50" s="4"/>
-      <c r="BE50" s="4"/>
-      <c r="BF50" s="4"/>
-      <c r="BG50" s="4"/>
-      <c r="BH50" s="4"/>
-      <c r="BI50" s="4"/>
-      <c r="BJ50" s="4"/>
-      <c r="BK50" s="4"/>
-      <c r="BL50" s="4"/>
-      <c r="BM50" s="4"/>
+      <c r="A50" s="8" t="n">
+        <v>304996</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>2426.27</v>
+      </c>
+      <c r="M50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O50" s="12" t="n">
+        <v>2349.89</v>
+      </c>
+      <c r="P50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="U50" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X50" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y50" s="12" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="Z50" s="12" t="n">
+        <v>2426.27</v>
+      </c>
+      <c r="AA50" s="12" t="n">
+        <v>169.84</v>
+      </c>
+      <c r="AB50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW50" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX50" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="AY50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG50" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI50" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ50" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="BK50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM50" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
-      <c r="AF51" s="4"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="4"/>
-      <c r="AI51" s="4"/>
-      <c r="AJ51" s="4"/>
-      <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AM51" s="4"/>
-      <c r="AN51" s="4"/>
-      <c r="AO51" s="4"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="4"/>
-      <c r="AR51" s="4"/>
-      <c r="AS51" s="4"/>
-      <c r="AT51" s="4"/>
-      <c r="AU51" s="4"/>
-      <c r="AV51" s="4"/>
-      <c r="AW51" s="4"/>
-      <c r="AX51" s="4"/>
-      <c r="AY51" s="4"/>
-      <c r="AZ51" s="4"/>
-      <c r="BA51" s="4"/>
-      <c r="BB51" s="4"/>
-      <c r="BC51" s="4"/>
-      <c r="BD51" s="4"/>
-      <c r="BE51" s="4"/>
-      <c r="BF51" s="4"/>
-      <c r="BG51" s="4"/>
-      <c r="BH51" s="4"/>
-      <c r="BI51" s="4"/>
-      <c r="BJ51" s="4"/>
-      <c r="BK51" s="4"/>
-      <c r="BL51" s="4"/>
-      <c r="BM51" s="4"/>
+      <c r="A51" s="8" t="n">
+        <v>305016</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>9425.55</v>
+      </c>
+      <c r="M51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" s="12" t="n">
+        <v>8510.75</v>
+      </c>
+      <c r="P51" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q51" s="13" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="R51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="U51" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V51" s="12" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="W51" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X51" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y51" s="12" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="Z51" s="12" t="n">
+        <v>8595.75</v>
+      </c>
+      <c r="AA51" s="12" t="n">
+        <v>343.83</v>
+      </c>
+      <c r="AB51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW51" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX51" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF51" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG51" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI51" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ51" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="BK51" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL51" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM51" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
-      <c r="AB52" s="4"/>
-      <c r="AC52" s="4"/>
-      <c r="AD52" s="4"/>
-      <c r="AE52" s="4"/>
-      <c r="AF52" s="4"/>
-      <c r="AG52" s="4"/>
-      <c r="AH52" s="4"/>
-      <c r="AI52" s="4"/>
-      <c r="AJ52" s="4"/>
-      <c r="AK52" s="4"/>
-      <c r="AL52" s="4"/>
-      <c r="AM52" s="4"/>
-      <c r="AN52" s="4"/>
-      <c r="AO52" s="4"/>
-      <c r="AP52" s="4"/>
-      <c r="AQ52" s="4"/>
-      <c r="AR52" s="4"/>
-      <c r="AS52" s="4"/>
-      <c r="AT52" s="4"/>
-      <c r="AU52" s="4"/>
-      <c r="AV52" s="4"/>
-      <c r="AW52" s="4"/>
-      <c r="AX52" s="4"/>
-      <c r="AY52" s="4"/>
-      <c r="AZ52" s="4"/>
-      <c r="BA52" s="4"/>
-      <c r="BB52" s="4"/>
-      <c r="BC52" s="4"/>
-      <c r="BD52" s="4"/>
-      <c r="BE52" s="4"/>
-      <c r="BF52" s="4"/>
-      <c r="BG52" s="4"/>
-      <c r="BH52" s="4"/>
-      <c r="BI52" s="4"/>
-      <c r="BJ52" s="4"/>
-      <c r="BK52" s="4"/>
-      <c r="BL52" s="4"/>
-      <c r="BM52" s="4"/>
+      <c r="A52" s="8" t="n">
+        <v>305035</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="M52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="P52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="13" t="n">
+        <v>0.859248</v>
+      </c>
+      <c r="R52" s="12" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="S52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="U52" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X52" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="AA52" s="12" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="AB52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW52" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX52" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AY52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF52" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG52" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI52" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ52" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="BK52" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL52" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM52" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AD53" s="4"/>
-      <c r="AE53" s="4"/>
-      <c r="AF53" s="4"/>
-      <c r="AG53" s="4"/>
-      <c r="AH53" s="4"/>
-      <c r="AI53" s="4"/>
-      <c r="AJ53" s="4"/>
-      <c r="AK53" s="4"/>
-      <c r="AL53" s="4"/>
-      <c r="AM53" s="4"/>
-      <c r="AN53" s="4"/>
-      <c r="AO53" s="4"/>
-      <c r="AP53" s="4"/>
-      <c r="AQ53" s="4"/>
-      <c r="AR53" s="4"/>
-      <c r="AS53" s="4"/>
-      <c r="AT53" s="4"/>
-      <c r="AU53" s="4"/>
-      <c r="AV53" s="4"/>
-      <c r="AW53" s="4"/>
-      <c r="AX53" s="4"/>
-      <c r="AY53" s="4"/>
-      <c r="AZ53" s="4"/>
-      <c r="BA53" s="4"/>
-      <c r="BB53" s="4"/>
-      <c r="BC53" s="4"/>
-      <c r="BD53" s="4"/>
-      <c r="BE53" s="4"/>
-      <c r="BF53" s="4"/>
-      <c r="BG53" s="4"/>
-      <c r="BH53" s="4"/>
-      <c r="BI53" s="4"/>
-      <c r="BJ53" s="4"/>
-      <c r="BK53" s="4"/>
-      <c r="BL53" s="4"/>
-      <c r="BM53" s="4"/>
+      <c r="A53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
-      <c r="AB54" s="4"/>
-      <c r="AC54" s="4"/>
-      <c r="AD54" s="4"/>
-      <c r="AE54" s="4"/>
-      <c r="AF54" s="4"/>
-      <c r="AG54" s="4"/>
-      <c r="AH54" s="4"/>
-      <c r="AI54" s="4"/>
-      <c r="AJ54" s="4"/>
-      <c r="AK54" s="4"/>
-      <c r="AL54" s="4"/>
-      <c r="AM54" s="4"/>
-      <c r="AN54" s="4"/>
-      <c r="AO54" s="4"/>
-      <c r="AP54" s="4"/>
-      <c r="AQ54" s="4"/>
-      <c r="AR54" s="4"/>
-      <c r="AS54" s="4"/>
-      <c r="AT54" s="4"/>
-      <c r="AU54" s="4"/>
-      <c r="AV54" s="4"/>
-      <c r="AW54" s="4"/>
-      <c r="AX54" s="4"/>
-      <c r="AY54" s="4"/>
-      <c r="AZ54" s="4"/>
-      <c r="BA54" s="4"/>
-      <c r="BB54" s="4"/>
-      <c r="BC54" s="4"/>
-      <c r="BD54" s="4"/>
-      <c r="BE54" s="4"/>
-      <c r="BF54" s="4"/>
-      <c r="BG54" s="4"/>
-      <c r="BH54" s="4"/>
-      <c r="BI54" s="4"/>
-      <c r="BJ54" s="4"/>
-      <c r="BK54" s="4"/>
-      <c r="BL54" s="4"/>
-      <c r="BM54" s="4"/>
+    <row r="54" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="17"/>
     </row>
-    <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="4"/>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="4"/>
-      <c r="AB55" s="4"/>
-      <c r="AC55" s="4"/>
-      <c r="AD55" s="4"/>
-      <c r="AE55" s="4"/>
-      <c r="AF55" s="4"/>
-      <c r="AG55" s="4"/>
-      <c r="AH55" s="4"/>
-      <c r="AI55" s="4"/>
-      <c r="AJ55" s="4"/>
-      <c r="AK55" s="4"/>
-      <c r="AL55" s="4"/>
-      <c r="AM55" s="4"/>
-      <c r="AN55" s="4"/>
-      <c r="AO55" s="4"/>
-      <c r="AP55" s="4"/>
-      <c r="AQ55" s="4"/>
-      <c r="AR55" s="4"/>
-      <c r="AS55" s="4"/>
-      <c r="AT55" s="4"/>
-      <c r="AU55" s="4"/>
-      <c r="AV55" s="4"/>
-      <c r="AW55" s="4"/>
-      <c r="AX55" s="4"/>
-      <c r="AY55" s="4"/>
-      <c r="AZ55" s="4"/>
-      <c r="BA55" s="4"/>
-      <c r="BB55" s="4"/>
-      <c r="BC55" s="4"/>
-      <c r="BD55" s="4"/>
-      <c r="BE55" s="4"/>
-      <c r="BF55" s="4"/>
-      <c r="BG55" s="4"/>
-      <c r="BH55" s="4"/>
-      <c r="BI55" s="4"/>
-      <c r="BJ55" s="4"/>
-      <c r="BK55" s="4"/>
-      <c r="BL55" s="4"/>
-      <c r="BM55" s="4"/>
+    <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L55" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M55" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="N55" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O55" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P55" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q55" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R55" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S55" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="T55" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="U55" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V55" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
-      <c r="AB56" s="4"/>
-      <c r="AC56" s="4"/>
-      <c r="AD56" s="4"/>
-      <c r="AE56" s="4"/>
-      <c r="AF56" s="4"/>
-      <c r="AG56" s="4"/>
-      <c r="AH56" s="4"/>
-      <c r="AI56" s="4"/>
-      <c r="AJ56" s="4"/>
-      <c r="AK56" s="4"/>
-      <c r="AL56" s="4"/>
-      <c r="AM56" s="4"/>
-      <c r="AN56" s="4"/>
-      <c r="AO56" s="4"/>
-      <c r="AP56" s="4"/>
-      <c r="AQ56" s="4"/>
-      <c r="AR56" s="4"/>
-      <c r="AS56" s="4"/>
-      <c r="AT56" s="4"/>
-      <c r="AU56" s="4"/>
-      <c r="AV56" s="4"/>
-      <c r="AW56" s="4"/>
-      <c r="AX56" s="4"/>
-      <c r="AY56" s="4"/>
-      <c r="AZ56" s="4"/>
-      <c r="BA56" s="4"/>
-      <c r="BB56" s="4"/>
-      <c r="BC56" s="4"/>
-      <c r="BD56" s="4"/>
-      <c r="BE56" s="4"/>
-      <c r="BF56" s="4"/>
-      <c r="BG56" s="4"/>
-      <c r="BH56" s="4"/>
-      <c r="BI56" s="4"/>
-      <c r="BJ56" s="4"/>
-      <c r="BK56" s="4"/>
-      <c r="BL56" s="4"/>
-      <c r="BM56" s="4"/>
+      <c r="A56" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>170</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>6066.6</v>
+      </c>
+      <c r="F56" s="19" t="n">
+        <v>243335.57</v>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>15568.01</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="19" t="n">
+        <v>249325.79</v>
+      </c>
+      <c r="L56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="20" t="n">
+        <v>39.855216</v>
+      </c>
+      <c r="S56" s="19" t="n">
+        <v>243089.19</v>
+      </c>
+      <c r="T56" s="19" t="n">
+        <v>249325.79</v>
+      </c>
+      <c r="U56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
-      <c r="Z57" s="4"/>
-      <c r="AA57" s="4"/>
-      <c r="AB57" s="4"/>
-      <c r="AC57" s="4"/>
-      <c r="AD57" s="4"/>
-      <c r="AE57" s="4"/>
-      <c r="AF57" s="4"/>
-      <c r="AG57" s="4"/>
-      <c r="AH57" s="4"/>
-      <c r="AI57" s="4"/>
-      <c r="AJ57" s="4"/>
-      <c r="AK57" s="4"/>
-      <c r="AL57" s="4"/>
-      <c r="AM57" s="4"/>
-      <c r="AN57" s="4"/>
-      <c r="AO57" s="4"/>
-      <c r="AP57" s="4"/>
-      <c r="AQ57" s="4"/>
-      <c r="AR57" s="4"/>
-      <c r="AS57" s="4"/>
-      <c r="AT57" s="4"/>
-      <c r="AU57" s="4"/>
-      <c r="AV57" s="4"/>
-      <c r="AW57" s="4"/>
-      <c r="AX57" s="4"/>
-      <c r="AY57" s="4"/>
-      <c r="AZ57" s="4"/>
-      <c r="BA57" s="4"/>
-      <c r="BB57" s="4"/>
-      <c r="BC57" s="4"/>
-      <c r="BD57" s="4"/>
-      <c r="BE57" s="4"/>
-      <c r="BF57" s="4"/>
-      <c r="BG57" s="4"/>
-      <c r="BH57" s="4"/>
-      <c r="BI57" s="4"/>
-      <c r="BJ57" s="4"/>
-      <c r="BK57" s="4"/>
-      <c r="BL57" s="4"/>
-      <c r="BM57" s="4"/>
+    <row r="57" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="L57" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="M57" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="19" t="n">
+        <v>4313.71</v>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="21"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21"/>
+      <c r="O60" s="21"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="21"/>
+      <c r="R60" s="21"/>
+      <c r="S60" s="21"/>
+      <c r="T60" s="21"/>
+      <c r="U60" s="21"/>
+      <c r="V60" s="21"/>
+      <c r="W60" s="21"/>
+      <c r="X60" s="21"/>
+      <c r="Y60" s="21"/>
+      <c r="Z60" s="21"/>
+      <c r="AA60" s="21"/>
+      <c r="AB60" s="21"/>
+      <c r="AC60" s="21"/>
+      <c r="AD60" s="21"/>
+      <c r="AE60" s="21"/>
+      <c r="AF60" s="21"/>
+      <c r="AG60" s="21"/>
+      <c r="AH60" s="21"/>
+      <c r="AI60" s="21"/>
+      <c r="AJ60" s="21"/>
+      <c r="AK60" s="21"/>
+      <c r="AL60" s="21"/>
+      <c r="AM60" s="21"/>
+      <c r="AN60" s="21"/>
+      <c r="AO60" s="21"/>
+      <c r="AP60" s="21"/>
+      <c r="AQ60" s="21"/>
+      <c r="AR60" s="21"/>
+      <c r="AS60" s="21"/>
+      <c r="AT60" s="21"/>
+      <c r="AU60" s="21"/>
+      <c r="AV60" s="21"/>
+      <c r="AW60" s="21"/>
+      <c r="AX60" s="21"/>
+      <c r="AY60" s="21"/>
+      <c r="AZ60" s="21"/>
+      <c r="BA60" s="21"/>
+      <c r="BB60" s="21"/>
+      <c r="BC60" s="21"/>
+      <c r="BD60" s="21"/>
+      <c r="BE60" s="21"/>
+      <c r="BF60" s="21"/>
+      <c r="BG60" s="21"/>
+      <c r="BH60" s="21"/>
+      <c r="BI60" s="21"/>
+      <c r="BJ60" s="21"/>
+      <c r="BK60" s="21"/>
+      <c r="BL60" s="21"/>
+      <c r="BM60" s="21"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
+      <c r="AB61" s="4"/>
+      <c r="AC61" s="4"/>
+      <c r="AD61" s="4"/>
+      <c r="AE61" s="4"/>
+      <c r="AF61" s="4"/>
+      <c r="AG61" s="4"/>
+      <c r="AH61" s="4"/>
+      <c r="AI61" s="4"/>
+      <c r="AJ61" s="4"/>
+      <c r="AK61" s="4"/>
+      <c r="AL61" s="4"/>
+      <c r="AM61" s="4"/>
+      <c r="AN61" s="4"/>
+      <c r="AO61" s="4"/>
+      <c r="AP61" s="4"/>
+      <c r="AQ61" s="4"/>
+      <c r="AR61" s="4"/>
+      <c r="AS61" s="4"/>
+      <c r="AT61" s="4"/>
+      <c r="AU61" s="4"/>
+      <c r="AV61" s="4"/>
+      <c r="AW61" s="4"/>
+      <c r="AX61" s="4"/>
+      <c r="AY61" s="4"/>
+      <c r="AZ61" s="4"/>
+      <c r="BA61" s="4"/>
+      <c r="BB61" s="4"/>
+      <c r="BC61" s="4"/>
+      <c r="BD61" s="4"/>
+      <c r="BE61" s="4"/>
+      <c r="BF61" s="4"/>
+      <c r="BG61" s="4"/>
+      <c r="BH61" s="4"/>
+      <c r="BI61" s="4"/>
+      <c r="BJ61" s="4"/>
+      <c r="BK61" s="4"/>
+      <c r="BL61" s="4"/>
+      <c r="BM61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
+      <c r="AB62" s="4"/>
+      <c r="AC62" s="4"/>
+      <c r="AD62" s="4"/>
+      <c r="AE62" s="4"/>
+      <c r="AF62" s="4"/>
+      <c r="AG62" s="4"/>
+      <c r="AH62" s="4"/>
+      <c r="AI62" s="4"/>
+      <c r="AJ62" s="4"/>
+      <c r="AK62" s="4"/>
+      <c r="AL62" s="4"/>
+      <c r="AM62" s="4"/>
+      <c r="AN62" s="4"/>
+      <c r="AO62" s="4"/>
+      <c r="AP62" s="4"/>
+      <c r="AQ62" s="4"/>
+      <c r="AR62" s="4"/>
+      <c r="AS62" s="4"/>
+      <c r="AT62" s="4"/>
+      <c r="AU62" s="4"/>
+      <c r="AV62" s="4"/>
+      <c r="AW62" s="4"/>
+      <c r="AX62" s="4"/>
+      <c r="AY62" s="4"/>
+      <c r="AZ62" s="4"/>
+      <c r="BA62" s="4"/>
+      <c r="BB62" s="4"/>
+      <c r="BC62" s="4"/>
+      <c r="BD62" s="4"/>
+      <c r="BE62" s="4"/>
+      <c r="BF62" s="4"/>
+      <c r="BG62" s="4"/>
+      <c r="BH62" s="4"/>
+      <c r="BI62" s="4"/>
+      <c r="BJ62" s="4"/>
+      <c r="BK62" s="4"/>
+      <c r="BL62" s="4"/>
+      <c r="BM62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
+      <c r="AB63" s="4"/>
+      <c r="AC63" s="4"/>
+      <c r="AD63" s="4"/>
+      <c r="AE63" s="4"/>
+      <c r="AF63" s="4"/>
+      <c r="AG63" s="4"/>
+      <c r="AH63" s="4"/>
+      <c r="AI63" s="4"/>
+      <c r="AJ63" s="4"/>
+      <c r="AK63" s="4"/>
+      <c r="AL63" s="4"/>
+      <c r="AM63" s="4"/>
+      <c r="AN63" s="4"/>
+      <c r="AO63" s="4"/>
+      <c r="AP63" s="4"/>
+      <c r="AQ63" s="4"/>
+      <c r="AR63" s="4"/>
+      <c r="AS63" s="4"/>
+      <c r="AT63" s="4"/>
+      <c r="AU63" s="4"/>
+      <c r="AV63" s="4"/>
+      <c r="AW63" s="4"/>
+      <c r="AX63" s="4"/>
+      <c r="AY63" s="4"/>
+      <c r="AZ63" s="4"/>
+      <c r="BA63" s="4"/>
+      <c r="BB63" s="4"/>
+      <c r="BC63" s="4"/>
+      <c r="BD63" s="4"/>
+      <c r="BE63" s="4"/>
+      <c r="BF63" s="4"/>
+      <c r="BG63" s="4"/>
+      <c r="BH63" s="4"/>
+      <c r="BI63" s="4"/>
+      <c r="BJ63" s="4"/>
+      <c r="BK63" s="4"/>
+      <c r="BL63" s="4"/>
+      <c r="BM63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="4"/>
+      <c r="AD64" s="4"/>
+      <c r="AE64" s="4"/>
+      <c r="AF64" s="4"/>
+      <c r="AG64" s="4"/>
+      <c r="AH64" s="4"/>
+      <c r="AI64" s="4"/>
+      <c r="AJ64" s="4"/>
+      <c r="AK64" s="4"/>
+      <c r="AL64" s="4"/>
+      <c r="AM64" s="4"/>
+      <c r="AN64" s="4"/>
+      <c r="AO64" s="4"/>
+      <c r="AP64" s="4"/>
+      <c r="AQ64" s="4"/>
+      <c r="AR64" s="4"/>
+      <c r="AS64" s="4"/>
+      <c r="AT64" s="4"/>
+      <c r="AU64" s="4"/>
+      <c r="AV64" s="4"/>
+      <c r="AW64" s="4"/>
+      <c r="AX64" s="4"/>
+      <c r="AY64" s="4"/>
+      <c r="AZ64" s="4"/>
+      <c r="BA64" s="4"/>
+      <c r="BB64" s="4"/>
+      <c r="BC64" s="4"/>
+      <c r="BD64" s="4"/>
+      <c r="BE64" s="4"/>
+      <c r="BF64" s="4"/>
+      <c r="BG64" s="4"/>
+      <c r="BH64" s="4"/>
+      <c r="BI64" s="4"/>
+      <c r="BJ64" s="4"/>
+      <c r="BK64" s="4"/>
+      <c r="BL64" s="4"/>
+      <c r="BM64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4"/>
+      <c r="AD65" s="4"/>
+      <c r="AE65" s="4"/>
+      <c r="AF65" s="4"/>
+      <c r="AG65" s="4"/>
+      <c r="AH65" s="4"/>
+      <c r="AI65" s="4"/>
+      <c r="AJ65" s="4"/>
+      <c r="AK65" s="4"/>
+      <c r="AL65" s="4"/>
+      <c r="AM65" s="4"/>
+      <c r="AN65" s="4"/>
+      <c r="AO65" s="4"/>
+      <c r="AP65" s="4"/>
+      <c r="AQ65" s="4"/>
+      <c r="AR65" s="4"/>
+      <c r="AS65" s="4"/>
+      <c r="AT65" s="4"/>
+      <c r="AU65" s="4"/>
+      <c r="AV65" s="4"/>
+      <c r="AW65" s="4"/>
+      <c r="AX65" s="4"/>
+      <c r="AY65" s="4"/>
+      <c r="AZ65" s="4"/>
+      <c r="BA65" s="4"/>
+      <c r="BB65" s="4"/>
+      <c r="BC65" s="4"/>
+      <c r="BD65" s="4"/>
+      <c r="BE65" s="4"/>
+      <c r="BF65" s="4"/>
+      <c r="BG65" s="4"/>
+      <c r="BH65" s="4"/>
+      <c r="BI65" s="4"/>
+      <c r="BJ65" s="4"/>
+      <c r="BK65" s="4"/>
+      <c r="BL65" s="4"/>
+      <c r="BM65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="4"/>
+      <c r="AD66" s="4"/>
+      <c r="AE66" s="4"/>
+      <c r="AF66" s="4"/>
+      <c r="AG66" s="4"/>
+      <c r="AH66" s="4"/>
+      <c r="AI66" s="4"/>
+      <c r="AJ66" s="4"/>
+      <c r="AK66" s="4"/>
+      <c r="AL66" s="4"/>
+      <c r="AM66" s="4"/>
+      <c r="AN66" s="4"/>
+      <c r="AO66" s="4"/>
+      <c r="AP66" s="4"/>
+      <c r="AQ66" s="4"/>
+      <c r="AR66" s="4"/>
+      <c r="AS66" s="4"/>
+      <c r="AT66" s="4"/>
+      <c r="AU66" s="4"/>
+      <c r="AV66" s="4"/>
+      <c r="AW66" s="4"/>
+      <c r="AX66" s="4"/>
+      <c r="AY66" s="4"/>
+      <c r="AZ66" s="4"/>
+      <c r="BA66" s="4"/>
+      <c r="BB66" s="4"/>
+      <c r="BC66" s="4"/>
+      <c r="BD66" s="4"/>
+      <c r="BE66" s="4"/>
+      <c r="BF66" s="4"/>
+      <c r="BG66" s="4"/>
+      <c r="BH66" s="4"/>
+      <c r="BI66" s="4"/>
+      <c r="BJ66" s="4"/>
+      <c r="BK66" s="4"/>
+      <c r="BL66" s="4"/>
+      <c r="BM66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4"/>
+      <c r="AD67" s="4"/>
+      <c r="AE67" s="4"/>
+      <c r="AF67" s="4"/>
+      <c r="AG67" s="4"/>
+      <c r="AH67" s="4"/>
+      <c r="AI67" s="4"/>
+      <c r="AJ67" s="4"/>
+      <c r="AK67" s="4"/>
+      <c r="AL67" s="4"/>
+      <c r="AM67" s="4"/>
+      <c r="AN67" s="4"/>
+      <c r="AO67" s="4"/>
+      <c r="AP67" s="4"/>
+      <c r="AQ67" s="4"/>
+      <c r="AR67" s="4"/>
+      <c r="AS67" s="4"/>
+      <c r="AT67" s="4"/>
+      <c r="AU67" s="4"/>
+      <c r="AV67" s="4"/>
+      <c r="AW67" s="4"/>
+      <c r="AX67" s="4"/>
+      <c r="AY67" s="4"/>
+      <c r="AZ67" s="4"/>
+      <c r="BA67" s="4"/>
+      <c r="BB67" s="4"/>
+      <c r="BC67" s="4"/>
+      <c r="BD67" s="4"/>
+      <c r="BE67" s="4"/>
+      <c r="BF67" s="4"/>
+      <c r="BG67" s="4"/>
+      <c r="BH67" s="4"/>
+      <c r="BI67" s="4"/>
+      <c r="BJ67" s="4"/>
+      <c r="BK67" s="4"/>
+      <c r="BL67" s="4"/>
+      <c r="BM67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
+      <c r="AB68" s="4"/>
+      <c r="AC68" s="4"/>
+      <c r="AD68" s="4"/>
+      <c r="AE68" s="4"/>
+      <c r="AF68" s="4"/>
+      <c r="AG68" s="4"/>
+      <c r="AH68" s="4"/>
+      <c r="AI68" s="4"/>
+      <c r="AJ68" s="4"/>
+      <c r="AK68" s="4"/>
+      <c r="AL68" s="4"/>
+      <c r="AM68" s="4"/>
+      <c r="AN68" s="4"/>
+      <c r="AO68" s="4"/>
+      <c r="AP68" s="4"/>
+      <c r="AQ68" s="4"/>
+      <c r="AR68" s="4"/>
+      <c r="AS68" s="4"/>
+      <c r="AT68" s="4"/>
+      <c r="AU68" s="4"/>
+      <c r="AV68" s="4"/>
+      <c r="AW68" s="4"/>
+      <c r="AX68" s="4"/>
+      <c r="AY68" s="4"/>
+      <c r="AZ68" s="4"/>
+      <c r="BA68" s="4"/>
+      <c r="BB68" s="4"/>
+      <c r="BC68" s="4"/>
+      <c r="BD68" s="4"/>
+      <c r="BE68" s="4"/>
+      <c r="BF68" s="4"/>
+      <c r="BG68" s="4"/>
+      <c r="BH68" s="4"/>
+      <c r="BI68" s="4"/>
+      <c r="BJ68" s="4"/>
+      <c r="BK68" s="4"/>
+      <c r="BL68" s="4"/>
+      <c r="BM68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
+      <c r="AB69" s="4"/>
+      <c r="AC69" s="4"/>
+      <c r="AD69" s="4"/>
+      <c r="AE69" s="4"/>
+      <c r="AF69" s="4"/>
+      <c r="AG69" s="4"/>
+      <c r="AH69" s="4"/>
+      <c r="AI69" s="4"/>
+      <c r="AJ69" s="4"/>
+      <c r="AK69" s="4"/>
+      <c r="AL69" s="4"/>
+      <c r="AM69" s="4"/>
+      <c r="AN69" s="4"/>
+      <c r="AO69" s="4"/>
+      <c r="AP69" s="4"/>
+      <c r="AQ69" s="4"/>
+      <c r="AR69" s="4"/>
+      <c r="AS69" s="4"/>
+      <c r="AT69" s="4"/>
+      <c r="AU69" s="4"/>
+      <c r="AV69" s="4"/>
+      <c r="AW69" s="4"/>
+      <c r="AX69" s="4"/>
+      <c r="AY69" s="4"/>
+      <c r="AZ69" s="4"/>
+      <c r="BA69" s="4"/>
+      <c r="BB69" s="4"/>
+      <c r="BC69" s="4"/>
+      <c r="BD69" s="4"/>
+      <c r="BE69" s="4"/>
+      <c r="BF69" s="4"/>
+      <c r="BG69" s="4"/>
+      <c r="BH69" s="4"/>
+      <c r="BI69" s="4"/>
+      <c r="BJ69" s="4"/>
+      <c r="BK69" s="4"/>
+      <c r="BL69" s="4"/>
+      <c r="BM69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="4"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="4"/>
+      <c r="AB70" s="4"/>
+      <c r="AC70" s="4"/>
+      <c r="AD70" s="4"/>
+      <c r="AE70" s="4"/>
+      <c r="AF70" s="4"/>
+      <c r="AG70" s="4"/>
+      <c r="AH70" s="4"/>
+      <c r="AI70" s="4"/>
+      <c r="AJ70" s="4"/>
+      <c r="AK70" s="4"/>
+      <c r="AL70" s="4"/>
+      <c r="AM70" s="4"/>
+      <c r="AN70" s="4"/>
+      <c r="AO70" s="4"/>
+      <c r="AP70" s="4"/>
+      <c r="AQ70" s="4"/>
+      <c r="AR70" s="4"/>
+      <c r="AS70" s="4"/>
+      <c r="AT70" s="4"/>
+      <c r="AU70" s="4"/>
+      <c r="AV70" s="4"/>
+      <c r="AW70" s="4"/>
+      <c r="AX70" s="4"/>
+      <c r="AY70" s="4"/>
+      <c r="AZ70" s="4"/>
+      <c r="BA70" s="4"/>
+      <c r="BB70" s="4"/>
+      <c r="BC70" s="4"/>
+      <c r="BD70" s="4"/>
+      <c r="BE70" s="4"/>
+      <c r="BF70" s="4"/>
+      <c r="BG70" s="4"/>
+      <c r="BH70" s="4"/>
+      <c r="BI70" s="4"/>
+      <c r="BJ70" s="4"/>
+      <c r="BK70" s="4"/>
+      <c r="BL70" s="4"/>
+      <c r="BM70" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="64">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -25057,18 +27711,31 @@
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A41:V41"/>
-    <mergeCell ref="A47:BM47"/>
-    <mergeCell ref="A48:BM48"/>
-    <mergeCell ref="A49:BM49"/>
-    <mergeCell ref="A50:BM50"/>
-    <mergeCell ref="A51:BM51"/>
-    <mergeCell ref="A52:BM52"/>
-    <mergeCell ref="A53:BM53"/>
-    <mergeCell ref="A54:BM54"/>
-    <mergeCell ref="A55:BM55"/>
-    <mergeCell ref="A56:BM56"/>
-    <mergeCell ref="A57:BM57"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="A54:V54"/>
+    <mergeCell ref="A60:BM60"/>
+    <mergeCell ref="A61:BM61"/>
+    <mergeCell ref="A62:BM62"/>
+    <mergeCell ref="A63:BM63"/>
+    <mergeCell ref="A64:BM64"/>
+    <mergeCell ref="A65:BM65"/>
+    <mergeCell ref="A66:BM66"/>
+    <mergeCell ref="A67:BM67"/>
+    <mergeCell ref="A68:BM68"/>
+    <mergeCell ref="A69:BM69"/>
+    <mergeCell ref="A70:BM70"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="306">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 14/04/2026 11:16:21</t>
+    <t xml:space="preserve">Emitido em: 23/04/2026 10:36:38</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -214,670 +214,673 @@
     <t xml:space="preserve">Fornecedor substituto tributário</t>
   </si>
   <si>
+    <t xml:space="preserve">2.486 - ROCA SANITARIOS BRASIL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.343.413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">889,55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ag. chegada da mercadoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - OBJETIVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260375801902000126550000013434131048927560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.343.415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">276,66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260375801902000126550000013434151618096070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.343.414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260375801902000126550000013434141873933791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.343.412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260375801902000126550000013434121976241790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.075,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260417781412000109550010000119751000316214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260430228132000136550010000087911857568506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260430228132000136550010000087901687286834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">862.382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.210,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008623821213560250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.386,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260417781412000109550010000119631000316094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.008,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260430228132000136550010000088161997156414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.462,51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260409306858000153550010000707721210311252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">862.414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.426,27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008624141130085348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.784 - SEKAPISO METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.291,91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260460225604000168550030000521961913645534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.852,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293,73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260454542238000178550010000964221000962230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260411389565000200570050003974461000835918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">612.288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.003,36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006122881786143830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.116 - MS DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.610,21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260414624251000151550010000460071000339888</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
-    <t xml:space="preserve">5.046.966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">610,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ag. chegada da mercadoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - OBJETIVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260397837181002190550010050469661542221472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">604.224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.246,77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080006042241145994235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">603.983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.366,08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080006039831017770061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.051.934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050519341887948807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.486 - ROCA SANITARIOS BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.343.413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">889,55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260375801902000126550000013434131048927560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.343.415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">276,66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260375801902000126550000013434151618096070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.343.414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260375801902000126550000013434141873933791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.343.412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260375801902000126550000013434121976241790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.596 - LIGHT ENGINE ILUMINACAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.562,38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260424546165000393550040000970501740544286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">605.229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.479,22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006052291003233999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">605.166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.594,98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006051661162702576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">604.762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.738,51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080006047621159929676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.282.304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.062,84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260450949528001232550010022823041750754496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">607.634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.091,08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006076341263058314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">607.630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.252,84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006076301160805037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.164,47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260410691158000370550010002902441710668858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">608.709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.607,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006087091043760114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">608.906</t>
+    <t xml:space="preserve">5.064.035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">623,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640351505728166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">614.972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.219,97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006149721103161297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.208,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008632001044837440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">614.141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.851,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006141411310114120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">613.556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.174,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006135561160634441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.664 - STANDARD ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.598,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260456365423000160550010000114651525296163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.426,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260412077181000133550030002237391325182136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">752.149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.015,45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260409641520000158550010007521491440180220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.825,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260458329608000144550010002586861002586870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.974 - USINA DESIGN IND E COMERCIO DE ILUMINACAO LTDA-ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.495,06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260410713221000160550020000074001000087894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">612.541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.678,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006125411397554499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">392,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640381144694271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640391069291419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640401380951817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640461295961530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640471507052381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050643931146292179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050643941609242127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050643951603608712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">837,05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656021851619813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.323,32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656031864823799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656041505799080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314,65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656111652042051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656121082142336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656131260967511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167,35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656201014371157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656211192558439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656221375141585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">616.791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">839,95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006167911610794090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">616.993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006169931514728672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">617.417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.815,95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006174171379260766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">618.465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">19/05/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.276,64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006089061264633475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">608.934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">927,64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006089341764149399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">861.764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">885,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008617641610848012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.784 - SEKAPISO METALURGICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.761,93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460225604000168550030000521301305613030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.059,31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475821546000102550040001393891438281462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.934 - MUNDIAL IMP. E EXP. COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.337,39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260417716263000102550010000105801385454533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.059 - JLR COM IMPORT. E EXP. DE MATERIAIS DE CONSTRUCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.075,33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000119751000316214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863,58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260452618139002817550030008635131693669711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.974 - USINA DESIGN IND E COMERCIO DE ILUMINACAO LTDA-ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.129,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260410713221000160550020000070231000080973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">601.180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323,73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080006011801803612809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">861.765</t>
+    <t xml:space="preserve">454,32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006184651995060434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.961.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">837,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260460561719009503550210019610101643781317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.351.353</t>
   </si>
   <si>
     <t xml:space="preserve">01/06/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16.301,36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008617651313480433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">611.156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.575,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006111561560583517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.346.333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.905,86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260475801902000126550000013463331173120485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.056.772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050567721381156465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.056.773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.076,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050567731210987181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.056.790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">738,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050567901062582821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.628 - VFL IMPORTADORA E DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.336,03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52260405104359000122550010000045981527339360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260430228132000136550010000087911857568506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">934,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260430228132000136550010000087901687286834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">862.382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.210,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008623821213560250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.925 - MOHAWK REVESTIMENTOS COCAL DO SUL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.378.595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.039,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260486532538003005550010013785951001161991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 - TRAMONTINA PLANALTO S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.224,34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52260400142240000120550010007046171954588381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.386,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000119631000316094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.224 - RFN ACABAMENTOS COMERCIO DE MATERIAIS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.750,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260427440377000118550010000568731093817604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.957.630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.293,33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460561719009503550210019576301529415683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.008,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260430228132000136550010000088161997156414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.582 - GRUPO MARMO E HIME COMERCIO, IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.865,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260420587017000285550010000389281318138378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.462,51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260409306858000153550010000707721210311252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">862.414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.426,27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008624141130085348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.425,55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260410691158000370550010002907811035993548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.660 - DEXCO S.A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181005963550010000422981834106576</t>
+    <t xml:space="preserve">902,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013513531420684669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.419,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008638011323501589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.089 - OTTO BAUMGART INDUSTRIA E COMERCIO S A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830,75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260460642774001209550010002052231454537290</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17123,7 +17126,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM70"/>
+  <dimension ref="A1:BM74"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17495,7 +17498,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>304166</v>
+        <v>304398</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17522,7 +17525,7 @@
         <v>70</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>610.53</v>
+        <v>889.55</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>0</v>
@@ -17531,16 +17534,16 @@
         <v>1</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>573.27</v>
+        <v>889.55</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>3.9E-005</v>
+        <v>0.02343</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>0.92</v>
+        <v>15</v>
       </c>
       <c r="S5" s="12" t="n">
         <v>0</v>
@@ -17552,7 +17555,7 @@
         <v>72</v>
       </c>
       <c r="V5" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W5" s="9" t="s">
         <v>73</v>
@@ -17561,13 +17564,13 @@
         <v>68</v>
       </c>
       <c r="Y5" s="12" t="n">
-        <v>37.26</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>573.27</v>
+        <v>889.55</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>40.13</v>
+        <v>62.27</v>
       </c>
       <c r="AB5" s="12" t="n">
         <v>0</v>
@@ -17663,57 +17666,57 @@
         <v>75</v>
       </c>
       <c r="BG5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH5" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BH5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI5" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ5" s="9" t="s">
+      <c r="BK5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM5" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="BK5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM5" s="16" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>304222</v>
+        <v>304399</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>5246.77</v>
+        <v>276.66</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
@@ -17722,28 +17725,28 @@
         <v>1</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>5246.77</v>
+        <v>276.66</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.04634</v>
+        <v>0.01898</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>7</v>
+        <v>10.69</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>73</v>
@@ -17755,10 +17758,10 @@
         <v>0</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>5246.77</v>
+        <v>276.66</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>367.27</v>
+        <v>19.37</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17854,16 +17857,16 @@
         <v>75</v>
       </c>
       <c r="BG6" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH6" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI6" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="BK6" s="9" t="s">
         <v>75</v>
@@ -17872,39 +17875,39 @@
         <v>75</v>
       </c>
       <c r="BM6" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>304274</v>
+        <v>304400</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>68</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>5366.08</v>
+        <v>223.24</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17913,28 +17916,28 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>5366.08</v>
+        <v>223.24</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.005996</v>
+        <v>0.024685</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>4.19</v>
+        <v>12.5</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
@@ -17946,10 +17949,10 @@
         <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>5366.08</v>
+        <v>223.24</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>375.63</v>
+        <v>15.63</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -18045,16 +18048,16 @@
         <v>75</v>
       </c>
       <c r="BG7" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH7" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI7" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -18063,12 +18066,12 @@
         <v>75</v>
       </c>
       <c r="BM7" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>304394</v>
+        <v>304401</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>64</v>
@@ -18077,25 +18080,25 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>181.71</v>
+        <v>312.87</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -18104,22 +18107,22 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>181.71</v>
+        <v>312.87</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.022383</v>
+        <v>0.05088</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>0.95</v>
+        <v>23.14</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
@@ -18131,16 +18134,16 @@
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="Y8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>181.71</v>
+        <v>312.87</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>12.72</v>
+        <v>21.9</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18209,7 +18212,7 @@
         <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -18236,16 +18239,16 @@
         <v>75</v>
       </c>
       <c r="BG8" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH8" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI8" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18254,39 +18257,39 @@
         <v>75</v>
       </c>
       <c r="BM8" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>304398</v>
+        <v>304664</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>889.55</v>
+        <v>1075.33</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -18295,43 +18298,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>889.55</v>
+        <v>979.8</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.02343</v>
+        <v>0</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>0</v>
+        <v>95.53</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>889.55</v>
+        <v>979.8</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>62.27</v>
+        <v>39.19</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18397,10 +18400,10 @@
         <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18427,16 +18430,16 @@
         <v>75</v>
       </c>
       <c r="BG9" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH9" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI9" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18445,39 +18448,39 @@
         <v>75</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>304399</v>
+        <v>304897</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="J10" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>276.66</v>
+        <v>39.92</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18486,16 +18489,16 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>276.66</v>
+        <v>36.37</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.01898</v>
+        <v>0.00483</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>10.69</v>
+        <v>0</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
@@ -18513,16 +18516,16 @@
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>276.66</v>
+        <v>36.37</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>19.37</v>
+        <v>2.55</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18591,7 +18594,7 @@
         <v>76</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18618,16 +18621,16 @@
         <v>75</v>
       </c>
       <c r="BG10" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH10" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI10" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18636,84 +18639,84 @@
         <v>75</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>304400</v>
+        <v>304900</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>223.24</v>
+        <v>934.7</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>223.24</v>
+        <v>851.66</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.024685</v>
+        <v>0.03381</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>83.04</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>223.24</v>
+        <v>851.66</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>15.63</v>
+        <v>59.62</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18782,7 +18785,7 @@
         <v>76</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18809,16 +18812,16 @@
         <v>75</v>
       </c>
       <c r="BG11" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH11" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI11" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18827,84 +18830,84 @@
         <v>75</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>304401</v>
+        <v>304904</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>312.87</v>
+        <v>3210.71</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>312.87</v>
+        <v>3150.8</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.05088</v>
+        <v>0.275443</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>23.14</v>
+        <v>19.52</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>0</v>
+        <v>59.91</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>312.87</v>
+        <v>3150.8</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>21.9</v>
+        <v>178.1</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18970,10 +18973,10 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -19000,16 +19003,16 @@
         <v>75</v>
       </c>
       <c r="BG12" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH12" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI12" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19018,48 +19021,48 @@
         <v>75</v>
       </c>
       <c r="BM12" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>304419</v>
+        <v>304944</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>92</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>3562.38</v>
+        <v>8386</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>3245.9</v>
+        <v>7641</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
@@ -19068,34 +19071,34 @@
         <v>0</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>45.67</v>
+        <v>120</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>316.48</v>
+        <v>745</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>3245.9</v>
+        <v>7641</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>215.11</v>
+        <v>305.64</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19161,10 +19164,10 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19191,16 +19194,16 @@
         <v>75</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH13" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI13" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19209,84 +19212,84 @@
         <v>75</v>
       </c>
       <c r="BM13" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>304445</v>
+        <v>304986</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6479.22</v>
+        <v>1008.04</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6479.22</v>
+        <v>918.49</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.002592</v>
+        <v>0.302016</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>0</v>
+        <v>89.55</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>6479.22</v>
+        <v>918.49</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>453.55</v>
+        <v>64.3</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19352,10 +19355,10 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19382,16 +19385,16 @@
         <v>75</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH14" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI14" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19400,84 +19403,84 @@
         <v>75</v>
       </c>
       <c r="BM14" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>304446</v>
+        <v>304995</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>1594.98</v>
+        <v>12462.51</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>1594.98</v>
+        <v>11355.36</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.024948</v>
+        <v>0.11544</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0.86</v>
+        <v>33.12</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>0</v>
+        <v>1107.15</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>1594.98</v>
+        <v>11355.36</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>111.65</v>
+        <v>794.87</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19546,7 +19549,7 @@
         <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19573,16 +19576,16 @@
         <v>75</v>
       </c>
       <c r="BG15" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH15" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI15" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19591,84 +19594,84 @@
         <v>75</v>
       </c>
       <c r="BM15" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>304447</v>
+        <v>304996</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>3738.51</v>
+        <v>2426.27</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>3738.51</v>
+        <v>2349.89</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.007419</v>
+        <v>0</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>0</v>
+        <v>76.38</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>3738.51</v>
+        <v>2426.27</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>261.7</v>
+        <v>169.84</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19734,10 +19737,10 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19764,16 +19767,16 @@
         <v>75</v>
       </c>
       <c r="BG16" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH16" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI16" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19782,84 +19785,84 @@
         <v>75</v>
       </c>
       <c r="BM16" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>304507</v>
+        <v>305041</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1062.84</v>
+        <v>3291.91</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1062.84</v>
+        <v>3291.91</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.0491</v>
+        <v>0</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>8.27</v>
+        <v>0</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>1062.84</v>
+        <v>3291.91</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>74.39</v>
+        <v>230.45</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19925,10 +19928,10 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19955,16 +19958,16 @@
         <v>75</v>
       </c>
       <c r="BG17" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH17" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI17" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19973,84 +19976,84 @@
         <v>75</v>
       </c>
       <c r="BM17" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>304509</v>
+        <v>305066</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6091.08</v>
+        <v>3852.31</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>6091.08</v>
+        <v>3824.94</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.016644</v>
+        <v>3.68868</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>2.94</v>
+        <v>454.38</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>0</v>
+        <v>27.37</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>6091.08</v>
+        <v>3824.94</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>426.38</v>
+        <v>267.75</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20059,7 +20062,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="12" t="n">
-        <v>0</v>
+        <v>293.73</v>
       </c>
       <c r="AE18" s="12" t="n">
         <v>0</v>
@@ -20116,10 +20119,10 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20140,63 +20143,63 @@
         <v>75</v>
       </c>
       <c r="BE18" s="14" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="BF18" s="9" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="BG18" s="9" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="BH18" s="14" t="s">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="BI18" s="9" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="BK18" s="9" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="BL18" s="9" t="s">
         <v>75</v>
       </c>
       <c r="BM18" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>304535</v>
+        <v>305080</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>2252.84</v>
+        <v>6003.36</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20205,22 +20208,22 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>2252.84</v>
+        <v>5636.96</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.017952</v>
+        <v>0.034</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>0.31</v>
+        <v>6.39</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -20232,16 +20235,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>0</v>
+        <v>366.4</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>2252.84</v>
+        <v>5636.96</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>157.7</v>
+        <v>394.59</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20307,10 +20310,10 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20337,16 +20340,16 @@
         <v>75</v>
       </c>
       <c r="BG19" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH19" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI19" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20355,84 +20358,84 @@
         <v>75</v>
       </c>
       <c r="BM19" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>304539</v>
+        <v>305124</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>8164.47</v>
+        <v>4610.21</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>7361.7</v>
+        <v>4234.43</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.039555</v>
+        <v>0.4</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>7.25</v>
+        <v>8.4</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>55.71</v>
+        <v>56</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>717.77</v>
+        <v>375.78</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>7446.7</v>
+        <v>4234.43</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>297.87</v>
+        <v>180.79</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20498,10 +20501,10 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20528,16 +20531,16 @@
         <v>75</v>
       </c>
       <c r="BG20" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH20" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI20" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20546,84 +20549,84 @@
         <v>75</v>
       </c>
       <c r="BM20" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>304625</v>
+        <v>305173</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>5607.1</v>
+        <v>623.96</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>5264.88</v>
+        <v>585.88</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.0582</v>
+        <v>0.002772</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>12.69</v>
+        <v>2.92</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>342.22</v>
+        <v>38.08</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>5264.88</v>
+        <v>585.88</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>368.54</v>
+        <v>23.44</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20692,7 +20695,7 @@
         <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20719,16 +20722,16 @@
         <v>75</v>
       </c>
       <c r="BG21" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH21" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI21" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20737,63 +20740,63 @@
         <v>75</v>
       </c>
       <c r="BM21" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>304627</v>
+        <v>305189</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>83</v>
-      </c>
       <c r="H22" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2276.64</v>
+        <v>7219.97</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>2276.64</v>
+        <v>7219.97</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.014952</v>
+        <v>0.032582</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>3.42</v>
+        <v>5.54</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20805,16 +20808,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>2276.64</v>
+        <v>7219.97</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>159.36</v>
+        <v>505.4</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20880,10 +20883,10 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20910,16 +20913,16 @@
         <v>75</v>
       </c>
       <c r="BG22" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH22" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI22" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20928,84 +20931,84 @@
         <v>75</v>
       </c>
       <c r="BM22" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>304628</v>
+        <v>305201</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>927.64</v>
+        <v>7208.54</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>927.64</v>
+        <v>7102.95</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.007392</v>
+        <v>0.20059</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0.13</v>
+        <v>26.91</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0</v>
+        <v>105.59</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>927.64</v>
+        <v>7102.95</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>64.93</v>
+        <v>434.45</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21071,10 +21074,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21101,16 +21104,16 @@
         <v>75</v>
       </c>
       <c r="BG23" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH23" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI23" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21119,84 +21122,84 @@
         <v>75</v>
       </c>
       <c r="BM23" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>304650</v>
+        <v>305217</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>885.6</v>
+        <v>18851.64</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>885.6</v>
+        <v>18851.64</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.0126</v>
+        <v>0.050995</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>2.52</v>
+        <v>29.1</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>885.6</v>
+        <v>18851.64</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>35.42</v>
+        <v>1319.62</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21262,10 +21265,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21292,16 +21295,16 @@
         <v>75</v>
       </c>
       <c r="BG24" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH24" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI24" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21310,84 +21313,84 @@
         <v>75</v>
       </c>
       <c r="BM24" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>304655</v>
+        <v>305239</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>2761.93</v>
+        <v>3174.14</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>2761.93</v>
+        <v>3174.14</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0</v>
+        <v>0.032173</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>2761.93</v>
+        <v>3174.14</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>193.34</v>
+        <v>222.19</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21453,10 +21456,10 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21483,16 +21486,16 @@
         <v>75</v>
       </c>
       <c r="BG25" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH25" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI25" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21501,84 +21504,84 @@
         <v>75</v>
       </c>
       <c r="BM25" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>304660</v>
+        <v>305240</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>8059.31</v>
+        <v>1598.62</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>8059.31</v>
+        <v>1456.6</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.157707</v>
+        <v>0</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>179.53</v>
+        <v>0</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>0</v>
+        <v>142.02</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>8059.31</v>
+        <v>1456.6</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>564.16</v>
+        <v>101.96</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21644,10 +21647,10 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21674,16 +21677,16 @@
         <v>75</v>
       </c>
       <c r="BG26" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH26" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI26" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21692,84 +21695,84 @@
         <v>75</v>
       </c>
       <c r="BM26" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>304662</v>
+        <v>305242</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>8337.39</v>
+        <v>3426.16</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>7596.72</v>
+        <v>3145.39</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0</v>
+        <v>0.0061</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>740.67</v>
+        <v>280.77</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>7596.72</v>
+        <v>3145.39</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>303.88</v>
+        <v>220.19</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21835,10 +21838,10 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21865,16 +21868,16 @@
         <v>75</v>
       </c>
       <c r="BG27" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH27" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI27" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21883,84 +21886,84 @@
         <v>75</v>
       </c>
       <c r="BM27" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>304664</v>
+        <v>305244</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1075.33</v>
+        <v>3015.45</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>979.8</v>
+        <v>3015.45</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.176664</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0</v>
+        <v>14.03</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>95.53</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>979.8</v>
+        <v>3015.45</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>39.19</v>
+        <v>211.09</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22026,10 +22029,10 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22056,16 +22059,16 @@
         <v>75</v>
       </c>
       <c r="BG28" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH28" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI28" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22074,39 +22077,39 @@
         <v>75</v>
       </c>
       <c r="BM28" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>304667</v>
+        <v>305253</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>863.58</v>
+        <v>7825.28</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -22115,43 +22118,43 @@
         <v>2</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>836.4</v>
+        <v>7130.1</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.00476</v>
+        <v>0</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>14</v>
+        <v>44.58</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>27.18</v>
+        <v>695.18</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>836.4</v>
+        <v>7130.1</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>58.55</v>
+        <v>499.11</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22217,10 +22220,10 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22247,16 +22250,16 @@
         <v>75</v>
       </c>
       <c r="BG29" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH29" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI29" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22265,54 +22268,54 @@
         <v>75</v>
       </c>
       <c r="BM29" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>304671</v>
+        <v>305256</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>1129.81</v>
+        <v>1495.06</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>1029.44</v>
+        <v>1362.24</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.014256</v>
+        <v>0.057024</v>
       </c>
       <c r="R30" s="12" t="n">
         <v>0</v>
@@ -22321,7 +22324,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
@@ -22333,16 +22336,16 @@
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>100.37</v>
+        <v>132.82</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>1029.44</v>
+        <v>1362.24</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>72.06</v>
+        <v>95.36</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22408,10 +22411,10 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AX30" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY30" s="14" t="s">
         <v>75</v>
@@ -22438,16 +22441,16 @@
         <v>75</v>
       </c>
       <c r="BG30" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH30" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI30" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22456,84 +22459,84 @@
         <v>75</v>
       </c>
       <c r="BM30" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>304692</v>
+        <v>305273</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>194</v>
+        <v>135</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>323.73</v>
+        <v>15678.49</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>323.73</v>
+        <v>15678.49</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.003838</v>
+        <v>0.066706</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>1.08</v>
+        <v>17.14</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="Y31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>323.73</v>
+        <v>15678.49</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>22.66</v>
+        <v>1097.5</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22599,10 +22602,10 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22629,16 +22632,16 @@
         <v>75</v>
       </c>
       <c r="BG31" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH31" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI31" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22647,84 +22650,84 @@
         <v>75</v>
       </c>
       <c r="BM31" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>304722</v>
+        <v>305282</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>16301.36</v>
+        <v>392.71</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>16082.24</v>
+        <v>368.74</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.898646</v>
+        <v>0.006789</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>113.2</v>
+        <v>3.81</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>219.12</v>
+        <v>23.97</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>16082.24</v>
+        <v>368.74</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>993.95</v>
+        <v>14.75</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22790,7 +22793,7 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AX32" s="10" t="s">
         <v>77</v>
@@ -22820,16 +22823,16 @@
         <v>75</v>
       </c>
       <c r="BG32" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH32" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI32" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22838,39 +22841,39 @@
         <v>75</v>
       </c>
       <c r="BM32" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>304768</v>
+        <v>305283</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>2575.16</v>
+        <v>392.71</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -22879,43 +22882,43 @@
         <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>2575.16</v>
+        <v>368.74</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.01105</v>
+        <v>0.006789</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>5.74</v>
+        <v>3.81</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>2575.16</v>
+        <v>368.74</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>180.26</v>
+        <v>14.75</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23011,16 +23014,16 @@
         <v>75</v>
       </c>
       <c r="BG33" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH33" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI33" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23029,39 +23032,39 @@
         <v>75</v>
       </c>
       <c r="BM33" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>304799</v>
+        <v>305284</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>2905.86</v>
+        <v>392.71</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -23070,43 +23073,43 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>2905.86</v>
+        <v>368.74</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.013842</v>
+        <v>0.006789</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>11.95</v>
+        <v>3.81</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>2905.86</v>
+        <v>368.74</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>203.41</v>
+        <v>14.75</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23172,7 +23175,7 @@
         <v>74</v>
       </c>
       <c r="AW34" s="14" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AX34" s="10" t="s">
         <v>77</v>
@@ -23202,16 +23205,16 @@
         <v>75</v>
       </c>
       <c r="BG34" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH34" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI34" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23220,39 +23223,39 @@
         <v>75</v>
       </c>
       <c r="BM34" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>304828</v>
+        <v>305426</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>189.4</v>
+        <v>163.48</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23261,43 +23264,43 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>177.84</v>
+        <v>153.5</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.003626</v>
+        <v>0.003456</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>11.56</v>
+        <v>9.98</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>177.84</v>
+        <v>153.5</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>12.45</v>
+        <v>6.14</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23393,16 +23396,16 @@
         <v>75</v>
       </c>
       <c r="BG35" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH35" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI35" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23411,39 +23414,39 @@
         <v>75</v>
       </c>
       <c r="BM35" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>304829</v>
+        <v>305427</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>215</v>
+        <v>69</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>10076.2</v>
+        <v>163.48</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -23452,43 +23455,43 @@
         <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>10076.2</v>
+        <v>153.5</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.04</v>
+        <v>0.003456</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>53.59</v>
+        <v>0.8</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>0</v>
+        <v>9.98</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>10076.2</v>
+        <v>153.5</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>705.33</v>
+        <v>6.14</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23584,16 +23587,16 @@
         <v>75</v>
       </c>
       <c r="BG36" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH36" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI36" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23602,84 +23605,84 @@
         <v>75</v>
       </c>
       <c r="BM36" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>304844</v>
+        <v>305445</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>738.32</v>
+        <v>327.31</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>693.26</v>
+        <v>307.33</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.011556</v>
+        <v>0.239381</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>45.06</v>
+        <v>19.98</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>693.26</v>
+        <v>307.33</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>48.53</v>
+        <v>12.3</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23775,16 +23778,16 @@
         <v>75</v>
       </c>
       <c r="BG37" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH37" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI37" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23793,39 +23796,39 @@
         <v>75</v>
       </c>
       <c r="BM37" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>304868</v>
+        <v>305446</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6336.03</v>
+        <v>327.31</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -23834,16 +23837,16 @@
         <v>2</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>6336.03</v>
+        <v>307.33</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.004185</v>
+        <v>0.239381</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>3.07</v>
+        <v>1.6</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
@@ -23855,22 +23858,22 @@
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>0</v>
+        <v>19.98</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>6336.03</v>
+        <v>307.33</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>253.44</v>
+        <v>12.3</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23966,16 +23969,16 @@
         <v>75</v>
       </c>
       <c r="BG38" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH38" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI38" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -23984,63 +23987,63 @@
         <v>75</v>
       </c>
       <c r="BM38" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>304897</v>
+        <v>305447</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>39.92</v>
+        <v>327.31</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>36.37</v>
+        <v>307.33</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.00483</v>
+        <v>0.239381</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
@@ -24052,16 +24055,16 @@
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>3.55</v>
+        <v>19.98</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>36.37</v>
+        <v>307.33</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>2.55</v>
+        <v>12.3</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24130,7 +24133,7 @@
         <v>76</v>
       </c>
       <c r="AX39" s="10" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AY39" s="14" t="s">
         <v>75</v>
@@ -24157,13 +24160,13 @@
         <v>75</v>
       </c>
       <c r="BG39" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH39" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI39" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
         <v>228</v>
@@ -24175,15 +24178,15 @@
         <v>75</v>
       </c>
       <c r="BM39" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>304900</v>
+        <v>305453</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -24192,67 +24195,67 @@
         <v>229</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>230</v>
+        <v>69</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>934.7</v>
+        <v>837.05</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>851.66</v>
+        <v>805.99</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.03381</v>
+        <v>0.210944</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>0</v>
+        <v>9.12</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>83.04</v>
+        <v>31.06</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>851.66</v>
+        <v>805.99</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>59.62</v>
+        <v>32.25</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24348,16 +24351,16 @@
         <v>75</v>
       </c>
       <c r="BG40" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH40" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI40" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24366,84 +24369,84 @@
         <v>75</v>
       </c>
       <c r="BM40" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>304904</v>
+        <v>305454</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>234</v>
+        <v>69</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>3210.71</v>
+        <v>2323.32</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>3150.8</v>
+        <v>2294.51</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.275443</v>
+        <v>0.233764</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>19.52</v>
+        <v>12.22</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="W41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>59.91</v>
+        <v>28.81</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>3150.8</v>
+        <v>2294.51</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>178.1</v>
+        <v>91.78</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24509,7 +24512,7 @@
         <v>74</v>
       </c>
       <c r="AW41" s="14" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AX41" s="10" t="s">
         <v>77</v>
@@ -24539,16 +24542,16 @@
         <v>75</v>
       </c>
       <c r="BG41" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH41" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI41" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24557,84 +24560,84 @@
         <v>75</v>
       </c>
       <c r="BM41" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>304909</v>
+        <v>305455</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>237</v>
+        <v>161</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>1039.92</v>
+        <v>800.16</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>1033.2</v>
+        <v>771.35</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.00222</v>
+        <v>0.205309</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>2.7</v>
+        <v>8.8</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>6.72</v>
+        <v>28.81</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>1033.2</v>
+        <v>771.35</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>72.32</v>
+        <v>30.86</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24700,7 +24703,7 @@
         <v>74</v>
       </c>
       <c r="AW42" s="14" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AX42" s="10" t="s">
         <v>77</v>
@@ -24730,16 +24733,16 @@
         <v>75</v>
       </c>
       <c r="BG42" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH42" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI42" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24748,84 +24751,84 @@
         <v>75</v>
       </c>
       <c r="BM42" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>304926</v>
+        <v>305464</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>244</v>
+        <v>69</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>10224.34</v>
+        <v>314.65</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>10224.34</v>
+        <v>295.45</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.114114</v>
+        <v>0.016472</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>24.5</v>
+        <v>1.6</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>10224.34</v>
+        <v>295.45</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>1226.92</v>
+        <v>11.81</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24921,16 +24924,16 @@
         <v>75</v>
       </c>
       <c r="BG43" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH43" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI43" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -24939,84 +24942,84 @@
         <v>75</v>
       </c>
       <c r="BM43" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>304944</v>
+        <v>305465</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>114</v>
+        <v>209</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>248</v>
+        <v>69</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>8386</v>
+        <v>314.65</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>7641</v>
+        <v>295.45</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0</v>
+        <v>0.016472</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>745</v>
+        <v>19.2</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>7641</v>
+        <v>295.45</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>305.64</v>
+        <v>11.81</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25082,7 +25085,7 @@
         <v>74</v>
       </c>
       <c r="AW44" s="14" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AX44" s="10" t="s">
         <v>77</v>
@@ -25112,16 +25115,16 @@
         <v>75</v>
       </c>
       <c r="BG44" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH44" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI44" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25130,63 +25133,63 @@
         <v>75</v>
       </c>
       <c r="BM44" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>304970</v>
+        <v>305466</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>251</v>
+        <v>161</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>9750.72</v>
+        <v>314.65</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>9750.72</v>
+        <v>295.45</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0</v>
+        <v>0.016472</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
@@ -25198,16 +25201,16 @@
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>9750.72</v>
+        <v>295.45</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>390.03</v>
+        <v>11.81</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25276,7 +25279,7 @@
         <v>76</v>
       </c>
       <c r="AX45" s="10" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AY45" s="14" t="s">
         <v>75</v>
@@ -25303,16 +25306,16 @@
         <v>75</v>
       </c>
       <c r="BG45" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH45" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI45" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25321,84 +25324,84 @@
         <v>75</v>
       </c>
       <c r="BM45" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>304984</v>
+        <v>305474</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>256</v>
+        <v>161</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>258</v>
+        <v>91</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>70293.33</v>
+        <v>167.35</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>70085.31</v>
+        <v>157.14</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>36.524292</v>
+        <v>0.014804</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>3660.57</v>
+        <v>2.51</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>208.02</v>
+        <v>10.21</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>70085.31</v>
+        <v>157.14</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>4667.44</v>
+        <v>6.29</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25464,7 +25467,7 @@
         <v>74</v>
       </c>
       <c r="AW46" s="14" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AX46" s="10" t="s">
         <v>77</v>
@@ -25494,16 +25497,16 @@
         <v>75</v>
       </c>
       <c r="BG46" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH46" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI46" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25512,39 +25515,39 @@
         <v>75</v>
       </c>
       <c r="BM46" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>304986</v>
+        <v>305475</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>262</v>
+        <v>69</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1008.04</v>
+        <v>83.19</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
@@ -25553,43 +25556,43 @@
         <v>3</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>918.49</v>
+        <v>78.12</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.302016</v>
+        <v>0.013886</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>89.55</v>
+        <v>5.07</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>918.49</v>
+        <v>78.12</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>64.3</v>
+        <v>3.13</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25655,7 +25658,7 @@
         <v>74</v>
       </c>
       <c r="AW47" s="14" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AX47" s="10" t="s">
         <v>77</v>
@@ -25685,16 +25688,16 @@
         <v>75</v>
       </c>
       <c r="BG47" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH47" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI47" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25703,39 +25706,39 @@
         <v>75</v>
       </c>
       <c r="BM47" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>304994</v>
+        <v>305476</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>267</v>
+        <v>69</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>1865.26</v>
+        <v>83.19</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
@@ -25744,43 +25747,43 @@
         <v>3</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>1661</v>
+        <v>78.12</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0</v>
+        <v>0.013886</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>3.6</v>
+        <v>0.93</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>204.26</v>
+        <v>5.07</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>1661</v>
+        <v>78.12</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>66.44</v>
+        <v>3.13</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25876,16 +25879,16 @@
         <v>75</v>
       </c>
       <c r="BG48" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH48" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI48" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="BK48" s="9" t="s">
         <v>75</v>
@@ -25894,84 +25897,84 @@
         <v>75</v>
       </c>
       <c r="BM48" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>304995</v>
+        <v>305543</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>272</v>
+        <v>126</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>12462.51</v>
+        <v>839.95</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>11355.36</v>
+        <v>839.95</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.11544</v>
+        <v>0.030474</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>33.12</v>
+        <v>5.42</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>1107.15</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>11355.36</v>
+        <v>839.95</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>794.87</v>
+        <v>58.79</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26040,7 +26043,7 @@
         <v>76</v>
       </c>
       <c r="AX49" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY49" s="14" t="s">
         <v>75</v>
@@ -26067,16 +26070,16 @@
         <v>75</v>
       </c>
       <c r="BG49" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH49" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI49" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26085,84 +26088,84 @@
         <v>75</v>
       </c>
       <c r="BM49" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>304996</v>
+        <v>305544</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>2426.27</v>
+        <v>297.63</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>2349.89</v>
+        <v>297.63</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0</v>
+        <v>0.001848</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="U50" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>76.38</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>2426.27</v>
+        <v>297.63</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>169.84</v>
+        <v>20.83</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26228,10 +26231,10 @@
         <v>74</v>
       </c>
       <c r="AW50" s="14" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AX50" s="10" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="AY50" s="14" t="s">
         <v>75</v>
@@ -26258,16 +26261,16 @@
         <v>75</v>
       </c>
       <c r="BG50" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH50" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI50" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26276,84 +26279,84 @@
         <v>75</v>
       </c>
       <c r="BM50" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>305016</v>
+        <v>305551</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>131</v>
+        <v>261</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>9425.55</v>
+        <v>2815.95</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>8510.75</v>
+        <v>2815.95</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.01625</v>
+        <v>0.002473</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V51" s="12" t="n">
-        <v>55.75</v>
+        <v>42</v>
       </c>
       <c r="W51" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>829.8</v>
+        <v>0</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>8595.75</v>
+        <v>2815.95</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>343.83</v>
+        <v>197.12</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26419,10 +26422,10 @@
         <v>74</v>
       </c>
       <c r="AW51" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX51" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY51" s="14" t="s">
         <v>75</v>
@@ -26449,16 +26452,16 @@
         <v>75</v>
       </c>
       <c r="BG51" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH51" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI51" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="BK51" s="9" t="s">
         <v>75</v>
@@ -26467,84 +26470,84 @@
         <v>75</v>
       </c>
       <c r="BM51" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>305035</v>
+        <v>305559</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>114</v>
+        <v>265</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>834.4</v>
+        <v>454.32</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>834.4</v>
+        <v>454.32</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0.859248</v>
+        <v>0.008017</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>50.49</v>
+        <v>2.02</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="Y52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>834.4</v>
+        <v>454.32</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>33.38</v>
+        <v>31.8</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26613,7 +26616,7 @@
         <v>76</v>
       </c>
       <c r="AX52" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AY52" s="14" t="s">
         <v>75</v>
@@ -26640,16 +26643,16 @@
         <v>75</v>
       </c>
       <c r="BG52" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH52" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI52" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="BK52" s="9" t="s">
         <v>75</v>
@@ -26658,607 +26661,1095 @@
         <v>75</v>
       </c>
       <c r="BM52" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4"/>
+      <c r="A53" s="8" t="n">
+        <v>305598</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>837.01</v>
+      </c>
+      <c r="M53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O53" s="12" t="n">
+        <v>806.92</v>
+      </c>
+      <c r="P53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="S53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="U53" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V53" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="W53" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X53" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y53" s="12" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="Z53" s="12" t="n">
+        <v>806.92</v>
+      </c>
+      <c r="AA53" s="12" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="AB53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV53" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW53" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AX53" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF53" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG53" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI53" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ53" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="BK53" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL53" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM53" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="54" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="17"/>
-      <c r="V54" s="17"/>
+    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="n">
+        <v>305613</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>902.64</v>
+      </c>
+      <c r="M54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="12" t="n">
+        <v>902.64</v>
+      </c>
+      <c r="P54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="13" t="n">
+        <v>0.01086</v>
+      </c>
+      <c r="R54" s="12" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="S54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="U54" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V54" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W54" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X54" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="12" t="n">
+        <v>902.64</v>
+      </c>
+      <c r="AA54" s="12" t="n">
+        <v>63.18</v>
+      </c>
+      <c r="AB54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV54" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW54" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AX54" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF54" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG54" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH54" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI54" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ54" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="BK54" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL54" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM54" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G55" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I55" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="J55" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K55" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L55" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M55" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="N55" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O55" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P55" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q55" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R55" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S55" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="T55" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="U55" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V55" s="18" t="s">
-        <v>37</v>
+    <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="n">
+        <v>305615</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>3419.5</v>
+      </c>
+      <c r="M55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="O55" s="12" t="n">
+        <v>3400.4</v>
+      </c>
+      <c r="P55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="13" t="n">
+        <v>0.068208</v>
+      </c>
+      <c r="R55" s="12" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="S55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="U55" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V55" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="W55" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X55" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y55" s="12" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Z55" s="12" t="n">
+        <v>3400.4</v>
+      </c>
+      <c r="AA55" s="12" t="n">
+        <v>199.84</v>
+      </c>
+      <c r="AB55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW55" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AX55" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF55" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG55" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH55" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI55" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ55" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="BK55" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL55" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM55" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="19" t="n">
-        <v>170</v>
-      </c>
-      <c r="D56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="19" t="n">
-        <v>6066.6</v>
-      </c>
-      <c r="F56" s="19" t="n">
-        <v>243335.57</v>
-      </c>
-      <c r="G56" s="19" t="n">
-        <v>15568.01</v>
-      </c>
-      <c r="H56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="19" t="n">
-        <v>249325.79</v>
-      </c>
-      <c r="L56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="20" t="n">
-        <v>39.855216</v>
-      </c>
-      <c r="S56" s="19" t="n">
-        <v>243089.19</v>
-      </c>
-      <c r="T56" s="19" t="n">
-        <v>249325.79</v>
-      </c>
-      <c r="U56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="19" t="n">
-        <v>0</v>
+      <c r="A56" s="8" t="n">
+        <v>305625</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>830.75</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="12" t="n">
+        <v>804.6</v>
+      </c>
+      <c r="P56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="13" t="n">
+        <v>0.16337</v>
+      </c>
+      <c r="R56" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="S56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="U56" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V56" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W56" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X56" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y56" s="12" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="Z56" s="12" t="n">
+        <v>804.6</v>
+      </c>
+      <c r="AA56" s="12" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="AB56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW56" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX56" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF56" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG56" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI56" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ56" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="BK56" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL56" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM56" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="18" t="s">
+    <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M59" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="N59" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O59" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P59" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q59" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S59" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="T59" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="U59" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V59" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>4817.9</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>132502.36</v>
+      </c>
+      <c r="G60" s="19" t="n">
+        <v>8517.83</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v>293.73</v>
+      </c>
+      <c r="K60" s="19" t="n">
+        <v>137243.88</v>
+      </c>
+      <c r="L60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="20" t="n">
+        <v>7.370481</v>
+      </c>
+      <c r="S60" s="19" t="n">
+        <v>132425.98</v>
+      </c>
+      <c r="T60" s="19" t="n">
+        <v>137243.88</v>
+      </c>
+      <c r="U60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="18" t="s">
+      <c r="B61" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C61" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D61" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E61" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F57" s="18" t="s">
+      <c r="F61" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="18" t="s">
+      <c r="G61" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H57" s="18" t="s">
+      <c r="H61" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I57" s="18" t="s">
+      <c r="I61" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J57" s="18" t="s">
+      <c r="J61" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K57" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="L57" s="18" t="s">
+      <c r="K61" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="M57" s="18" t="s">
+      <c r="L61" s="18" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="19" t="n">
-        <v>4313.71</v>
-      </c>
-      <c r="B58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="19" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="21" t="s">
+      <c r="M61" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="21"/>
-      <c r="L60" s="21"/>
-      <c r="M60" s="21"/>
-      <c r="N60" s="21"/>
-      <c r="O60" s="21"/>
-      <c r="P60" s="21"/>
-      <c r="Q60" s="21"/>
-      <c r="R60" s="21"/>
-      <c r="S60" s="21"/>
-      <c r="T60" s="21"/>
-      <c r="U60" s="21"/>
-      <c r="V60" s="21"/>
-      <c r="W60" s="21"/>
-      <c r="X60" s="21"/>
-      <c r="Y60" s="21"/>
-      <c r="Z60" s="21"/>
-      <c r="AA60" s="21"/>
-      <c r="AB60" s="21"/>
-      <c r="AC60" s="21"/>
-      <c r="AD60" s="21"/>
-      <c r="AE60" s="21"/>
-      <c r="AF60" s="21"/>
-      <c r="AG60" s="21"/>
-      <c r="AH60" s="21"/>
-      <c r="AI60" s="21"/>
-      <c r="AJ60" s="21"/>
-      <c r="AK60" s="21"/>
-      <c r="AL60" s="21"/>
-      <c r="AM60" s="21"/>
-      <c r="AN60" s="21"/>
-      <c r="AO60" s="21"/>
-      <c r="AP60" s="21"/>
-      <c r="AQ60" s="21"/>
-      <c r="AR60" s="21"/>
-      <c r="AS60" s="21"/>
-      <c r="AT60" s="21"/>
-      <c r="AU60" s="21"/>
-      <c r="AV60" s="21"/>
-      <c r="AW60" s="21"/>
-      <c r="AX60" s="21"/>
-      <c r="AY60" s="21"/>
-      <c r="AZ60" s="21"/>
-      <c r="BA60" s="21"/>
-      <c r="BB60" s="21"/>
-      <c r="BC60" s="21"/>
-      <c r="BD60" s="21"/>
-      <c r="BE60" s="21"/>
-      <c r="BF60" s="21"/>
-      <c r="BG60" s="21"/>
-      <c r="BH60" s="21"/>
-      <c r="BI60" s="21"/>
-      <c r="BJ60" s="21"/>
-      <c r="BK60" s="21"/>
-      <c r="BL60" s="21"/>
-      <c r="BM60" s="21"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="4"/>
-      <c r="AB61" s="4"/>
-      <c r="AC61" s="4"/>
-      <c r="AD61" s="4"/>
-      <c r="AE61" s="4"/>
-      <c r="AF61" s="4"/>
-      <c r="AG61" s="4"/>
-      <c r="AH61" s="4"/>
-      <c r="AI61" s="4"/>
-      <c r="AJ61" s="4"/>
-      <c r="AK61" s="4"/>
-      <c r="AL61" s="4"/>
-      <c r="AM61" s="4"/>
-      <c r="AN61" s="4"/>
-      <c r="AO61" s="4"/>
-      <c r="AP61" s="4"/>
-      <c r="AQ61" s="4"/>
-      <c r="AR61" s="4"/>
-      <c r="AS61" s="4"/>
-      <c r="AT61" s="4"/>
-      <c r="AU61" s="4"/>
-      <c r="AV61" s="4"/>
-      <c r="AW61" s="4"/>
-      <c r="AX61" s="4"/>
-      <c r="AY61" s="4"/>
-      <c r="AZ61" s="4"/>
-      <c r="BA61" s="4"/>
-      <c r="BB61" s="4"/>
-      <c r="BC61" s="4"/>
-      <c r="BD61" s="4"/>
-      <c r="BE61" s="4"/>
-      <c r="BF61" s="4"/>
-      <c r="BG61" s="4"/>
-      <c r="BH61" s="4"/>
-      <c r="BI61" s="4"/>
-      <c r="BJ61" s="4"/>
-      <c r="BK61" s="4"/>
-      <c r="BL61" s="4"/>
-      <c r="BM61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="4"/>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="4"/>
-      <c r="Z62" s="4"/>
-      <c r="AA62" s="4"/>
-      <c r="AB62" s="4"/>
-      <c r="AC62" s="4"/>
-      <c r="AD62" s="4"/>
-      <c r="AE62" s="4"/>
-      <c r="AF62" s="4"/>
-      <c r="AG62" s="4"/>
-      <c r="AH62" s="4"/>
-      <c r="AI62" s="4"/>
-      <c r="AJ62" s="4"/>
-      <c r="AK62" s="4"/>
-      <c r="AL62" s="4"/>
-      <c r="AM62" s="4"/>
-      <c r="AN62" s="4"/>
-      <c r="AO62" s="4"/>
-      <c r="AP62" s="4"/>
-      <c r="AQ62" s="4"/>
-      <c r="AR62" s="4"/>
-      <c r="AS62" s="4"/>
-      <c r="AT62" s="4"/>
-      <c r="AU62" s="4"/>
-      <c r="AV62" s="4"/>
-      <c r="AW62" s="4"/>
-      <c r="AX62" s="4"/>
-      <c r="AY62" s="4"/>
-      <c r="AZ62" s="4"/>
-      <c r="BA62" s="4"/>
-      <c r="BB62" s="4"/>
-      <c r="BC62" s="4"/>
-      <c r="BD62" s="4"/>
-      <c r="BE62" s="4"/>
-      <c r="BF62" s="4"/>
-      <c r="BG62" s="4"/>
-      <c r="BH62" s="4"/>
-      <c r="BI62" s="4"/>
-      <c r="BJ62" s="4"/>
-      <c r="BK62" s="4"/>
-      <c r="BL62" s="4"/>
-      <c r="BM62" s="4"/>
+      <c r="A62" s="19" t="n">
+        <v>904.01</v>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
-      <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
-      <c r="Y63" s="4"/>
-      <c r="Z63" s="4"/>
-      <c r="AA63" s="4"/>
-      <c r="AB63" s="4"/>
-      <c r="AC63" s="4"/>
-      <c r="AD63" s="4"/>
-      <c r="AE63" s="4"/>
-      <c r="AF63" s="4"/>
-      <c r="AG63" s="4"/>
-      <c r="AH63" s="4"/>
-      <c r="AI63" s="4"/>
-      <c r="AJ63" s="4"/>
-      <c r="AK63" s="4"/>
-      <c r="AL63" s="4"/>
-      <c r="AM63" s="4"/>
-      <c r="AN63" s="4"/>
-      <c r="AO63" s="4"/>
-      <c r="AP63" s="4"/>
-      <c r="AQ63" s="4"/>
-      <c r="AR63" s="4"/>
-      <c r="AS63" s="4"/>
-      <c r="AT63" s="4"/>
-      <c r="AU63" s="4"/>
-      <c r="AV63" s="4"/>
-      <c r="AW63" s="4"/>
-      <c r="AX63" s="4"/>
-      <c r="AY63" s="4"/>
-      <c r="AZ63" s="4"/>
-      <c r="BA63" s="4"/>
-      <c r="BB63" s="4"/>
-      <c r="BC63" s="4"/>
-      <c r="BD63" s="4"/>
-      <c r="BE63" s="4"/>
-      <c r="BF63" s="4"/>
-      <c r="BG63" s="4"/>
-      <c r="BH63" s="4"/>
-      <c r="BI63" s="4"/>
-      <c r="BJ63" s="4"/>
-      <c r="BK63" s="4"/>
-      <c r="BL63" s="4"/>
-      <c r="BM63" s="4"/>
+      <c r="A63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4"/>
-      <c r="U64" s="4"/>
-      <c r="V64" s="4"/>
-      <c r="W64" s="4"/>
-      <c r="X64" s="4"/>
-      <c r="Y64" s="4"/>
-      <c r="Z64" s="4"/>
-      <c r="AA64" s="4"/>
-      <c r="AB64" s="4"/>
-      <c r="AC64" s="4"/>
-      <c r="AD64" s="4"/>
-      <c r="AE64" s="4"/>
-      <c r="AF64" s="4"/>
-      <c r="AG64" s="4"/>
-      <c r="AH64" s="4"/>
-      <c r="AI64" s="4"/>
-      <c r="AJ64" s="4"/>
-      <c r="AK64" s="4"/>
-      <c r="AL64" s="4"/>
-      <c r="AM64" s="4"/>
-      <c r="AN64" s="4"/>
-      <c r="AO64" s="4"/>
-      <c r="AP64" s="4"/>
-      <c r="AQ64" s="4"/>
-      <c r="AR64" s="4"/>
-      <c r="AS64" s="4"/>
-      <c r="AT64" s="4"/>
-      <c r="AU64" s="4"/>
-      <c r="AV64" s="4"/>
-      <c r="AW64" s="4"/>
-      <c r="AX64" s="4"/>
-      <c r="AY64" s="4"/>
-      <c r="AZ64" s="4"/>
-      <c r="BA64" s="4"/>
-      <c r="BB64" s="4"/>
-      <c r="BC64" s="4"/>
-      <c r="BD64" s="4"/>
-      <c r="BE64" s="4"/>
-      <c r="BF64" s="4"/>
-      <c r="BG64" s="4"/>
-      <c r="BH64" s="4"/>
-      <c r="BI64" s="4"/>
-      <c r="BJ64" s="4"/>
-      <c r="BK64" s="4"/>
-      <c r="BL64" s="4"/>
-      <c r="BM64" s="4"/>
+    <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="21"/>
+      <c r="M64" s="21"/>
+      <c r="N64" s="21"/>
+      <c r="O64" s="21"/>
+      <c r="P64" s="21"/>
+      <c r="Q64" s="21"/>
+      <c r="R64" s="21"/>
+      <c r="S64" s="21"/>
+      <c r="T64" s="21"/>
+      <c r="U64" s="21"/>
+      <c r="V64" s="21"/>
+      <c r="W64" s="21"/>
+      <c r="X64" s="21"/>
+      <c r="Y64" s="21"/>
+      <c r="Z64" s="21"/>
+      <c r="AA64" s="21"/>
+      <c r="AB64" s="21"/>
+      <c r="AC64" s="21"/>
+      <c r="AD64" s="21"/>
+      <c r="AE64" s="21"/>
+      <c r="AF64" s="21"/>
+      <c r="AG64" s="21"/>
+      <c r="AH64" s="21"/>
+      <c r="AI64" s="21"/>
+      <c r="AJ64" s="21"/>
+      <c r="AK64" s="21"/>
+      <c r="AL64" s="21"/>
+      <c r="AM64" s="21"/>
+      <c r="AN64" s="21"/>
+      <c r="AO64" s="21"/>
+      <c r="AP64" s="21"/>
+      <c r="AQ64" s="21"/>
+      <c r="AR64" s="21"/>
+      <c r="AS64" s="21"/>
+      <c r="AT64" s="21"/>
+      <c r="AU64" s="21"/>
+      <c r="AV64" s="21"/>
+      <c r="AW64" s="21"/>
+      <c r="AX64" s="21"/>
+      <c r="AY64" s="21"/>
+      <c r="AZ64" s="21"/>
+      <c r="BA64" s="21"/>
+      <c r="BB64" s="21"/>
+      <c r="BC64" s="21"/>
+      <c r="BD64" s="21"/>
+      <c r="BE64" s="21"/>
+      <c r="BF64" s="21"/>
+      <c r="BG64" s="21"/>
+      <c r="BH64" s="21"/>
+      <c r="BI64" s="21"/>
+      <c r="BJ64" s="21"/>
+      <c r="BK64" s="21"/>
+      <c r="BL64" s="21"/>
+      <c r="BM64" s="21"/>
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -27327,7 +27818,7 @@
     </row>
     <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -27396,7 +27887,7 @@
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -27465,7 +27956,7 @@
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -27534,7 +28025,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>303</v>
+        <v>22</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -27603,7 +28094,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -27670,8 +28161,284 @@
       <c r="BL70" s="4"/>
       <c r="BM70" s="4"/>
     </row>
+    <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="4"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="4"/>
+      <c r="AB71" s="4"/>
+      <c r="AC71" s="4"/>
+      <c r="AD71" s="4"/>
+      <c r="AE71" s="4"/>
+      <c r="AF71" s="4"/>
+      <c r="AG71" s="4"/>
+      <c r="AH71" s="4"/>
+      <c r="AI71" s="4"/>
+      <c r="AJ71" s="4"/>
+      <c r="AK71" s="4"/>
+      <c r="AL71" s="4"/>
+      <c r="AM71" s="4"/>
+      <c r="AN71" s="4"/>
+      <c r="AO71" s="4"/>
+      <c r="AP71" s="4"/>
+      <c r="AQ71" s="4"/>
+      <c r="AR71" s="4"/>
+      <c r="AS71" s="4"/>
+      <c r="AT71" s="4"/>
+      <c r="AU71" s="4"/>
+      <c r="AV71" s="4"/>
+      <c r="AW71" s="4"/>
+      <c r="AX71" s="4"/>
+      <c r="AY71" s="4"/>
+      <c r="AZ71" s="4"/>
+      <c r="BA71" s="4"/>
+      <c r="BB71" s="4"/>
+      <c r="BC71" s="4"/>
+      <c r="BD71" s="4"/>
+      <c r="BE71" s="4"/>
+      <c r="BF71" s="4"/>
+      <c r="BG71" s="4"/>
+      <c r="BH71" s="4"/>
+      <c r="BI71" s="4"/>
+      <c r="BJ71" s="4"/>
+      <c r="BK71" s="4"/>
+      <c r="BL71" s="4"/>
+      <c r="BM71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="4"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="4"/>
+      <c r="AB72" s="4"/>
+      <c r="AC72" s="4"/>
+      <c r="AD72" s="4"/>
+      <c r="AE72" s="4"/>
+      <c r="AF72" s="4"/>
+      <c r="AG72" s="4"/>
+      <c r="AH72" s="4"/>
+      <c r="AI72" s="4"/>
+      <c r="AJ72" s="4"/>
+      <c r="AK72" s="4"/>
+      <c r="AL72" s="4"/>
+      <c r="AM72" s="4"/>
+      <c r="AN72" s="4"/>
+      <c r="AO72" s="4"/>
+      <c r="AP72" s="4"/>
+      <c r="AQ72" s="4"/>
+      <c r="AR72" s="4"/>
+      <c r="AS72" s="4"/>
+      <c r="AT72" s="4"/>
+      <c r="AU72" s="4"/>
+      <c r="AV72" s="4"/>
+      <c r="AW72" s="4"/>
+      <c r="AX72" s="4"/>
+      <c r="AY72" s="4"/>
+      <c r="AZ72" s="4"/>
+      <c r="BA72" s="4"/>
+      <c r="BB72" s="4"/>
+      <c r="BC72" s="4"/>
+      <c r="BD72" s="4"/>
+      <c r="BE72" s="4"/>
+      <c r="BF72" s="4"/>
+      <c r="BG72" s="4"/>
+      <c r="BH72" s="4"/>
+      <c r="BI72" s="4"/>
+      <c r="BJ72" s="4"/>
+      <c r="BK72" s="4"/>
+      <c r="BL72" s="4"/>
+      <c r="BM72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+      <c r="S73" s="4"/>
+      <c r="T73" s="4"/>
+      <c r="U73" s="4"/>
+      <c r="V73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+      <c r="AA73" s="4"/>
+      <c r="AB73" s="4"/>
+      <c r="AC73" s="4"/>
+      <c r="AD73" s="4"/>
+      <c r="AE73" s="4"/>
+      <c r="AF73" s="4"/>
+      <c r="AG73" s="4"/>
+      <c r="AH73" s="4"/>
+      <c r="AI73" s="4"/>
+      <c r="AJ73" s="4"/>
+      <c r="AK73" s="4"/>
+      <c r="AL73" s="4"/>
+      <c r="AM73" s="4"/>
+      <c r="AN73" s="4"/>
+      <c r="AO73" s="4"/>
+      <c r="AP73" s="4"/>
+      <c r="AQ73" s="4"/>
+      <c r="AR73" s="4"/>
+      <c r="AS73" s="4"/>
+      <c r="AT73" s="4"/>
+      <c r="AU73" s="4"/>
+      <c r="AV73" s="4"/>
+      <c r="AW73" s="4"/>
+      <c r="AX73" s="4"/>
+      <c r="AY73" s="4"/>
+      <c r="AZ73" s="4"/>
+      <c r="BA73" s="4"/>
+      <c r="BB73" s="4"/>
+      <c r="BC73" s="4"/>
+      <c r="BD73" s="4"/>
+      <c r="BE73" s="4"/>
+      <c r="BF73" s="4"/>
+      <c r="BG73" s="4"/>
+      <c r="BH73" s="4"/>
+      <c r="BI73" s="4"/>
+      <c r="BJ73" s="4"/>
+      <c r="BK73" s="4"/>
+      <c r="BL73" s="4"/>
+      <c r="BM73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+      <c r="T74" s="4"/>
+      <c r="U74" s="4"/>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="4"/>
+      <c r="AB74" s="4"/>
+      <c r="AC74" s="4"/>
+      <c r="AD74" s="4"/>
+      <c r="AE74" s="4"/>
+      <c r="AF74" s="4"/>
+      <c r="AG74" s="4"/>
+      <c r="AH74" s="4"/>
+      <c r="AI74" s="4"/>
+      <c r="AJ74" s="4"/>
+      <c r="AK74" s="4"/>
+      <c r="AL74" s="4"/>
+      <c r="AM74" s="4"/>
+      <c r="AN74" s="4"/>
+      <c r="AO74" s="4"/>
+      <c r="AP74" s="4"/>
+      <c r="AQ74" s="4"/>
+      <c r="AR74" s="4"/>
+      <c r="AS74" s="4"/>
+      <c r="AT74" s="4"/>
+      <c r="AU74" s="4"/>
+      <c r="AV74" s="4"/>
+      <c r="AW74" s="4"/>
+      <c r="AX74" s="4"/>
+      <c r="AY74" s="4"/>
+      <c r="AZ74" s="4"/>
+      <c r="BA74" s="4"/>
+      <c r="BB74" s="4"/>
+      <c r="BC74" s="4"/>
+      <c r="BD74" s="4"/>
+      <c r="BE74" s="4"/>
+      <c r="BF74" s="4"/>
+      <c r="BG74" s="4"/>
+      <c r="BH74" s="4"/>
+      <c r="BI74" s="4"/>
+      <c r="BJ74" s="4"/>
+      <c r="BK74" s="4"/>
+      <c r="BL74" s="4"/>
+      <c r="BM74" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="68">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -27724,11 +28491,11 @@
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="A54:V54"/>
-    <mergeCell ref="A60:BM60"/>
-    <mergeCell ref="A61:BM61"/>
-    <mergeCell ref="A62:BM62"/>
-    <mergeCell ref="A63:BM63"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A58:V58"/>
     <mergeCell ref="A64:BM64"/>
     <mergeCell ref="A65:BM65"/>
     <mergeCell ref="A66:BM66"/>
@@ -27736,6 +28503,10 @@
     <mergeCell ref="A68:BM68"/>
     <mergeCell ref="A69:BM69"/>
     <mergeCell ref="A70:BM70"/>
+    <mergeCell ref="A71:BM71"/>
+    <mergeCell ref="A72:BM72"/>
+    <mergeCell ref="A73:BM73"/>
+    <mergeCell ref="A74:BM74"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="316">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 23/04/2026 10:36:38</t>
+    <t xml:space="preserve">Emitido em: 24/04/2026 09:30:17</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -319,568 +319,598 @@
     <t xml:space="preserve">41260417781412000109550010000119751000316214</t>
   </si>
   <si>
+    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">862.382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.210,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008623821213560250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.386,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260417781412000109550010000119631000316094</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">8.791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39,92</t>
+    <t xml:space="preserve">8.816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.008,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260430228132000136550010000088161997156414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">862.414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.426,27</t>
   </si>
   <si>
     <t xml:space="preserve">2.910</t>
   </si>
   <si>
-    <t xml:space="preserve">35260430228132000136550010000087911857568506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">934,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260430228132000136550010000087901687286834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">862.382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.210,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008623821213560250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.386,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000119631000316094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.008,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260430228132000136550010000088161997156414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.772</t>
+    <t xml:space="preserve">42260481604803000157550010008624141130085348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">612.288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.003,36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006122881786143830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.116 - MS DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.610,21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260414624251000151550010000460071000339888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">623,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640351505728166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">614.972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.219,97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006149721103161297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.208,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008632001044837440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">614.141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.851,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006141411310114120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">613.556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.174,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006135561160634441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.664 - STANDARD ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.598,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260456365423000160550010000114651525296163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.426,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260412077181000133550030002237391325182136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">752.149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.015,45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260409641520000158550010007521491440180220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.825,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260458329608000144550010002586861002586870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.974 - USINA DESIGN IND E COMERCIO DE ILUMINACAO LTDA-ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.495,06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260410713221000160550020000074001000087894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">612.541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.678,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006125411397554499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">392,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640381144694271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640391069291419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640401380951817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640461295961530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050640471507052381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050643931146292179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050643941609242127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.064.395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050643951603608712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">837,05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656021851619813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.323,32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656031864823799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656041505799080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314,65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656111652042051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656121082142336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656131260967511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167,35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656201014371157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656211192558439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.065.622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050656221375141585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">616.791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15/05/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.462,51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260409306858000153550010000707721210311252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">862.414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.426,27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008624141130085348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.784 - SEKAPISO METALURGICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.291,91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460225604000168550030000521961913645534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.852,31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293,73</t>
+    <t xml:space="preserve">839,95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006167911610794090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">616.993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006169931514728672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">617.417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.815,95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006174171379260766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">618.465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">454,32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006184651995060434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.961.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">837,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260460561719009503550210019610101643781317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.351.353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">902,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013513531420684669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.419,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008638011323501589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.089 - OTTO BAUMGART INDUSTRIA E COMERCIO S A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830,75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260460642774001209550010002052231454537290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.715 - LUMIERE COMERCIO INTERNACIONAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.070</t>
   </si>
   <si>
     <t xml:space="preserve">23/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">35260454542238000178550010000964221000962230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260411389565000200570050003974461000835918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">612.288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.003,36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006122881786143830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.116 - MS DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.610,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260414624251000151550010000460071000339888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">623,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640351505728166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">614.972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.219,97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006149721103161297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.208,54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008632001044837440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">614.141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.851,64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006141411310114120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">613.556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.174,14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006135561160634441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.664 - STANDARD ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.598,62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260456365423000160550010000114651525296163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.426,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260412077181000133550030002237391325182136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">752.149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.015,45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260409641520000158550010007521491440180220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.825,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260458329608000144550010002586861002586870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.974 - USINA DESIGN IND E COMERCIO DE ILUMINACAO LTDA-ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.495,06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260410713221000160550020000074001000087894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">612.541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.678,49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006125411397554499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">392,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640381144694271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640391069291419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640401380951817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163,48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640461295961530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050640471507052381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327,31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050643931146292179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050643941609242127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.064.395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050643951603608712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">837,05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656021851619813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.323,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656031864823799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">800,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656041505799080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314,65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656111652042051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656121082142336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656131260967511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167,35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656201014371157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83,19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656211192558439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.065.622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050656221375141585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">616.791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">839,95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006167911610794090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">616.993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297,63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006169931514728672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">617.417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.815,95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006174171379260766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">618.465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">454,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006184651995060434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.961.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">837,01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460561719009503550210019610101643781317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.351.353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">902,64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260475801902000126550000013513531420684669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.419,50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008638011323501589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.089 - OTTO BAUMGART INDUSTRIA E COMERCIO S A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830,75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460642774001209550010002052231454537290</t>
+    <t xml:space="preserve">22/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.057,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260424855633000140550010000760701142490768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">621.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.783,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006211121320114228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">621.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.261,84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006210121916909071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">736 - BEMFIXA INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.283,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461801973000114550010002102901467490335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">620.300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.332,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006203001930196827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.998 - LIGHTFLEX BRASIL COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.511,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53260437040654000159550020000006691000013683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.204,74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53260437040654000159550020000006661000013649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600 - CENSI INDUSTRIA E COMERCIO DE REPAROS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">448.133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.650,36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260402308456000149550050004481331387647143</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17126,7 +17156,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM74"/>
+  <dimension ref="A1:BM77"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -18453,7 +18483,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>304897</v>
+        <v>304904</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>99</v>
@@ -18474,43 +18504,43 @@
         <v>102</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>39.92</v>
+        <v>3210.71</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>36.37</v>
+        <v>3150.8</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.00483</v>
+        <v>0.275443</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0</v>
+        <v>19.52</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
@@ -18519,13 +18549,13 @@
         <v>102</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>3.55</v>
+        <v>59.91</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>36.37</v>
+        <v>3150.8</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>2.55</v>
+        <v>178.1</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18591,10 +18621,10 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18644,10 +18674,10 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>304900</v>
+        <v>304944</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -18659,7 +18689,7 @@
         <v>91</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>102</v>
@@ -18671,22 +18701,22 @@
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>934.7</v>
+        <v>8386</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>851.66</v>
+        <v>7641</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.03381</v>
+        <v>0</v>
       </c>
       <c r="R11" s="12" t="n">
         <v>0</v>
@@ -18701,7 +18731,7 @@
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
@@ -18710,13 +18740,13 @@
         <v>102</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>83.04</v>
+        <v>745</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>851.66</v>
+        <v>7641</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>59.62</v>
+        <v>305.64</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18782,7 +18812,7 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>97</v>
@@ -18835,7 +18865,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>304904</v>
+        <v>304986</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>110</v>
@@ -18850,64 +18880,64 @@
         <v>91</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>3210.71</v>
+        <v>1008.04</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3150.8</v>
+        <v>918.49</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.275443</v>
+        <v>0.302016</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>19.52</v>
+        <v>0</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>59.91</v>
+        <v>89.55</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>3150.8</v>
+        <v>918.49</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>178.1</v>
+        <v>64.3</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -19012,7 +19042,7 @@
         <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19026,43 +19056,43 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>304944</v>
+        <v>304996</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>8386</v>
+        <v>2426.27</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>7641</v>
+        <v>2349.89</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
@@ -19083,22 +19113,22 @@
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>745</v>
+        <v>76.38</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>7641</v>
+        <v>2426.27</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>305.64</v>
+        <v>169.84</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19167,7 +19197,7 @@
         <v>96</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19203,7 +19233,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19217,79 +19247,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>304986</v>
+        <v>305080</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1008.04</v>
+        <v>6003.36</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>918.49</v>
+        <v>5636.96</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.302016</v>
+        <v>0.034</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>89.55</v>
+        <v>366.4</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>918.49</v>
+        <v>5636.96</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>64.3</v>
+        <v>394.59</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19394,7 +19424,7 @@
         <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19408,79 +19438,79 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>304995</v>
+        <v>305124</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>12462.51</v>
+        <v>4610.21</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>11355.36</v>
+        <v>4234.43</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.11544</v>
+        <v>0.4</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>33.12</v>
+        <v>8.4</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>1107.15</v>
+        <v>375.78</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>11355.36</v>
+        <v>4234.43</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>794.87</v>
+        <v>180.79</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19546,7 +19576,7 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX15" s="10" t="s">
         <v>97</v>
@@ -19585,7 +19615,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19599,79 +19629,79 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>304996</v>
+        <v>305173</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2426.27</v>
+        <v>623.96</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>2349.89</v>
+        <v>585.88</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0</v>
+        <v>0.002772</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>76.38</v>
+        <v>38.08</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>2426.27</v>
+        <v>585.88</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>169.84</v>
+        <v>23.44</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19737,10 +19767,10 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19776,7 +19806,7 @@
         <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19790,64 +19820,64 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305041</v>
+        <v>305189</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>135</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>3291.91</v>
+        <v>7219.97</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>3291.91</v>
+        <v>7219.97</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0</v>
+        <v>0.032582</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
@@ -19859,10 +19889,10 @@
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>3291.91</v>
+        <v>7219.97</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>230.45</v>
+        <v>505.4</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19967,7 +19997,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19981,79 +20011,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305066</v>
+        <v>305201</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>3852.31</v>
+        <v>7208.54</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>3824.94</v>
+        <v>7102.95</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>3.68868</v>
+        <v>0.20059</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>454.38</v>
+        <v>26.91</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>27.37</v>
+        <v>105.59</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>3824.94</v>
+        <v>7102.95</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>267.75</v>
+        <v>434.45</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20062,7 +20092,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="12" t="n">
-        <v>293.73</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="12" t="n">
         <v>0</v>
@@ -20143,25 +20173,25 @@
         <v>75</v>
       </c>
       <c r="BE18" s="14" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="BF18" s="9" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="BG18" s="9" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="BH18" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI18" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ18" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="BI18" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="BJ18" s="9" t="s">
-        <v>148</v>
-      </c>
       <c r="BK18" s="9" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="BL18" s="9" t="s">
         <v>75</v>
@@ -20172,79 +20202,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305080</v>
+        <v>305217</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="H19" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>141</v>
-      </c>
       <c r="J19" s="9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>6003.36</v>
+        <v>18851.64</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>5636.96</v>
+        <v>18851.64</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.034</v>
+        <v>0.050995</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>6.39</v>
+        <v>29.1</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>366.4</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>5636.96</v>
+        <v>18851.64</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>394.59</v>
+        <v>1319.62</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20349,7 +20379,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20363,79 +20393,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305124</v>
+        <v>305239</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>4610.21</v>
+        <v>3174.14</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>4234.43</v>
+        <v>3174.14</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.4</v>
+        <v>0.032173</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>8.4</v>
+        <v>4.98</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>375.78</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>4234.43</v>
+        <v>3174.14</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>180.79</v>
+        <v>222.19</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20540,7 +20570,7 @@
         <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20554,58 +20584,58 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305173</v>
+        <v>305240</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>623.96</v>
+        <v>1598.62</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>585.88</v>
+        <v>1456.6</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.002772</v>
+        <v>0</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
@@ -20617,16 +20647,16 @@
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>38.08</v>
+        <v>142.02</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>585.88</v>
+        <v>1456.6</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>23.44</v>
+        <v>101.96</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20692,7 +20722,7 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX21" s="10" t="s">
         <v>97</v>
@@ -20731,7 +20761,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20745,58 +20775,58 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305189</v>
+        <v>305242</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G22" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>152</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>7219.97</v>
+        <v>3426.16</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>7219.97</v>
+        <v>3145.39</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.032582</v>
+        <v>0.0061</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>5.54</v>
+        <v>3.59</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20808,16 +20838,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>280.77</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>7219.97</v>
+        <v>3145.39</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>505.4</v>
+        <v>220.19</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20922,7 +20952,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20936,79 +20966,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305201</v>
+        <v>305244</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>7208.54</v>
+        <v>3015.45</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>7102.95</v>
+        <v>3015.45</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.20059</v>
+        <v>0.176664</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>26.91</v>
+        <v>14.03</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>105.59</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>7102.95</v>
+        <v>3015.45</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>434.45</v>
+        <v>211.09</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21113,7 +21143,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21127,34 +21157,34 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305217</v>
+        <v>305253</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>18851.64</v>
+        <v>7825.28</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -21163,43 +21193,43 @@
         <v>2</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>18851.64</v>
+        <v>7130.1</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.050995</v>
+        <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>29.1</v>
+        <v>0</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>42</v>
+        <v>44.58</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>0</v>
+        <v>695.18</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>18851.64</v>
+        <v>7130.1</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>1319.62</v>
+        <v>499.11</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21304,7 +21334,7 @@
         <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21318,58 +21348,58 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305239</v>
+        <v>305256</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>3174.14</v>
+        <v>1495.06</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>3174.14</v>
+        <v>1362.24</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.032173</v>
+        <v>0.057024</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
@@ -21381,16 +21411,16 @@
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>0</v>
+        <v>132.82</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>3174.14</v>
+        <v>1362.24</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>222.19</v>
+        <v>95.36</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21495,7 +21525,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21509,79 +21539,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305240</v>
+        <v>305273</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>183</v>
+        <v>120</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>1598.62</v>
+        <v>15678.49</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>1456.6</v>
+        <v>15678.49</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.066706</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0</v>
+        <v>17.14</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>142.02</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>1456.6</v>
+        <v>15678.49</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>101.96</v>
+        <v>1097.5</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21686,7 +21716,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21700,79 +21730,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305242</v>
+        <v>305282</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>3426.16</v>
+        <v>392.71</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>3145.39</v>
+        <v>368.74</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.0061</v>
+        <v>0.006789</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>3.59</v>
+        <v>3.81</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>280.77</v>
+        <v>23.97</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>3145.39</v>
+        <v>368.74</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>220.19</v>
+        <v>14.75</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21838,10 +21868,10 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21877,7 +21907,7 @@
         <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21891,16 +21921,16 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305244</v>
+        <v>305283</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>91</v>
@@ -21909,61 +21939,61 @@
         <v>135</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>3015.45</v>
+        <v>392.71</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>3015.45</v>
+        <v>368.74</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.176664</v>
+        <v>0.006789</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>14.03</v>
+        <v>3.81</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>3015.45</v>
+        <v>368.74</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>211.09</v>
+        <v>14.75</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22029,10 +22059,10 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22068,7 +22098,7 @@
         <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22082,16 +22112,16 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305253</v>
+        <v>305284</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>91</v>
@@ -22100,61 +22130,61 @@
         <v>135</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>7825.28</v>
+        <v>392.71</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>7130.1</v>
+        <v>368.74</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0</v>
+        <v>0.006789</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>44.58</v>
+        <v>0</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>695.18</v>
+        <v>23.97</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>7130.1</v>
+        <v>368.74</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>499.11</v>
+        <v>14.75</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22220,10 +22250,10 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22259,7 +22289,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22273,34 +22303,34 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>305256</v>
+        <v>305426</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>201</v>
+        <v>91</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>135</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>1495.06</v>
+        <v>163.48</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22309,43 +22339,43 @@
         <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>1362.24</v>
+        <v>153.5</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.057024</v>
+        <v>0.003456</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>132.82</v>
+        <v>9.98</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>1362.24</v>
+        <v>153.5</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>95.36</v>
+        <v>6.14</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22411,10 +22441,10 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX30" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY30" s="14" t="s">
         <v>75</v>
@@ -22450,7 +22480,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22464,79 +22494,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>305273</v>
+        <v>305427</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>135</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>205</v>
+        <v>69</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>15678.49</v>
+        <v>163.48</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>15678.49</v>
+        <v>153.5</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.066706</v>
+        <v>0.003456</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>17.14</v>
+        <v>0.8</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>0</v>
+        <v>9.98</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>15678.49</v>
+        <v>153.5</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>1097.5</v>
+        <v>6.14</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22602,10 +22632,10 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22641,7 +22671,7 @@
         <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22655,25 +22685,25 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>305282</v>
+        <v>305445</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>69</v>
@@ -22682,31 +22712,31 @@
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>392.71</v>
+        <v>327.31</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>368.74</v>
+        <v>307.33</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.006789</v>
+        <v>0.239381</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>3.81</v>
+        <v>1.6</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
@@ -22718,16 +22748,16 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>23.97</v>
+        <v>19.98</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>368.74</v>
+        <v>307.33</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>14.75</v>
+        <v>12.3</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22832,7 +22862,7 @@
         <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22846,25 +22876,25 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>305283</v>
+        <v>305446</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>69</v>
@@ -22873,31 +22903,31 @@
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>392.71</v>
+        <v>327.31</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>368.74</v>
+        <v>307.33</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.006789</v>
+        <v>0.239381</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>3.81</v>
+        <v>1.6</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
@@ -22909,16 +22939,16 @@
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>23.97</v>
+        <v>19.98</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>368.74</v>
+        <v>307.33</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>14.75</v>
+        <v>12.3</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23023,7 +23053,7 @@
         <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23037,25 +23067,25 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>305284</v>
+        <v>305447</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>69</v>
@@ -23064,31 +23094,31 @@
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>392.71</v>
+        <v>327.31</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>368.74</v>
+        <v>307.33</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.006789</v>
+        <v>0.239381</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>3.81</v>
+        <v>1.6</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
@@ -23100,16 +23130,16 @@
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>23.97</v>
+        <v>19.98</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>368.74</v>
+        <v>307.33</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>14.75</v>
+        <v>12.3</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23214,7 +23244,7 @@
         <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23228,25 +23258,25 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>305426</v>
+        <v>305453</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>69</v>
@@ -23255,31 +23285,31 @@
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>163.48</v>
+        <v>837.05</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>153.5</v>
+        <v>805.99</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.003456</v>
+        <v>0.210944</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>0.8</v>
+        <v>9.12</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
@@ -23291,16 +23321,16 @@
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>9.98</v>
+        <v>31.06</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>153.5</v>
+        <v>805.99</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>6.14</v>
+        <v>32.25</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23405,7 +23435,7 @@
         <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23419,25 +23449,25 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>305427</v>
+        <v>305454</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>69</v>
@@ -23446,31 +23476,31 @@
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>163.48</v>
+        <v>2323.32</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>153.5</v>
+        <v>2294.51</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.003456</v>
+        <v>0.233764</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>0.8</v>
+        <v>12.22</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
@@ -23482,16 +23512,16 @@
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>9.98</v>
+        <v>28.81</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>153.5</v>
+        <v>2294.51</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>6.14</v>
+        <v>91.78</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23596,7 +23626,7 @@
         <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23610,25 +23640,25 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>305445</v>
+        <v>305455</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>69</v>
@@ -23637,31 +23667,31 @@
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>327.31</v>
+        <v>800.16</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>307.33</v>
+        <v>771.35</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.239381</v>
+        <v>0.205309</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>1.6</v>
+        <v>8.8</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
@@ -23673,16 +23703,16 @@
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>19.98</v>
+        <v>28.81</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>307.33</v>
+        <v>771.35</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>12.3</v>
+        <v>30.86</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23787,7 +23817,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23801,25 +23831,25 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>305446</v>
+        <v>305464</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>69</v>
@@ -23828,7 +23858,7 @@
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>327.31</v>
+        <v>314.65</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -23837,13 +23867,13 @@
         <v>2</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>307.33</v>
+        <v>295.45</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.239381</v>
+        <v>0.016472</v>
       </c>
       <c r="R38" s="12" t="n">
         <v>1.6</v>
@@ -23852,7 +23882,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
@@ -23864,16 +23894,16 @@
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>19.98</v>
+        <v>19.2</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>307.33</v>
+        <v>295.45</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>12.3</v>
+        <v>11.81</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23978,7 +24008,7 @@
         <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -23992,25 +24022,25 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>305447</v>
+        <v>305465</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>69</v>
@@ -24019,7 +24049,7 @@
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>327.31</v>
+        <v>314.65</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -24028,13 +24058,13 @@
         <v>2</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>307.33</v>
+        <v>295.45</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.239381</v>
+        <v>0.016472</v>
       </c>
       <c r="R39" s="12" t="n">
         <v>1.6</v>
@@ -24043,7 +24073,7 @@
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
@@ -24055,16 +24085,16 @@
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>19.98</v>
+        <v>19.2</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>307.33</v>
+        <v>295.45</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>12.3</v>
+        <v>11.81</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24169,7 +24199,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24183,25 +24213,25 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>305453</v>
+        <v>305466</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>69</v>
@@ -24210,31 +24240,31 @@
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>837.05</v>
+        <v>314.65</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>805.99</v>
+        <v>295.45</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.210944</v>
+        <v>0.016472</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>9.12</v>
+        <v>1.6</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
@@ -24246,16 +24276,16 @@
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>31.06</v>
+        <v>19.2</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>805.99</v>
+        <v>295.45</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>32.25</v>
+        <v>11.81</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24360,7 +24390,7 @@
         <v>69</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24374,25 +24404,25 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>305454</v>
+        <v>305474</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>69</v>
@@ -24401,31 +24431,31 @@
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>2323.32</v>
+        <v>167.35</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>2294.51</v>
+        <v>157.14</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.233764</v>
+        <v>0.014804</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>12.22</v>
+        <v>2.51</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
@@ -24437,16 +24467,16 @@
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>28.81</v>
+        <v>10.21</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>2294.51</v>
+        <v>157.14</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>91.78</v>
+        <v>6.29</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24551,7 +24581,7 @@
         <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24565,25 +24595,25 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>305455</v>
+        <v>305475</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>69</v>
@@ -24592,31 +24622,31 @@
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>800.16</v>
+        <v>83.19</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>771.35</v>
+        <v>78.12</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.205309</v>
+        <v>0.013886</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>8.8</v>
+        <v>0.93</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
@@ -24628,16 +24658,16 @@
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>28.81</v>
+        <v>5.07</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>771.35</v>
+        <v>78.12</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>30.86</v>
+        <v>3.13</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24742,7 +24772,7 @@
         <v>69</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24756,25 +24786,25 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>305464</v>
+        <v>305476</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>69</v>
@@ -24783,31 +24813,31 @@
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>314.65</v>
+        <v>83.19</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>295.45</v>
+        <v>78.12</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.013886</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>1.6</v>
+        <v>0.93</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
@@ -24819,16 +24849,16 @@
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>19.2</v>
+        <v>5.07</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>295.45</v>
+        <v>78.12</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>11.81</v>
+        <v>3.13</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24933,7 +24963,7 @@
         <v>69</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -24947,34 +24977,34 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>305465</v>
+        <v>305543</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>69</v>
+        <v>228</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>314.65</v>
+        <v>839.95</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -24983,43 +25013,43 @@
         <v>2</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>295.45</v>
+        <v>839.95</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.030474</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>1.6</v>
+        <v>5.42</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>295.45</v>
+        <v>839.95</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>11.81</v>
+        <v>58.79</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25088,7 +25118,7 @@
         <v>76</v>
       </c>
       <c r="AX44" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY44" s="14" t="s">
         <v>75</v>
@@ -25124,7 +25154,7 @@
         <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25138,79 +25168,79 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>305466</v>
+        <v>305544</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>69</v>
+        <v>228</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>314.65</v>
+        <v>297.63</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>295.45</v>
+        <v>297.63</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.001848</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>295.45</v>
+        <v>297.63</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>11.81</v>
+        <v>20.83</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25279,7 +25309,7 @@
         <v>76</v>
       </c>
       <c r="AX45" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY45" s="14" t="s">
         <v>75</v>
@@ -25315,7 +25345,7 @@
         <v>69</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25329,79 +25359,79 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>305474</v>
+        <v>305551</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>69</v>
+        <v>235</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>167.35</v>
+        <v>2815.95</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>157.14</v>
+        <v>2815.95</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.014804</v>
+        <v>0.002473</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>10.21</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>157.14</v>
+        <v>2815.95</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>6.29</v>
+        <v>197.12</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25467,10 +25497,10 @@
         <v>74</v>
       </c>
       <c r="AW46" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX46" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY46" s="14" t="s">
         <v>75</v>
@@ -25506,7 +25536,7 @@
         <v>69</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25520,79 +25550,79 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>305475</v>
+        <v>305559</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>69</v>
+        <v>240</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>83.19</v>
+        <v>454.32</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>78.12</v>
+        <v>454.32</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.013886</v>
+        <v>0.008017</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>0.93</v>
+        <v>2.02</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>78.12</v>
+        <v>454.32</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>3.13</v>
+        <v>31.8</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25661,7 +25691,7 @@
         <v>76</v>
       </c>
       <c r="AX47" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY47" s="14" t="s">
         <v>75</v>
@@ -25697,7 +25727,7 @@
         <v>69</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25711,79 +25741,79 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>305476</v>
+        <v>305598</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>161</v>
+        <v>243</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>83.19</v>
+        <v>837.01</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>78.12</v>
+        <v>806.92</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.013886</v>
+        <v>0</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>0.93</v>
+        <v>22</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>5.07</v>
+        <v>30.09</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>78.12</v>
+        <v>806.92</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>3.13</v>
+        <v>56.48</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25849,10 +25879,10 @@
         <v>74</v>
       </c>
       <c r="AW48" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX48" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY48" s="14" t="s">
         <v>75</v>
@@ -25888,7 +25918,7 @@
         <v>69</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BK48" s="9" t="s">
         <v>75</v>
@@ -25902,79 +25932,79 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>305543</v>
+        <v>305613</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>126</v>
+        <v>249</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>839.95</v>
+        <v>902.64</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>839.95</v>
+        <v>902.64</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.030474</v>
+        <v>0.01086</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>5.42</v>
+        <v>9.93</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="Y49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>839.95</v>
+        <v>902.64</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>58.79</v>
+        <v>63.18</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26040,7 +26070,7 @@
         <v>74</v>
       </c>
       <c r="AW49" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX49" s="10" t="s">
         <v>97</v>
@@ -26079,7 +26109,7 @@
         <v>69</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26093,79 +26123,79 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>305544</v>
+        <v>305615</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>297.63</v>
+        <v>3419.5</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>297.63</v>
+        <v>3400.4</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.001848</v>
+        <v>0.068208</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>1.52</v>
+        <v>15.85</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="U50" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>297.63</v>
+        <v>3400.4</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>20.83</v>
+        <v>199.84</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26231,7 +26261,7 @@
         <v>74</v>
       </c>
       <c r="AW50" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX50" s="10" t="s">
         <v>97</v>
@@ -26270,7 +26300,7 @@
         <v>69</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26284,34 +26314,34 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>305551</v>
+        <v>305625</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>2815.95</v>
+        <v>830.75</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
@@ -26320,43 +26350,43 @@
         <v>1</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>2815.95</v>
+        <v>804.6</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.16337</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>2.8</v>
+        <v>100</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V51" s="12" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="W51" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>0</v>
+        <v>26.15</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>2815.95</v>
+        <v>804.6</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>197.12</v>
+        <v>56.32</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26422,7 +26452,7 @@
         <v>74</v>
       </c>
       <c r="AW51" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX51" s="10" t="s">
         <v>97</v>
@@ -26461,7 +26491,7 @@
         <v>69</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BK51" s="9" t="s">
         <v>75</v>
@@ -26475,79 +26505,79 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>305559</v>
+        <v>305678</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="J52" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>454.32</v>
+        <v>1057.92</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>454.32</v>
+        <v>992.36</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0.008017</v>
+        <v>0.00078</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>2.02</v>
+        <v>4.81</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Y52" s="12" t="n">
-        <v>0</v>
+        <v>65.56</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>454.32</v>
+        <v>992.36</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>31.8</v>
+        <v>39.69</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26652,7 +26682,7 @@
         <v>69</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="BK52" s="9" t="s">
         <v>75</v>
@@ -26666,34 +26696,34 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>305598</v>
+        <v>305695</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>269</v>
+        <v>120</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>271</v>
+        <v>122</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>121</v>
+        <v>268</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>837.01</v>
+        <v>6783</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
@@ -26702,43 +26732,43 @@
         <v>2</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>806.92</v>
+        <v>6783</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0</v>
+        <v>0.037508</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>22</v>
+        <v>13.58</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="U53" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V53" s="12" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="W53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Y53" s="12" t="n">
-        <v>30.09</v>
+        <v>0</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>806.92</v>
+        <v>6783</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>56.48</v>
+        <v>474.81</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -26843,7 +26873,7 @@
         <v>69</v>
       </c>
       <c r="BJ53" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="BK53" s="9" t="s">
         <v>75</v>
@@ -26857,34 +26887,34 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>305613</v>
+        <v>305701</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>902.64</v>
+        <v>6261.84</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
@@ -26893,43 +26923,43 @@
         <v>1</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>902.64</v>
+        <v>6261.84</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0.01086</v>
+        <v>0.01302</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>9.93</v>
+        <v>1.46</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V54" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W54" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Y54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>902.64</v>
+        <v>6261.84</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>63.18</v>
+        <v>438.33</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27034,7 +27064,7 @@
         <v>69</v>
       </c>
       <c r="BJ54" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="BK54" s="9" t="s">
         <v>75</v>
@@ -27048,79 +27078,79 @@
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>305615</v>
+        <v>305715</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>3419.5</v>
+        <v>1283.63</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>3400.4</v>
+        <v>1217.81</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>0.068208</v>
+        <v>0.105</v>
       </c>
       <c r="R55" s="12" t="n">
-        <v>15.85</v>
+        <v>8</v>
       </c>
       <c r="S55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="U55" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V55" s="12" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="W55" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X55" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Y55" s="12" t="n">
-        <v>19.1</v>
+        <v>65.82</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>3400.4</v>
+        <v>1217.81</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>199.84</v>
+        <v>81.63</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27186,7 +27216,7 @@
         <v>74</v>
       </c>
       <c r="AW55" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX55" s="10" t="s">
         <v>97</v>
@@ -27225,7 +27255,7 @@
         <v>69</v>
       </c>
       <c r="BJ55" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="BK55" s="9" t="s">
         <v>75</v>
@@ -27239,34 +27269,34 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>305625</v>
+        <v>305726</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>282</v>
+        <v>120</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>830.75</v>
+        <v>2332.2</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
@@ -27275,43 +27305,43 @@
         <v>1</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>804.6</v>
+        <v>2332.2</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>0.16337</v>
+        <v>0.026208</v>
       </c>
       <c r="R56" s="12" t="n">
-        <v>100</v>
+        <v>6.96</v>
       </c>
       <c r="S56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T56" s="14" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="U56" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V56" s="12" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="W56" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X56" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Y56" s="12" t="n">
-        <v>26.15</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="12" t="n">
-        <v>804.6</v>
+        <v>2332.2</v>
       </c>
       <c r="AA56" s="12" t="n">
-        <v>56.32</v>
+        <v>163.25</v>
       </c>
       <c r="AB56" s="12" t="n">
         <v>0</v>
@@ -27377,7 +27407,7 @@
         <v>74</v>
       </c>
       <c r="AW56" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX56" s="10" t="s">
         <v>97</v>
@@ -27416,7 +27446,7 @@
         <v>69</v>
       </c>
       <c r="BJ56" s="9" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="BK56" s="9" t="s">
         <v>75</v>
@@ -27429,534 +27459,900 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4"/>
+      <c r="A57" s="8" t="n">
+        <v>305746</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>1511.1</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>1511.1</v>
+      </c>
+      <c r="P57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="U57" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V57" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W57" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X57" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="12" t="n">
+        <v>1511.1</v>
+      </c>
+      <c r="AA57" s="12" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="AB57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW57" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX57" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="AY57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG57" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI57" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ57" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="BK57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM57" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="17" t="s">
+    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="n">
+        <v>305748</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>1204.74</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="12" t="n">
+        <v>1204.74</v>
+      </c>
+      <c r="P58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="U58" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V58" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W58" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X58" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="12" t="n">
+        <v>1204.74</v>
+      </c>
+      <c r="AA58" s="12" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="AB58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW58" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX58" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
-      <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="17"/>
-      <c r="S58" s="17"/>
-      <c r="T58" s="17"/>
-      <c r="U58" s="17"/>
-      <c r="V58" s="17"/>
+      <c r="AY58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF58" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG58" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI58" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ58" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="BK58" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL58" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM58" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="59" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G59" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I59" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="J59" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K59" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L59" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M59" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="N59" s="18" t="s">
+    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="n">
+        <v>305752</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L59" s="12" t="n">
+        <v>15650.36</v>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="O59" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P59" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q59" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R59" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S59" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="T59" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="U59" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V59" s="18" t="s">
-        <v>37</v>
+      <c r="O59" s="12" t="n">
+        <v>15353.13</v>
+      </c>
+      <c r="P59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="13" t="n">
+        <v>0.492454</v>
+      </c>
+      <c r="R59" s="12" t="n">
+        <v>108.26</v>
+      </c>
+      <c r="S59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="U59" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V59" s="12" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="W59" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X59" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y59" s="12" t="n">
+        <v>297.23</v>
+      </c>
+      <c r="Z59" s="12" t="n">
+        <v>15353.13</v>
+      </c>
+      <c r="AA59" s="12" t="n">
+        <v>693.38</v>
+      </c>
+      <c r="AB59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW59" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX59" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG59" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI59" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ59" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="BK59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM59" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="19" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="19" t="n">
-        <v>4817.9</v>
-      </c>
-      <c r="F60" s="19" t="n">
-        <v>132502.36</v>
-      </c>
-      <c r="G60" s="19" t="n">
-        <v>8517.83</v>
-      </c>
-      <c r="H60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="19" t="n">
-        <v>293.73</v>
-      </c>
-      <c r="K60" s="19" t="n">
-        <v>137243.88</v>
-      </c>
-      <c r="L60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="20" t="n">
-        <v>7.370481</v>
-      </c>
-      <c r="S60" s="19" t="n">
-        <v>132425.98</v>
-      </c>
-      <c r="T60" s="19" t="n">
-        <v>137243.88</v>
-      </c>
-      <c r="U60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F61" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G61" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H61" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I61" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J61" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K61" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="L61" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="M61" s="18" t="s">
-        <v>296</v>
-      </c>
+      <c r="A61" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" s="17"/>
+      <c r="O61" s="17"/>
+      <c r="P61" s="17"/>
+      <c r="Q61" s="17"/>
+      <c r="R61" s="17"/>
+      <c r="S61" s="17"/>
+      <c r="T61" s="17"/>
+      <c r="U61" s="17"/>
+      <c r="V61" s="17"/>
     </row>
-    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="19" t="n">
-        <v>904.01</v>
-      </c>
-      <c r="B62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="19" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="E62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="19" t="n">
-        <v>0</v>
+    <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L62" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M62" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="N62" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O62" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P62" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q62" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R62" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S62" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="T62" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="U62" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V62" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4"/>
+      <c r="A63" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="B63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>4025.4</v>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>148798.3</v>
+      </c>
+      <c r="G63" s="19" t="n">
+        <v>9111.53</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="19" t="n">
+        <v>152747.32</v>
+      </c>
+      <c r="L63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="20" t="n">
+        <v>4.202691</v>
+      </c>
+      <c r="S63" s="19" t="n">
+        <v>148721.92</v>
+      </c>
+      <c r="T63" s="19" t="n">
+        <v>152747.32</v>
+      </c>
+      <c r="U63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="21"/>
-      <c r="L64" s="21"/>
-      <c r="M64" s="21"/>
-      <c r="N64" s="21"/>
-      <c r="O64" s="21"/>
-      <c r="P64" s="21"/>
-      <c r="Q64" s="21"/>
-      <c r="R64" s="21"/>
-      <c r="S64" s="21"/>
-      <c r="T64" s="21"/>
-      <c r="U64" s="21"/>
-      <c r="V64" s="21"/>
-      <c r="W64" s="21"/>
-      <c r="X64" s="21"/>
-      <c r="Y64" s="21"/>
-      <c r="Z64" s="21"/>
-      <c r="AA64" s="21"/>
-      <c r="AB64" s="21"/>
-      <c r="AC64" s="21"/>
-      <c r="AD64" s="21"/>
-      <c r="AE64" s="21"/>
-      <c r="AF64" s="21"/>
-      <c r="AG64" s="21"/>
-      <c r="AH64" s="21"/>
-      <c r="AI64" s="21"/>
-      <c r="AJ64" s="21"/>
-      <c r="AK64" s="21"/>
-      <c r="AL64" s="21"/>
-      <c r="AM64" s="21"/>
-      <c r="AN64" s="21"/>
-      <c r="AO64" s="21"/>
-      <c r="AP64" s="21"/>
-      <c r="AQ64" s="21"/>
-      <c r="AR64" s="21"/>
-      <c r="AS64" s="21"/>
-      <c r="AT64" s="21"/>
-      <c r="AU64" s="21"/>
-      <c r="AV64" s="21"/>
-      <c r="AW64" s="21"/>
-      <c r="AX64" s="21"/>
-      <c r="AY64" s="21"/>
-      <c r="AZ64" s="21"/>
-      <c r="BA64" s="21"/>
-      <c r="BB64" s="21"/>
-      <c r="BC64" s="21"/>
-      <c r="BD64" s="21"/>
-      <c r="BE64" s="21"/>
-      <c r="BF64" s="21"/>
-      <c r="BG64" s="21"/>
-      <c r="BH64" s="21"/>
-      <c r="BI64" s="21"/>
-      <c r="BJ64" s="21"/>
-      <c r="BK64" s="21"/>
-      <c r="BL64" s="21"/>
-      <c r="BM64" s="21"/>
+      <c r="A64" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I64" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J64" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K64" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="L64" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="M64" s="18" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
-      <c r="Z65" s="4"/>
-      <c r="AA65" s="4"/>
-      <c r="AB65" s="4"/>
-      <c r="AC65" s="4"/>
-      <c r="AD65" s="4"/>
-      <c r="AE65" s="4"/>
-      <c r="AF65" s="4"/>
-      <c r="AG65" s="4"/>
-      <c r="AH65" s="4"/>
-      <c r="AI65" s="4"/>
-      <c r="AJ65" s="4"/>
-      <c r="AK65" s="4"/>
-      <c r="AL65" s="4"/>
-      <c r="AM65" s="4"/>
-      <c r="AN65" s="4"/>
-      <c r="AO65" s="4"/>
-      <c r="AP65" s="4"/>
-      <c r="AQ65" s="4"/>
-      <c r="AR65" s="4"/>
-      <c r="AS65" s="4"/>
-      <c r="AT65" s="4"/>
-      <c r="AU65" s="4"/>
-      <c r="AV65" s="4"/>
-      <c r="AW65" s="4"/>
-      <c r="AX65" s="4"/>
-      <c r="AY65" s="4"/>
-      <c r="AZ65" s="4"/>
-      <c r="BA65" s="4"/>
-      <c r="BB65" s="4"/>
-      <c r="BC65" s="4"/>
-      <c r="BD65" s="4"/>
-      <c r="BE65" s="4"/>
-      <c r="BF65" s="4"/>
-      <c r="BG65" s="4"/>
-      <c r="BH65" s="4"/>
-      <c r="BI65" s="4"/>
-      <c r="BJ65" s="4"/>
-      <c r="BK65" s="4"/>
-      <c r="BL65" s="4"/>
-      <c r="BM65" s="4"/>
+      <c r="A65" s="19" t="n">
+        <v>559.58</v>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
-      <c r="Z66" s="4"/>
-      <c r="AA66" s="4"/>
-      <c r="AB66" s="4"/>
-      <c r="AC66" s="4"/>
-      <c r="AD66" s="4"/>
-      <c r="AE66" s="4"/>
-      <c r="AF66" s="4"/>
-      <c r="AG66" s="4"/>
-      <c r="AH66" s="4"/>
-      <c r="AI66" s="4"/>
-      <c r="AJ66" s="4"/>
-      <c r="AK66" s="4"/>
-      <c r="AL66" s="4"/>
-      <c r="AM66" s="4"/>
-      <c r="AN66" s="4"/>
-      <c r="AO66" s="4"/>
-      <c r="AP66" s="4"/>
-      <c r="AQ66" s="4"/>
-      <c r="AR66" s="4"/>
-      <c r="AS66" s="4"/>
-      <c r="AT66" s="4"/>
-      <c r="AU66" s="4"/>
-      <c r="AV66" s="4"/>
-      <c r="AW66" s="4"/>
-      <c r="AX66" s="4"/>
-      <c r="AY66" s="4"/>
-      <c r="AZ66" s="4"/>
-      <c r="BA66" s="4"/>
-      <c r="BB66" s="4"/>
-      <c r="BC66" s="4"/>
-      <c r="BD66" s="4"/>
-      <c r="BE66" s="4"/>
-      <c r="BF66" s="4"/>
-      <c r="BG66" s="4"/>
-      <c r="BH66" s="4"/>
-      <c r="BI66" s="4"/>
-      <c r="BJ66" s="4"/>
-      <c r="BK66" s="4"/>
-      <c r="BL66" s="4"/>
-      <c r="BM66" s="4"/>
+      <c r="A66" s="4"/>
     </row>
-    <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="4"/>
-      <c r="AB67" s="4"/>
-      <c r="AC67" s="4"/>
-      <c r="AD67" s="4"/>
-      <c r="AE67" s="4"/>
-      <c r="AF67" s="4"/>
-      <c r="AG67" s="4"/>
-      <c r="AH67" s="4"/>
-      <c r="AI67" s="4"/>
-      <c r="AJ67" s="4"/>
-      <c r="AK67" s="4"/>
-      <c r="AL67" s="4"/>
-      <c r="AM67" s="4"/>
-      <c r="AN67" s="4"/>
-      <c r="AO67" s="4"/>
-      <c r="AP67" s="4"/>
-      <c r="AQ67" s="4"/>
-      <c r="AR67" s="4"/>
-      <c r="AS67" s="4"/>
-      <c r="AT67" s="4"/>
-      <c r="AU67" s="4"/>
-      <c r="AV67" s="4"/>
-      <c r="AW67" s="4"/>
-      <c r="AX67" s="4"/>
-      <c r="AY67" s="4"/>
-      <c r="AZ67" s="4"/>
-      <c r="BA67" s="4"/>
-      <c r="BB67" s="4"/>
-      <c r="BC67" s="4"/>
-      <c r="BD67" s="4"/>
-      <c r="BE67" s="4"/>
-      <c r="BF67" s="4"/>
-      <c r="BG67" s="4"/>
-      <c r="BH67" s="4"/>
-      <c r="BI67" s="4"/>
-      <c r="BJ67" s="4"/>
-      <c r="BK67" s="4"/>
-      <c r="BL67" s="4"/>
-      <c r="BM67" s="4"/>
+    <row r="67" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="21"/>
+      <c r="M67" s="21"/>
+      <c r="N67" s="21"/>
+      <c r="O67" s="21"/>
+      <c r="P67" s="21"/>
+      <c r="Q67" s="21"/>
+      <c r="R67" s="21"/>
+      <c r="S67" s="21"/>
+      <c r="T67" s="21"/>
+      <c r="U67" s="21"/>
+      <c r="V67" s="21"/>
+      <c r="W67" s="21"/>
+      <c r="X67" s="21"/>
+      <c r="Y67" s="21"/>
+      <c r="Z67" s="21"/>
+      <c r="AA67" s="21"/>
+      <c r="AB67" s="21"/>
+      <c r="AC67" s="21"/>
+      <c r="AD67" s="21"/>
+      <c r="AE67" s="21"/>
+      <c r="AF67" s="21"/>
+      <c r="AG67" s="21"/>
+      <c r="AH67" s="21"/>
+      <c r="AI67" s="21"/>
+      <c r="AJ67" s="21"/>
+      <c r="AK67" s="21"/>
+      <c r="AL67" s="21"/>
+      <c r="AM67" s="21"/>
+      <c r="AN67" s="21"/>
+      <c r="AO67" s="21"/>
+      <c r="AP67" s="21"/>
+      <c r="AQ67" s="21"/>
+      <c r="AR67" s="21"/>
+      <c r="AS67" s="21"/>
+      <c r="AT67" s="21"/>
+      <c r="AU67" s="21"/>
+      <c r="AV67" s="21"/>
+      <c r="AW67" s="21"/>
+      <c r="AX67" s="21"/>
+      <c r="AY67" s="21"/>
+      <c r="AZ67" s="21"/>
+      <c r="BA67" s="21"/>
+      <c r="BB67" s="21"/>
+      <c r="BC67" s="21"/>
+      <c r="BD67" s="21"/>
+      <c r="BE67" s="21"/>
+      <c r="BF67" s="21"/>
+      <c r="BG67" s="21"/>
+      <c r="BH67" s="21"/>
+      <c r="BI67" s="21"/>
+      <c r="BJ67" s="21"/>
+      <c r="BK67" s="21"/>
+      <c r="BL67" s="21"/>
+      <c r="BM67" s="21"/>
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -28025,7 +28421,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -28094,7 +28490,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -28163,7 +28559,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -28232,7 +28628,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>303</v>
+        <v>22</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -28301,7 +28697,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -28370,7 +28766,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -28437,8 +28833,215 @@
       <c r="BL74" s="4"/>
       <c r="BM74" s="4"/>
     </row>
+    <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="4"/>
+      <c r="AB75" s="4"/>
+      <c r="AC75" s="4"/>
+      <c r="AD75" s="4"/>
+      <c r="AE75" s="4"/>
+      <c r="AF75" s="4"/>
+      <c r="AG75" s="4"/>
+      <c r="AH75" s="4"/>
+      <c r="AI75" s="4"/>
+      <c r="AJ75" s="4"/>
+      <c r="AK75" s="4"/>
+      <c r="AL75" s="4"/>
+      <c r="AM75" s="4"/>
+      <c r="AN75" s="4"/>
+      <c r="AO75" s="4"/>
+      <c r="AP75" s="4"/>
+      <c r="AQ75" s="4"/>
+      <c r="AR75" s="4"/>
+      <c r="AS75" s="4"/>
+      <c r="AT75" s="4"/>
+      <c r="AU75" s="4"/>
+      <c r="AV75" s="4"/>
+      <c r="AW75" s="4"/>
+      <c r="AX75" s="4"/>
+      <c r="AY75" s="4"/>
+      <c r="AZ75" s="4"/>
+      <c r="BA75" s="4"/>
+      <c r="BB75" s="4"/>
+      <c r="BC75" s="4"/>
+      <c r="BD75" s="4"/>
+      <c r="BE75" s="4"/>
+      <c r="BF75" s="4"/>
+      <c r="BG75" s="4"/>
+      <c r="BH75" s="4"/>
+      <c r="BI75" s="4"/>
+      <c r="BJ75" s="4"/>
+      <c r="BK75" s="4"/>
+      <c r="BL75" s="4"/>
+      <c r="BM75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="4"/>
+      <c r="AB76" s="4"/>
+      <c r="AC76" s="4"/>
+      <c r="AD76" s="4"/>
+      <c r="AE76" s="4"/>
+      <c r="AF76" s="4"/>
+      <c r="AG76" s="4"/>
+      <c r="AH76" s="4"/>
+      <c r="AI76" s="4"/>
+      <c r="AJ76" s="4"/>
+      <c r="AK76" s="4"/>
+      <c r="AL76" s="4"/>
+      <c r="AM76" s="4"/>
+      <c r="AN76" s="4"/>
+      <c r="AO76" s="4"/>
+      <c r="AP76" s="4"/>
+      <c r="AQ76" s="4"/>
+      <c r="AR76" s="4"/>
+      <c r="AS76" s="4"/>
+      <c r="AT76" s="4"/>
+      <c r="AU76" s="4"/>
+      <c r="AV76" s="4"/>
+      <c r="AW76" s="4"/>
+      <c r="AX76" s="4"/>
+      <c r="AY76" s="4"/>
+      <c r="AZ76" s="4"/>
+      <c r="BA76" s="4"/>
+      <c r="BB76" s="4"/>
+      <c r="BC76" s="4"/>
+      <c r="BD76" s="4"/>
+      <c r="BE76" s="4"/>
+      <c r="BF76" s="4"/>
+      <c r="BG76" s="4"/>
+      <c r="BH76" s="4"/>
+      <c r="BI76" s="4"/>
+      <c r="BJ76" s="4"/>
+      <c r="BK76" s="4"/>
+      <c r="BL76" s="4"/>
+      <c r="BM76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="4"/>
+      <c r="AB77" s="4"/>
+      <c r="AC77" s="4"/>
+      <c r="AD77" s="4"/>
+      <c r="AE77" s="4"/>
+      <c r="AF77" s="4"/>
+      <c r="AG77" s="4"/>
+      <c r="AH77" s="4"/>
+      <c r="AI77" s="4"/>
+      <c r="AJ77" s="4"/>
+      <c r="AK77" s="4"/>
+      <c r="AL77" s="4"/>
+      <c r="AM77" s="4"/>
+      <c r="AN77" s="4"/>
+      <c r="AO77" s="4"/>
+      <c r="AP77" s="4"/>
+      <c r="AQ77" s="4"/>
+      <c r="AR77" s="4"/>
+      <c r="AS77" s="4"/>
+      <c r="AT77" s="4"/>
+      <c r="AU77" s="4"/>
+      <c r="AV77" s="4"/>
+      <c r="AW77" s="4"/>
+      <c r="AX77" s="4"/>
+      <c r="AY77" s="4"/>
+      <c r="AZ77" s="4"/>
+      <c r="BA77" s="4"/>
+      <c r="BB77" s="4"/>
+      <c r="BC77" s="4"/>
+      <c r="BD77" s="4"/>
+      <c r="BE77" s="4"/>
+      <c r="BF77" s="4"/>
+      <c r="BG77" s="4"/>
+      <c r="BH77" s="4"/>
+      <c r="BI77" s="4"/>
+      <c r="BJ77" s="4"/>
+      <c r="BK77" s="4"/>
+      <c r="BL77" s="4"/>
+      <c r="BM77" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="71">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -28495,10 +29098,10 @@
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B56:E56"/>
-    <mergeCell ref="A58:V58"/>
-    <mergeCell ref="A64:BM64"/>
-    <mergeCell ref="A65:BM65"/>
-    <mergeCell ref="A66:BM66"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A61:V61"/>
     <mergeCell ref="A67:BM67"/>
     <mergeCell ref="A68:BM68"/>
     <mergeCell ref="A69:BM69"/>
@@ -28507,6 +29110,9 @@
     <mergeCell ref="A72:BM72"/>
     <mergeCell ref="A73:BM73"/>
     <mergeCell ref="A74:BM74"/>
+    <mergeCell ref="A75:BM75"/>
+    <mergeCell ref="A76:BM76"/>
+    <mergeCell ref="A77:BM77"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="328">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 24/04/2026 09:30:17</t>
+    <t xml:space="preserve">Emitido em: 27/04/2026 08:59:35</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -352,27 +352,12 @@
     <t xml:space="preserve">41260417781412000109550010000119631000316094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.816</t>
+    <t xml:space="preserve">862.414</t>
   </si>
   <si>
     <t xml:space="preserve">13/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">02/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.008,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260430228132000136550010000088161997156414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">862.414</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.426,27</t>
   </si>
   <si>
@@ -751,21 +736,6 @@
     <t xml:space="preserve">42260475339051000141550080006184651995060434</t>
   </si>
   <si>
-    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.961.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">837,01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460561719009503550210019610101643781317</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.351.353</t>
   </si>
   <si>
@@ -911,6 +881,72 @@
   </si>
   <si>
     <t xml:space="preserve">42260402308456000149550050004481331387647143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.626,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260412077181000133550030002239361899532783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260411389565000200570050003977821000839703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.702 - TRAMONTINA S/A CUTELARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.347.675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.365,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260490050238000114550010013476751216452879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.288 - ITAMONTE ILUM EIRELI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">910,75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260427160810000161550010000073371764553504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260411389565000200570050003978401000840308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">754.155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">916,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260409641520000158550010007541551062741704</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17156,7 +17192,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM77"/>
+  <dimension ref="A1:BM79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -18865,49 +18901,49 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>304986</v>
+        <v>304996</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>1008.04</v>
+        <v>2426.27</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>918.49</v>
+        <v>2349.89</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.302016</v>
+        <v>0</v>
       </c>
       <c r="R12" s="12" t="n">
         <v>0</v>
@@ -18916,28 +18952,28 @@
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>89.55</v>
+        <v>76.38</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>918.49</v>
+        <v>2426.27</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>64.3</v>
+        <v>169.84</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -19006,7 +19042,7 @@
         <v>96</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -19042,7 +19078,7 @@
         <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19056,10 +19092,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>304996</v>
+        <v>305080</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -19068,67 +19104,67 @@
         <v>116</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>2426.27</v>
+        <v>6003.36</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>2349.89</v>
+        <v>5636.96</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>76.38</v>
+        <v>366.4</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>2426.27</v>
+        <v>5636.96</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>169.84</v>
+        <v>394.59</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19197,7 +19233,7 @@
         <v>96</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19233,7 +19269,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19247,25 +19283,25 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305080</v>
+        <v>305124</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>125</v>
@@ -19274,25 +19310,25 @@
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6003.36</v>
+        <v>4610.21</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>5636.96</v>
+        <v>4234.43</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.034</v>
+        <v>0.4</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>6.39</v>
+        <v>8.4</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
@@ -19304,22 +19340,22 @@
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>366.4</v>
+        <v>375.78</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>5636.96</v>
+        <v>4234.43</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>394.59</v>
+        <v>180.79</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19438,7 +19474,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305124</v>
+        <v>305173</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>128</v>
@@ -19453,64 +19489,64 @@
         <v>91</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>4610.21</v>
+        <v>623.96</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>4234.43</v>
+        <v>585.88</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.4</v>
+        <v>0.002772</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>8.4</v>
+        <v>2.92</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>375.78</v>
+        <v>38.08</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>4234.43</v>
+        <v>585.88</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>180.79</v>
+        <v>23.44</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19576,7 +19612,7 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
         <v>97</v>
@@ -19615,7 +19651,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19629,10 +19665,10 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305173</v>
+        <v>305189</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -19641,67 +19677,67 @@
         <v>134</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="H16" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>136</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>623.96</v>
+        <v>7219.97</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>585.88</v>
+        <v>7219.97</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.002772</v>
+        <v>0.032582</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>2.92</v>
+        <v>5.54</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>38.08</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>585.88</v>
+        <v>7219.97</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>23.44</v>
+        <v>505.4</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19767,7 +19803,7 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX16" s="10" t="s">
         <v>97</v>
@@ -19806,7 +19842,7 @@
         <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19820,79 +19856,79 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305189</v>
+        <v>305201</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>7219.97</v>
+        <v>7208.54</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>7219.97</v>
+        <v>7102.95</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.032582</v>
+        <v>0.20059</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>5.54</v>
+        <v>26.91</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>0</v>
+        <v>105.59</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>7219.97</v>
+        <v>7102.95</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>505.4</v>
+        <v>434.45</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19997,7 +20033,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -20011,79 +20047,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305201</v>
+        <v>305217</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>144</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>7208.54</v>
+        <v>18851.64</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>7102.95</v>
+        <v>18851.64</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.20059</v>
+        <v>0.050995</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>26.91</v>
+        <v>29.1</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>105.59</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>7102.95</v>
+        <v>18851.64</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>434.45</v>
+        <v>1319.62</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20188,7 +20224,7 @@
         <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20202,79 +20238,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305217</v>
+        <v>305239</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>18851.64</v>
+        <v>3174.14</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>18851.64</v>
+        <v>3174.14</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.050995</v>
+        <v>0.032173</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>29.1</v>
+        <v>4.98</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>18851.64</v>
+        <v>3174.14</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>1319.62</v>
+        <v>222.19</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20379,7 +20415,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20393,10 +20429,10 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305239</v>
+        <v>305240</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -20405,46 +20441,46 @@
         <v>151</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>3174.14</v>
+        <v>1598.62</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>3174.14</v>
+        <v>1456.6</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.032173</v>
+        <v>0</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
@@ -20456,16 +20492,16 @@
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>142.02</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>3174.14</v>
+        <v>1456.6</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>222.19</v>
+        <v>101.96</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20570,7 +20606,7 @@
         <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20584,52 +20620,52 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305240</v>
+        <v>305242</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>91</v>
-      </c>
       <c r="H21" s="9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1598.62</v>
+        <v>3426.16</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1456.6</v>
+        <v>3145.39</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0</v>
+        <v>0.0061</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
@@ -20641,22 +20677,22 @@
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>142.02</v>
+        <v>280.77</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>1456.6</v>
+        <v>3145.39</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>101.96</v>
+        <v>220.19</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20775,7 +20811,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305242</v>
+        <v>305244</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>159</v>
@@ -20787,67 +20823,67 @@
         <v>160</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>3426.16</v>
+        <v>3015.45</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>3145.39</v>
+        <v>3015.45</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.0061</v>
+        <v>0.176664</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>3.59</v>
+        <v>14.03</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>280.77</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>3145.39</v>
+        <v>3015.45</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>220.19</v>
+        <v>211.09</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20952,7 +20988,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20966,79 +21002,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305244</v>
+        <v>305253</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>3015.45</v>
+        <v>7825.28</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>3015.45</v>
+        <v>7130.1</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.176664</v>
+        <v>0</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>14.03</v>
+        <v>0</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>62</v>
+        <v>44.58</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0</v>
+        <v>695.18</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>3015.45</v>
+        <v>7130.1</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>211.09</v>
+        <v>499.11</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21143,7 +21179,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21157,49 +21193,49 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305253</v>
+        <v>305256</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>91</v>
-      </c>
       <c r="H24" s="9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>7825.28</v>
+        <v>1495.06</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>7130.1</v>
+        <v>1362.24</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0</v>
+        <v>0.057024</v>
       </c>
       <c r="R24" s="12" t="n">
         <v>0</v>
@@ -21214,22 +21250,22 @@
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>44.58</v>
+        <v>28</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>695.18</v>
+        <v>132.82</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>7130.1</v>
+        <v>1362.24</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>499.11</v>
+        <v>95.36</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21348,79 +21384,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305256</v>
+        <v>305273</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1495.06</v>
+        <v>15678.49</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>1362.24</v>
+        <v>15678.49</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.057024</v>
+        <v>0.066706</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>0</v>
+        <v>17.14</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>132.82</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>1362.24</v>
+        <v>15678.49</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>95.36</v>
+        <v>1097.5</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21525,7 +21561,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21539,79 +21575,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305273</v>
+        <v>305282</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>135</v>
-      </c>
       <c r="J26" s="9" t="s">
-        <v>178</v>
+        <v>69</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>15678.49</v>
+        <v>392.71</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>15678.49</v>
+        <v>368.74</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.066706</v>
+        <v>0.006789</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>17.14</v>
+        <v>3.81</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>15678.49</v>
+        <v>368.74</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>1097.5</v>
+        <v>14.75</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21677,10 +21713,10 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21716,7 +21752,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21730,25 +21766,25 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305282</v>
+        <v>305283</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>69</v>
@@ -21781,7 +21817,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
@@ -21793,7 +21829,7 @@
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>23.97</v>
@@ -21907,7 +21943,7 @@
         <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21921,25 +21957,25 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305283</v>
+        <v>305284</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>69</v>
@@ -21972,7 +22008,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
@@ -21984,7 +22020,7 @@
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="Y28" s="12" t="n">
         <v>23.97</v>
@@ -22098,7 +22134,7 @@
         <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22112,25 +22148,25 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305284</v>
+        <v>305426</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>69</v>
@@ -22139,7 +22175,7 @@
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>392.71</v>
+        <v>163.48</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -22148,22 +22184,22 @@
         <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>368.74</v>
+        <v>153.5</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.006789</v>
+        <v>0.003456</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>3.81</v>
+        <v>0.8</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
@@ -22175,16 +22211,16 @@
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>23.97</v>
+        <v>9.98</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>368.74</v>
+        <v>153.5</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>14.75</v>
+        <v>6.14</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22289,7 +22325,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22303,25 +22339,25 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>305426</v>
+        <v>305427</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>69</v>
@@ -22354,7 +22390,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
@@ -22366,7 +22402,7 @@
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>9.98</v>
@@ -22480,7 +22516,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22494,25 +22530,25 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>305427</v>
+        <v>305445</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>69</v>
@@ -22521,25 +22557,25 @@
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>163.48</v>
+        <v>327.31</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>153.5</v>
+        <v>307.33</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.003456</v>
+        <v>0.239381</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
@@ -22557,16 +22593,16 @@
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>9.98</v>
+        <v>19.98</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>153.5</v>
+        <v>307.33</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>6.14</v>
+        <v>12.3</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22671,7 +22707,7 @@
         <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22685,25 +22721,25 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>305445</v>
+        <v>305446</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>69</v>
@@ -22736,7 +22772,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
@@ -22748,7 +22784,7 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>19.98</v>
@@ -22862,7 +22898,7 @@
         <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22876,25 +22912,25 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>305446</v>
+        <v>305447</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>69</v>
@@ -22927,7 +22963,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
@@ -22939,7 +22975,7 @@
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y33" s="12" t="n">
         <v>19.98</v>
@@ -23053,7 +23089,7 @@
         <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23067,25 +23103,25 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>305447</v>
+        <v>305453</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>69</v>
@@ -23094,31 +23130,31 @@
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>327.31</v>
+        <v>837.05</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>307.33</v>
+        <v>805.99</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.239381</v>
+        <v>0.210944</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>1.6</v>
+        <v>9.12</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
@@ -23130,16 +23166,16 @@
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>19.98</v>
+        <v>31.06</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>307.33</v>
+        <v>805.99</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>12.3</v>
+        <v>32.25</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23244,7 +23280,7 @@
         <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23258,25 +23294,25 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>305453</v>
+        <v>305454</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>69</v>
@@ -23285,31 +23321,31 @@
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>837.05</v>
+        <v>2323.32</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>805.99</v>
+        <v>2294.51</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.210944</v>
+        <v>0.233764</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>9.12</v>
+        <v>12.22</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
@@ -23321,16 +23357,16 @@
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>31.06</v>
+        <v>28.81</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>805.99</v>
+        <v>2294.51</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>32.25</v>
+        <v>91.78</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23435,7 +23471,7 @@
         <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23449,25 +23485,25 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>305454</v>
+        <v>305455</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>69</v>
@@ -23476,31 +23512,31 @@
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>2323.32</v>
+        <v>800.16</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>2294.51</v>
+        <v>771.35</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.233764</v>
+        <v>0.205309</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>12.22</v>
+        <v>8.8</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
@@ -23512,16 +23548,16 @@
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y36" s="12" t="n">
         <v>28.81</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>2294.51</v>
+        <v>771.35</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>91.78</v>
+        <v>30.86</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23626,7 +23662,7 @@
         <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23640,25 +23676,25 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>305455</v>
+        <v>305464</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>69</v>
@@ -23667,31 +23703,31 @@
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>800.16</v>
+        <v>314.65</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>771.35</v>
+        <v>295.45</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.205309</v>
+        <v>0.016472</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>8.8</v>
+        <v>1.6</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
@@ -23703,16 +23739,16 @@
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>28.81</v>
+        <v>19.2</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>771.35</v>
+        <v>295.45</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>30.86</v>
+        <v>11.81</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23817,7 +23853,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23831,25 +23867,25 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>305464</v>
+        <v>305465</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>69</v>
@@ -23882,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
@@ -23894,7 +23930,7 @@
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y38" s="12" t="n">
         <v>19.2</v>
@@ -24008,7 +24044,7 @@
         <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24022,25 +24058,25 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>305465</v>
+        <v>305466</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>69</v>
@@ -24073,7 +24109,7 @@
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
@@ -24085,7 +24121,7 @@
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y39" s="12" t="n">
         <v>19.2</v>
@@ -24199,7 +24235,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24213,25 +24249,25 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>305466</v>
+        <v>305474</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>69</v>
@@ -24240,31 +24276,31 @@
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>314.65</v>
+        <v>167.35</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>295.45</v>
+        <v>157.14</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.014804</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>1.6</v>
+        <v>2.51</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
@@ -24276,16 +24312,16 @@
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>19.2</v>
+        <v>10.21</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>295.45</v>
+        <v>157.14</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>11.81</v>
+        <v>6.29</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24390,7 +24426,7 @@
         <v>69</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24404,25 +24440,25 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>305474</v>
+        <v>305475</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>69</v>
@@ -24431,31 +24467,31 @@
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>167.35</v>
+        <v>83.19</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>157.14</v>
+        <v>78.12</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.014804</v>
+        <v>0.013886</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>2.51</v>
+        <v>0.93</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
@@ -24467,16 +24503,16 @@
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>10.21</v>
+        <v>5.07</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>157.14</v>
+        <v>78.12</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>6.29</v>
+        <v>3.13</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24581,7 +24617,7 @@
         <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24595,25 +24631,25 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>305475</v>
+        <v>305476</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>69</v>
@@ -24646,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
@@ -24658,7 +24694,7 @@
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Y42" s="12" t="n">
         <v>5.07</v>
@@ -24772,7 +24808,7 @@
         <v>69</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24786,79 +24822,79 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>305476</v>
+        <v>305543</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>69</v>
+        <v>223</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>83.19</v>
+        <v>839.95</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>78.12</v>
+        <v>839.95</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.013886</v>
+        <v>0.030474</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>0.93</v>
+        <v>5.42</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>78.12</v>
+        <v>839.95</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>3.13</v>
+        <v>58.79</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24927,7 +24963,7 @@
         <v>76</v>
       </c>
       <c r="AX43" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY43" s="14" t="s">
         <v>75</v>
@@ -24977,10 +25013,10 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>305543</v>
+        <v>305544</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
@@ -24989,46 +25025,46 @@
         <v>226</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>839.95</v>
+        <v>297.63</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>839.95</v>
+        <v>297.63</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.030474</v>
+        <v>0.001848</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>5.42</v>
+        <v>1.52</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
@@ -25040,16 +25076,16 @@
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Y44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>839.95</v>
+        <v>297.63</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>58.79</v>
+        <v>20.83</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25154,7 +25190,7 @@
         <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25168,34 +25204,34 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>305544</v>
+        <v>305551</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>297.63</v>
+        <v>2815.95</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
@@ -25204,43 +25240,43 @@
         <v>1</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>297.63</v>
+        <v>2815.95</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.001848</v>
+        <v>0.002473</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Y45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>297.63</v>
+        <v>2815.95</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>20.83</v>
+        <v>197.12</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25306,7 +25342,7 @@
         <v>74</v>
       </c>
       <c r="AW45" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX45" s="10" t="s">
         <v>97</v>
@@ -25345,7 +25381,7 @@
         <v>69</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25359,25 +25395,25 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>305551</v>
+        <v>305559</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H46" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="G46" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>182</v>
-      </c>
       <c r="I46" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>235</v>
@@ -25386,25 +25422,25 @@
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>2815.95</v>
+        <v>454.32</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>2815.95</v>
+        <v>454.32</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.002473</v>
+        <v>0.008017</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
@@ -25416,22 +25452,22 @@
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Y46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>2815.95</v>
+        <v>454.32</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>197.12</v>
+        <v>31.8</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25497,7 +25533,7 @@
         <v>74</v>
       </c>
       <c r="AW46" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX46" s="10" t="s">
         <v>97</v>
@@ -25550,10 +25586,10 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>305559</v>
+        <v>305613</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
@@ -25562,67 +25598,67 @@
         <v>238</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="H47" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="J47" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>454.32</v>
+        <v>902.64</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>454.32</v>
+        <v>902.64</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.008017</v>
+        <v>0.01086</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>2.02</v>
+        <v>9.93</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Y47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>454.32</v>
+        <v>902.64</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>31.8</v>
+        <v>63.18</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25688,7 +25724,7 @@
         <v>74</v>
       </c>
       <c r="AW47" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX47" s="10" t="s">
         <v>97</v>
@@ -25727,7 +25763,7 @@
         <v>69</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25741,79 +25777,79 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>305598</v>
+        <v>305615</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>243</v>
+        <v>99</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>245</v>
+        <v>91</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>837.01</v>
+        <v>3419.5</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>806.92</v>
+        <v>3400.4</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0</v>
+        <v>0.068208</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>22</v>
+        <v>15.85</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>30.09</v>
+        <v>19.1</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>806.92</v>
+        <v>3400.4</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>56.48</v>
+        <v>199.84</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25918,7 +25954,7 @@
         <v>69</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="BK48" s="9" t="s">
         <v>75</v>
@@ -25932,34 +25968,34 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>305613</v>
+        <v>305625</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>64</v>
+        <v>246</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="J49" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>902.64</v>
+        <v>830.75</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
@@ -25968,43 +26004,43 @@
         <v>1</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>902.64</v>
+        <v>804.6</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.01086</v>
+        <v>0.16337</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>9.93</v>
+        <v>100</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>0</v>
+        <v>26.15</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>902.64</v>
+        <v>804.6</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>63.18</v>
+        <v>56.32</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26070,7 +26106,7 @@
         <v>74</v>
       </c>
       <c r="AW49" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX49" s="10" t="s">
         <v>97</v>
@@ -26109,7 +26145,7 @@
         <v>69</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26123,10 +26159,10 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>305615</v>
+        <v>305678</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
@@ -26138,64 +26174,64 @@
         <v>91</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>190</v>
+        <v>253</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>3419.5</v>
+        <v>1057.92</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>3400.4</v>
+        <v>992.36</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.068208</v>
+        <v>0.00078</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>15.85</v>
+        <v>4.81</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="U50" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>19.1</v>
+        <v>65.56</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>3400.4</v>
+        <v>992.36</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>199.84</v>
+        <v>39.69</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26261,7 +26297,7 @@
         <v>74</v>
       </c>
       <c r="AW50" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX50" s="10" t="s">
         <v>97</v>
@@ -26300,7 +26336,7 @@
         <v>69</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26314,10 +26350,10 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>305625</v>
+        <v>305695</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>256</v>
+        <v>115</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
@@ -26326,13 +26362,13 @@
         <v>257</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="J51" s="9" t="s">
         <v>258</v>
@@ -26341,25 +26377,25 @@
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>830.75</v>
+        <v>6783</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>804.6</v>
+        <v>6783</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.16337</v>
+        <v>0.037508</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>100</v>
+        <v>13.58</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
@@ -26371,22 +26407,22 @@
         <v>72</v>
       </c>
       <c r="V51" s="12" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="W51" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>26.15</v>
+        <v>0</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>804.6</v>
+        <v>6783</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>56.32</v>
+        <v>474.81</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26452,7 +26488,7 @@
         <v>74</v>
       </c>
       <c r="AW51" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX51" s="10" t="s">
         <v>97</v>
@@ -26505,79 +26541,79 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>305678</v>
+        <v>305701</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>261</v>
+        <v>115</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J52" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>264</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>1057.92</v>
+        <v>6261.84</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>992.36</v>
+        <v>6261.84</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0.00078</v>
+        <v>0.01302</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>4.81</v>
+        <v>1.46</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="Y52" s="12" t="n">
-        <v>65.56</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>992.36</v>
+        <v>6261.84</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>39.69</v>
+        <v>438.33</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26643,7 +26679,7 @@
         <v>74</v>
       </c>
       <c r="AW52" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX52" s="10" t="s">
         <v>97</v>
@@ -26682,7 +26718,7 @@
         <v>69</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="BK52" s="9" t="s">
         <v>75</v>
@@ -26696,79 +26732,79 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>305695</v>
+        <v>305715</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>120</v>
+        <v>265</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>6783</v>
+        <v>1283.63</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>6783</v>
+        <v>1217.81</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0.037508</v>
+        <v>0.105</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>13.58</v>
+        <v>8</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="U53" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V53" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="Y53" s="12" t="n">
-        <v>0</v>
+        <v>65.82</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>6783</v>
+        <v>1217.81</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>474.81</v>
+        <v>81.63</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -26834,7 +26870,7 @@
         <v>74</v>
       </c>
       <c r="AW53" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX53" s="10" t="s">
         <v>97</v>
@@ -26873,7 +26909,7 @@
         <v>69</v>
       </c>
       <c r="BJ53" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BK53" s="9" t="s">
         <v>75</v>
@@ -26887,34 +26923,34 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>305701</v>
+        <v>305726</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>6261.84</v>
+        <v>2332.2</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
@@ -26923,43 +26959,43 @@
         <v>1</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6261.84</v>
+        <v>2332.2</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0.01302</v>
+        <v>0.026208</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>1.46</v>
+        <v>6.96</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V54" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W54" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="Y54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>6261.84</v>
+        <v>2332.2</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>438.33</v>
+        <v>163.25</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27064,7 +27100,7 @@
         <v>69</v>
       </c>
       <c r="BJ54" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="BK54" s="9" t="s">
         <v>75</v>
@@ -27078,79 +27114,79 @@
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>305715</v>
+        <v>305746</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>1283.63</v>
+        <v>1511.1</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>1217.81</v>
+        <v>1511.1</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="R55" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U55" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V55" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W55" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X55" s="9" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="Y55" s="12" t="n">
-        <v>65.82</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>1217.81</v>
+        <v>1511.1</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>81.63</v>
+        <v>32.19</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27219,7 +27255,7 @@
         <v>76</v>
       </c>
       <c r="AX55" s="10" t="s">
-        <v>97</v>
+        <v>277</v>
       </c>
       <c r="AY55" s="14" t="s">
         <v>75</v>
@@ -27269,10 +27305,10 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>305726</v>
+        <v>305748</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
@@ -27281,22 +27317,22 @@
         <v>279</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2332.2</v>
+        <v>1204.74</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
@@ -27305,16 +27341,16 @@
         <v>1</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>2332.2</v>
+        <v>1204.74</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>0.026208</v>
+        <v>0</v>
       </c>
       <c r="R56" s="12" t="n">
-        <v>6.96</v>
+        <v>0</v>
       </c>
       <c r="S56" s="12" t="n">
         <v>0</v>
@@ -27326,22 +27362,22 @@
         <v>72</v>
       </c>
       <c r="V56" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W56" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X56" s="9" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="Y56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z56" s="12" t="n">
-        <v>2332.2</v>
+        <v>1204.74</v>
       </c>
       <c r="AA56" s="12" t="n">
-        <v>163.25</v>
+        <v>25.66</v>
       </c>
       <c r="AB56" s="12" t="n">
         <v>0</v>
@@ -27407,10 +27443,10 @@
         <v>74</v>
       </c>
       <c r="AW56" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX56" s="10" t="s">
-        <v>97</v>
+        <v>277</v>
       </c>
       <c r="AY56" s="14" t="s">
         <v>75</v>
@@ -27460,7 +27496,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
-        <v>305746</v>
+        <v>305752</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>282</v>
@@ -27472,67 +27508,67 @@
         <v>283</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>174</v>
+        <v>284</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>263</v>
+        <v>118</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>285</v>
+        <v>131</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>1511.1</v>
+        <v>15650.36</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>1511.1</v>
+        <v>15353.13</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="13" t="n">
-        <v>0</v>
+        <v>0.492454</v>
       </c>
       <c r="R57" s="12" t="n">
-        <v>0</v>
+        <v>108.26</v>
       </c>
       <c r="S57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="U57" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V57" s="12" t="n">
-        <v>42</v>
+        <v>75.5</v>
       </c>
       <c r="W57" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X57" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="Y57" s="12" t="n">
-        <v>0</v>
+        <v>297.23</v>
       </c>
       <c r="Z57" s="12" t="n">
-        <v>1511.1</v>
+        <v>15353.13</v>
       </c>
       <c r="AA57" s="12" t="n">
-        <v>32.19</v>
+        <v>693.38</v>
       </c>
       <c r="AB57" s="12" t="n">
         <v>0</v>
@@ -27601,7 +27637,7 @@
         <v>76</v>
       </c>
       <c r="AX57" s="10" t="s">
-        <v>287</v>
+        <v>97</v>
       </c>
       <c r="AY57" s="14" t="s">
         <v>75</v>
@@ -27637,7 +27673,7 @@
         <v>69</v>
       </c>
       <c r="BJ57" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="BK57" s="9" t="s">
         <v>75</v>
@@ -27651,43 +27687,43 @@
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
-        <v>305748</v>
+        <v>305780</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>282</v>
+        <v>154</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>1204.74</v>
+        <v>2626.19</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O58" s="12" t="n">
-        <v>1204.74</v>
+        <v>2402.04</v>
       </c>
       <c r="P58" s="12" t="n">
         <v>0</v>
@@ -27696,13 +27732,13 @@
         <v>0</v>
       </c>
       <c r="R58" s="12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="14" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="U58" s="15" t="s">
         <v>72</v>
@@ -27714,16 +27750,16 @@
         <v>73</v>
       </c>
       <c r="X58" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="Y58" s="12" t="n">
-        <v>0</v>
+        <v>224.15</v>
       </c>
       <c r="Z58" s="12" t="n">
-        <v>1204.74</v>
+        <v>2402.04</v>
       </c>
       <c r="AA58" s="12" t="n">
-        <v>25.66</v>
+        <v>168.14</v>
       </c>
       <c r="AB58" s="12" t="n">
         <v>0</v>
@@ -27732,7 +27768,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="12" t="n">
-        <v>0</v>
+        <v>89.72</v>
       </c>
       <c r="AE58" s="12" t="n">
         <v>0</v>
@@ -27789,10 +27825,10 @@
         <v>74</v>
       </c>
       <c r="AW58" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX58" s="10" t="s">
-        <v>287</v>
+        <v>97</v>
       </c>
       <c r="AY58" s="14" t="s">
         <v>75</v>
@@ -27813,25 +27849,25 @@
         <v>75</v>
       </c>
       <c r="BE58" s="14" t="s">
-        <v>75</v>
+        <v>289</v>
       </c>
       <c r="BF58" s="9" t="s">
-        <v>75</v>
+        <v>290</v>
       </c>
       <c r="BG58" s="9" t="s">
-        <v>69</v>
+        <v>222</v>
       </c>
       <c r="BH58" s="14" t="s">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="BI58" s="9" t="s">
-        <v>69</v>
+        <v>253</v>
       </c>
       <c r="BJ58" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BK58" s="9" t="s">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="BL58" s="9" t="s">
         <v>75</v>
@@ -27842,79 +27878,79 @@
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
-        <v>305752</v>
+        <v>305786</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
       <c r="F59" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>294</v>
+        <v>91</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>136</v>
+        <v>296</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>15650.36</v>
+        <v>4365.87</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>15353.13</v>
+        <v>4095.24</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="13" t="n">
-        <v>0.492454</v>
+        <v>0.161246</v>
       </c>
       <c r="R59" s="12" t="n">
-        <v>108.26</v>
+        <v>17.08</v>
       </c>
       <c r="S59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T59" s="14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="U59" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V59" s="12" t="n">
-        <v>75.5</v>
+        <v>60</v>
       </c>
       <c r="W59" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X59" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="Y59" s="12" t="n">
-        <v>297.23</v>
+        <v>270.63</v>
       </c>
       <c r="Z59" s="12" t="n">
-        <v>15353.13</v>
+        <v>4095.24</v>
       </c>
       <c r="AA59" s="12" t="n">
-        <v>693.38</v>
+        <v>286.65</v>
       </c>
       <c r="AB59" s="12" t="n">
         <v>0</v>
@@ -28019,7 +28055,7 @@
         <v>69</v>
       </c>
       <c r="BJ59" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="BK59" s="9" t="s">
         <v>75</v>
@@ -28032,214 +28068,487 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4"/>
+      <c r="A60" s="8" t="n">
+        <v>305790</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L60" s="12" t="n">
+        <v>910.75</v>
+      </c>
+      <c r="M60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O60" s="12" t="n">
+        <v>910.75</v>
+      </c>
+      <c r="P60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="U60" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X60" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="12" t="n">
+        <v>910.75</v>
+      </c>
+      <c r="AA60" s="12" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="AB60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="12" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="AE60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW60" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AX60" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE60" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="BF60" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="BG60" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="BH60" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="BI60" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="BJ60" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK60" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="BL60" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM60" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="61" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="17"/>
-      <c r="P61" s="17"/>
-      <c r="Q61" s="17"/>
-      <c r="R61" s="17"/>
-      <c r="S61" s="17"/>
-      <c r="T61" s="17"/>
-      <c r="U61" s="17"/>
-      <c r="V61" s="17"/>
+    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="n">
+        <v>305871</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>916.85</v>
+      </c>
+      <c r="M61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O61" s="12" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="P61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="13" t="n">
+        <v>0.104928</v>
+      </c>
+      <c r="R61" s="12" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="S61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="U61" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V61" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="W61" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X61" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y61" s="12" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="Z61" s="12" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="AA61" s="12" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="AB61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW61" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX61" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF61" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG61" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI61" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ61" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="BK61" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL61" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM61" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I62" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="J62" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K62" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L62" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M62" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="N62" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O62" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P62" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q62" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R62" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S62" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="T62" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="U62" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V62" s="18" t="s">
-        <v>37</v>
-      </c>
+    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="19" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="19" t="n">
-        <v>4025.4</v>
-      </c>
-      <c r="F63" s="19" t="n">
-        <v>148798.3</v>
-      </c>
-      <c r="G63" s="19" t="n">
-        <v>9111.53</v>
-      </c>
-      <c r="H63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="19" t="n">
-        <v>152747.32</v>
-      </c>
-      <c r="L63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="20" t="n">
-        <v>4.202691</v>
-      </c>
-      <c r="S63" s="19" t="n">
-        <v>148721.92</v>
-      </c>
-      <c r="T63" s="19" t="n">
-        <v>152747.32</v>
-      </c>
-      <c r="U63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="19" t="n">
-        <v>0</v>
-      </c>
+    <row r="63" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="17"/>
+      <c r="O63" s="17"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="17"/>
+      <c r="V63" s="17"/>
     </row>
     <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="18" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>44</v>
+        <v>312</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K64" s="18" t="s">
-        <v>304</v>
+        <v>19</v>
       </c>
       <c r="L64" s="18" t="s">
-        <v>305</v>
+        <v>30</v>
       </c>
       <c r="M64" s="18" t="s">
-        <v>306</v>
+        <v>313</v>
+      </c>
+      <c r="N64" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O64" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P64" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R64" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S64" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="T64" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="U64" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V64" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="n">
-        <v>559.58</v>
+        <v>57</v>
       </c>
       <c r="B65" s="19" t="n">
         <v>0</v>
@@ -28248,16 +28557,16 @@
         <v>0</v>
       </c>
       <c r="D65" s="19" t="n">
-        <v>46.49</v>
+        <v>0</v>
       </c>
       <c r="E65" s="19" t="n">
-        <v>0</v>
+        <v>4417.49</v>
       </c>
       <c r="F65" s="19" t="n">
-        <v>0</v>
+        <v>155380.82</v>
       </c>
       <c r="G65" s="19" t="n">
-        <v>0</v>
+        <v>9515.75</v>
       </c>
       <c r="H65" s="19" t="n">
         <v>0</v>
@@ -28266,10 +28575,10 @@
         <v>0</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>0</v>
+        <v>179.44</v>
       </c>
       <c r="K65" s="19" t="n">
-        <v>0</v>
+        <v>159721.93</v>
       </c>
       <c r="L65" s="19" t="n">
         <v>0</v>
@@ -28277,220 +28586,191 @@
       <c r="M65" s="19" t="n">
         <v>0</v>
       </c>
+      <c r="N65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="20" t="n">
+        <v>4.166849</v>
+      </c>
+      <c r="S65" s="19" t="n">
+        <v>155304.44</v>
+      </c>
+      <c r="T65" s="19" t="n">
+        <v>159721.93</v>
+      </c>
+      <c r="U65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4"/>
+    <row r="66" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I66" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J66" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K66" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="L66" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="M66" s="18" t="s">
+        <v>318</v>
+      </c>
     </row>
-    <row r="67" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21"/>
-      <c r="K67" s="21"/>
-      <c r="L67" s="21"/>
-      <c r="M67" s="21"/>
-      <c r="N67" s="21"/>
-      <c r="O67" s="21"/>
-      <c r="P67" s="21"/>
-      <c r="Q67" s="21"/>
-      <c r="R67" s="21"/>
-      <c r="S67" s="21"/>
-      <c r="T67" s="21"/>
-      <c r="U67" s="21"/>
-      <c r="V67" s="21"/>
-      <c r="W67" s="21"/>
-      <c r="X67" s="21"/>
-      <c r="Y67" s="21"/>
-      <c r="Z67" s="21"/>
-      <c r="AA67" s="21"/>
-      <c r="AB67" s="21"/>
-      <c r="AC67" s="21"/>
-      <c r="AD67" s="21"/>
-      <c r="AE67" s="21"/>
-      <c r="AF67" s="21"/>
-      <c r="AG67" s="21"/>
-      <c r="AH67" s="21"/>
-      <c r="AI67" s="21"/>
-      <c r="AJ67" s="21"/>
-      <c r="AK67" s="21"/>
-      <c r="AL67" s="21"/>
-      <c r="AM67" s="21"/>
-      <c r="AN67" s="21"/>
-      <c r="AO67" s="21"/>
-      <c r="AP67" s="21"/>
-      <c r="AQ67" s="21"/>
-      <c r="AR67" s="21"/>
-      <c r="AS67" s="21"/>
-      <c r="AT67" s="21"/>
-      <c r="AU67" s="21"/>
-      <c r="AV67" s="21"/>
-      <c r="AW67" s="21"/>
-      <c r="AX67" s="21"/>
-      <c r="AY67" s="21"/>
-      <c r="AZ67" s="21"/>
-      <c r="BA67" s="21"/>
-      <c r="BB67" s="21"/>
-      <c r="BC67" s="21"/>
-      <c r="BD67" s="21"/>
-      <c r="BE67" s="21"/>
-      <c r="BF67" s="21"/>
-      <c r="BG67" s="21"/>
-      <c r="BH67" s="21"/>
-      <c r="BI67" s="21"/>
-      <c r="BJ67" s="21"/>
-      <c r="BK67" s="21"/>
-      <c r="BL67" s="21"/>
-      <c r="BM67" s="21"/>
+    <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="19" t="n">
+        <v>562.55</v>
+      </c>
+      <c r="B67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="E67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
-      <c r="Y68" s="4"/>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="4"/>
-      <c r="AB68" s="4"/>
-      <c r="AC68" s="4"/>
-      <c r="AD68" s="4"/>
-      <c r="AE68" s="4"/>
-      <c r="AF68" s="4"/>
-      <c r="AG68" s="4"/>
-      <c r="AH68" s="4"/>
-      <c r="AI68" s="4"/>
-      <c r="AJ68" s="4"/>
-      <c r="AK68" s="4"/>
-      <c r="AL68" s="4"/>
-      <c r="AM68" s="4"/>
-      <c r="AN68" s="4"/>
-      <c r="AO68" s="4"/>
-      <c r="AP68" s="4"/>
-      <c r="AQ68" s="4"/>
-      <c r="AR68" s="4"/>
-      <c r="AS68" s="4"/>
-      <c r="AT68" s="4"/>
-      <c r="AU68" s="4"/>
-      <c r="AV68" s="4"/>
-      <c r="AW68" s="4"/>
-      <c r="AX68" s="4"/>
-      <c r="AY68" s="4"/>
-      <c r="AZ68" s="4"/>
-      <c r="BA68" s="4"/>
-      <c r="BB68" s="4"/>
-      <c r="BC68" s="4"/>
-      <c r="BD68" s="4"/>
-      <c r="BE68" s="4"/>
-      <c r="BF68" s="4"/>
-      <c r="BG68" s="4"/>
-      <c r="BH68" s="4"/>
-      <c r="BI68" s="4"/>
-      <c r="BJ68" s="4"/>
-      <c r="BK68" s="4"/>
-      <c r="BL68" s="4"/>
-      <c r="BM68" s="4"/>
+      <c r="A68" s="4"/>
     </row>
-    <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
-      <c r="Y69" s="4"/>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
-      <c r="AB69" s="4"/>
-      <c r="AC69" s="4"/>
-      <c r="AD69" s="4"/>
-      <c r="AE69" s="4"/>
-      <c r="AF69" s="4"/>
-      <c r="AG69" s="4"/>
-      <c r="AH69" s="4"/>
-      <c r="AI69" s="4"/>
-      <c r="AJ69" s="4"/>
-      <c r="AK69" s="4"/>
-      <c r="AL69" s="4"/>
-      <c r="AM69" s="4"/>
-      <c r="AN69" s="4"/>
-      <c r="AO69" s="4"/>
-      <c r="AP69" s="4"/>
-      <c r="AQ69" s="4"/>
-      <c r="AR69" s="4"/>
-      <c r="AS69" s="4"/>
-      <c r="AT69" s="4"/>
-      <c r="AU69" s="4"/>
-      <c r="AV69" s="4"/>
-      <c r="AW69" s="4"/>
-      <c r="AX69" s="4"/>
-      <c r="AY69" s="4"/>
-      <c r="AZ69" s="4"/>
-      <c r="BA69" s="4"/>
-      <c r="BB69" s="4"/>
-      <c r="BC69" s="4"/>
-      <c r="BD69" s="4"/>
-      <c r="BE69" s="4"/>
-      <c r="BF69" s="4"/>
-      <c r="BG69" s="4"/>
-      <c r="BH69" s="4"/>
-      <c r="BI69" s="4"/>
-      <c r="BJ69" s="4"/>
-      <c r="BK69" s="4"/>
-      <c r="BL69" s="4"/>
-      <c r="BM69" s="4"/>
+    <row r="69" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="21"/>
+      <c r="R69" s="21"/>
+      <c r="S69" s="21"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="21"/>
+      <c r="V69" s="21"/>
+      <c r="W69" s="21"/>
+      <c r="X69" s="21"/>
+      <c r="Y69" s="21"/>
+      <c r="Z69" s="21"/>
+      <c r="AA69" s="21"/>
+      <c r="AB69" s="21"/>
+      <c r="AC69" s="21"/>
+      <c r="AD69" s="21"/>
+      <c r="AE69" s="21"/>
+      <c r="AF69" s="21"/>
+      <c r="AG69" s="21"/>
+      <c r="AH69" s="21"/>
+      <c r="AI69" s="21"/>
+      <c r="AJ69" s="21"/>
+      <c r="AK69" s="21"/>
+      <c r="AL69" s="21"/>
+      <c r="AM69" s="21"/>
+      <c r="AN69" s="21"/>
+      <c r="AO69" s="21"/>
+      <c r="AP69" s="21"/>
+      <c r="AQ69" s="21"/>
+      <c r="AR69" s="21"/>
+      <c r="AS69" s="21"/>
+      <c r="AT69" s="21"/>
+      <c r="AU69" s="21"/>
+      <c r="AV69" s="21"/>
+      <c r="AW69" s="21"/>
+      <c r="AX69" s="21"/>
+      <c r="AY69" s="21"/>
+      <c r="AZ69" s="21"/>
+      <c r="BA69" s="21"/>
+      <c r="BB69" s="21"/>
+      <c r="BC69" s="21"/>
+      <c r="BD69" s="21"/>
+      <c r="BE69" s="21"/>
+      <c r="BF69" s="21"/>
+      <c r="BG69" s="21"/>
+      <c r="BH69" s="21"/>
+      <c r="BI69" s="21"/>
+      <c r="BJ69" s="21"/>
+      <c r="BK69" s="21"/>
+      <c r="BL69" s="21"/>
+      <c r="BM69" s="21"/>
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>309</v>
+        <v>75</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -28559,7 +28839,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -28628,7 +28908,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>22</v>
+        <v>321</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -28697,7 +28977,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -28766,7 +29046,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>312</v>
+        <v>22</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -28835,7 +29115,7 @@
     </row>
     <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -28904,7 +29184,7 @@
     </row>
     <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -28973,7 +29253,7 @@
     </row>
     <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -29040,8 +29320,146 @@
       <c r="BL77" s="4"/>
       <c r="BM77" s="4"/>
     </row>
+    <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="4"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="4"/>
+      <c r="AB78" s="4"/>
+      <c r="AC78" s="4"/>
+      <c r="AD78" s="4"/>
+      <c r="AE78" s="4"/>
+      <c r="AF78" s="4"/>
+      <c r="AG78" s="4"/>
+      <c r="AH78" s="4"/>
+      <c r="AI78" s="4"/>
+      <c r="AJ78" s="4"/>
+      <c r="AK78" s="4"/>
+      <c r="AL78" s="4"/>
+      <c r="AM78" s="4"/>
+      <c r="AN78" s="4"/>
+      <c r="AO78" s="4"/>
+      <c r="AP78" s="4"/>
+      <c r="AQ78" s="4"/>
+      <c r="AR78" s="4"/>
+      <c r="AS78" s="4"/>
+      <c r="AT78" s="4"/>
+      <c r="AU78" s="4"/>
+      <c r="AV78" s="4"/>
+      <c r="AW78" s="4"/>
+      <c r="AX78" s="4"/>
+      <c r="AY78" s="4"/>
+      <c r="AZ78" s="4"/>
+      <c r="BA78" s="4"/>
+      <c r="BB78" s="4"/>
+      <c r="BC78" s="4"/>
+      <c r="BD78" s="4"/>
+      <c r="BE78" s="4"/>
+      <c r="BF78" s="4"/>
+      <c r="BG78" s="4"/>
+      <c r="BH78" s="4"/>
+      <c r="BI78" s="4"/>
+      <c r="BJ78" s="4"/>
+      <c r="BK78" s="4"/>
+      <c r="BL78" s="4"/>
+      <c r="BM78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="4"/>
+      <c r="U79" s="4"/>
+      <c r="V79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="4"/>
+      <c r="AB79" s="4"/>
+      <c r="AC79" s="4"/>
+      <c r="AD79" s="4"/>
+      <c r="AE79" s="4"/>
+      <c r="AF79" s="4"/>
+      <c r="AG79" s="4"/>
+      <c r="AH79" s="4"/>
+      <c r="AI79" s="4"/>
+      <c r="AJ79" s="4"/>
+      <c r="AK79" s="4"/>
+      <c r="AL79" s="4"/>
+      <c r="AM79" s="4"/>
+      <c r="AN79" s="4"/>
+      <c r="AO79" s="4"/>
+      <c r="AP79" s="4"/>
+      <c r="AQ79" s="4"/>
+      <c r="AR79" s="4"/>
+      <c r="AS79" s="4"/>
+      <c r="AT79" s="4"/>
+      <c r="AU79" s="4"/>
+      <c r="AV79" s="4"/>
+      <c r="AW79" s="4"/>
+      <c r="AX79" s="4"/>
+      <c r="AY79" s="4"/>
+      <c r="AZ79" s="4"/>
+      <c r="BA79" s="4"/>
+      <c r="BB79" s="4"/>
+      <c r="BC79" s="4"/>
+      <c r="BD79" s="4"/>
+      <c r="BE79" s="4"/>
+      <c r="BF79" s="4"/>
+      <c r="BG79" s="4"/>
+      <c r="BH79" s="4"/>
+      <c r="BI79" s="4"/>
+      <c r="BJ79" s="4"/>
+      <c r="BK79" s="4"/>
+      <c r="BL79" s="4"/>
+      <c r="BM79" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="71">
+  <mergeCells count="73">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -29101,9 +29519,9 @@
     <mergeCell ref="B57:E57"/>
     <mergeCell ref="B58:E58"/>
     <mergeCell ref="B59:E59"/>
-    <mergeCell ref="A61:V61"/>
-    <mergeCell ref="A67:BM67"/>
-    <mergeCell ref="A68:BM68"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A63:V63"/>
     <mergeCell ref="A69:BM69"/>
     <mergeCell ref="A70:BM70"/>
     <mergeCell ref="A71:BM71"/>
@@ -29113,6 +29531,8 @@
     <mergeCell ref="A75:BM75"/>
     <mergeCell ref="A76:BM76"/>
     <mergeCell ref="A77:BM77"/>
+    <mergeCell ref="A78:BM78"/>
+    <mergeCell ref="A79:BM79"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="282">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 29/04/2026 05:30:28</t>
+    <t xml:space="preserve">Emitido em: 30/04/2026 05:30:25</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -319,93 +319,6 @@
     <t xml:space="preserve">41260417781412000109550010000119631000316094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.116 - MS DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.610,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260414624251000151550010000460071000339888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.664 - STANDARD ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.598,62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260456365423000160550010000114651525296163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.426,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260412077181000133550030002237391325182136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.825,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260458329608000144550010002586861002586870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.974 - USINA DESIGN IND E COMERCIO DE ILUMINACAO LTDA-ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.495,06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260410713221000160550020000074001000087894</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
@@ -538,394 +451,364 @@
     <t xml:space="preserve">42260481604803000157550010008638011323501589</t>
   </si>
   <si>
-    <t xml:space="preserve">29.089 - OTTO BAUMGART INDUSTRIA E COMERCIO S A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.223</t>
+    <t xml:space="preserve">22.715 - LUMIERE COMERCIO INTERNACIONAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.057,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260424855633000140550010000760701142490768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">621.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.783,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006211121320114228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">621.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.261,84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006210121916909071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">736 - BEMFIXA INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.283,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461801973000114550010002102901467490335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">620.300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.332,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006203001930196827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.702 - TRAMONTINA S/A CUTELARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.347.675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.365,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260490050238000114550010013476751216452879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">754.155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">916,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260409641520000158550010007541551062741704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695201354273189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695211938958901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695221872963560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695281115188545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695291649724608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695301303896479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329,55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695371809818437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695381716406268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695391590180182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714641905481935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714651839238222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714661571703506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714711852116426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050715191999755287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">623.210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.102,32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006232101918141087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">623.997</t>
   </si>
   <si>
     <t xml:space="preserve">25/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">830,75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460642774001209550010002052231454537290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.715 - LUMIERE COMERCIO INTERNACIONAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.057,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260424855633000140550010000760701142490768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">621.112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.783,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006211121320114228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">621.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.261,84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006210121916909071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">736 - BEMFIXA INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.283,63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461801973000114550010002102901467490335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">620.300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.332,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006203001930196827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.626,19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260412077181000133550030002239361899532783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260411389565000200570050003977821000839703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.702 - TRAMONTINA S/A CUTELARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.347.675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.365,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260490050238000114550010013476751216452879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.288 - ITAMONTE ILUM EIRELI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">910,75</t>
+    <t xml:space="preserve">23/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.094,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006239971637984323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">626.544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.369,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006265441239051805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.962.855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.890,08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260460561719009503550210019628551927233756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">627.234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.669,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006272341190506717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">864.814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.549,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008648141564184649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">864.815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.268,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008648151583820340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.329 - S &amp; L SOUZA E LIMA FABRICACAO E COMERCIO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">914,21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260410394416000195550010000478481000251217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.680 - METALURGICA ITAMONTE LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.328,69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260496339478000110550010000255941716221345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385,70</t>
   </si>
   <si>
     <t xml:space="preserve">2.910</t>
   </si>
   <si>
-    <t xml:space="preserve">397.840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260427160810000161550010000073371764553504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260411389565000200570050003978401000840308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">754.155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">916,85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260409641520000158550010007541551062741704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366,64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695201354273189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695211938958901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695221872963560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695281115188545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695291649724608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695301303896479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329,55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695371809818437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695381716406268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695391590180182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714641905481935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714651839238222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714661571703506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714711852116426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050715191999755287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">623.210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.102,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006232101918141087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.376,48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260417781412000109550010000120301000336685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">623.997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.094,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006239971637984323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">626.544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.369,19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006265441239051805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.962.855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.890,08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460561719009503550210019628551927233756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">627.234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.669,54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006272341190506717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">864.814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.549,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008648141564184649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">864.815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.268,41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008648151583820340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.329 - S &amp; L SOUZA E LIMA FABRICACAO E COMERCIO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">914,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260410394416000195550010000478481000251217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.680 - METALURGICA ITAMONTE LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.328,69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260496339478000110550010000255941716221345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385,70</t>
-  </si>
-  <si>
     <t xml:space="preserve">35260496339478000110550010000255951049840057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.312,45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008650891043450563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600 - CENSI INDUSTRIA E COMERCIO DE REPAROS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">449.696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.691,05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260402308456000149550050004496961432351351</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17171,7 +17054,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM79"/>
+  <dimension ref="A1:BM72"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -18498,7 +18381,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305124</v>
+        <v>305453</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>99</v>
@@ -18519,43 +18402,43 @@
         <v>102</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>4610.21</v>
+        <v>837.05</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>4234.43</v>
+        <v>805.99</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.4</v>
+        <v>0.210944</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>8.4</v>
+        <v>9.12</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
@@ -18564,13 +18447,13 @@
         <v>102</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>375.78</v>
+        <v>31.06</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>4234.43</v>
+        <v>805.99</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>180.79</v>
+        <v>32.25</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18636,10 +18519,10 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18675,7 +18558,7 @@
         <v>69</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18689,79 +18572,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305240</v>
+        <v>305454</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="J11" s="9" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>1598.62</v>
+        <v>2323.32</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>1456.6</v>
+        <v>2294.51</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0</v>
+        <v>0.233764</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>0</v>
+        <v>12.22</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>142.02</v>
+        <v>28.81</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>1456.6</v>
+        <v>2294.51</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>101.96</v>
+        <v>91.78</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18827,10 +18710,10 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18866,7 +18749,7 @@
         <v>69</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18880,79 +18763,79 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305242</v>
+        <v>305455</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="H12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="J12" s="9" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>3426.16</v>
+        <v>800.16</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3145.39</v>
+        <v>771.35</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.0061</v>
+        <v>0.205309</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>3.59</v>
+        <v>8.8</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>280.77</v>
+        <v>28.81</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>3145.39</v>
+        <v>771.35</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>220.19</v>
+        <v>30.86</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -19018,10 +18901,10 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -19057,7 +18940,7 @@
         <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19071,34 +18954,34 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305253</v>
+        <v>305464</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>7825.28</v>
+        <v>314.65</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -19107,43 +18990,43 @@
         <v>2</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>7130.1</v>
+        <v>295.45</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0</v>
+        <v>0.016472</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>44.58</v>
+        <v>0</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>695.18</v>
+        <v>19.2</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>7130.1</v>
+        <v>295.45</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>499.11</v>
+        <v>11.81</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19209,10 +19092,10 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19248,7 +19131,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19262,79 +19145,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305256</v>
+        <v>305465</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1495.06</v>
+        <v>314.65</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>1362.24</v>
+        <v>295.45</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.057024</v>
+        <v>0.016472</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>132.82</v>
+        <v>19.2</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>1362.24</v>
+        <v>295.45</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>95.36</v>
+        <v>11.81</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19400,10 +19283,10 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19439,7 +19322,7 @@
         <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19453,25 +19336,25 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305453</v>
+        <v>305466</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>69</v>
@@ -19480,31 +19363,31 @@
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>837.05</v>
+        <v>314.65</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>805.99</v>
+        <v>295.45</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.210944</v>
+        <v>0.016472</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>9.12</v>
+        <v>1.6</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
@@ -19516,16 +19399,16 @@
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>31.06</v>
+        <v>19.2</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>805.99</v>
+        <v>295.45</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>32.25</v>
+        <v>11.81</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19630,7 +19513,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19644,25 +19527,25 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305454</v>
+        <v>305474</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>69</v>
@@ -19671,31 +19554,31 @@
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2323.32</v>
+        <v>167.35</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>2294.51</v>
+        <v>157.14</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.233764</v>
+        <v>0.014804</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>12.22</v>
+        <v>2.51</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19707,16 +19590,16 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>28.81</v>
+        <v>10.21</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>2294.51</v>
+        <v>157.14</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>91.78</v>
+        <v>6.29</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19821,7 +19704,7 @@
         <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19835,25 +19718,25 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305455</v>
+        <v>305475</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>69</v>
@@ -19862,31 +19745,31 @@
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>800.16</v>
+        <v>83.19</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>771.35</v>
+        <v>78.12</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.205309</v>
+        <v>0.013886</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>8.8</v>
+        <v>0.93</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19898,16 +19781,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>28.81</v>
+        <v>5.07</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>771.35</v>
+        <v>78.12</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>30.86</v>
+        <v>3.13</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -20012,7 +19895,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -20026,25 +19909,25 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305464</v>
+        <v>305476</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>69</v>
@@ -20053,31 +19936,31 @@
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>314.65</v>
+        <v>83.19</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>295.45</v>
+        <v>78.12</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.013886</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>1.6</v>
+        <v>0.93</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
@@ -20089,16 +19972,16 @@
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>19.2</v>
+        <v>5.07</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>295.45</v>
+        <v>78.12</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>11.81</v>
+        <v>3.13</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20203,7 +20086,7 @@
         <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20217,34 +20100,34 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305465</v>
+        <v>305559</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="H19" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="J19" s="9" t="s">
         <v>131</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>314.65</v>
+        <v>454.32</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20253,43 +20136,43 @@
         <v>2</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>295.45</v>
+        <v>454.32</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.008017</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>295.45</v>
+        <v>454.32</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>11.81</v>
+        <v>31.8</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20358,7 +20241,7 @@
         <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20394,7 +20277,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20408,79 +20291,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305466</v>
+        <v>305613</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>131</v>
-      </c>
       <c r="J20" s="9" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>314.65</v>
+        <v>902.64</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>295.45</v>
+        <v>902.64</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.016472</v>
+        <v>0.01086</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>1.6</v>
+        <v>9.93</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>295.45</v>
+        <v>902.64</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>11.81</v>
+        <v>63.18</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20546,10 +20429,10 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20585,7 +20468,7 @@
         <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20599,79 +20482,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305474</v>
+        <v>305615</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>131</v>
-      </c>
       <c r="J21" s="9" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>167.35</v>
+        <v>3419.5</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>157.14</v>
+        <v>3400.4</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.014804</v>
+        <v>0.068208</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>2.51</v>
+        <v>15.85</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>10.21</v>
+        <v>19.1</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>157.14</v>
+        <v>3400.4</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>6.29</v>
+        <v>199.84</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20737,10 +20620,10 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20776,7 +20659,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20790,34 +20673,34 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305475</v>
+        <v>305678</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>83.19</v>
+        <v>1057.92</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20826,43 +20709,43 @@
         <v>3</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>78.12</v>
+        <v>992.36</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.013886</v>
+        <v>0.00078</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>0.93</v>
+        <v>4.81</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>5.07</v>
+        <v>65.56</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>78.12</v>
+        <v>992.36</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>3.13</v>
+        <v>39.69</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20931,7 +20814,7 @@
         <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20967,7 +20850,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20981,52 +20864,52 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305476</v>
+        <v>305695</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>130</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>83.19</v>
+        <v>6783</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>78.12</v>
+        <v>6783</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.013886</v>
+        <v>0.037508</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0.93</v>
+        <v>13.58</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
@@ -21038,22 +20921,22 @@
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>78.12</v>
+        <v>6783</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>3.13</v>
+        <v>474.81</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21119,10 +21002,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21158,7 +21041,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21172,58 +21055,58 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305559</v>
+        <v>305701</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>454.32</v>
+        <v>6261.84</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>454.32</v>
+        <v>6261.84</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.008017</v>
+        <v>0.01302</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>2.02</v>
+        <v>1.46</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
@@ -21235,16 +21118,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>454.32</v>
+        <v>6261.84</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>31.8</v>
+        <v>438.33</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21310,7 +21193,7 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX24" s="10" t="s">
         <v>97</v>
@@ -21349,7 +21232,7 @@
         <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21363,79 +21246,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305613</v>
+        <v>305715</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>902.64</v>
+        <v>1283.63</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>902.64</v>
+        <v>1217.81</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.01086</v>
+        <v>0.105</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>9.93</v>
+        <v>8</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>0</v>
+        <v>65.82</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>902.64</v>
+        <v>1217.81</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>63.18</v>
+        <v>81.63</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21501,7 +21384,7 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
         <v>97</v>
@@ -21540,7 +21423,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21554,79 +21437,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305615</v>
+        <v>305726</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>3419.5</v>
+        <v>2332.2</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>3400.4</v>
+        <v>2332.2</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.068208</v>
+        <v>0.026208</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>15.85</v>
+        <v>6.96</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>3400.4</v>
+        <v>2332.2</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>199.84</v>
+        <v>163.25</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21731,7 +21614,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21745,79 +21628,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305625</v>
+        <v>305786</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>830.75</v>
+        <v>4365.87</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>804.6</v>
+        <v>4095.24</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.16337</v>
+        <v>0.161246</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>100</v>
+        <v>17.08</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>26.15</v>
+        <v>270.63</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>804.6</v>
+        <v>4095.24</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>56.32</v>
+        <v>286.65</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21922,7 +21805,7 @@
         <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21936,79 +21819,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305678</v>
+        <v>305871</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1057.92</v>
+        <v>916.85</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>992.36</v>
+        <v>899.9</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.00078</v>
+        <v>0.104928</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>4.81</v>
+        <v>6.69</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>65.56</v>
+        <v>16.95</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>992.36</v>
+        <v>899.9</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>39.69</v>
+        <v>43.07</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22113,7 +21996,7 @@
         <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22127,79 +22010,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305695</v>
+        <v>305914</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>6783</v>
+        <v>366.64</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>6783</v>
+        <v>344.26</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.037508</v>
+        <v>0.007989</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>13.58</v>
+        <v>1.76</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>6783</v>
+        <v>344.26</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>474.81</v>
+        <v>13.77</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22265,10 +22148,10 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22304,7 +22187,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22318,34 +22201,34 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>305701</v>
+        <v>305915</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6261.84</v>
+        <v>366.64</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22354,43 +22237,43 @@
         <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>6261.84</v>
+        <v>344.26</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.01302</v>
+        <v>0.007989</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>6261.84</v>
+        <v>344.26</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>438.33</v>
+        <v>13.77</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22456,10 +22339,10 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX30" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY30" s="14" t="s">
         <v>75</v>
@@ -22495,7 +22378,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22509,79 +22392,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>305715</v>
+        <v>305916</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>191</v>
+        <v>99</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1283.63</v>
+        <v>366.64</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>1217.81</v>
+        <v>344.26</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.105</v>
+        <v>0.007989</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>8</v>
+        <v>1.76</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>65.82</v>
+        <v>22.38</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>1217.81</v>
+        <v>344.26</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>81.63</v>
+        <v>13.77</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22650,7 +22533,7 @@
         <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22686,7 +22569,7 @@
         <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22700,34 +22583,34 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>305726</v>
+        <v>305936</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>2332.2</v>
+        <v>42.44</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22736,43 +22619,43 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>2332.2</v>
+        <v>39.85</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.026208</v>
+        <v>0.002284</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>6.96</v>
+        <v>0.8</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>2332.2</v>
+        <v>39.85</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>163.25</v>
+        <v>1.59</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22838,10 +22721,10 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX32" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY32" s="14" t="s">
         <v>75</v>
@@ -22877,7 +22760,7 @@
         <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22891,79 +22774,79 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>305780</v>
+        <v>305937</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>160</v>
+        <v>69</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>2626.19</v>
+        <v>42.44</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>2402.04</v>
+        <v>39.85</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0</v>
+        <v>0.002284</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>224.15</v>
+        <v>2.59</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>2402.04</v>
+        <v>39.85</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>168.14</v>
+        <v>1.59</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22972,7 +22855,7 @@
         <v>0</v>
       </c>
       <c r="AD33" s="12" t="n">
-        <v>89.72</v>
+        <v>0</v>
       </c>
       <c r="AE33" s="12" t="n">
         <v>0</v>
@@ -23029,10 +22912,10 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -23053,25 +22936,25 @@
         <v>75</v>
       </c>
       <c r="BE33" s="14" t="s">
-        <v>201</v>
+        <v>75</v>
       </c>
       <c r="BF33" s="9" t="s">
-        <v>202</v>
+        <v>75</v>
       </c>
       <c r="BG33" s="9" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="BH33" s="14" t="s">
-        <v>203</v>
+        <v>75</v>
       </c>
       <c r="BI33" s="9" t="s">
-        <v>179</v>
+        <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="BK33" s="9" t="s">
-        <v>205</v>
+        <v>75</v>
       </c>
       <c r="BL33" s="9" t="s">
         <v>75</v>
@@ -23082,79 +22965,79 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>305786</v>
+        <v>305938</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>206</v>
+        <v>99</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>4365.87</v>
+        <v>42.44</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>4095.24</v>
+        <v>39.85</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.161246</v>
+        <v>0.002284</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>17.08</v>
+        <v>0.8</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>270.63</v>
+        <v>2.59</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>4095.24</v>
+        <v>39.85</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>286.65</v>
+        <v>1.59</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23223,7 +23106,7 @@
         <v>76</v>
       </c>
       <c r="AX34" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY34" s="14" t="s">
         <v>75</v>
@@ -23259,7 +23142,7 @@
         <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23273,25 +23156,25 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>305790</v>
+        <v>305947</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>69</v>
@@ -23300,31 +23183,31 @@
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>910.75</v>
+        <v>329.55</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>910.75</v>
+        <v>309.44</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0</v>
+        <v>0.017132</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
@@ -23336,16 +23219,16 @@
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>0</v>
+        <v>20.11</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>910.75</v>
+        <v>309.44</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>27.14</v>
+        <v>12.38</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23354,7 +23237,7 @@
         <v>0</v>
       </c>
       <c r="AD35" s="12" t="n">
-        <v>89.72</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="12" t="n">
         <v>0</v>
@@ -23411,10 +23294,10 @@
         <v>74</v>
       </c>
       <c r="AW35" s="14" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23435,25 +23318,25 @@
         <v>75</v>
       </c>
       <c r="BE35" s="14" t="s">
-        <v>215</v>
+        <v>75</v>
       </c>
       <c r="BF35" s="9" t="s">
-        <v>202</v>
+        <v>75</v>
       </c>
       <c r="BG35" s="9" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="BH35" s="14" t="s">
-        <v>203</v>
+        <v>75</v>
       </c>
       <c r="BI35" s="9" t="s">
-        <v>179</v>
+        <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="BK35" s="9" t="s">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="BL35" s="9" t="s">
         <v>75</v>
@@ -23464,79 +23347,79 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>305871</v>
+        <v>305948</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>916.85</v>
+        <v>329.55</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>899.9</v>
+        <v>309.44</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.104928</v>
+        <v>0.017132</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>6.69</v>
+        <v>0.8</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>16.95</v>
+        <v>20.11</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>899.9</v>
+        <v>309.44</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>43.07</v>
+        <v>12.38</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23605,7 +23488,7 @@
         <v>76</v>
       </c>
       <c r="AX36" s="10" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AY36" s="14" t="s">
         <v>75</v>
@@ -23641,7 +23524,7 @@
         <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23655,25 +23538,25 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>305914</v>
+        <v>305949</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>69</v>
@@ -23682,7 +23565,7 @@
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>366.64</v>
+        <v>329.55</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -23691,22 +23574,22 @@
         <v>1</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>344.26</v>
+        <v>309.44</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.017132</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
@@ -23718,16 +23601,16 @@
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>22.38</v>
+        <v>20.11</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>344.26</v>
+        <v>309.44</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>13.77</v>
+        <v>12.38</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23832,7 +23715,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23846,25 +23729,25 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>305915</v>
+        <v>305954</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>69</v>
@@ -23873,7 +23756,7 @@
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>366.64</v>
+        <v>126.7</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -23882,22 +23765,22 @@
         <v>1</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>344.26</v>
+        <v>118.97</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.001512</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
@@ -23909,16 +23792,16 @@
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>22.38</v>
+        <v>7.73</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>344.26</v>
+        <v>118.97</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>13.77</v>
+        <v>4.76</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -24023,7 +23906,7 @@
         <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24037,25 +23920,25 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>305916</v>
+        <v>305955</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>69</v>
@@ -24064,7 +23947,7 @@
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>366.64</v>
+        <v>126.7</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -24073,22 +23956,22 @@
         <v>1</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>344.26</v>
+        <v>118.97</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.001512</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
@@ -24100,16 +23983,16 @@
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>22.38</v>
+        <v>7.73</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>344.26</v>
+        <v>118.97</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>13.77</v>
+        <v>4.76</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24214,7 +24097,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24228,25 +24111,25 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>305936</v>
+        <v>305956</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>69</v>
@@ -24255,7 +24138,7 @@
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>42.44</v>
+        <v>126.7</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
@@ -24264,22 +24147,22 @@
         <v>1</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>39.85</v>
+        <v>118.97</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.001512</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
@@ -24291,16 +24174,16 @@
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>2.59</v>
+        <v>7.73</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>39.85</v>
+        <v>118.97</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>1.59</v>
+        <v>4.76</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24405,7 +24288,7 @@
         <v>69</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24419,25 +24302,25 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>305937</v>
+        <v>305964</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>69</v>
@@ -24446,7 +24329,7 @@
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>42.44</v>
+        <v>84.16</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
@@ -24455,22 +24338,22 @@
         <v>1</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>39.85</v>
+        <v>79.02</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.000918</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
@@ -24482,16 +24365,16 @@
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>2.59</v>
+        <v>5.14</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>39.85</v>
+        <v>79.02</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>1.59</v>
+        <v>3.16</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24596,7 +24479,7 @@
         <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24610,25 +24493,25 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>305938</v>
+        <v>305972</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>69</v>
@@ -24637,7 +24520,7 @@
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>42.44</v>
+        <v>84.16</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
@@ -24646,22 +24529,22 @@
         <v>1</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>39.85</v>
+        <v>79.02</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.000918</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
@@ -24673,16 +24556,16 @@
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>2.59</v>
+        <v>5.14</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>39.85</v>
+        <v>79.02</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>1.59</v>
+        <v>3.16</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24787,7 +24670,7 @@
         <v>69</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24801,34 +24684,34 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>305947</v>
+        <v>305997</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>329.55</v>
+        <v>1102.32</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
@@ -24837,43 +24720,43 @@
         <v>1</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>309.44</v>
+        <v>1102.32</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.00217</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>20.11</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>309.44</v>
+        <v>1102.32</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>12.38</v>
+        <v>77.16</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24939,10 +24822,10 @@
         <v>74</v>
       </c>
       <c r="AW43" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX43" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY43" s="14" t="s">
         <v>75</v>
@@ -24978,7 +24861,7 @@
         <v>69</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -24992,34 +24875,34 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>305948</v>
+        <v>306035</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>69</v>
+        <v>215</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>329.55</v>
+        <v>3094.56</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -25028,43 +24911,43 @@
         <v>1</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>309.44</v>
+        <v>3094.56</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.008928</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>0.8</v>
+        <v>10.08</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>20.11</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>309.44</v>
+        <v>3094.56</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>12.38</v>
+        <v>216.62</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25130,10 +25013,10 @@
         <v>74</v>
       </c>
       <c r="AW44" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX44" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY44" s="14" t="s">
         <v>75</v>
@@ -25169,7 +25052,7 @@
         <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25183,79 +25066,79 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>305949</v>
+        <v>306038</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>329.55</v>
+        <v>21369.19</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>309.44</v>
+        <v>21369.19</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.055839</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>0.8</v>
+        <v>14.66</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>20.11</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>309.44</v>
+        <v>21369.19</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>12.38</v>
+        <v>1495.86</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25324,7 +25207,7 @@
         <v>76</v>
       </c>
       <c r="AX45" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY45" s="14" t="s">
         <v>75</v>
@@ -25360,7 +25243,7 @@
         <v>69</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25374,79 +25257,79 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>305954</v>
+        <v>306057</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>128</v>
+        <v>222</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>126.7</v>
+        <v>16890.08</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>118.97</v>
+        <v>16890.08</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.001512</v>
+        <v>0</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>1.58</v>
+        <v>843.54</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>118.97</v>
+        <v>16890.08</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>4.76</v>
+        <v>1182.31</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25512,10 +25395,10 @@
         <v>74</v>
       </c>
       <c r="AW46" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX46" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY46" s="14" t="s">
         <v>75</v>
@@ -25551,7 +25434,7 @@
         <v>69</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25565,79 +25448,79 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>305955</v>
+        <v>306124</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>69</v>
+        <v>229</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>126.7</v>
+        <v>6669.54</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>118.97</v>
+        <v>6669.54</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.018906</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>1.58</v>
+        <v>19.29</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>118.97</v>
+        <v>6669.54</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>4.76</v>
+        <v>466.87</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25703,10 +25586,10 @@
         <v>74</v>
       </c>
       <c r="AW47" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX47" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY47" s="14" t="s">
         <v>75</v>
@@ -25742,7 +25625,7 @@
         <v>69</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25756,79 +25639,79 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>305956</v>
+        <v>306164</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>69</v>
+        <v>233</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>126.7</v>
+        <v>1549.53</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>118.97</v>
+        <v>1549.53</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.018879</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>118.97</v>
+        <v>1549.53</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>4.76</v>
+        <v>108.47</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25894,10 +25777,10 @@
         <v>74</v>
       </c>
       <c r="AW48" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX48" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY48" s="14" t="s">
         <v>75</v>
@@ -25933,7 +25816,7 @@
         <v>69</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="BK48" s="9" t="s">
         <v>75</v>
@@ -25947,79 +25830,79 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>305964</v>
+        <v>306165</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>69</v>
+        <v>237</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>84.16</v>
+        <v>9268.41</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>79.02</v>
+        <v>9121.79</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.000918</v>
+        <v>0.520657</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>1.58</v>
+        <v>53.62</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>5.14</v>
+        <v>146.62</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>79.02</v>
+        <v>9121.79</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>3.16</v>
+        <v>552.41</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26085,10 +25968,10 @@
         <v>74</v>
       </c>
       <c r="AW49" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX49" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY49" s="14" t="s">
         <v>75</v>
@@ -26124,7 +26007,7 @@
         <v>69</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26138,79 +26021,79 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>305972</v>
+        <v>306178</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>84.16</v>
+        <v>914.21</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>79.02</v>
+        <v>833</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.000918</v>
+        <v>0.000966</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="U50" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>5.14</v>
+        <v>81.21</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>79.02</v>
+        <v>833</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>3.16</v>
+        <v>58.31</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26279,7 +26162,7 @@
         <v>76</v>
       </c>
       <c r="AX50" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AY50" s="14" t="s">
         <v>75</v>
@@ -26315,7 +26198,7 @@
         <v>69</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26329,79 +26212,79 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>305997</v>
+        <v>306181</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>155</v>
+        <v>244</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>1102.32</v>
+        <v>5328.69</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>1102.32</v>
+        <v>5328.69</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.00217</v>
+        <v>0</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V51" s="12" t="n">
-        <v>28</v>
+        <v>62.33</v>
       </c>
       <c r="W51" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="Y51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>1102.32</v>
+        <v>5328.69</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>77.16</v>
+        <v>161.46</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26506,7 +26389,7 @@
         <v>69</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="BK51" s="9" t="s">
         <v>75</v>
@@ -26520,43 +26403,43 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>306022</v>
+        <v>306182</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>244</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>258</v>
+        <v>176</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>6376.48</v>
+        <v>385.7</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>6106</v>
+        <v>385.7</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
@@ -26565,34 +26448,34 @@
         <v>0</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="Y52" s="12" t="n">
-        <v>566.48</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>5810</v>
+        <v>385.7</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>232.4</v>
+        <v>11.69</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26658,10 +26541,10 @@
         <v>74</v>
       </c>
       <c r="AW52" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AX52" s="10" t="s">
-        <v>97</v>
+        <v>251</v>
       </c>
       <c r="AY52" s="14" t="s">
         <v>75</v>
@@ -26697,7 +26580,7 @@
         <v>69</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="BK52" s="9" t="s">
         <v>75</v>
@@ -26711,79 +26594,79 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>306035</v>
+        <v>306234</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>3094.56</v>
+        <v>6312.45</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>3094.56</v>
+        <v>6283.33</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0.008928</v>
+        <v>0.298205</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>10.08</v>
+        <v>59.6</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="14" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="U53" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V53" s="12" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="W53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Y53" s="12" t="n">
-        <v>0</v>
+        <v>29.12</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>3094.56</v>
+        <v>6283.33</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>216.62</v>
+        <v>408.48</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -26888,7 +26771,7 @@
         <v>69</v>
       </c>
       <c r="BJ53" s="9" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="BK53" s="9" t="s">
         <v>75</v>
@@ -26902,79 +26785,79 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>306038</v>
+        <v>306235</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>155</v>
+        <v>257</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>157</v>
+        <v>259</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>21369.19</v>
+        <v>6691.05</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>21369.19</v>
+        <v>6571.46</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0.055839</v>
+        <v>0.237857</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>14.66</v>
+        <v>48.54</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V54" s="12" t="n">
-        <v>28</v>
+        <v>75.5</v>
       </c>
       <c r="W54" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Y54" s="12" t="n">
-        <v>0</v>
+        <v>119.59</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>21369.19</v>
+        <v>6571.46</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>1495.86</v>
+        <v>296.24</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27079,7 +26962,7 @@
         <v>69</v>
       </c>
       <c r="BJ54" s="9" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="BK54" s="9" t="s">
         <v>75</v>
@@ -27092,1664 +26975,810 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="n">
-        <v>306057</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J55" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>16890.08</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>16890.08</v>
-      </c>
-      <c r="P55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="12" t="n">
-        <v>843.54</v>
-      </c>
-      <c r="S55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="U55" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V55" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="W55" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X55" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="12" t="n">
-        <v>16890.08</v>
-      </c>
-      <c r="AA55" s="12" t="n">
-        <v>1182.31</v>
-      </c>
-      <c r="AB55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW55" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX55" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF55" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG55" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI55" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ55" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="BK55" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL55" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM55" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="n">
-        <v>306124</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J56" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>6669.54</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O56" s="12" t="n">
-        <v>6669.54</v>
-      </c>
-      <c r="P56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="13" t="n">
-        <v>0.018906</v>
-      </c>
-      <c r="R56" s="12" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="S56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="U56" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V56" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W56" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X56" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="12" t="n">
-        <v>6669.54</v>
-      </c>
-      <c r="AA56" s="12" t="n">
-        <v>466.87</v>
-      </c>
-      <c r="AB56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW56" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX56" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF56" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG56" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI56" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ56" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="BK56" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL56" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM56" s="16" t="s">
-        <v>79</v>
-      </c>
+    <row r="56" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="17"/>
+      <c r="S56" s="17"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="17"/>
+      <c r="V56" s="17"/>
     </row>
-    <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="n">
-        <v>306164</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>1549.53</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>1549.53</v>
-      </c>
-      <c r="P57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="13" t="n">
-        <v>0.018879</v>
-      </c>
-      <c r="R57" s="12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="U57" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V57" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="W57" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X57" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="12" t="n">
-        <v>1549.53</v>
-      </c>
-      <c r="AA57" s="12" t="n">
-        <v>108.47</v>
-      </c>
-      <c r="AB57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW57" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX57" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG57" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI57" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ57" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="BK57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM57" s="16" t="s">
-        <v>79</v>
+    <row r="57" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L57" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M57" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="N57" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O57" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P57" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R57" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S57" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="T57" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="U57" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V57" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="n">
-        <v>306165</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L58" s="12" t="n">
-        <v>9268.41</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="12" t="n">
+      <c r="A58" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>1894.94</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>123549.4</v>
+      </c>
+      <c r="G58" s="19" t="n">
+        <v>7589.63</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="19" t="n">
+        <v>125444.34</v>
+      </c>
+      <c r="L58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="20" t="n">
+        <v>2.646753</v>
+      </c>
+      <c r="S58" s="19" t="n">
+        <v>123549.4</v>
+      </c>
+      <c r="T58" s="19" t="n">
+        <v>125444.34</v>
+      </c>
+      <c r="U58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I59" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="O58" s="12" t="n">
-        <v>9121.79</v>
-      </c>
-      <c r="P58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="13" t="n">
-        <v>0.520657</v>
-      </c>
-      <c r="R58" s="12" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="S58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="U58" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V58" s="12" t="n">
-        <v>121</v>
-      </c>
-      <c r="W58" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X58" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y58" s="12" t="n">
-        <v>146.62</v>
-      </c>
-      <c r="Z58" s="12" t="n">
-        <v>9121.79</v>
-      </c>
-      <c r="AA58" s="12" t="n">
-        <v>552.41</v>
-      </c>
-      <c r="AB58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW58" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX58" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG58" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI58" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ58" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="BK58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM58" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="n">
-        <v>306178</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>914.21</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O59" s="12" t="n">
-        <v>833</v>
-      </c>
-      <c r="P59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="13" t="n">
-        <v>0.000966</v>
-      </c>
-      <c r="R59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="U59" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V59" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W59" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X59" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y59" s="12" t="n">
-        <v>81.21</v>
-      </c>
-      <c r="Z59" s="12" t="n">
-        <v>833</v>
-      </c>
-      <c r="AA59" s="12" t="n">
-        <v>58.31</v>
-      </c>
-      <c r="AB59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW59" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX59" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG59" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI59" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ59" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="BK59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM59" s="16" t="s">
-        <v>79</v>
+      <c r="J59" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="M59" s="18" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="n">
-        <v>306181</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="K60" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L60" s="12" t="n">
-        <v>5328.69</v>
-      </c>
-      <c r="M60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O60" s="12" t="n">
-        <v>5328.69</v>
-      </c>
-      <c r="P60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="U60" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V60" s="12" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="W60" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X60" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="12" t="n">
-        <v>5328.69</v>
-      </c>
-      <c r="AA60" s="12" t="n">
-        <v>161.46</v>
-      </c>
-      <c r="AB60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW60" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX60" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF60" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG60" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI60" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ60" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="BK60" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL60" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM60" s="16" t="s">
-        <v>79</v>
+      <c r="A60" s="19" t="n">
+        <v>1255.96</v>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="n">
-        <v>306182</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="I61" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>385.7</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>385.7</v>
-      </c>
-      <c r="P61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="U61" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X61" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="12" t="n">
-        <v>385.7</v>
-      </c>
-      <c r="AA61" s="12" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="AB61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW61" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX61" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="AY61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG61" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI61" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ61" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="BK61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM61" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4"/>
+    <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="21"/>
+      <c r="M62" s="21"/>
+      <c r="N62" s="21"/>
+      <c r="O62" s="21"/>
+      <c r="P62" s="21"/>
+      <c r="Q62" s="21"/>
+      <c r="R62" s="21"/>
+      <c r="S62" s="21"/>
+      <c r="T62" s="21"/>
+      <c r="U62" s="21"/>
+      <c r="V62" s="21"/>
+      <c r="W62" s="21"/>
+      <c r="X62" s="21"/>
+      <c r="Y62" s="21"/>
+      <c r="Z62" s="21"/>
+      <c r="AA62" s="21"/>
+      <c r="AB62" s="21"/>
+      <c r="AC62" s="21"/>
+      <c r="AD62" s="21"/>
+      <c r="AE62" s="21"/>
+      <c r="AF62" s="21"/>
+      <c r="AG62" s="21"/>
+      <c r="AH62" s="21"/>
+      <c r="AI62" s="21"/>
+      <c r="AJ62" s="21"/>
+      <c r="AK62" s="21"/>
+      <c r="AL62" s="21"/>
+      <c r="AM62" s="21"/>
+      <c r="AN62" s="21"/>
+      <c r="AO62" s="21"/>
+      <c r="AP62" s="21"/>
+      <c r="AQ62" s="21"/>
+      <c r="AR62" s="21"/>
+      <c r="AS62" s="21"/>
+      <c r="AT62" s="21"/>
+      <c r="AU62" s="21"/>
+      <c r="AV62" s="21"/>
+      <c r="AW62" s="21"/>
+      <c r="AX62" s="21"/>
+      <c r="AY62" s="21"/>
+      <c r="AZ62" s="21"/>
+      <c r="BA62" s="21"/>
+      <c r="BB62" s="21"/>
+      <c r="BC62" s="21"/>
+      <c r="BD62" s="21"/>
+      <c r="BE62" s="21"/>
+      <c r="BF62" s="21"/>
+      <c r="BG62" s="21"/>
+      <c r="BH62" s="21"/>
+      <c r="BI62" s="21"/>
+      <c r="BJ62" s="21"/>
+      <c r="BK62" s="21"/>
+      <c r="BL62" s="21"/>
+      <c r="BM62" s="21"/>
     </row>
-    <row r="63" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="17"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
-      <c r="S63" s="17"/>
-      <c r="T63" s="17"/>
-      <c r="U63" s="17"/>
-      <c r="V63" s="17"/>
+    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
+      <c r="AB63" s="4"/>
+      <c r="AC63" s="4"/>
+      <c r="AD63" s="4"/>
+      <c r="AE63" s="4"/>
+      <c r="AF63" s="4"/>
+      <c r="AG63" s="4"/>
+      <c r="AH63" s="4"/>
+      <c r="AI63" s="4"/>
+      <c r="AJ63" s="4"/>
+      <c r="AK63" s="4"/>
+      <c r="AL63" s="4"/>
+      <c r="AM63" s="4"/>
+      <c r="AN63" s="4"/>
+      <c r="AO63" s="4"/>
+      <c r="AP63" s="4"/>
+      <c r="AQ63" s="4"/>
+      <c r="AR63" s="4"/>
+      <c r="AS63" s="4"/>
+      <c r="AT63" s="4"/>
+      <c r="AU63" s="4"/>
+      <c r="AV63" s="4"/>
+      <c r="AW63" s="4"/>
+      <c r="AX63" s="4"/>
+      <c r="AY63" s="4"/>
+      <c r="AZ63" s="4"/>
+      <c r="BA63" s="4"/>
+      <c r="BB63" s="4"/>
+      <c r="BC63" s="4"/>
+      <c r="BD63" s="4"/>
+      <c r="BE63" s="4"/>
+      <c r="BF63" s="4"/>
+      <c r="BG63" s="4"/>
+      <c r="BH63" s="4"/>
+      <c r="BI63" s="4"/>
+      <c r="BJ63" s="4"/>
+      <c r="BK63" s="4"/>
+      <c r="BL63" s="4"/>
+      <c r="BM63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="B64" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F64" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I64" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="J64" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K64" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L64" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M64" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="N64" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O64" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P64" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q64" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R64" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S64" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="T64" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="U64" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V64" s="18" t="s">
-        <v>37</v>
-      </c>
+    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="4"/>
+      <c r="AD64" s="4"/>
+      <c r="AE64" s="4"/>
+      <c r="AF64" s="4"/>
+      <c r="AG64" s="4"/>
+      <c r="AH64" s="4"/>
+      <c r="AI64" s="4"/>
+      <c r="AJ64" s="4"/>
+      <c r="AK64" s="4"/>
+      <c r="AL64" s="4"/>
+      <c r="AM64" s="4"/>
+      <c r="AN64" s="4"/>
+      <c r="AO64" s="4"/>
+      <c r="AP64" s="4"/>
+      <c r="AQ64" s="4"/>
+      <c r="AR64" s="4"/>
+      <c r="AS64" s="4"/>
+      <c r="AT64" s="4"/>
+      <c r="AU64" s="4"/>
+      <c r="AV64" s="4"/>
+      <c r="AW64" s="4"/>
+      <c r="AX64" s="4"/>
+      <c r="AY64" s="4"/>
+      <c r="AZ64" s="4"/>
+      <c r="BA64" s="4"/>
+      <c r="BB64" s="4"/>
+      <c r="BC64" s="4"/>
+      <c r="BD64" s="4"/>
+      <c r="BE64" s="4"/>
+      <c r="BF64" s="4"/>
+      <c r="BG64" s="4"/>
+      <c r="BH64" s="4"/>
+      <c r="BI64" s="4"/>
+      <c r="BJ64" s="4"/>
+      <c r="BK64" s="4"/>
+      <c r="BL64" s="4"/>
+      <c r="BM64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="19" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="19" t="n">
-        <v>296</v>
-      </c>
-      <c r="C65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="19" t="n">
-        <v>4189.58</v>
-      </c>
-      <c r="F65" s="19" t="n">
-        <v>137950.76</v>
-      </c>
-      <c r="G65" s="19" t="n">
-        <v>8466.32</v>
-      </c>
-      <c r="H65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="19" t="n">
-        <v>179.44</v>
-      </c>
-      <c r="K65" s="19" t="n">
-        <v>142140.34</v>
-      </c>
-      <c r="L65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="20" t="n">
-        <v>2.737185</v>
-      </c>
-      <c r="S65" s="19" t="n">
-        <v>138246.76</v>
-      </c>
-      <c r="T65" s="19" t="n">
-        <v>142140.34</v>
-      </c>
-      <c r="U65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A65" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4"/>
+      <c r="AD65" s="4"/>
+      <c r="AE65" s="4"/>
+      <c r="AF65" s="4"/>
+      <c r="AG65" s="4"/>
+      <c r="AH65" s="4"/>
+      <c r="AI65" s="4"/>
+      <c r="AJ65" s="4"/>
+      <c r="AK65" s="4"/>
+      <c r="AL65" s="4"/>
+      <c r="AM65" s="4"/>
+      <c r="AN65" s="4"/>
+      <c r="AO65" s="4"/>
+      <c r="AP65" s="4"/>
+      <c r="AQ65" s="4"/>
+      <c r="AR65" s="4"/>
+      <c r="AS65" s="4"/>
+      <c r="AT65" s="4"/>
+      <c r="AU65" s="4"/>
+      <c r="AV65" s="4"/>
+      <c r="AW65" s="4"/>
+      <c r="AX65" s="4"/>
+      <c r="AY65" s="4"/>
+      <c r="AZ65" s="4"/>
+      <c r="BA65" s="4"/>
+      <c r="BB65" s="4"/>
+      <c r="BC65" s="4"/>
+      <c r="BD65" s="4"/>
+      <c r="BE65" s="4"/>
+      <c r="BF65" s="4"/>
+      <c r="BG65" s="4"/>
+      <c r="BH65" s="4"/>
+      <c r="BI65" s="4"/>
+      <c r="BJ65" s="4"/>
+      <c r="BK65" s="4"/>
+      <c r="BL65" s="4"/>
+      <c r="BM65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B66" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I66" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J66" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K66" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="L66" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="M66" s="18" t="s">
-        <v>311</v>
-      </c>
+    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="4"/>
+      <c r="AD66" s="4"/>
+      <c r="AE66" s="4"/>
+      <c r="AF66" s="4"/>
+      <c r="AG66" s="4"/>
+      <c r="AH66" s="4"/>
+      <c r="AI66" s="4"/>
+      <c r="AJ66" s="4"/>
+      <c r="AK66" s="4"/>
+      <c r="AL66" s="4"/>
+      <c r="AM66" s="4"/>
+      <c r="AN66" s="4"/>
+      <c r="AO66" s="4"/>
+      <c r="AP66" s="4"/>
+      <c r="AQ66" s="4"/>
+      <c r="AR66" s="4"/>
+      <c r="AS66" s="4"/>
+      <c r="AT66" s="4"/>
+      <c r="AU66" s="4"/>
+      <c r="AV66" s="4"/>
+      <c r="AW66" s="4"/>
+      <c r="AX66" s="4"/>
+      <c r="AY66" s="4"/>
+      <c r="AZ66" s="4"/>
+      <c r="BA66" s="4"/>
+      <c r="BB66" s="4"/>
+      <c r="BC66" s="4"/>
+      <c r="BD66" s="4"/>
+      <c r="BE66" s="4"/>
+      <c r="BF66" s="4"/>
+      <c r="BG66" s="4"/>
+      <c r="BH66" s="4"/>
+      <c r="BI66" s="4"/>
+      <c r="BJ66" s="4"/>
+      <c r="BK66" s="4"/>
+      <c r="BL66" s="4"/>
+      <c r="BM66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="19" t="n">
-        <v>1271.01</v>
-      </c>
-      <c r="B67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="19" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="E67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4"/>
+      <c r="AD67" s="4"/>
+      <c r="AE67" s="4"/>
+      <c r="AF67" s="4"/>
+      <c r="AG67" s="4"/>
+      <c r="AH67" s="4"/>
+      <c r="AI67" s="4"/>
+      <c r="AJ67" s="4"/>
+      <c r="AK67" s="4"/>
+      <c r="AL67" s="4"/>
+      <c r="AM67" s="4"/>
+      <c r="AN67" s="4"/>
+      <c r="AO67" s="4"/>
+      <c r="AP67" s="4"/>
+      <c r="AQ67" s="4"/>
+      <c r="AR67" s="4"/>
+      <c r="AS67" s="4"/>
+      <c r="AT67" s="4"/>
+      <c r="AU67" s="4"/>
+      <c r="AV67" s="4"/>
+      <c r="AW67" s="4"/>
+      <c r="AX67" s="4"/>
+      <c r="AY67" s="4"/>
+      <c r="AZ67" s="4"/>
+      <c r="BA67" s="4"/>
+      <c r="BB67" s="4"/>
+      <c r="BC67" s="4"/>
+      <c r="BD67" s="4"/>
+      <c r="BE67" s="4"/>
+      <c r="BF67" s="4"/>
+      <c r="BG67" s="4"/>
+      <c r="BH67" s="4"/>
+      <c r="BI67" s="4"/>
+      <c r="BJ67" s="4"/>
+      <c r="BK67" s="4"/>
+      <c r="BL67" s="4"/>
+      <c r="BM67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4"/>
+      <c r="A68" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
+      <c r="AB68" s="4"/>
+      <c r="AC68" s="4"/>
+      <c r="AD68" s="4"/>
+      <c r="AE68" s="4"/>
+      <c r="AF68" s="4"/>
+      <c r="AG68" s="4"/>
+      <c r="AH68" s="4"/>
+      <c r="AI68" s="4"/>
+      <c r="AJ68" s="4"/>
+      <c r="AK68" s="4"/>
+      <c r="AL68" s="4"/>
+      <c r="AM68" s="4"/>
+      <c r="AN68" s="4"/>
+      <c r="AO68" s="4"/>
+      <c r="AP68" s="4"/>
+      <c r="AQ68" s="4"/>
+      <c r="AR68" s="4"/>
+      <c r="AS68" s="4"/>
+      <c r="AT68" s="4"/>
+      <c r="AU68" s="4"/>
+      <c r="AV68" s="4"/>
+      <c r="AW68" s="4"/>
+      <c r="AX68" s="4"/>
+      <c r="AY68" s="4"/>
+      <c r="AZ68" s="4"/>
+      <c r="BA68" s="4"/>
+      <c r="BB68" s="4"/>
+      <c r="BC68" s="4"/>
+      <c r="BD68" s="4"/>
+      <c r="BE68" s="4"/>
+      <c r="BF68" s="4"/>
+      <c r="BG68" s="4"/>
+      <c r="BH68" s="4"/>
+      <c r="BI68" s="4"/>
+      <c r="BJ68" s="4"/>
+      <c r="BK68" s="4"/>
+      <c r="BL68" s="4"/>
+      <c r="BM68" s="4"/>
     </row>
-    <row r="69" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
-      <c r="P69" s="21"/>
-      <c r="Q69" s="21"/>
-      <c r="R69" s="21"/>
-      <c r="S69" s="21"/>
-      <c r="T69" s="21"/>
-      <c r="U69" s="21"/>
-      <c r="V69" s="21"/>
-      <c r="W69" s="21"/>
-      <c r="X69" s="21"/>
-      <c r="Y69" s="21"/>
-      <c r="Z69" s="21"/>
-      <c r="AA69" s="21"/>
-      <c r="AB69" s="21"/>
-      <c r="AC69" s="21"/>
-      <c r="AD69" s="21"/>
-      <c r="AE69" s="21"/>
-      <c r="AF69" s="21"/>
-      <c r="AG69" s="21"/>
-      <c r="AH69" s="21"/>
-      <c r="AI69" s="21"/>
-      <c r="AJ69" s="21"/>
-      <c r="AK69" s="21"/>
-      <c r="AL69" s="21"/>
-      <c r="AM69" s="21"/>
-      <c r="AN69" s="21"/>
-      <c r="AO69" s="21"/>
-      <c r="AP69" s="21"/>
-      <c r="AQ69" s="21"/>
-      <c r="AR69" s="21"/>
-      <c r="AS69" s="21"/>
-      <c r="AT69" s="21"/>
-      <c r="AU69" s="21"/>
-      <c r="AV69" s="21"/>
-      <c r="AW69" s="21"/>
-      <c r="AX69" s="21"/>
-      <c r="AY69" s="21"/>
-      <c r="AZ69" s="21"/>
-      <c r="BA69" s="21"/>
-      <c r="BB69" s="21"/>
-      <c r="BC69" s="21"/>
-      <c r="BD69" s="21"/>
-      <c r="BE69" s="21"/>
-      <c r="BF69" s="21"/>
-      <c r="BG69" s="21"/>
-      <c r="BH69" s="21"/>
-      <c r="BI69" s="21"/>
-      <c r="BJ69" s="21"/>
-      <c r="BK69" s="21"/>
-      <c r="BL69" s="21"/>
-      <c r="BM69" s="21"/>
+    <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
+      <c r="AB69" s="4"/>
+      <c r="AC69" s="4"/>
+      <c r="AD69" s="4"/>
+      <c r="AE69" s="4"/>
+      <c r="AF69" s="4"/>
+      <c r="AG69" s="4"/>
+      <c r="AH69" s="4"/>
+      <c r="AI69" s="4"/>
+      <c r="AJ69" s="4"/>
+      <c r="AK69" s="4"/>
+      <c r="AL69" s="4"/>
+      <c r="AM69" s="4"/>
+      <c r="AN69" s="4"/>
+      <c r="AO69" s="4"/>
+      <c r="AP69" s="4"/>
+      <c r="AQ69" s="4"/>
+      <c r="AR69" s="4"/>
+      <c r="AS69" s="4"/>
+      <c r="AT69" s="4"/>
+      <c r="AU69" s="4"/>
+      <c r="AV69" s="4"/>
+      <c r="AW69" s="4"/>
+      <c r="AX69" s="4"/>
+      <c r="AY69" s="4"/>
+      <c r="AZ69" s="4"/>
+      <c r="BA69" s="4"/>
+      <c r="BB69" s="4"/>
+      <c r="BC69" s="4"/>
+      <c r="BD69" s="4"/>
+      <c r="BE69" s="4"/>
+      <c r="BF69" s="4"/>
+      <c r="BG69" s="4"/>
+      <c r="BH69" s="4"/>
+      <c r="BI69" s="4"/>
+      <c r="BJ69" s="4"/>
+      <c r="BK69" s="4"/>
+      <c r="BL69" s="4"/>
+      <c r="BM69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -28818,7 +27847,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -28887,7 +27916,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -28954,491 +27983,8 @@
       <c r="BL72" s="4"/>
       <c r="BM72" s="4"/>
     </row>
-    <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4"/>
-      <c r="U73" s="4"/>
-      <c r="V73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73" s="4"/>
-      <c r="Y73" s="4"/>
-      <c r="Z73" s="4"/>
-      <c r="AA73" s="4"/>
-      <c r="AB73" s="4"/>
-      <c r="AC73" s="4"/>
-      <c r="AD73" s="4"/>
-      <c r="AE73" s="4"/>
-      <c r="AF73" s="4"/>
-      <c r="AG73" s="4"/>
-      <c r="AH73" s="4"/>
-      <c r="AI73" s="4"/>
-      <c r="AJ73" s="4"/>
-      <c r="AK73" s="4"/>
-      <c r="AL73" s="4"/>
-      <c r="AM73" s="4"/>
-      <c r="AN73" s="4"/>
-      <c r="AO73" s="4"/>
-      <c r="AP73" s="4"/>
-      <c r="AQ73" s="4"/>
-      <c r="AR73" s="4"/>
-      <c r="AS73" s="4"/>
-      <c r="AT73" s="4"/>
-      <c r="AU73" s="4"/>
-      <c r="AV73" s="4"/>
-      <c r="AW73" s="4"/>
-      <c r="AX73" s="4"/>
-      <c r="AY73" s="4"/>
-      <c r="AZ73" s="4"/>
-      <c r="BA73" s="4"/>
-      <c r="BB73" s="4"/>
-      <c r="BC73" s="4"/>
-      <c r="BD73" s="4"/>
-      <c r="BE73" s="4"/>
-      <c r="BF73" s="4"/>
-      <c r="BG73" s="4"/>
-      <c r="BH73" s="4"/>
-      <c r="BI73" s="4"/>
-      <c r="BJ73" s="4"/>
-      <c r="BK73" s="4"/>
-      <c r="BL73" s="4"/>
-      <c r="BM73" s="4"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4"/>
-      <c r="U74" s="4"/>
-      <c r="V74" s="4"/>
-      <c r="W74" s="4"/>
-      <c r="X74" s="4"/>
-      <c r="Y74" s="4"/>
-      <c r="Z74" s="4"/>
-      <c r="AA74" s="4"/>
-      <c r="AB74" s="4"/>
-      <c r="AC74" s="4"/>
-      <c r="AD74" s="4"/>
-      <c r="AE74" s="4"/>
-      <c r="AF74" s="4"/>
-      <c r="AG74" s="4"/>
-      <c r="AH74" s="4"/>
-      <c r="AI74" s="4"/>
-      <c r="AJ74" s="4"/>
-      <c r="AK74" s="4"/>
-      <c r="AL74" s="4"/>
-      <c r="AM74" s="4"/>
-      <c r="AN74" s="4"/>
-      <c r="AO74" s="4"/>
-      <c r="AP74" s="4"/>
-      <c r="AQ74" s="4"/>
-      <c r="AR74" s="4"/>
-      <c r="AS74" s="4"/>
-      <c r="AT74" s="4"/>
-      <c r="AU74" s="4"/>
-      <c r="AV74" s="4"/>
-      <c r="AW74" s="4"/>
-      <c r="AX74" s="4"/>
-      <c r="AY74" s="4"/>
-      <c r="AZ74" s="4"/>
-      <c r="BA74" s="4"/>
-      <c r="BB74" s="4"/>
-      <c r="BC74" s="4"/>
-      <c r="BD74" s="4"/>
-      <c r="BE74" s="4"/>
-      <c r="BF74" s="4"/>
-      <c r="BG74" s="4"/>
-      <c r="BH74" s="4"/>
-      <c r="BI74" s="4"/>
-      <c r="BJ74" s="4"/>
-      <c r="BK74" s="4"/>
-      <c r="BL74" s="4"/>
-      <c r="BM74" s="4"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
-      <c r="V75" s="4"/>
-      <c r="W75" s="4"/>
-      <c r="X75" s="4"/>
-      <c r="Y75" s="4"/>
-      <c r="Z75" s="4"/>
-      <c r="AA75" s="4"/>
-      <c r="AB75" s="4"/>
-      <c r="AC75" s="4"/>
-      <c r="AD75" s="4"/>
-      <c r="AE75" s="4"/>
-      <c r="AF75" s="4"/>
-      <c r="AG75" s="4"/>
-      <c r="AH75" s="4"/>
-      <c r="AI75" s="4"/>
-      <c r="AJ75" s="4"/>
-      <c r="AK75" s="4"/>
-      <c r="AL75" s="4"/>
-      <c r="AM75" s="4"/>
-      <c r="AN75" s="4"/>
-      <c r="AO75" s="4"/>
-      <c r="AP75" s="4"/>
-      <c r="AQ75" s="4"/>
-      <c r="AR75" s="4"/>
-      <c r="AS75" s="4"/>
-      <c r="AT75" s="4"/>
-      <c r="AU75" s="4"/>
-      <c r="AV75" s="4"/>
-      <c r="AW75" s="4"/>
-      <c r="AX75" s="4"/>
-      <c r="AY75" s="4"/>
-      <c r="AZ75" s="4"/>
-      <c r="BA75" s="4"/>
-      <c r="BB75" s="4"/>
-      <c r="BC75" s="4"/>
-      <c r="BD75" s="4"/>
-      <c r="BE75" s="4"/>
-      <c r="BF75" s="4"/>
-      <c r="BG75" s="4"/>
-      <c r="BH75" s="4"/>
-      <c r="BI75" s="4"/>
-      <c r="BJ75" s="4"/>
-      <c r="BK75" s="4"/>
-      <c r="BL75" s="4"/>
-      <c r="BM75" s="4"/>
-    </row>
-    <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4"/>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
-      <c r="X76" s="4"/>
-      <c r="Y76" s="4"/>
-      <c r="Z76" s="4"/>
-      <c r="AA76" s="4"/>
-      <c r="AB76" s="4"/>
-      <c r="AC76" s="4"/>
-      <c r="AD76" s="4"/>
-      <c r="AE76" s="4"/>
-      <c r="AF76" s="4"/>
-      <c r="AG76" s="4"/>
-      <c r="AH76" s="4"/>
-      <c r="AI76" s="4"/>
-      <c r="AJ76" s="4"/>
-      <c r="AK76" s="4"/>
-      <c r="AL76" s="4"/>
-      <c r="AM76" s="4"/>
-      <c r="AN76" s="4"/>
-      <c r="AO76" s="4"/>
-      <c r="AP76" s="4"/>
-      <c r="AQ76" s="4"/>
-      <c r="AR76" s="4"/>
-      <c r="AS76" s="4"/>
-      <c r="AT76" s="4"/>
-      <c r="AU76" s="4"/>
-      <c r="AV76" s="4"/>
-      <c r="AW76" s="4"/>
-      <c r="AX76" s="4"/>
-      <c r="AY76" s="4"/>
-      <c r="AZ76" s="4"/>
-      <c r="BA76" s="4"/>
-      <c r="BB76" s="4"/>
-      <c r="BC76" s="4"/>
-      <c r="BD76" s="4"/>
-      <c r="BE76" s="4"/>
-      <c r="BF76" s="4"/>
-      <c r="BG76" s="4"/>
-      <c r="BH76" s="4"/>
-      <c r="BI76" s="4"/>
-      <c r="BJ76" s="4"/>
-      <c r="BK76" s="4"/>
-      <c r="BL76" s="4"/>
-      <c r="BM76" s="4"/>
-    </row>
-    <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4"/>
-      <c r="V77" s="4"/>
-      <c r="W77" s="4"/>
-      <c r="X77" s="4"/>
-      <c r="Y77" s="4"/>
-      <c r="Z77" s="4"/>
-      <c r="AA77" s="4"/>
-      <c r="AB77" s="4"/>
-      <c r="AC77" s="4"/>
-      <c r="AD77" s="4"/>
-      <c r="AE77" s="4"/>
-      <c r="AF77" s="4"/>
-      <c r="AG77" s="4"/>
-      <c r="AH77" s="4"/>
-      <c r="AI77" s="4"/>
-      <c r="AJ77" s="4"/>
-      <c r="AK77" s="4"/>
-      <c r="AL77" s="4"/>
-      <c r="AM77" s="4"/>
-      <c r="AN77" s="4"/>
-      <c r="AO77" s="4"/>
-      <c r="AP77" s="4"/>
-      <c r="AQ77" s="4"/>
-      <c r="AR77" s="4"/>
-      <c r="AS77" s="4"/>
-      <c r="AT77" s="4"/>
-      <c r="AU77" s="4"/>
-      <c r="AV77" s="4"/>
-      <c r="AW77" s="4"/>
-      <c r="AX77" s="4"/>
-      <c r="AY77" s="4"/>
-      <c r="AZ77" s="4"/>
-      <c r="BA77" s="4"/>
-      <c r="BB77" s="4"/>
-      <c r="BC77" s="4"/>
-      <c r="BD77" s="4"/>
-      <c r="BE77" s="4"/>
-      <c r="BF77" s="4"/>
-      <c r="BG77" s="4"/>
-      <c r="BH77" s="4"/>
-      <c r="BI77" s="4"/>
-      <c r="BJ77" s="4"/>
-      <c r="BK77" s="4"/>
-      <c r="BL77" s="4"/>
-      <c r="BM77" s="4"/>
-    </row>
-    <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="4"/>
-      <c r="U78" s="4"/>
-      <c r="V78" s="4"/>
-      <c r="W78" s="4"/>
-      <c r="X78" s="4"/>
-      <c r="Y78" s="4"/>
-      <c r="Z78" s="4"/>
-      <c r="AA78" s="4"/>
-      <c r="AB78" s="4"/>
-      <c r="AC78" s="4"/>
-      <c r="AD78" s="4"/>
-      <c r="AE78" s="4"/>
-      <c r="AF78" s="4"/>
-      <c r="AG78" s="4"/>
-      <c r="AH78" s="4"/>
-      <c r="AI78" s="4"/>
-      <c r="AJ78" s="4"/>
-      <c r="AK78" s="4"/>
-      <c r="AL78" s="4"/>
-      <c r="AM78" s="4"/>
-      <c r="AN78" s="4"/>
-      <c r="AO78" s="4"/>
-      <c r="AP78" s="4"/>
-      <c r="AQ78" s="4"/>
-      <c r="AR78" s="4"/>
-      <c r="AS78" s="4"/>
-      <c r="AT78" s="4"/>
-      <c r="AU78" s="4"/>
-      <c r="AV78" s="4"/>
-      <c r="AW78" s="4"/>
-      <c r="AX78" s="4"/>
-      <c r="AY78" s="4"/>
-      <c r="AZ78" s="4"/>
-      <c r="BA78" s="4"/>
-      <c r="BB78" s="4"/>
-      <c r="BC78" s="4"/>
-      <c r="BD78" s="4"/>
-      <c r="BE78" s="4"/>
-      <c r="BF78" s="4"/>
-      <c r="BG78" s="4"/>
-      <c r="BH78" s="4"/>
-      <c r="BI78" s="4"/>
-      <c r="BJ78" s="4"/>
-      <c r="BK78" s="4"/>
-      <c r="BL78" s="4"/>
-      <c r="BM78" s="4"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="4"/>
-      <c r="U79" s="4"/>
-      <c r="V79" s="4"/>
-      <c r="W79" s="4"/>
-      <c r="X79" s="4"/>
-      <c r="Y79" s="4"/>
-      <c r="Z79" s="4"/>
-      <c r="AA79" s="4"/>
-      <c r="AB79" s="4"/>
-      <c r="AC79" s="4"/>
-      <c r="AD79" s="4"/>
-      <c r="AE79" s="4"/>
-      <c r="AF79" s="4"/>
-      <c r="AG79" s="4"/>
-      <c r="AH79" s="4"/>
-      <c r="AI79" s="4"/>
-      <c r="AJ79" s="4"/>
-      <c r="AK79" s="4"/>
-      <c r="AL79" s="4"/>
-      <c r="AM79" s="4"/>
-      <c r="AN79" s="4"/>
-      <c r="AO79" s="4"/>
-      <c r="AP79" s="4"/>
-      <c r="AQ79" s="4"/>
-      <c r="AR79" s="4"/>
-      <c r="AS79" s="4"/>
-      <c r="AT79" s="4"/>
-      <c r="AU79" s="4"/>
-      <c r="AV79" s="4"/>
-      <c r="AW79" s="4"/>
-      <c r="AX79" s="4"/>
-      <c r="AY79" s="4"/>
-      <c r="AZ79" s="4"/>
-      <c r="BA79" s="4"/>
-      <c r="BB79" s="4"/>
-      <c r="BC79" s="4"/>
-      <c r="BD79" s="4"/>
-      <c r="BE79" s="4"/>
-      <c r="BF79" s="4"/>
-      <c r="BG79" s="4"/>
-      <c r="BH79" s="4"/>
-      <c r="BI79" s="4"/>
-      <c r="BJ79" s="4"/>
-      <c r="BK79" s="4"/>
-      <c r="BL79" s="4"/>
-      <c r="BM79" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="66">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -29493,25 +28039,18 @@
     <mergeCell ref="B52:E52"/>
     <mergeCell ref="B53:E53"/>
     <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="A63:V63"/>
+    <mergeCell ref="A56:V56"/>
+    <mergeCell ref="A62:BM62"/>
+    <mergeCell ref="A63:BM63"/>
+    <mergeCell ref="A64:BM64"/>
+    <mergeCell ref="A65:BM65"/>
+    <mergeCell ref="A66:BM66"/>
+    <mergeCell ref="A67:BM67"/>
+    <mergeCell ref="A68:BM68"/>
     <mergeCell ref="A69:BM69"/>
     <mergeCell ref="A70:BM70"/>
     <mergeCell ref="A71:BM71"/>
     <mergeCell ref="A72:BM72"/>
-    <mergeCell ref="A73:BM73"/>
-    <mergeCell ref="A74:BM74"/>
-    <mergeCell ref="A75:BM75"/>
-    <mergeCell ref="A76:BM76"/>
-    <mergeCell ref="A77:BM77"/>
-    <mergeCell ref="A78:BM78"/>
-    <mergeCell ref="A79:BM79"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2952" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3072" uniqueCount="358">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 04/05/2026 07:42:43</t>
+    <t xml:space="preserve">Emitido em: 05/05/2026 07:39:20</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -373,393 +373,297 @@
     <t xml:space="preserve">35260497837181002190550010050656221375141585</t>
   </si>
   <si>
+    <t xml:space="preserve">1.351.353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">902,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013513531420684669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">736 - BEMFIXA INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.283,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461801973000114550010002102901467490335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695201354273189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695211938958901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695221872963560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695281115188545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695291649724608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695301303896479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329,55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695371809818437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695381716406268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695391590180182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714641905481935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714651839238222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714661571703506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050714711852116426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.071.519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050715191999755287</t>
+  </si>
+  <si>
     <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">618.465</t>
+    <t xml:space="preserve">623.210</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">21/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">454,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006184651995060434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.351.353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">902,64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260475801902000126550000013513531420684669</t>
+    <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.102,32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006232101918141087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">623.997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.094,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006239971637984323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">626.544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.369,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006265441239051805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">627.234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.669,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006272341190506717</t>
   </si>
   <si>
     <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">863.801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.419,50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008638011323501589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">621.112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.783,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006211121320114228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">621.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.261,84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006210121916909071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">736 - BEMFIXA INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.283,63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461801973000114550010002102901467490335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">620.300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.332,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006203001930196827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.702 - TRAMONTINA S/A CUTELARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.347.675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.365,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260490050238000114550010013476751216452879</t>
+    <t xml:space="preserve">864.814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.549,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008648141564184649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">864.815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.268,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008648151583820340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.680 - METALURGICA ITAMONTE LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.328,69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260496339478000110550010000255941716221345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260496339478000110550010000255951049840057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.312,45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260481604803000157550010008650891043450563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600 - CENSI INDUSTRIA E COMERCIO DE REPAROS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">449.696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.691,05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260402308456000149550050004496961432351351</t>
   </si>
   <si>
     <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">754.155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">916,85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260409641520000158550010007541551062741704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366,64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695201354273189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695211938958901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695221872963560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695281115188545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695291649724608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695301303896479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329,55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695371809818437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695381716406268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.069.539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050695391590180182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714641905481935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714651839238222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714661571703506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714711852116426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050715191999755287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">623.210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.102,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006232101918141087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">623.997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.094,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006239971637984323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">626.544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.369,19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006265441239051805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">627.234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.669,54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006272341190506717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">864.814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.549,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008648141564184649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">864.815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.268,41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008648151583820340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.329 - S &amp; L SOUZA E LIMA FABRICACAO E COMERCIO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">914,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260410394416000195550010000478481000251217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.680 - METALURGICA ITAMONTE LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.328,69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260496339478000110550010000255941716221345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260496339478000110550010000255951049840057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">865.089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.312,45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260481604803000157550010008650891043450563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">600 - CENSI INDUSTRIA E COMERCIO DE REPAROS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">449.696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.691,05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260402308456000149550050004496961432351351</t>
-  </si>
-  <si>
     <t xml:space="preserve">754.429</t>
   </si>
   <si>
@@ -998,6 +902,141 @@
   </si>
   <si>
     <t xml:space="preserve">41260417781412000109550010000120321000336698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.347.090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013470901102502541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.348.013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">574,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013480131368351583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.660 - DEXCO S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.959,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181005963550010000441041890695732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.352,98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181005963550010000441051713167463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.456,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181005963550010000441061882923483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.148.254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002271550010021482541648435968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">631.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.916,35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006311151642868226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.596 - LIGHT ENGINE ILUMINACAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.481,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260424546165000393550040000978321120610091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.247 - NOVA ROCHA INDUSTRIA DE TINTAS LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">552.880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.812,79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260403005123000103550010005528801581503331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.968,88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260435635346000140550020001111961551052939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.167 - ATLAS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">683.719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.473,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260489723837000172550000006837191121562860</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17243,7 +17282,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM93"/>
+  <dimension ref="A1:BM96"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -20098,148 +20137,148 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305559</v>
+        <v>305613</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="J18" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>122</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>454.32</v>
+        <v>902.64</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>454.32</v>
+        <v>902.64</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.008017</v>
+        <v>0.01086</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>2.02</v>
+        <v>9.93</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="12" t="n">
+        <v>902.64</v>
+      </c>
+      <c r="AA18" s="12" t="n">
+        <v>63.18</v>
+      </c>
+      <c r="AB18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO18" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW18" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="Y18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="12" t="n">
-        <v>454.32</v>
-      </c>
-      <c r="AA18" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="AB18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW18" s="14" t="s">
-        <v>76</v>
-      </c>
       <c r="AX18" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20275,7 +20314,7 @@
         <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20289,25 +20328,25 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>305613</v>
+        <v>305715</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>127</v>
@@ -20316,25 +20355,25 @@
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>902.64</v>
+        <v>1283.63</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>902.64</v>
+        <v>1217.81</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.01086</v>
+        <v>0.105</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>9.93</v>
+        <v>8</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
@@ -20346,22 +20385,22 @@
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>0</v>
+        <v>65.82</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>902.64</v>
+        <v>1217.81</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>63.18</v>
+        <v>81.63</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20427,10 +20466,10 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20466,7 +20505,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20480,79 +20519,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>305615</v>
+        <v>305914</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>3419.5</v>
+        <v>366.64</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>3400.4</v>
+        <v>344.26</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.068208</v>
+        <v>0.007989</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>15.85</v>
+        <v>1.76</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>19.1</v>
+        <v>22.38</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>3400.4</v>
+        <v>344.26</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>199.84</v>
+        <v>13.77</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20618,10 +20657,10 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20657,7 +20696,7 @@
         <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20671,79 +20710,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>305695</v>
+        <v>305915</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6783</v>
+        <v>366.64</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>6783</v>
+        <v>344.26</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.037508</v>
+        <v>0.007989</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>13.58</v>
+        <v>1.76</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>6783</v>
+        <v>344.26</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>474.81</v>
+        <v>13.77</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20809,10 +20848,10 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20848,7 +20887,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20862,34 +20901,34 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>305701</v>
+        <v>305916</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6261.84</v>
+        <v>366.64</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20898,43 +20937,43 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>6261.84</v>
+        <v>344.26</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.01302</v>
+        <v>0.007989</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>6261.84</v>
+        <v>344.26</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>438.33</v>
+        <v>13.77</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -21000,10 +21039,10 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -21039,7 +21078,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -21053,79 +21092,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>305715</v>
+        <v>305936</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1283.63</v>
+        <v>42.44</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>1217.81</v>
+        <v>39.85</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.105</v>
+        <v>0.002284</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>65.82</v>
+        <v>2.59</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>1217.81</v>
+        <v>39.85</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>81.63</v>
+        <v>1.59</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21194,7 +21233,7 @@
         <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21230,7 +21269,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21244,34 +21283,34 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>305726</v>
+        <v>305937</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2332.2</v>
+        <v>42.44</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -21280,43 +21319,43 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>2332.2</v>
+        <v>39.85</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.026208</v>
+        <v>0.002284</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>6.96</v>
+        <v>0.8</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>2332.2</v>
+        <v>39.85</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>163.25</v>
+        <v>1.59</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21382,10 +21421,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21421,7 +21460,7 @@
         <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21435,79 +21474,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>305786</v>
+        <v>305938</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>4365.87</v>
+        <v>42.44</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>4095.24</v>
+        <v>39.85</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.161246</v>
+        <v>0.002284</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>17.08</v>
+        <v>0.8</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>270.63</v>
+        <v>2.59</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>4095.24</v>
+        <v>39.85</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>286.65</v>
+        <v>1.59</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21576,7 +21615,7 @@
         <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21612,7 +21651,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21626,79 +21665,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>305871</v>
+        <v>305947</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>160</v>
+        <v>69</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>916.85</v>
+        <v>329.55</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>899.9</v>
+        <v>309.44</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.104928</v>
+        <v>0.017132</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>6.69</v>
+        <v>0.8</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>16.95</v>
+        <v>20.11</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>899.9</v>
+        <v>309.44</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>43.07</v>
+        <v>12.38</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21767,7 +21806,7 @@
         <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21803,7 +21842,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21817,7 +21856,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>305914</v>
+        <v>305948</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>89</v>
@@ -21826,16 +21865,16 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>69</v>
@@ -21844,7 +21883,7 @@
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>366.64</v>
+        <v>329.55</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21853,22 +21892,22 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>344.26</v>
+        <v>309.44</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.017132</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
@@ -21880,16 +21919,16 @@
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>22.38</v>
+        <v>20.11</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>344.26</v>
+        <v>309.44</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>13.77</v>
+        <v>12.38</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21994,7 +22033,7 @@
         <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -22008,7 +22047,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305915</v>
+        <v>305949</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>89</v>
@@ -22017,16 +22056,16 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>69</v>
@@ -22035,7 +22074,7 @@
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>366.64</v>
+        <v>329.55</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -22044,22 +22083,22 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>344.26</v>
+        <v>309.44</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.017132</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
@@ -22071,16 +22110,16 @@
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>22.38</v>
+        <v>20.11</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>344.26</v>
+        <v>309.44</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>13.77</v>
+        <v>12.38</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22185,7 +22224,7 @@
         <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22199,7 +22238,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305916</v>
+        <v>305954</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>89</v>
@@ -22208,16 +22247,16 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>69</v>
@@ -22226,7 +22265,7 @@
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>366.64</v>
+        <v>126.7</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -22235,22 +22274,22 @@
         <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>344.26</v>
+        <v>118.97</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.001512</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
@@ -22262,16 +22301,16 @@
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>22.38</v>
+        <v>7.73</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>344.26</v>
+        <v>118.97</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>13.77</v>
+        <v>4.76</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22376,7 +22415,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22390,7 +22429,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>305936</v>
+        <v>305955</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>89</v>
@@ -22399,16 +22438,16 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>69</v>
@@ -22417,7 +22456,7 @@
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>42.44</v>
+        <v>126.7</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22426,22 +22465,22 @@
         <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>39.85</v>
+        <v>118.97</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.001512</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
@@ -22453,16 +22492,16 @@
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>2.59</v>
+        <v>7.73</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>39.85</v>
+        <v>118.97</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>1.59</v>
+        <v>4.76</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22567,7 +22606,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22581,7 +22620,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>305937</v>
+        <v>305956</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>89</v>
@@ -22590,16 +22629,16 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>69</v>
@@ -22608,7 +22647,7 @@
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>42.44</v>
+        <v>126.7</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -22617,22 +22656,22 @@
         <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>39.85</v>
+        <v>118.97</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.001512</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
@@ -22644,16 +22683,16 @@
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>2.59</v>
+        <v>7.73</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>39.85</v>
+        <v>118.97</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>1.59</v>
+        <v>4.76</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22758,7 +22797,7 @@
         <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22772,7 +22811,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>305938</v>
+        <v>305964</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>89</v>
@@ -22781,16 +22820,16 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>69</v>
@@ -22799,7 +22838,7 @@
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>42.44</v>
+        <v>84.16</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22808,22 +22847,22 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>39.85</v>
+        <v>79.02</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.000918</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
@@ -22835,16 +22874,16 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>2.59</v>
+        <v>5.14</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>39.85</v>
+        <v>79.02</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>1.59</v>
+        <v>3.16</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22949,7 +22988,7 @@
         <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22963,7 +23002,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>305947</v>
+        <v>305972</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>89</v>
@@ -22972,16 +23011,16 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>69</v>
@@ -22990,7 +23029,7 @@
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>329.55</v>
+        <v>84.16</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -22999,22 +23038,22 @@
         <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>309.44</v>
+        <v>79.02</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.000918</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
@@ -23026,16 +23065,16 @@
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>20.11</v>
+        <v>5.14</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>309.44</v>
+        <v>79.02</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>12.38</v>
+        <v>3.16</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23140,7 +23179,7 @@
         <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23154,34 +23193,34 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>305948</v>
+        <v>305997</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>329.55</v>
+        <v>1102.32</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -23190,43 +23229,43 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>309.44</v>
+        <v>1102.32</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.00217</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>20.11</v>
+        <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>309.44</v>
+        <v>1102.32</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>12.38</v>
+        <v>77.16</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23292,10 +23331,10 @@
         <v>74</v>
       </c>
       <c r="AW34" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX34" s="10" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AY34" s="14" t="s">
         <v>75</v>
@@ -23331,7 +23370,7 @@
         <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23345,34 +23384,34 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>305949</v>
+        <v>306035</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>329.55</v>
+        <v>3094.56</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23381,43 +23420,43 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>309.44</v>
+        <v>3094.56</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.008928</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>0.8</v>
+        <v>10.08</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>20.11</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>309.44</v>
+        <v>3094.56</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>12.38</v>
+        <v>216.62</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23483,10 +23522,10 @@
         <v>74</v>
       </c>
       <c r="AW35" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23522,7 +23561,7 @@
         <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23536,79 +23575,79 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>305954</v>
+        <v>306038</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>126.7</v>
+        <v>21369.19</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>118.97</v>
+        <v>21369.19</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.055839</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>1.58</v>
+        <v>14.66</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>118.97</v>
+        <v>21369.19</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>4.76</v>
+        <v>1495.86</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23677,7 +23716,7 @@
         <v>76</v>
       </c>
       <c r="AX36" s="10" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AY36" s="14" t="s">
         <v>75</v>
@@ -23713,7 +23752,7 @@
         <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23727,79 +23766,79 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>305955</v>
+        <v>306124</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>69</v>
+        <v>182</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>126.7</v>
+        <v>6669.54</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>118.97</v>
+        <v>6669.54</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.018906</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>1.58</v>
+        <v>19.29</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>118.97</v>
+        <v>6669.54</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>4.76</v>
+        <v>466.87</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23865,10 +23904,10 @@
         <v>74</v>
       </c>
       <c r="AW37" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX37" s="10" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AY37" s="14" t="s">
         <v>75</v>
@@ -23904,7 +23943,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23918,79 +23957,79 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>305956</v>
+        <v>306164</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>126.7</v>
+        <v>1549.53</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>118.97</v>
+        <v>1549.53</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.018879</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>118.97</v>
+        <v>1549.53</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>4.76</v>
+        <v>108.47</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -24056,10 +24095,10 @@
         <v>74</v>
       </c>
       <c r="AW38" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX38" s="10" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AY38" s="14" t="s">
         <v>75</v>
@@ -24095,7 +24134,7 @@
         <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24109,79 +24148,79 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>305964</v>
+        <v>306165</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>84.16</v>
+        <v>9268.41</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>79.02</v>
+        <v>9121.79</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.000918</v>
+        <v>0.520657</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>1.58</v>
+        <v>53.62</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>5.14</v>
+        <v>146.62</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>79.02</v>
+        <v>9121.79</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>3.16</v>
+        <v>552.41</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24247,10 +24286,10 @@
         <v>74</v>
       </c>
       <c r="AW39" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX39" s="10" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AY39" s="14" t="s">
         <v>75</v>
@@ -24286,7 +24325,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24300,10 +24339,10 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>305972</v>
+        <v>306181</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -24315,64 +24354,64 @@
         <v>91</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>84.16</v>
+        <v>5328.69</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>79.02</v>
+        <v>5328.69</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.000918</v>
+        <v>0</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>0</v>
+        <v>62.33</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>79.02</v>
+        <v>5328.69</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>3.16</v>
+        <v>161.46</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24438,10 +24477,10 @@
         <v>74</v>
       </c>
       <c r="AW40" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX40" s="10" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AY40" s="14" t="s">
         <v>75</v>
@@ -24477,7 +24516,7 @@
         <v>69</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24491,52 +24530,52 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>305997</v>
+        <v>306182</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1102.32</v>
+        <v>385.7</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>1102.32</v>
+        <v>385.7</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.00217</v>
+        <v>0</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
@@ -24548,22 +24587,22 @@
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="Y41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>1102.32</v>
+        <v>385.7</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>77.16</v>
+        <v>11.69</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24629,10 +24668,10 @@
         <v>74</v>
       </c>
       <c r="AW41" s="14" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="AX41" s="10" t="s">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="AY41" s="14" t="s">
         <v>75</v>
@@ -24668,7 +24707,7 @@
         <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24682,52 +24721,52 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>306035</v>
+        <v>306234</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>3094.56</v>
+        <v>6312.45</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>3094.56</v>
+        <v>6283.33</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.008928</v>
+        <v>0.298205</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>10.08</v>
+        <v>59.6</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
@@ -24739,22 +24778,22 @@
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>0</v>
+        <v>29.12</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>3094.56</v>
+        <v>6283.33</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>216.62</v>
+        <v>408.48</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24820,10 +24859,10 @@
         <v>74</v>
       </c>
       <c r="AW42" s="14" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="AX42" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY42" s="14" t="s">
         <v>75</v>
@@ -24873,79 +24912,79 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>306038</v>
+        <v>306235</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>119</v>
+        <v>209</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>21369.19</v>
+        <v>6691.05</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>21369.19</v>
+        <v>6571.46</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.055839</v>
+        <v>0.237857</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>14.66</v>
+        <v>48.54</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>28</v>
+        <v>75.5</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>0</v>
+        <v>119.59</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>21369.19</v>
+        <v>6571.46</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>1495.86</v>
+        <v>296.24</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -25014,7 +25053,7 @@
         <v>76</v>
       </c>
       <c r="AX43" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY43" s="14" t="s">
         <v>75</v>
@@ -25050,7 +25089,7 @@
         <v>69</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -25064,79 +25103,79 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>306124</v>
+        <v>306280</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>6669.54</v>
+        <v>1450.46</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>6669.54</v>
+        <v>1405.3</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.018906</v>
+        <v>0.090678</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>19.29</v>
+        <v>11</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>0</v>
+        <v>45.16</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>6669.54</v>
+        <v>1405.3</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>466.87</v>
+        <v>75.76</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25202,10 +25241,10 @@
         <v>74</v>
       </c>
       <c r="AW44" s="14" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="AX44" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY44" s="14" t="s">
         <v>75</v>
@@ -25241,7 +25280,7 @@
         <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25255,79 +25294,79 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>306164</v>
+        <v>306282</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>1549.53</v>
+        <v>191.34</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>1549.53</v>
+        <v>179.66</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.018879</v>
+        <v>0.205156</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>1.39</v>
+        <v>3.22</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>0</v>
+        <v>11.68</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>1549.53</v>
+        <v>179.66</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>108.47</v>
+        <v>7.19</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25393,10 +25432,10 @@
         <v>74</v>
       </c>
       <c r="AW45" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX45" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY45" s="14" t="s">
         <v>75</v>
@@ -25432,7 +25471,7 @@
         <v>69</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25446,25 +25485,25 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>306165</v>
+        <v>306283</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>220</v>
@@ -25473,52 +25512,52 @@
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>9268.41</v>
+        <v>454.42</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>9121.79</v>
+        <v>454.42</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.520657</v>
+        <v>0.001</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>53.62</v>
+        <v>1.29</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>146.62</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>9121.79</v>
+        <v>454.42</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>552.41</v>
+        <v>31.81</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25584,10 +25623,10 @@
         <v>74</v>
       </c>
       <c r="AW46" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX46" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY46" s="14" t="s">
         <v>75</v>
@@ -25623,7 +25662,7 @@
         <v>69</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25637,58 +25676,58 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>306178</v>
+        <v>306284</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>223</v>
+        <v>89</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>914.21</v>
+        <v>335.13</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>833</v>
+        <v>314.68</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.000966</v>
+        <v>0.011556</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
@@ -25700,16 +25739,16 @@
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>81.21</v>
+        <v>20.45</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>833</v>
+        <v>314.68</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>58.31</v>
+        <v>22.03</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25778,7 +25817,7 @@
         <v>76</v>
       </c>
       <c r="AX47" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY47" s="14" t="s">
         <v>75</v>
@@ -25814,7 +25853,7 @@
         <v>69</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25828,52 +25867,52 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>306181</v>
+        <v>306285</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>227</v>
+        <v>89</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>5328.69</v>
+        <v>716</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5328.69</v>
+        <v>716</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0</v>
+        <v>0.01128</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
@@ -25885,22 +25924,22 @@
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>62.33</v>
+        <v>28</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="Y48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>5328.69</v>
+        <v>716</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>161.46</v>
+        <v>50.12</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25966,10 +26005,10 @@
         <v>74</v>
       </c>
       <c r="AW48" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX48" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY48" s="14" t="s">
         <v>75</v>
@@ -26019,10 +26058,10 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>306182</v>
+        <v>306286</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>227</v>
+        <v>89</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
@@ -26034,37 +26073,37 @@
         <v>91</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>385.7</v>
+        <v>1187.8</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>385.7</v>
+        <v>1187.8</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0</v>
+        <v>0.002016</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
@@ -26076,22 +26115,22 @@
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="Y49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>385.7</v>
+        <v>1187.8</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>11.69</v>
+        <v>83.15</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26157,10 +26196,10 @@
         <v>74</v>
       </c>
       <c r="AW49" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX49" s="10" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="AY49" s="14" t="s">
         <v>75</v>
@@ -26196,7 +26235,7 @@
         <v>69</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26210,79 +26249,79 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>306234</v>
+        <v>306287</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>6312.45</v>
+        <v>119.02</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>6283.33</v>
+        <v>119.02</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.298205</v>
+        <v>0.000604</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>59.6</v>
+        <v>0.51</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="U50" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>29.12</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>6283.33</v>
+        <v>119.02</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>408.48</v>
+        <v>4.76</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26348,10 +26387,10 @@
         <v>74</v>
       </c>
       <c r="AW50" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX50" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY50" s="14" t="s">
         <v>75</v>
@@ -26387,7 +26426,7 @@
         <v>69</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26401,79 +26440,79 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>306235</v>
+        <v>306288</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>6691.05</v>
+        <v>674.23</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>6571.46</v>
+        <v>633.08</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.237857</v>
+        <v>0.015978</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>48.54</v>
+        <v>3.52</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V51" s="12" t="n">
-        <v>75.5</v>
+        <v>28</v>
       </c>
       <c r="W51" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>119.59</v>
+        <v>41.15</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>6571.46</v>
+        <v>633.08</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>296.24</v>
+        <v>25.32</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26542,7 +26581,7 @@
         <v>76</v>
       </c>
       <c r="AX51" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY51" s="14" t="s">
         <v>75</v>
@@ -26578,7 +26617,7 @@
         <v>69</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="BK51" s="9" t="s">
         <v>75</v>
@@ -26592,79 +26631,79 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>306280</v>
+        <v>306289</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>1450.46</v>
+        <v>796.07</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>1405.3</v>
+        <v>747.48</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0.090678</v>
+        <v>0.014938</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y52" s="12" t="n">
-        <v>45.16</v>
+        <v>48.59</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>1405.3</v>
+        <v>747.48</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>75.76</v>
+        <v>52.32</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26730,10 +26769,10 @@
         <v>74</v>
       </c>
       <c r="AW52" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AX52" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY52" s="14" t="s">
         <v>75</v>
@@ -26769,7 +26808,7 @@
         <v>69</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="BK52" s="9" t="s">
         <v>75</v>
@@ -26783,7 +26822,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>306282</v>
+        <v>306290</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>89</v>
@@ -26792,49 +26831,49 @@
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>191.34</v>
+        <v>2089.26</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>179.66</v>
+        <v>2089.26</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0.205156</v>
+        <v>0.035616</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>3.22</v>
+        <v>8.45</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="14" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="U53" s="15" t="s">
         <v>72</v>
@@ -26846,16 +26885,16 @@
         <v>73</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y53" s="12" t="n">
-        <v>11.68</v>
+        <v>0</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>179.66</v>
+        <v>2089.26</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>7.19</v>
+        <v>102.14</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -26924,7 +26963,7 @@
         <v>76</v>
       </c>
       <c r="AX53" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY53" s="14" t="s">
         <v>75</v>
@@ -26960,7 +26999,7 @@
         <v>69</v>
       </c>
       <c r="BJ53" s="9" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="BK53" s="9" t="s">
         <v>75</v>
@@ -26974,7 +27013,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>306283</v>
+        <v>306291</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>89</v>
@@ -26983,49 +27022,49 @@
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>454.42</v>
+        <v>8241.66</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>454.42</v>
+        <v>8241.66</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0.001</v>
+        <v>0.094884</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>1.29</v>
+        <v>23.66</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
@@ -27037,16 +27076,16 @@
         <v>73</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>454.42</v>
+        <v>8241.66</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>31.81</v>
+        <v>573.68</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27115,7 +27154,7 @@
         <v>76</v>
       </c>
       <c r="AX54" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY54" s="14" t="s">
         <v>75</v>
@@ -27151,7 +27190,7 @@
         <v>69</v>
       </c>
       <c r="BJ54" s="9" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="BK54" s="9" t="s">
         <v>75</v>
@@ -27165,7 +27204,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>306284</v>
+        <v>306292</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>89</v>
@@ -27174,49 +27213,49 @@
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>335.13</v>
+        <v>3481.24</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>314.68</v>
+        <v>3481.24</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>0.011556</v>
+        <v>0.057132</v>
       </c>
       <c r="R55" s="12" t="n">
-        <v>1.23</v>
+        <v>9.71</v>
       </c>
       <c r="S55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="14" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="U55" s="15" t="s">
         <v>72</v>
@@ -27228,16 +27267,16 @@
         <v>73</v>
       </c>
       <c r="X55" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y55" s="12" t="n">
-        <v>20.45</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>314.68</v>
+        <v>3481.24</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>22.03</v>
+        <v>243.69</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27306,7 +27345,7 @@
         <v>76</v>
       </c>
       <c r="AX55" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY55" s="14" t="s">
         <v>75</v>
@@ -27342,7 +27381,7 @@
         <v>69</v>
       </c>
       <c r="BJ55" s="9" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="BK55" s="9" t="s">
         <v>75</v>
@@ -27356,7 +27395,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>306285</v>
+        <v>306294</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>89</v>
@@ -27365,49 +27404,49 @@
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>716</v>
+        <v>8601.06</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>716</v>
+        <v>8501.24</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>0.01128</v>
+        <v>0.192508</v>
       </c>
       <c r="R56" s="12" t="n">
-        <v>1.04</v>
+        <v>27.22</v>
       </c>
       <c r="S56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T56" s="14" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="U56" s="15" t="s">
         <v>72</v>
@@ -27419,16 +27458,16 @@
         <v>73</v>
       </c>
       <c r="X56" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y56" s="12" t="n">
-        <v>0</v>
+        <v>99.82</v>
       </c>
       <c r="Z56" s="12" t="n">
-        <v>716</v>
+        <v>8501.24</v>
       </c>
       <c r="AA56" s="12" t="n">
-        <v>50.12</v>
+        <v>595.09</v>
       </c>
       <c r="AB56" s="12" t="n">
         <v>0</v>
@@ -27497,7 +27536,7 @@
         <v>76</v>
       </c>
       <c r="AX56" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY56" s="14" t="s">
         <v>75</v>
@@ -27533,7 +27572,7 @@
         <v>69</v>
       </c>
       <c r="BJ56" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="BK56" s="9" t="s">
         <v>75</v>
@@ -27547,7 +27586,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
-        <v>306286</v>
+        <v>306295</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>89</v>
@@ -27556,49 +27595,49 @@
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>1187.8</v>
+        <v>114148.98</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>1187.8</v>
+        <v>113148.24</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="13" t="n">
-        <v>0.002016</v>
+        <v>4.99477</v>
       </c>
       <c r="R57" s="12" t="n">
-        <v>2.66</v>
+        <v>313.53</v>
       </c>
       <c r="S57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="14" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="U57" s="15" t="s">
         <v>72</v>
@@ -27610,16 +27649,16 @@
         <v>73</v>
       </c>
       <c r="X57" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y57" s="12" t="n">
-        <v>0</v>
+        <v>1000.74</v>
       </c>
       <c r="Z57" s="12" t="n">
-        <v>1187.8</v>
+        <v>113148.24</v>
       </c>
       <c r="AA57" s="12" t="n">
-        <v>83.15</v>
+        <v>7362.41</v>
       </c>
       <c r="AB57" s="12" t="n">
         <v>0</v>
@@ -27688,7 +27727,7 @@
         <v>76</v>
       </c>
       <c r="AX57" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY57" s="14" t="s">
         <v>75</v>
@@ -27724,7 +27763,7 @@
         <v>69</v>
       </c>
       <c r="BJ57" s="9" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="BK57" s="9" t="s">
         <v>75</v>
@@ -27738,7 +27777,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
-        <v>306287</v>
+        <v>306296</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>89</v>
@@ -27747,25 +27786,25 @@
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="G58" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>119.02</v>
+        <v>1817.7</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
@@ -27774,22 +27813,22 @@
         <v>1</v>
       </c>
       <c r="O58" s="12" t="n">
-        <v>119.02</v>
+        <v>1817.7</v>
       </c>
       <c r="P58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="13" t="n">
-        <v>0.000604</v>
+        <v>0.002</v>
       </c>
       <c r="R58" s="12" t="n">
-        <v>0.51</v>
+        <v>2.58</v>
       </c>
       <c r="S58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="14" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="U58" s="15" t="s">
         <v>72</v>
@@ -27801,16 +27840,16 @@
         <v>73</v>
       </c>
       <c r="X58" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="12" t="n">
-        <v>119.02</v>
+        <v>1817.7</v>
       </c>
       <c r="AA58" s="12" t="n">
-        <v>4.76</v>
+        <v>127.24</v>
       </c>
       <c r="AB58" s="12" t="n">
         <v>0</v>
@@ -27879,7 +27918,7 @@
         <v>76</v>
       </c>
       <c r="AX58" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY58" s="14" t="s">
         <v>75</v>
@@ -27915,7 +27954,7 @@
         <v>69</v>
       </c>
       <c r="BJ58" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="BK58" s="9" t="s">
         <v>75</v>
@@ -27929,58 +27968,58 @@
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
-        <v>306288</v>
+        <v>306297</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>89</v>
+        <v>262</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
       <c r="F59" s="9" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>674.23</v>
+        <v>32189.81</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>633.08</v>
+        <v>32170.78</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="13" t="n">
-        <v>0.015978</v>
+        <v>12.805694</v>
       </c>
       <c r="R59" s="12" t="n">
-        <v>3.52</v>
+        <v>1682.52</v>
       </c>
       <c r="S59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T59" s="14" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="U59" s="15" t="s">
         <v>72</v>
@@ -27992,16 +28031,16 @@
         <v>73</v>
       </c>
       <c r="X59" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y59" s="12" t="n">
-        <v>41.15</v>
+        <v>19.03</v>
       </c>
       <c r="Z59" s="12" t="n">
-        <v>633.08</v>
+        <v>32170.78</v>
       </c>
       <c r="AA59" s="12" t="n">
-        <v>25.32</v>
+        <v>2239.23</v>
       </c>
       <c r="AB59" s="12" t="n">
         <v>0</v>
@@ -28070,7 +28109,7 @@
         <v>76</v>
       </c>
       <c r="AX59" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY59" s="14" t="s">
         <v>75</v>
@@ -28106,7 +28145,7 @@
         <v>69</v>
       </c>
       <c r="BJ59" s="9" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="BK59" s="9" t="s">
         <v>75</v>
@@ -28120,58 +28159,58 @@
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
-        <v>306289</v>
+        <v>306298</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>89</v>
+        <v>262</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
       <c r="F60" s="9" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>796.07</v>
+        <v>1875.58</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O60" s="12" t="n">
-        <v>747.48</v>
+        <v>1875.58</v>
       </c>
       <c r="P60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="13" t="n">
-        <v>0.014938</v>
+        <v>2.01284</v>
       </c>
       <c r="R60" s="12" t="n">
-        <v>1</v>
+        <v>74.93</v>
       </c>
       <c r="S60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T60" s="14" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="U60" s="15" t="s">
         <v>72</v>
@@ -28183,16 +28222,16 @@
         <v>73</v>
       </c>
       <c r="X60" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y60" s="12" t="n">
-        <v>48.59</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="12" t="n">
-        <v>747.48</v>
+        <v>1875.58</v>
       </c>
       <c r="AA60" s="12" t="n">
-        <v>52.32</v>
+        <v>131.29</v>
       </c>
       <c r="AB60" s="12" t="n">
         <v>0</v>
@@ -28261,7 +28300,7 @@
         <v>76</v>
       </c>
       <c r="AX60" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY60" s="14" t="s">
         <v>75</v>
@@ -28297,7 +28336,7 @@
         <v>69</v>
       </c>
       <c r="BJ60" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="BK60" s="9" t="s">
         <v>75</v>
@@ -28311,58 +28350,58 @@
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
-        <v>306290</v>
+        <v>306323</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>89</v>
+        <v>262</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
       <c r="F61" s="9" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>2089.26</v>
+        <v>362.1</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O61" s="12" t="n">
-        <v>2089.26</v>
+        <v>362.1</v>
       </c>
       <c r="P61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="13" t="n">
-        <v>0.035616</v>
+        <v>0.00542</v>
       </c>
       <c r="R61" s="12" t="n">
-        <v>8.45</v>
+        <v>3.7</v>
       </c>
       <c r="S61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T61" s="14" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="U61" s="15" t="s">
         <v>72</v>
@@ -28374,16 +28413,16 @@
         <v>73</v>
       </c>
       <c r="X61" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z61" s="12" t="n">
-        <v>2089.26</v>
+        <v>362.1</v>
       </c>
       <c r="AA61" s="12" t="n">
-        <v>102.14</v>
+        <v>25.35</v>
       </c>
       <c r="AB61" s="12" t="n">
         <v>0</v>
@@ -28452,7 +28491,7 @@
         <v>76</v>
       </c>
       <c r="AX61" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY61" s="14" t="s">
         <v>75</v>
@@ -28488,7 +28527,7 @@
         <v>69</v>
       </c>
       <c r="BJ61" s="9" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="BK61" s="9" t="s">
         <v>75</v>
@@ -28502,58 +28541,58 @@
     </row>
     <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
-        <v>306291</v>
+        <v>306324</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>89</v>
+        <v>262</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
       <c r="F62" s="9" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>8241.66</v>
+        <v>661.68</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O62" s="12" t="n">
-        <v>8241.66</v>
+        <v>661.68</v>
       </c>
       <c r="P62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="13" t="n">
-        <v>0.094884</v>
+        <v>0.18432</v>
       </c>
       <c r="R62" s="12" t="n">
-        <v>23.66</v>
+        <v>60</v>
       </c>
       <c r="S62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T62" s="14" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="U62" s="15" t="s">
         <v>72</v>
@@ -28565,16 +28604,16 @@
         <v>73</v>
       </c>
       <c r="X62" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z62" s="12" t="n">
-        <v>8241.66</v>
+        <v>661.68</v>
       </c>
       <c r="AA62" s="12" t="n">
-        <v>573.68</v>
+        <v>46.32</v>
       </c>
       <c r="AB62" s="12" t="n">
         <v>0</v>
@@ -28643,7 +28682,7 @@
         <v>76</v>
       </c>
       <c r="AX62" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY62" s="14" t="s">
         <v>75</v>
@@ -28679,7 +28718,7 @@
         <v>69</v>
       </c>
       <c r="BJ62" s="9" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="BK62" s="9" t="s">
         <v>75</v>
@@ -28693,79 +28732,79 @@
     </row>
     <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
-        <v>306292</v>
+        <v>306331</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
       <c r="F63" s="9" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>3481.24</v>
+        <v>2276.64</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O63" s="12" t="n">
-        <v>3481.24</v>
+        <v>2276.64</v>
       </c>
       <c r="P63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="13" t="n">
-        <v>0.057132</v>
+        <v>0.013104</v>
       </c>
       <c r="R63" s="12" t="n">
-        <v>9.71</v>
+        <v>2.82</v>
       </c>
       <c r="S63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T63" s="14" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="U63" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V63" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W63" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X63" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z63" s="12" t="n">
-        <v>3481.24</v>
+        <v>2276.64</v>
       </c>
       <c r="AA63" s="12" t="n">
-        <v>243.69</v>
+        <v>159.36</v>
       </c>
       <c r="AB63" s="12" t="n">
         <v>0</v>
@@ -28834,7 +28873,7 @@
         <v>76</v>
       </c>
       <c r="AX63" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY63" s="14" t="s">
         <v>75</v>
@@ -28870,7 +28909,7 @@
         <v>69</v>
       </c>
       <c r="BJ63" s="9" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="BK63" s="9" t="s">
         <v>75</v>
@@ -28884,58 +28923,58 @@
     </row>
     <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
-        <v>306294</v>
+        <v>306332</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
       <c r="F64" s="9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>8601.06</v>
+        <v>801.62</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O64" s="12" t="n">
-        <v>8501.24</v>
+        <v>801.62</v>
       </c>
       <c r="P64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="13" t="n">
-        <v>0.192508</v>
+        <v>0.00125</v>
       </c>
       <c r="R64" s="12" t="n">
-        <v>27.22</v>
+        <v>1.86</v>
       </c>
       <c r="S64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T64" s="14" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="U64" s="15" t="s">
         <v>72</v>
@@ -28947,16 +28986,16 @@
         <v>73</v>
       </c>
       <c r="X64" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y64" s="12" t="n">
-        <v>99.82</v>
+        <v>0</v>
       </c>
       <c r="Z64" s="12" t="n">
-        <v>8501.24</v>
+        <v>801.62</v>
       </c>
       <c r="AA64" s="12" t="n">
-        <v>595.09</v>
+        <v>32.06</v>
       </c>
       <c r="AB64" s="12" t="n">
         <v>0</v>
@@ -29025,7 +29064,7 @@
         <v>76</v>
       </c>
       <c r="AX64" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY64" s="14" t="s">
         <v>75</v>
@@ -29061,7 +29100,7 @@
         <v>69</v>
       </c>
       <c r="BJ64" s="9" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="BK64" s="9" t="s">
         <v>75</v>
@@ -29075,58 +29114,58 @@
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
-        <v>306295</v>
+        <v>306334</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
       <c r="F65" s="9" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>114148.98</v>
+        <v>5177.88</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="O65" s="12" t="n">
-        <v>113148.24</v>
+        <v>5177.88</v>
       </c>
       <c r="P65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="13" t="n">
-        <v>4.99477</v>
+        <v>0.51249</v>
       </c>
       <c r="R65" s="12" t="n">
-        <v>313.53</v>
+        <v>176.94</v>
       </c>
       <c r="S65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T65" s="14" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="U65" s="15" t="s">
         <v>72</v>
@@ -29138,16 +29177,16 @@
         <v>73</v>
       </c>
       <c r="X65" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y65" s="12" t="n">
-        <v>1000.74</v>
+        <v>0</v>
       </c>
       <c r="Z65" s="12" t="n">
-        <v>113148.24</v>
+        <v>5177.88</v>
       </c>
       <c r="AA65" s="12" t="n">
-        <v>7362.41</v>
+        <v>207.12</v>
       </c>
       <c r="AB65" s="12" t="n">
         <v>0</v>
@@ -29216,7 +29255,7 @@
         <v>76</v>
       </c>
       <c r="AX65" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY65" s="14" t="s">
         <v>75</v>
@@ -29252,7 +29291,7 @@
         <v>69</v>
       </c>
       <c r="BJ65" s="9" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="BK65" s="9" t="s">
         <v>75</v>
@@ -29266,58 +29305,58 @@
     </row>
     <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
-        <v>306296</v>
+        <v>306336</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
       <c r="F66" s="9" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>1817.7</v>
+        <v>10197.33</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O66" s="12" t="n">
-        <v>1817.7</v>
+        <v>10197.33</v>
       </c>
       <c r="P66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="13" t="n">
-        <v>0.002</v>
+        <v>2.477648</v>
       </c>
       <c r="R66" s="12" t="n">
-        <v>2.58</v>
+        <v>829.6</v>
       </c>
       <c r="S66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T66" s="14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="U66" s="15" t="s">
         <v>72</v>
@@ -29329,16 +29368,16 @@
         <v>73</v>
       </c>
       <c r="X66" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z66" s="12" t="n">
-        <v>1817.7</v>
+        <v>10197.33</v>
       </c>
       <c r="AA66" s="12" t="n">
-        <v>127.24</v>
+        <v>407.9</v>
       </c>
       <c r="AB66" s="12" t="n">
         <v>0</v>
@@ -29407,7 +29446,7 @@
         <v>76</v>
       </c>
       <c r="AX66" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY66" s="14" t="s">
         <v>75</v>
@@ -29443,7 +29482,7 @@
         <v>69</v>
       </c>
       <c r="BJ66" s="9" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="BK66" s="9" t="s">
         <v>75</v>
@@ -29457,79 +29496,79 @@
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
-        <v>306297</v>
+        <v>306381</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
       <c r="F67" s="9" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>237</v>
+        <v>168</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>32189.81</v>
+        <v>5216.64</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0</v>
+        <v>838.8</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="O67" s="12" t="n">
-        <v>32170.78</v>
+        <v>5592</v>
       </c>
       <c r="P67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="13" t="n">
-        <v>12.805694</v>
+        <v>0</v>
       </c>
       <c r="R67" s="12" t="n">
-        <v>1682.52</v>
+        <v>7.42</v>
       </c>
       <c r="S67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T67" s="14" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="U67" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V67" s="12" t="n">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="W67" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X67" s="9" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Y67" s="12" t="n">
-        <v>19.03</v>
+        <v>463.44</v>
       </c>
       <c r="Z67" s="12" t="n">
-        <v>32170.78</v>
+        <v>4753.2</v>
       </c>
       <c r="AA67" s="12" t="n">
-        <v>2239.23</v>
+        <v>190.13</v>
       </c>
       <c r="AB67" s="12" t="n">
         <v>0</v>
@@ -29598,7 +29637,7 @@
         <v>76</v>
       </c>
       <c r="AX67" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY67" s="14" t="s">
         <v>75</v>
@@ -29634,7 +29673,7 @@
         <v>69</v>
       </c>
       <c r="BJ67" s="9" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="BK67" s="9" t="s">
         <v>75</v>
@@ -29648,79 +29687,79 @@
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
-        <v>306298</v>
+        <v>306452</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>294</v>
+        <v>64</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
       <c r="F68" s="9" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>237</v>
+        <v>295</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>296</v>
+        <v>69</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>1875.58</v>
+        <v>555.19</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O68" s="12" t="n">
-        <v>1875.58</v>
+        <v>555.19</v>
       </c>
       <c r="P68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="13" t="n">
-        <v>2.01284</v>
+        <v>0.08136</v>
       </c>
       <c r="R68" s="12" t="n">
-        <v>74.93</v>
+        <v>26.3</v>
       </c>
       <c r="S68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T68" s="14" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="U68" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V68" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W68" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X68" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Y68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z68" s="12" t="n">
-        <v>1875.58</v>
+        <v>555.19</v>
       </c>
       <c r="AA68" s="12" t="n">
-        <v>131.29</v>
+        <v>38.86</v>
       </c>
       <c r="AB68" s="12" t="n">
         <v>0</v>
@@ -29789,7 +29828,7 @@
         <v>76</v>
       </c>
       <c r="AX68" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY68" s="14" t="s">
         <v>75</v>
@@ -29825,7 +29864,7 @@
         <v>69</v>
       </c>
       <c r="BJ68" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="BK68" s="9" t="s">
         <v>75</v>
@@ -29839,34 +29878,34 @@
     </row>
     <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
-        <v>306323</v>
+        <v>306453</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>294</v>
+        <v>64</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
       <c r="F69" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>237</v>
+        <v>300</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>296</v>
+        <v>69</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>362.1</v>
+        <v>574.56</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>0</v>
@@ -29875,43 +29914,43 @@
         <v>1</v>
       </c>
       <c r="O69" s="12" t="n">
-        <v>362.1</v>
+        <v>574.56</v>
       </c>
       <c r="P69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="13" t="n">
-        <v>0.00542</v>
+        <v>0.08064</v>
       </c>
       <c r="R69" s="12" t="n">
-        <v>3.7</v>
+        <v>25.28</v>
       </c>
       <c r="S69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T69" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U69" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V69" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W69" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X69" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Y69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z69" s="12" t="n">
-        <v>362.1</v>
+        <v>574.56</v>
       </c>
       <c r="AA69" s="12" t="n">
-        <v>25.35</v>
+        <v>40.22</v>
       </c>
       <c r="AB69" s="12" t="n">
         <v>0</v>
@@ -29980,7 +30019,7 @@
         <v>76</v>
       </c>
       <c r="AX69" s="10" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AY69" s="14" t="s">
         <v>75</v>
@@ -30016,7 +30055,7 @@
         <v>69</v>
       </c>
       <c r="BJ69" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="BK69" s="9" t="s">
         <v>75</v>
@@ -30030,58 +30069,58 @@
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
-        <v>306324</v>
+        <v>306482</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
       <c r="F70" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>661.68</v>
+        <v>15959.1</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O70" s="12" t="n">
-        <v>661.68</v>
+        <v>15959.1</v>
       </c>
       <c r="P70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="13" t="n">
-        <v>0.18432</v>
+        <v>2.59191</v>
       </c>
       <c r="R70" s="12" t="n">
-        <v>60</v>
+        <v>1194.89</v>
       </c>
       <c r="S70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T70" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="U70" s="15" t="s">
         <v>72</v>
@@ -30093,16 +30132,16 @@
         <v>73</v>
       </c>
       <c r="X70" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Y70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z70" s="12" t="n">
-        <v>661.68</v>
+        <v>15959.1</v>
       </c>
       <c r="AA70" s="12" t="n">
-        <v>46.32</v>
+        <v>766.71</v>
       </c>
       <c r="AB70" s="12" t="n">
         <v>0</v>
@@ -30171,7 +30210,7 @@
         <v>76</v>
       </c>
       <c r="AX70" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY70" s="14" t="s">
         <v>75</v>
@@ -30207,7 +30246,7 @@
         <v>69</v>
       </c>
       <c r="BJ70" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="BK70" s="9" t="s">
         <v>75</v>
@@ -30221,34 +30260,34 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
-        <v>306331</v>
+        <v>306483</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>117</v>
+        <v>303</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
       <c r="F71" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>309</v>
+        <v>210</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>2276.64</v>
+        <v>1352.98</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>0</v>
@@ -30257,43 +30296,43 @@
         <v>1</v>
       </c>
       <c r="O71" s="12" t="n">
-        <v>2276.64</v>
+        <v>1352.98</v>
       </c>
       <c r="P71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="13" t="n">
-        <v>0.013104</v>
+        <v>0.17024</v>
       </c>
       <c r="R71" s="12" t="n">
-        <v>2.82</v>
+        <v>48.56</v>
       </c>
       <c r="S71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="U71" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V71" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W71" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X71" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Y71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="12" t="n">
-        <v>2276.64</v>
+        <v>1352.98</v>
       </c>
       <c r="AA71" s="12" t="n">
-        <v>159.36</v>
+        <v>54.12</v>
       </c>
       <c r="AB71" s="12" t="n">
         <v>0</v>
@@ -30362,7 +30401,7 @@
         <v>76</v>
       </c>
       <c r="AX71" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY71" s="14" t="s">
         <v>75</v>
@@ -30398,7 +30437,7 @@
         <v>69</v>
       </c>
       <c r="BJ71" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="BK71" s="9" t="s">
         <v>75</v>
@@ -30412,34 +30451,34 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
-        <v>306332</v>
+        <v>306484</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>117</v>
+        <v>303</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
       <c r="F72" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>801.62</v>
+        <v>5456.6</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>0</v>
@@ -30448,22 +30487,22 @@
         <v>1</v>
       </c>
       <c r="O72" s="12" t="n">
-        <v>801.62</v>
+        <v>5456.6</v>
       </c>
       <c r="P72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="13" t="n">
-        <v>0.00125</v>
+        <v>0</v>
       </c>
       <c r="R72" s="12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T72" s="14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="U72" s="15" t="s">
         <v>72</v>
@@ -30475,16 +30514,16 @@
         <v>73</v>
       </c>
       <c r="X72" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Y72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z72" s="12" t="n">
-        <v>801.62</v>
+        <v>5456.6</v>
       </c>
       <c r="AA72" s="12" t="n">
-        <v>32.06</v>
+        <v>218.26</v>
       </c>
       <c r="AB72" s="12" t="n">
         <v>0</v>
@@ -30553,7 +30592,7 @@
         <v>76</v>
       </c>
       <c r="AX72" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY72" s="14" t="s">
         <v>75</v>
@@ -30589,7 +30628,7 @@
         <v>69</v>
       </c>
       <c r="BJ72" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="BK72" s="9" t="s">
         <v>75</v>
@@ -30603,34 +30642,34 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
-        <v>306334</v>
+        <v>306489</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>117</v>
+        <v>262</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
       <c r="F73" s="9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>5177.88</v>
+        <v>424.48</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>0</v>
@@ -30639,22 +30678,22 @@
         <v>1</v>
       </c>
       <c r="O73" s="12" t="n">
-        <v>5177.88</v>
+        <v>424.48</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="13" t="n">
-        <v>0.51249</v>
+        <v>0.152152</v>
       </c>
       <c r="R73" s="12" t="n">
-        <v>176.94</v>
+        <v>44.26</v>
       </c>
       <c r="S73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T73" s="14" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="U73" s="15" t="s">
         <v>72</v>
@@ -30666,16 +30705,16 @@
         <v>73</v>
       </c>
       <c r="X73" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Y73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z73" s="12" t="n">
-        <v>5177.88</v>
+        <v>424.48</v>
       </c>
       <c r="AA73" s="12" t="n">
-        <v>207.12</v>
+        <v>29.71</v>
       </c>
       <c r="AB73" s="12" t="n">
         <v>0</v>
@@ -30741,10 +30780,10 @@
         <v>74</v>
       </c>
       <c r="AW73" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX73" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY73" s="14" t="s">
         <v>75</v>
@@ -30780,7 +30819,7 @@
         <v>69</v>
       </c>
       <c r="BJ73" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="BK73" s="9" t="s">
         <v>75</v>
@@ -30794,58 +30833,58 @@
     </row>
     <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
-        <v>306336</v>
+        <v>306495</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
       <c r="F74" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>10197.33</v>
+        <v>3916.35</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O74" s="12" t="n">
-        <v>10197.33</v>
+        <v>3762.32</v>
       </c>
       <c r="P74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="13" t="n">
-        <v>2.477648</v>
+        <v>0.032372</v>
       </c>
       <c r="R74" s="12" t="n">
-        <v>829.6</v>
+        <v>8.6</v>
       </c>
       <c r="S74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T74" s="14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="U74" s="15" t="s">
         <v>72</v>
@@ -30857,16 +30896,16 @@
         <v>73</v>
       </c>
       <c r="X74" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Y74" s="12" t="n">
-        <v>0</v>
+        <v>154.03</v>
       </c>
       <c r="Z74" s="12" t="n">
-        <v>10197.33</v>
+        <v>3762.32</v>
       </c>
       <c r="AA74" s="12" t="n">
-        <v>407.9</v>
+        <v>263.36</v>
       </c>
       <c r="AB74" s="12" t="n">
         <v>0</v>
@@ -30932,10 +30971,10 @@
         <v>74</v>
       </c>
       <c r="AW74" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX74" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY74" s="14" t="s">
         <v>75</v>
@@ -30971,7 +31010,7 @@
         <v>69</v>
       </c>
       <c r="BJ74" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="BK74" s="9" t="s">
         <v>75</v>
@@ -30985,43 +31024,43 @@
     </row>
     <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
-        <v>306381</v>
+        <v>306559</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
       <c r="F75" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>91</v>
+        <v>321</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>323</v>
+        <v>210</v>
       </c>
       <c r="K75" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>5216.64</v>
+        <v>1481.49</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>838.8</v>
+        <v>0</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O75" s="12" t="n">
-        <v>5592</v>
+        <v>1249.88</v>
       </c>
       <c r="P75" s="12" t="n">
         <v>0</v>
@@ -31030,34 +31069,34 @@
         <v>0</v>
       </c>
       <c r="R75" s="12" t="n">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="S75" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T75" s="14" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="U75" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V75" s="12" t="n">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="W75" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X75" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="Y75" s="12" t="n">
-        <v>463.44</v>
+        <v>131.61</v>
       </c>
       <c r="Z75" s="12" t="n">
-        <v>4753.2</v>
+        <v>1349.88</v>
       </c>
       <c r="AA75" s="12" t="n">
-        <v>190.13</v>
+        <v>84.33</v>
       </c>
       <c r="AB75" s="12" t="n">
         <v>0</v>
@@ -31123,10 +31162,10 @@
         <v>74</v>
       </c>
       <c r="AW75" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX75" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AY75" s="14" t="s">
         <v>75</v>
@@ -31162,7 +31201,7 @@
         <v>69</v>
       </c>
       <c r="BJ75" s="9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BK75" s="9" t="s">
         <v>75</v>
@@ -31175,534 +31214,900 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4"/>
+      <c r="A76" s="8" t="n">
+        <v>306567</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>31812.79</v>
+      </c>
+      <c r="M76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O76" s="12" t="n">
+        <v>31611.91</v>
+      </c>
+      <c r="P76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="13" t="n">
+        <v>2.652322</v>
+      </c>
+      <c r="R76" s="12" t="n">
+        <v>12352.88</v>
+      </c>
+      <c r="S76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="U76" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V76" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="W76" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X76" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y76" s="12" t="n">
+        <v>200.88</v>
+      </c>
+      <c r="Z76" s="12" t="n">
+        <v>31611.91</v>
+      </c>
+      <c r="AA76" s="12" t="n">
+        <v>3793.41</v>
+      </c>
+      <c r="AB76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW76" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX76" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF76" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG76" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI76" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ76" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="BK76" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL76" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM76" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="77" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="17"/>
-      <c r="M77" s="17"/>
-      <c r="N77" s="17"/>
-      <c r="O77" s="17"/>
-      <c r="P77" s="17"/>
-      <c r="Q77" s="17"/>
-      <c r="R77" s="17"/>
-      <c r="S77" s="17"/>
-      <c r="T77" s="17"/>
-      <c r="U77" s="17"/>
-      <c r="V77" s="17"/>
+    <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8" t="n">
+        <v>306575</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L77" s="12" t="n">
+        <v>3968.88</v>
+      </c>
+      <c r="M77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O77" s="12" t="n">
+        <v>3780.6</v>
+      </c>
+      <c r="P77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="13" t="n">
+        <v>0.02738</v>
+      </c>
+      <c r="R77" s="12" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="S77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="U77" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V77" s="12" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="W77" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X77" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y77" s="12" t="n">
+        <v>188.28</v>
+      </c>
+      <c r="Z77" s="12" t="n">
+        <v>3780.6</v>
+      </c>
+      <c r="AA77" s="12" t="n">
+        <v>151.22</v>
+      </c>
+      <c r="AB77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW77" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX77" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF77" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG77" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI77" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ77" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="BK77" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL77" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM77" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="78" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="B78" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="E78" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F78" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G78" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I78" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="J78" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K78" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L78" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M78" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="N78" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O78" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P78" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q78" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R78" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S78" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="T78" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="U78" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V78" s="18" t="s">
-        <v>37</v>
+    <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="n">
+        <v>306580</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L78" s="12" t="n">
+        <v>12473.85</v>
+      </c>
+      <c r="M78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="O78" s="12" t="n">
+        <v>12183.07</v>
+      </c>
+      <c r="P78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="13" t="n">
+        <v>3.009833</v>
+      </c>
+      <c r="R78" s="12" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="S78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="U78" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V78" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="W78" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X78" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y78" s="12" t="n">
+        <v>290.78</v>
+      </c>
+      <c r="Z78" s="12" t="n">
+        <v>12183.07</v>
+      </c>
+      <c r="AA78" s="12" t="n">
+        <v>704.43</v>
+      </c>
+      <c r="AB78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW78" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX78" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF78" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG78" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI78" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ78" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="BK78" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL78" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM78" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="19" t="n">
-        <v>71</v>
-      </c>
-      <c r="B79" s="19" t="n">
-        <v>838.8</v>
-      </c>
-      <c r="C79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="19" t="n">
-        <v>2834.44</v>
-      </c>
-      <c r="F79" s="19" t="n">
-        <v>299339.55</v>
-      </c>
-      <c r="G79" s="19" t="n">
-        <v>18857.46</v>
-      </c>
-      <c r="H79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="19" t="n">
-        <v>302173.99</v>
-      </c>
-      <c r="L79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="20" t="n">
-        <v>26.388855</v>
-      </c>
-      <c r="S79" s="19" t="n">
-        <v>300178.35</v>
-      </c>
-      <c r="T79" s="19" t="n">
-        <v>302173.99</v>
-      </c>
-      <c r="U79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B80" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D80" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E80" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F80" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G80" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H80" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I80" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J80" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K80" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="L80" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="M80" s="18" t="s">
-        <v>335</v>
-      </c>
+      <c r="A80" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+      <c r="L80" s="17"/>
+      <c r="M80" s="17"/>
+      <c r="N80" s="17"/>
+      <c r="O80" s="17"/>
+      <c r="P80" s="17"/>
+      <c r="Q80" s="17"/>
+      <c r="R80" s="17"/>
+      <c r="S80" s="17"/>
+      <c r="T80" s="17"/>
+      <c r="U80" s="17"/>
+      <c r="V80" s="17"/>
     </row>
-    <row r="81" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="19" t="n">
-        <v>3658.03</v>
-      </c>
-      <c r="B81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="19" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="E81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="19" t="n">
-        <v>0</v>
+    <row r="81" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="J81" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K81" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L81" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="N81" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O81" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P81" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q81" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R81" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S81" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="T81" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="U81" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V81" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4"/>
+      <c r="A82" s="19" t="n">
+        <v>74</v>
+      </c>
+      <c r="B82" s="19" t="n">
+        <v>838.8</v>
+      </c>
+      <c r="C82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E82" s="19" t="n">
+        <v>3412.13</v>
+      </c>
+      <c r="F82" s="19" t="n">
+        <v>351290.34</v>
+      </c>
+      <c r="G82" s="19" t="n">
+        <v>23306.03</v>
+      </c>
+      <c r="H82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="19" t="n">
+        <v>354702.47</v>
+      </c>
+      <c r="L82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="20" t="n">
+        <v>34.766963</v>
+      </c>
+      <c r="S82" s="19" t="n">
+        <v>352029.14</v>
+      </c>
+      <c r="T82" s="19" t="n">
+        <v>354702.47</v>
+      </c>
+      <c r="U82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="B83" s="21"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
-      <c r="J83" s="21"/>
-      <c r="K83" s="21"/>
-      <c r="L83" s="21"/>
-      <c r="M83" s="21"/>
-      <c r="N83" s="21"/>
-      <c r="O83" s="21"/>
-      <c r="P83" s="21"/>
-      <c r="Q83" s="21"/>
-      <c r="R83" s="21"/>
-      <c r="S83" s="21"/>
-      <c r="T83" s="21"/>
-      <c r="U83" s="21"/>
-      <c r="V83" s="21"/>
-      <c r="W83" s="21"/>
-      <c r="X83" s="21"/>
-      <c r="Y83" s="21"/>
-      <c r="Z83" s="21"/>
-      <c r="AA83" s="21"/>
-      <c r="AB83" s="21"/>
-      <c r="AC83" s="21"/>
-      <c r="AD83" s="21"/>
-      <c r="AE83" s="21"/>
-      <c r="AF83" s="21"/>
-      <c r="AG83" s="21"/>
-      <c r="AH83" s="21"/>
-      <c r="AI83" s="21"/>
-      <c r="AJ83" s="21"/>
-      <c r="AK83" s="21"/>
-      <c r="AL83" s="21"/>
-      <c r="AM83" s="21"/>
-      <c r="AN83" s="21"/>
-      <c r="AO83" s="21"/>
-      <c r="AP83" s="21"/>
-      <c r="AQ83" s="21"/>
-      <c r="AR83" s="21"/>
-      <c r="AS83" s="21"/>
-      <c r="AT83" s="21"/>
-      <c r="AU83" s="21"/>
-      <c r="AV83" s="21"/>
-      <c r="AW83" s="21"/>
-      <c r="AX83" s="21"/>
-      <c r="AY83" s="21"/>
-      <c r="AZ83" s="21"/>
-      <c r="BA83" s="21"/>
-      <c r="BB83" s="21"/>
-      <c r="BC83" s="21"/>
-      <c r="BD83" s="21"/>
-      <c r="BE83" s="21"/>
-      <c r="BF83" s="21"/>
-      <c r="BG83" s="21"/>
-      <c r="BH83" s="21"/>
-      <c r="BI83" s="21"/>
-      <c r="BJ83" s="21"/>
-      <c r="BK83" s="21"/>
-      <c r="BL83" s="21"/>
-      <c r="BM83" s="21"/>
+      <c r="A83" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I83" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J83" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K83" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="L83" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="M83" s="18" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
-      <c r="Q84" s="4"/>
-      <c r="R84" s="4"/>
-      <c r="S84" s="4"/>
-      <c r="T84" s="4"/>
-      <c r="U84" s="4"/>
-      <c r="V84" s="4"/>
-      <c r="W84" s="4"/>
-      <c r="X84" s="4"/>
-      <c r="Y84" s="4"/>
-      <c r="Z84" s="4"/>
-      <c r="AA84" s="4"/>
-      <c r="AB84" s="4"/>
-      <c r="AC84" s="4"/>
-      <c r="AD84" s="4"/>
-      <c r="AE84" s="4"/>
-      <c r="AF84" s="4"/>
-      <c r="AG84" s="4"/>
-      <c r="AH84" s="4"/>
-      <c r="AI84" s="4"/>
-      <c r="AJ84" s="4"/>
-      <c r="AK84" s="4"/>
-      <c r="AL84" s="4"/>
-      <c r="AM84" s="4"/>
-      <c r="AN84" s="4"/>
-      <c r="AO84" s="4"/>
-      <c r="AP84" s="4"/>
-      <c r="AQ84" s="4"/>
-      <c r="AR84" s="4"/>
-      <c r="AS84" s="4"/>
-      <c r="AT84" s="4"/>
-      <c r="AU84" s="4"/>
-      <c r="AV84" s="4"/>
-      <c r="AW84" s="4"/>
-      <c r="AX84" s="4"/>
-      <c r="AY84" s="4"/>
-      <c r="AZ84" s="4"/>
-      <c r="BA84" s="4"/>
-      <c r="BB84" s="4"/>
-      <c r="BC84" s="4"/>
-      <c r="BD84" s="4"/>
-      <c r="BE84" s="4"/>
-      <c r="BF84" s="4"/>
-      <c r="BG84" s="4"/>
-      <c r="BH84" s="4"/>
-      <c r="BI84" s="4"/>
-      <c r="BJ84" s="4"/>
-      <c r="BK84" s="4"/>
-      <c r="BL84" s="4"/>
-      <c r="BM84" s="4"/>
+      <c r="A84" s="19" t="n">
+        <v>17567.93</v>
+      </c>
+      <c r="B84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="19" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="E84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="4"/>
-      <c r="Q85" s="4"/>
-      <c r="R85" s="4"/>
-      <c r="S85" s="4"/>
-      <c r="T85" s="4"/>
-      <c r="U85" s="4"/>
-      <c r="V85" s="4"/>
-      <c r="W85" s="4"/>
-      <c r="X85" s="4"/>
-      <c r="Y85" s="4"/>
-      <c r="Z85" s="4"/>
-      <c r="AA85" s="4"/>
-      <c r="AB85" s="4"/>
-      <c r="AC85" s="4"/>
-      <c r="AD85" s="4"/>
-      <c r="AE85" s="4"/>
-      <c r="AF85" s="4"/>
-      <c r="AG85" s="4"/>
-      <c r="AH85" s="4"/>
-      <c r="AI85" s="4"/>
-      <c r="AJ85" s="4"/>
-      <c r="AK85" s="4"/>
-      <c r="AL85" s="4"/>
-      <c r="AM85" s="4"/>
-      <c r="AN85" s="4"/>
-      <c r="AO85" s="4"/>
-      <c r="AP85" s="4"/>
-      <c r="AQ85" s="4"/>
-      <c r="AR85" s="4"/>
-      <c r="AS85" s="4"/>
-      <c r="AT85" s="4"/>
-      <c r="AU85" s="4"/>
-      <c r="AV85" s="4"/>
-      <c r="AW85" s="4"/>
-      <c r="AX85" s="4"/>
-      <c r="AY85" s="4"/>
-      <c r="AZ85" s="4"/>
-      <c r="BA85" s="4"/>
-      <c r="BB85" s="4"/>
-      <c r="BC85" s="4"/>
-      <c r="BD85" s="4"/>
-      <c r="BE85" s="4"/>
-      <c r="BF85" s="4"/>
-      <c r="BG85" s="4"/>
-      <c r="BH85" s="4"/>
-      <c r="BI85" s="4"/>
-      <c r="BJ85" s="4"/>
-      <c r="BK85" s="4"/>
-      <c r="BL85" s="4"/>
-      <c r="BM85" s="4"/>
+      <c r="A85" s="4"/>
     </row>
-    <row r="86" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4"/>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-      <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
-      <c r="Q86" s="4"/>
-      <c r="R86" s="4"/>
-      <c r="S86" s="4"/>
-      <c r="T86" s="4"/>
-      <c r="U86" s="4"/>
-      <c r="V86" s="4"/>
-      <c r="W86" s="4"/>
-      <c r="X86" s="4"/>
-      <c r="Y86" s="4"/>
-      <c r="Z86" s="4"/>
-      <c r="AA86" s="4"/>
-      <c r="AB86" s="4"/>
-      <c r="AC86" s="4"/>
-      <c r="AD86" s="4"/>
-      <c r="AE86" s="4"/>
-      <c r="AF86" s="4"/>
-      <c r="AG86" s="4"/>
-      <c r="AH86" s="4"/>
-      <c r="AI86" s="4"/>
-      <c r="AJ86" s="4"/>
-      <c r="AK86" s="4"/>
-      <c r="AL86" s="4"/>
-      <c r="AM86" s="4"/>
-      <c r="AN86" s="4"/>
-      <c r="AO86" s="4"/>
-      <c r="AP86" s="4"/>
-      <c r="AQ86" s="4"/>
-      <c r="AR86" s="4"/>
-      <c r="AS86" s="4"/>
-      <c r="AT86" s="4"/>
-      <c r="AU86" s="4"/>
-      <c r="AV86" s="4"/>
-      <c r="AW86" s="4"/>
-      <c r="AX86" s="4"/>
-      <c r="AY86" s="4"/>
-      <c r="AZ86" s="4"/>
-      <c r="BA86" s="4"/>
-      <c r="BB86" s="4"/>
-      <c r="BC86" s="4"/>
-      <c r="BD86" s="4"/>
-      <c r="BE86" s="4"/>
-      <c r="BF86" s="4"/>
-      <c r="BG86" s="4"/>
-      <c r="BH86" s="4"/>
-      <c r="BI86" s="4"/>
-      <c r="BJ86" s="4"/>
-      <c r="BK86" s="4"/>
-      <c r="BL86" s="4"/>
-      <c r="BM86" s="4"/>
+    <row r="86" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="B86" s="21"/>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="21"/>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+      <c r="I86" s="21"/>
+      <c r="J86" s="21"/>
+      <c r="K86" s="21"/>
+      <c r="L86" s="21"/>
+      <c r="M86" s="21"/>
+      <c r="N86" s="21"/>
+      <c r="O86" s="21"/>
+      <c r="P86" s="21"/>
+      <c r="Q86" s="21"/>
+      <c r="R86" s="21"/>
+      <c r="S86" s="21"/>
+      <c r="T86" s="21"/>
+      <c r="U86" s="21"/>
+      <c r="V86" s="21"/>
+      <c r="W86" s="21"/>
+      <c r="X86" s="21"/>
+      <c r="Y86" s="21"/>
+      <c r="Z86" s="21"/>
+      <c r="AA86" s="21"/>
+      <c r="AB86" s="21"/>
+      <c r="AC86" s="21"/>
+      <c r="AD86" s="21"/>
+      <c r="AE86" s="21"/>
+      <c r="AF86" s="21"/>
+      <c r="AG86" s="21"/>
+      <c r="AH86" s="21"/>
+      <c r="AI86" s="21"/>
+      <c r="AJ86" s="21"/>
+      <c r="AK86" s="21"/>
+      <c r="AL86" s="21"/>
+      <c r="AM86" s="21"/>
+      <c r="AN86" s="21"/>
+      <c r="AO86" s="21"/>
+      <c r="AP86" s="21"/>
+      <c r="AQ86" s="21"/>
+      <c r="AR86" s="21"/>
+      <c r="AS86" s="21"/>
+      <c r="AT86" s="21"/>
+      <c r="AU86" s="21"/>
+      <c r="AV86" s="21"/>
+      <c r="AW86" s="21"/>
+      <c r="AX86" s="21"/>
+      <c r="AY86" s="21"/>
+      <c r="AZ86" s="21"/>
+      <c r="BA86" s="21"/>
+      <c r="BB86" s="21"/>
+      <c r="BC86" s="21"/>
+      <c r="BD86" s="21"/>
+      <c r="BE86" s="21"/>
+      <c r="BF86" s="21"/>
+      <c r="BG86" s="21"/>
+      <c r="BH86" s="21"/>
+      <c r="BI86" s="21"/>
+      <c r="BJ86" s="21"/>
+      <c r="BK86" s="21"/>
+      <c r="BL86" s="21"/>
+      <c r="BM86" s="21"/>
     </row>
     <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -31771,7 +32176,7 @@
     </row>
     <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>22</v>
+        <v>350</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -31840,7 +32245,7 @@
     </row>
     <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -31909,7 +32314,7 @@
     </row>
     <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -31978,7 +32383,7 @@
     </row>
     <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>342</v>
+        <v>22</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -32047,7 +32452,7 @@
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -32116,7 +32521,7 @@
     </row>
     <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -32183,8 +32588,215 @@
       <c r="BL93" s="4"/>
       <c r="BM93" s="4"/>
     </row>
+    <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="4"/>
+      <c r="R94" s="4"/>
+      <c r="S94" s="4"/>
+      <c r="T94" s="4"/>
+      <c r="U94" s="4"/>
+      <c r="V94" s="4"/>
+      <c r="W94" s="4"/>
+      <c r="X94" s="4"/>
+      <c r="Y94" s="4"/>
+      <c r="Z94" s="4"/>
+      <c r="AA94" s="4"/>
+      <c r="AB94" s="4"/>
+      <c r="AC94" s="4"/>
+      <c r="AD94" s="4"/>
+      <c r="AE94" s="4"/>
+      <c r="AF94" s="4"/>
+      <c r="AG94" s="4"/>
+      <c r="AH94" s="4"/>
+      <c r="AI94" s="4"/>
+      <c r="AJ94" s="4"/>
+      <c r="AK94" s="4"/>
+      <c r="AL94" s="4"/>
+      <c r="AM94" s="4"/>
+      <c r="AN94" s="4"/>
+      <c r="AO94" s="4"/>
+      <c r="AP94" s="4"/>
+      <c r="AQ94" s="4"/>
+      <c r="AR94" s="4"/>
+      <c r="AS94" s="4"/>
+      <c r="AT94" s="4"/>
+      <c r="AU94" s="4"/>
+      <c r="AV94" s="4"/>
+      <c r="AW94" s="4"/>
+      <c r="AX94" s="4"/>
+      <c r="AY94" s="4"/>
+      <c r="AZ94" s="4"/>
+      <c r="BA94" s="4"/>
+      <c r="BB94" s="4"/>
+      <c r="BC94" s="4"/>
+      <c r="BD94" s="4"/>
+      <c r="BE94" s="4"/>
+      <c r="BF94" s="4"/>
+      <c r="BG94" s="4"/>
+      <c r="BH94" s="4"/>
+      <c r="BI94" s="4"/>
+      <c r="BJ94" s="4"/>
+      <c r="BK94" s="4"/>
+      <c r="BL94" s="4"/>
+      <c r="BM94" s="4"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4"/>
+      <c r="S95" s="4"/>
+      <c r="T95" s="4"/>
+      <c r="U95" s="4"/>
+      <c r="V95" s="4"/>
+      <c r="W95" s="4"/>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="4"/>
+      <c r="AB95" s="4"/>
+      <c r="AC95" s="4"/>
+      <c r="AD95" s="4"/>
+      <c r="AE95" s="4"/>
+      <c r="AF95" s="4"/>
+      <c r="AG95" s="4"/>
+      <c r="AH95" s="4"/>
+      <c r="AI95" s="4"/>
+      <c r="AJ95" s="4"/>
+      <c r="AK95" s="4"/>
+      <c r="AL95" s="4"/>
+      <c r="AM95" s="4"/>
+      <c r="AN95" s="4"/>
+      <c r="AO95" s="4"/>
+      <c r="AP95" s="4"/>
+      <c r="AQ95" s="4"/>
+      <c r="AR95" s="4"/>
+      <c r="AS95" s="4"/>
+      <c r="AT95" s="4"/>
+      <c r="AU95" s="4"/>
+      <c r="AV95" s="4"/>
+      <c r="AW95" s="4"/>
+      <c r="AX95" s="4"/>
+      <c r="AY95" s="4"/>
+      <c r="AZ95" s="4"/>
+      <c r="BA95" s="4"/>
+      <c r="BB95" s="4"/>
+      <c r="BC95" s="4"/>
+      <c r="BD95" s="4"/>
+      <c r="BE95" s="4"/>
+      <c r="BF95" s="4"/>
+      <c r="BG95" s="4"/>
+      <c r="BH95" s="4"/>
+      <c r="BI95" s="4"/>
+      <c r="BJ95" s="4"/>
+      <c r="BK95" s="4"/>
+      <c r="BL95" s="4"/>
+      <c r="BM95" s="4"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="4"/>
+      <c r="S96" s="4"/>
+      <c r="T96" s="4"/>
+      <c r="U96" s="4"/>
+      <c r="V96" s="4"/>
+      <c r="W96" s="4"/>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+      <c r="AA96" s="4"/>
+      <c r="AB96" s="4"/>
+      <c r="AC96" s="4"/>
+      <c r="AD96" s="4"/>
+      <c r="AE96" s="4"/>
+      <c r="AF96" s="4"/>
+      <c r="AG96" s="4"/>
+      <c r="AH96" s="4"/>
+      <c r="AI96" s="4"/>
+      <c r="AJ96" s="4"/>
+      <c r="AK96" s="4"/>
+      <c r="AL96" s="4"/>
+      <c r="AM96" s="4"/>
+      <c r="AN96" s="4"/>
+      <c r="AO96" s="4"/>
+      <c r="AP96" s="4"/>
+      <c r="AQ96" s="4"/>
+      <c r="AR96" s="4"/>
+      <c r="AS96" s="4"/>
+      <c r="AT96" s="4"/>
+      <c r="AU96" s="4"/>
+      <c r="AV96" s="4"/>
+      <c r="AW96" s="4"/>
+      <c r="AX96" s="4"/>
+      <c r="AY96" s="4"/>
+      <c r="AZ96" s="4"/>
+      <c r="BA96" s="4"/>
+      <c r="BB96" s="4"/>
+      <c r="BC96" s="4"/>
+      <c r="BD96" s="4"/>
+      <c r="BE96" s="4"/>
+      <c r="BF96" s="4"/>
+      <c r="BG96" s="4"/>
+      <c r="BH96" s="4"/>
+      <c r="BI96" s="4"/>
+      <c r="BJ96" s="4"/>
+      <c r="BK96" s="4"/>
+      <c r="BL96" s="4"/>
+      <c r="BM96" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="87">
+  <mergeCells count="90">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -32260,10 +32872,10 @@
     <mergeCell ref="B73:E73"/>
     <mergeCell ref="B74:E74"/>
     <mergeCell ref="B75:E75"/>
-    <mergeCell ref="A77:V77"/>
-    <mergeCell ref="A83:BM83"/>
-    <mergeCell ref="A84:BM84"/>
-    <mergeCell ref="A85:BM85"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="A80:V80"/>
     <mergeCell ref="A86:BM86"/>
     <mergeCell ref="A87:BM87"/>
     <mergeCell ref="A88:BM88"/>
@@ -32272,6 +32884,9 @@
     <mergeCell ref="A91:BM91"/>
     <mergeCell ref="A92:BM92"/>
     <mergeCell ref="A93:BM93"/>
+    <mergeCell ref="A94:BM94"/>
+    <mergeCell ref="A95:BM95"/>
+    <mergeCell ref="A96:BM96"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 05/05/2026 07:39:20</t>
+    <t xml:space="preserve">Emitido em: 05/05/2026 10:35:14</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3072" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3992" uniqueCount="439">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 05/05/2026 10:35:14</t>
+    <t xml:space="preserve">Emitido em: 06/05/2026 08:38:37</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -994,21 +994,6 @@
     <t xml:space="preserve">42260424546165000393550040000978321120610091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.247 - NOVA ROCHA INDUSTRIA DE TINTAS LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">552.880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.812,79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52260403005123000103550010005528801581503331</t>
-  </si>
-  <si>
     <t xml:space="preserve">21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
   </si>
   <si>
@@ -1037,6 +1022,264 @@
   </si>
   <si>
     <t xml:space="preserve">43260489723837000172550000006837191121562860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.338 - ELGIN DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">381.073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.657,42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260407023429000143550010003810731343740022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">886,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763471396106554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356,46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763481366796487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">775,84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763491770168627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">736,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763501118430863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.401,68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763511515410130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488,88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763521617247244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.005,65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763531356462470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168,59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763541281024088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763551201608263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.312,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763561437548512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.582 - GRUPO MARMO E HIME COMERCIO, IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.895,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260420587017000285550010000393321433515191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763571452555700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.772,88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763581451430234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.467,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006331971064436652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 - TRAMONTINA PLANALTO S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">708.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.471,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260400142240000120550010007080221947081752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.025 - FRESNOMAQ INDUSTRIA DE MAQUINAS S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.320,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32260406337280001186550010000599891874418073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.445 - PERFIS VISCARDI LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.671,86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260414570742000329550010000100791085820910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.352.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013520891393486645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.352.088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013520881842296450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.352.087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013520871369635550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.353.846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.070,58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013538461061418038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.003 - JAPI SA INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">769.903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.773,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260571522460000128550050007699031909928743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.666,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260510691158000370550010002923951294218725</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17282,7 +17525,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM96"/>
+  <dimension ref="A1:BM119"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -31215,7 +31458,7 @@
     </row>
     <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
-        <v>306567</v>
+        <v>306575</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>324</v>
@@ -31227,40 +31470,40 @@
         <v>325</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>91</v>
+        <v>326</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="I76" s="9" t="s">
         <v>296</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>326</v>
+        <v>264</v>
       </c>
       <c r="K76" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>31812.79</v>
+        <v>3968.88</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O76" s="12" t="n">
-        <v>31611.91</v>
+        <v>3780.6</v>
       </c>
       <c r="P76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="13" t="n">
-        <v>2.652322</v>
+        <v>0.02738</v>
       </c>
       <c r="R76" s="12" t="n">
-        <v>12352.88</v>
+        <v>21.28</v>
       </c>
       <c r="S76" s="12" t="n">
         <v>0</v>
@@ -31272,7 +31515,7 @@
         <v>72</v>
       </c>
       <c r="V76" s="12" t="n">
-        <v>75</v>
+        <v>54.67</v>
       </c>
       <c r="W76" s="9" t="s">
         <v>73</v>
@@ -31281,13 +31524,13 @@
         <v>296</v>
       </c>
       <c r="Y76" s="12" t="n">
-        <v>200.88</v>
+        <v>188.28</v>
       </c>
       <c r="Z76" s="12" t="n">
-        <v>31611.91</v>
+        <v>3780.6</v>
       </c>
       <c r="AA76" s="12" t="n">
-        <v>3793.41</v>
+        <v>151.22</v>
       </c>
       <c r="AB76" s="12" t="n">
         <v>0</v>
@@ -31353,7 +31596,7 @@
         <v>74</v>
       </c>
       <c r="AW76" s="14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AX76" s="10" t="s">
         <v>122</v>
@@ -31406,7 +31649,7 @@
     </row>
     <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
-        <v>306575</v>
+        <v>306580</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>329</v>
@@ -31418,7 +31661,7 @@
         <v>330</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>331</v>
+        <v>66</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>204</v>
@@ -31427,31 +31670,31 @@
         <v>296</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>264</v>
+        <v>331</v>
       </c>
       <c r="K77" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>3968.88</v>
+        <v>12473.85</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="O77" s="12" t="n">
-        <v>3780.6</v>
+        <v>12183.07</v>
       </c>
       <c r="P77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="13" t="n">
-        <v>0.02738</v>
+        <v>3.009833</v>
       </c>
       <c r="R77" s="12" t="n">
-        <v>21.28</v>
+        <v>251.5</v>
       </c>
       <c r="S77" s="12" t="n">
         <v>0</v>
@@ -31463,7 +31706,7 @@
         <v>72</v>
       </c>
       <c r="V77" s="12" t="n">
-        <v>54.67</v>
+        <v>60</v>
       </c>
       <c r="W77" s="9" t="s">
         <v>73</v>
@@ -31472,13 +31715,13 @@
         <v>296</v>
       </c>
       <c r="Y77" s="12" t="n">
-        <v>188.28</v>
+        <v>290.78</v>
       </c>
       <c r="Z77" s="12" t="n">
-        <v>3780.6</v>
+        <v>12183.07</v>
       </c>
       <c r="AA77" s="12" t="n">
-        <v>151.22</v>
+        <v>704.43</v>
       </c>
       <c r="AB77" s="12" t="n">
         <v>0</v>
@@ -31597,7 +31840,7 @@
     </row>
     <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
-        <v>306580</v>
+        <v>306605</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>334</v>
@@ -31609,67 +31852,67 @@
         <v>335</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K78" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>12473.85</v>
+        <v>9657.42</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="O78" s="12" t="n">
-        <v>12183.07</v>
+        <v>8945.04</v>
       </c>
       <c r="P78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="13" t="n">
-        <v>3.009833</v>
+        <v>0</v>
       </c>
       <c r="R78" s="12" t="n">
-        <v>251.5</v>
+        <v>0</v>
       </c>
       <c r="S78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T78" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="U78" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V78" s="12" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="W78" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X78" s="9" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="Y78" s="12" t="n">
-        <v>290.78</v>
+        <v>712.38</v>
       </c>
       <c r="Z78" s="12" t="n">
-        <v>12183.07</v>
+        <v>8945.04</v>
       </c>
       <c r="AA78" s="12" t="n">
-        <v>704.43</v>
+        <v>357.79</v>
       </c>
       <c r="AB78" s="12" t="n">
         <v>0</v>
@@ -31735,7 +31978,7 @@
         <v>74</v>
       </c>
       <c r="AW78" s="14" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AX78" s="10" t="s">
         <v>122</v>
@@ -31774,7 +32017,7 @@
         <v>69</v>
       </c>
       <c r="BJ78" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="BK78" s="9" t="s">
         <v>75</v>
@@ -31787,1016 +32030,5409 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4"/>
+      <c r="A79" s="8" t="n">
+        <v>306679</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>886.44</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="12" t="n">
+        <v>886.44</v>
+      </c>
+      <c r="P79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="13" t="n">
+        <v>0.000216</v>
+      </c>
+      <c r="R79" s="12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="U79" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V79" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W79" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X79" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="12" t="n">
+        <v>886.44</v>
+      </c>
+      <c r="AA79" s="12" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="AB79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW79" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX79" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF79" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG79" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI79" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ79" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="BK79" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL79" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM79" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="80" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="17"/>
-      <c r="M80" s="17"/>
-      <c r="N80" s="17"/>
-      <c r="O80" s="17"/>
-      <c r="P80" s="17"/>
-      <c r="Q80" s="17"/>
-      <c r="R80" s="17"/>
-      <c r="S80" s="17"/>
-      <c r="T80" s="17"/>
-      <c r="U80" s="17"/>
-      <c r="V80" s="17"/>
+    <row r="80" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="n">
+        <v>306680</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L80" s="12" t="n">
+        <v>356.46</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="12" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="P80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="13" t="n">
+        <v>0.000284</v>
+      </c>
+      <c r="R80" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="S80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="U80" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V80" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W80" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X80" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y80" s="12" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="Z80" s="12" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="AA80" s="12" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="AB80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW80" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX80" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG80" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI80" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ80" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="BK80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM80" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="81" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="B81" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="E81" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F81" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I81" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="J81" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K81" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L81" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M81" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="N81" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O81" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P81" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q81" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R81" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S81" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="T81" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="U81" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V81" s="18" t="s">
-        <v>37</v>
+    <row r="81" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="n">
+        <v>306681</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L81" s="12" t="n">
+        <v>775.84</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" s="12" t="n">
+        <v>775.84</v>
+      </c>
+      <c r="P81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="13" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="R81" s="12" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="S81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="U81" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V81" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W81" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X81" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="12" t="n">
+        <v>775.84</v>
+      </c>
+      <c r="AA81" s="12" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="AB81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW81" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX81" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG81" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI81" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ81" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="BK81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM81" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="19" t="n">
-        <v>74</v>
-      </c>
-      <c r="B82" s="19" t="n">
-        <v>838.8</v>
-      </c>
-      <c r="C82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E82" s="19" t="n">
-        <v>3412.13</v>
-      </c>
-      <c r="F82" s="19" t="n">
-        <v>351290.34</v>
-      </c>
-      <c r="G82" s="19" t="n">
-        <v>23306.03</v>
-      </c>
-      <c r="H82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="19" t="n">
-        <v>354702.47</v>
-      </c>
-      <c r="L82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="20" t="n">
-        <v>34.766963</v>
-      </c>
-      <c r="S82" s="19" t="n">
-        <v>352029.14</v>
-      </c>
-      <c r="T82" s="19" t="n">
-        <v>354702.47</v>
-      </c>
-      <c r="U82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="19" t="n">
-        <v>0</v>
+      <c r="A82" s="8" t="n">
+        <v>306682</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L82" s="12" t="n">
+        <v>736.02</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="12" t="n">
+        <v>691.1</v>
+      </c>
+      <c r="P82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="13" t="n">
+        <v>0.00211</v>
+      </c>
+      <c r="R82" s="12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="U82" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V82" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W82" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X82" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y82" s="12" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="Z82" s="12" t="n">
+        <v>691.1</v>
+      </c>
+      <c r="AA82" s="12" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="AB82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW82" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX82" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG82" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI82" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ82" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="BK82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM82" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B83" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F83" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G83" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I83" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J83" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K83" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="L83" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="M83" s="18" t="s">
-        <v>348</v>
+    <row r="83" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="8" t="n">
+        <v>306683</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <v>1401.68</v>
+      </c>
+      <c r="M83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" s="12" t="n">
+        <v>1401.68</v>
+      </c>
+      <c r="P83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="13" t="n">
+        <v>0.013104</v>
+      </c>
+      <c r="R83" s="12" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="S83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="U83" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V83" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W83" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X83" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="12" t="n">
+        <v>1401.68</v>
+      </c>
+      <c r="AA83" s="12" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="AB83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW83" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX83" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG83" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI83" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ83" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="BK83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM83" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="19" t="n">
-        <v>17567.93</v>
-      </c>
-      <c r="B84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="19" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="E84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="19" t="n">
-        <v>0</v>
+      <c r="A84" s="8" t="n">
+        <v>306684</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>488.88</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" s="12" t="n">
+        <v>488.88</v>
+      </c>
+      <c r="P84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="13" t="n">
+        <v>0.012896</v>
+      </c>
+      <c r="R84" s="12" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="U84" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W84" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X84" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="12" t="n">
+        <v>488.88</v>
+      </c>
+      <c r="AA84" s="12" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="AB84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW84" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX84" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG84" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI84" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ84" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="BK84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM84" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4"/>
+      <c r="A85" s="8" t="n">
+        <v>306685</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>1005.65</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <v>944.28</v>
+      </c>
+      <c r="P85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="13" t="n">
+        <v>0.01056</v>
+      </c>
+      <c r="R85" s="12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="U85" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V85" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W85" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X85" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y85" s="12" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="Z85" s="12" t="n">
+        <v>944.28</v>
+      </c>
+      <c r="AA85" s="12" t="n">
+        <v>66.1</v>
+      </c>
+      <c r="AB85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW85" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX85" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG85" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI85" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ85" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="BK85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM85" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="86" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="B86" s="21"/>
-      <c r="C86" s="21"/>
-      <c r="D86" s="21"/>
-      <c r="E86" s="21"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21"/>
-      <c r="K86" s="21"/>
-      <c r="L86" s="21"/>
-      <c r="M86" s="21"/>
-      <c r="N86" s="21"/>
-      <c r="O86" s="21"/>
-      <c r="P86" s="21"/>
-      <c r="Q86" s="21"/>
-      <c r="R86" s="21"/>
-      <c r="S86" s="21"/>
-      <c r="T86" s="21"/>
-      <c r="U86" s="21"/>
-      <c r="V86" s="21"/>
-      <c r="W86" s="21"/>
-      <c r="X86" s="21"/>
-      <c r="Y86" s="21"/>
-      <c r="Z86" s="21"/>
-      <c r="AA86" s="21"/>
-      <c r="AB86" s="21"/>
-      <c r="AC86" s="21"/>
-      <c r="AD86" s="21"/>
-      <c r="AE86" s="21"/>
-      <c r="AF86" s="21"/>
-      <c r="AG86" s="21"/>
-      <c r="AH86" s="21"/>
-      <c r="AI86" s="21"/>
-      <c r="AJ86" s="21"/>
-      <c r="AK86" s="21"/>
-      <c r="AL86" s="21"/>
-      <c r="AM86" s="21"/>
-      <c r="AN86" s="21"/>
-      <c r="AO86" s="21"/>
-      <c r="AP86" s="21"/>
-      <c r="AQ86" s="21"/>
-      <c r="AR86" s="21"/>
-      <c r="AS86" s="21"/>
-      <c r="AT86" s="21"/>
-      <c r="AU86" s="21"/>
-      <c r="AV86" s="21"/>
-      <c r="AW86" s="21"/>
-      <c r="AX86" s="21"/>
-      <c r="AY86" s="21"/>
-      <c r="AZ86" s="21"/>
-      <c r="BA86" s="21"/>
-      <c r="BB86" s="21"/>
-      <c r="BC86" s="21"/>
-      <c r="BD86" s="21"/>
-      <c r="BE86" s="21"/>
-      <c r="BF86" s="21"/>
-      <c r="BG86" s="21"/>
-      <c r="BH86" s="21"/>
-      <c r="BI86" s="21"/>
-      <c r="BJ86" s="21"/>
-      <c r="BK86" s="21"/>
-      <c r="BL86" s="21"/>
-      <c r="BM86" s="21"/>
+    <row r="86" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="n">
+        <v>306686</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>168.59</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" s="12" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="P86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="13" t="n">
+        <v>0.001836</v>
+      </c>
+      <c r="R86" s="12" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="S86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="U86" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V86" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W86" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X86" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y86" s="12" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="Z86" s="12" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="AA86" s="12" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="AB86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW86" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX86" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG86" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI86" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ86" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="BK86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM86" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="4"/>
-      <c r="X87" s="4"/>
-      <c r="Y87" s="4"/>
-      <c r="Z87" s="4"/>
-      <c r="AA87" s="4"/>
-      <c r="AB87" s="4"/>
-      <c r="AC87" s="4"/>
-      <c r="AD87" s="4"/>
-      <c r="AE87" s="4"/>
-      <c r="AF87" s="4"/>
-      <c r="AG87" s="4"/>
-      <c r="AH87" s="4"/>
-      <c r="AI87" s="4"/>
-      <c r="AJ87" s="4"/>
-      <c r="AK87" s="4"/>
-      <c r="AL87" s="4"/>
-      <c r="AM87" s="4"/>
-      <c r="AN87" s="4"/>
-      <c r="AO87" s="4"/>
-      <c r="AP87" s="4"/>
-      <c r="AQ87" s="4"/>
-      <c r="AR87" s="4"/>
-      <c r="AS87" s="4"/>
-      <c r="AT87" s="4"/>
-      <c r="AU87" s="4"/>
-      <c r="AV87" s="4"/>
-      <c r="AW87" s="4"/>
-      <c r="AX87" s="4"/>
-      <c r="AY87" s="4"/>
-      <c r="AZ87" s="4"/>
-      <c r="BA87" s="4"/>
-      <c r="BB87" s="4"/>
-      <c r="BC87" s="4"/>
-      <c r="BD87" s="4"/>
-      <c r="BE87" s="4"/>
-      <c r="BF87" s="4"/>
-      <c r="BG87" s="4"/>
-      <c r="BH87" s="4"/>
-      <c r="BI87" s="4"/>
-      <c r="BJ87" s="4"/>
-      <c r="BK87" s="4"/>
-      <c r="BL87" s="4"/>
-      <c r="BM87" s="4"/>
+      <c r="A87" s="8" t="n">
+        <v>306687</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>488.88</v>
+      </c>
+      <c r="M87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="12" t="n">
+        <v>488.88</v>
+      </c>
+      <c r="P87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="13" t="n">
+        <v>0.012896</v>
+      </c>
+      <c r="R87" s="12" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="U87" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V87" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W87" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X87" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="12" t="n">
+        <v>488.88</v>
+      </c>
+      <c r="AA87" s="12" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="AB87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW87" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX87" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG87" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI87" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ87" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="BK87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM87" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4"/>
-      <c r="W88" s="4"/>
-      <c r="X88" s="4"/>
-      <c r="Y88" s="4"/>
-      <c r="Z88" s="4"/>
-      <c r="AA88" s="4"/>
-      <c r="AB88" s="4"/>
-      <c r="AC88" s="4"/>
-      <c r="AD88" s="4"/>
-      <c r="AE88" s="4"/>
-      <c r="AF88" s="4"/>
-      <c r="AG88" s="4"/>
-      <c r="AH88" s="4"/>
-      <c r="AI88" s="4"/>
-      <c r="AJ88" s="4"/>
-      <c r="AK88" s="4"/>
-      <c r="AL88" s="4"/>
-      <c r="AM88" s="4"/>
-      <c r="AN88" s="4"/>
-      <c r="AO88" s="4"/>
-      <c r="AP88" s="4"/>
-      <c r="AQ88" s="4"/>
-      <c r="AR88" s="4"/>
-      <c r="AS88" s="4"/>
-      <c r="AT88" s="4"/>
-      <c r="AU88" s="4"/>
-      <c r="AV88" s="4"/>
-      <c r="AW88" s="4"/>
-      <c r="AX88" s="4"/>
-      <c r="AY88" s="4"/>
-      <c r="AZ88" s="4"/>
-      <c r="BA88" s="4"/>
-      <c r="BB88" s="4"/>
-      <c r="BC88" s="4"/>
-      <c r="BD88" s="4"/>
-      <c r="BE88" s="4"/>
-      <c r="BF88" s="4"/>
-      <c r="BG88" s="4"/>
-      <c r="BH88" s="4"/>
-      <c r="BI88" s="4"/>
-      <c r="BJ88" s="4"/>
-      <c r="BK88" s="4"/>
-      <c r="BL88" s="4"/>
-      <c r="BM88" s="4"/>
+      <c r="A88" s="8" t="n">
+        <v>306688</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>1312.96</v>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" s="12" t="n">
+        <v>1312.96</v>
+      </c>
+      <c r="P88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="13" t="n">
+        <v>0.000576</v>
+      </c>
+      <c r="R88" s="12" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="S88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="U88" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V88" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W88" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X88" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="12" t="n">
+        <v>1312.96</v>
+      </c>
+      <c r="AA88" s="12" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="AB88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW88" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX88" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG88" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI88" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ88" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="BK88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM88" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
-      <c r="X89" s="4"/>
-      <c r="Y89" s="4"/>
-      <c r="Z89" s="4"/>
-      <c r="AA89" s="4"/>
-      <c r="AB89" s="4"/>
-      <c r="AC89" s="4"/>
-      <c r="AD89" s="4"/>
-      <c r="AE89" s="4"/>
-      <c r="AF89" s="4"/>
-      <c r="AG89" s="4"/>
-      <c r="AH89" s="4"/>
-      <c r="AI89" s="4"/>
-      <c r="AJ89" s="4"/>
-      <c r="AK89" s="4"/>
-      <c r="AL89" s="4"/>
-      <c r="AM89" s="4"/>
-      <c r="AN89" s="4"/>
-      <c r="AO89" s="4"/>
-      <c r="AP89" s="4"/>
-      <c r="AQ89" s="4"/>
-      <c r="AR89" s="4"/>
-      <c r="AS89" s="4"/>
-      <c r="AT89" s="4"/>
-      <c r="AU89" s="4"/>
-      <c r="AV89" s="4"/>
-      <c r="AW89" s="4"/>
-      <c r="AX89" s="4"/>
-      <c r="AY89" s="4"/>
-      <c r="AZ89" s="4"/>
-      <c r="BA89" s="4"/>
-      <c r="BB89" s="4"/>
-      <c r="BC89" s="4"/>
-      <c r="BD89" s="4"/>
-      <c r="BE89" s="4"/>
-      <c r="BF89" s="4"/>
-      <c r="BG89" s="4"/>
-      <c r="BH89" s="4"/>
-      <c r="BI89" s="4"/>
-      <c r="BJ89" s="4"/>
-      <c r="BK89" s="4"/>
-      <c r="BL89" s="4"/>
-      <c r="BM89" s="4"/>
+      <c r="A89" s="8" t="n">
+        <v>306689</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>24895.71</v>
+      </c>
+      <c r="M89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>22256</v>
+      </c>
+      <c r="P89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="12" t="n">
+        <v>290</v>
+      </c>
+      <c r="S89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="U89" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V89" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="W89" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X89" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y89" s="12" t="n">
+        <v>2639.71</v>
+      </c>
+      <c r="Z89" s="12" t="n">
+        <v>22256</v>
+      </c>
+      <c r="AA89" s="12" t="n">
+        <v>890.23</v>
+      </c>
+      <c r="AB89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW89" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX89" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG89" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI89" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ89" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="BK89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM89" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-      <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
-      <c r="V90" s="4"/>
-      <c r="W90" s="4"/>
-      <c r="X90" s="4"/>
-      <c r="Y90" s="4"/>
-      <c r="Z90" s="4"/>
-      <c r="AA90" s="4"/>
-      <c r="AB90" s="4"/>
-      <c r="AC90" s="4"/>
-      <c r="AD90" s="4"/>
-      <c r="AE90" s="4"/>
-      <c r="AF90" s="4"/>
-      <c r="AG90" s="4"/>
-      <c r="AH90" s="4"/>
-      <c r="AI90" s="4"/>
-      <c r="AJ90" s="4"/>
-      <c r="AK90" s="4"/>
-      <c r="AL90" s="4"/>
-      <c r="AM90" s="4"/>
-      <c r="AN90" s="4"/>
-      <c r="AO90" s="4"/>
-      <c r="AP90" s="4"/>
-      <c r="AQ90" s="4"/>
-      <c r="AR90" s="4"/>
-      <c r="AS90" s="4"/>
-      <c r="AT90" s="4"/>
-      <c r="AU90" s="4"/>
-      <c r="AV90" s="4"/>
-      <c r="AW90" s="4"/>
-      <c r="AX90" s="4"/>
-      <c r="AY90" s="4"/>
-      <c r="AZ90" s="4"/>
-      <c r="BA90" s="4"/>
-      <c r="BB90" s="4"/>
-      <c r="BC90" s="4"/>
-      <c r="BD90" s="4"/>
-      <c r="BE90" s="4"/>
-      <c r="BF90" s="4"/>
-      <c r="BG90" s="4"/>
-      <c r="BH90" s="4"/>
-      <c r="BI90" s="4"/>
-      <c r="BJ90" s="4"/>
-      <c r="BK90" s="4"/>
-      <c r="BL90" s="4"/>
-      <c r="BM90" s="4"/>
+      <c r="A90" s="8" t="n">
+        <v>306690</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>181.28</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="12" t="n">
+        <v>181.28</v>
+      </c>
+      <c r="P90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="13" t="n">
+        <v>0.000444</v>
+      </c>
+      <c r="R90" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="U90" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V90" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W90" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X90" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="12" t="n">
+        <v>181.28</v>
+      </c>
+      <c r="AA90" s="12" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="AB90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW90" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX90" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG90" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI90" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ90" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="BK90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM90" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
-      <c r="X91" s="4"/>
-      <c r="Y91" s="4"/>
-      <c r="Z91" s="4"/>
-      <c r="AA91" s="4"/>
-      <c r="AB91" s="4"/>
-      <c r="AC91" s="4"/>
-      <c r="AD91" s="4"/>
-      <c r="AE91" s="4"/>
-      <c r="AF91" s="4"/>
-      <c r="AG91" s="4"/>
-      <c r="AH91" s="4"/>
-      <c r="AI91" s="4"/>
-      <c r="AJ91" s="4"/>
-      <c r="AK91" s="4"/>
-      <c r="AL91" s="4"/>
-      <c r="AM91" s="4"/>
-      <c r="AN91" s="4"/>
-      <c r="AO91" s="4"/>
-      <c r="AP91" s="4"/>
-      <c r="AQ91" s="4"/>
-      <c r="AR91" s="4"/>
-      <c r="AS91" s="4"/>
-      <c r="AT91" s="4"/>
-      <c r="AU91" s="4"/>
-      <c r="AV91" s="4"/>
-      <c r="AW91" s="4"/>
-      <c r="AX91" s="4"/>
-      <c r="AY91" s="4"/>
-      <c r="AZ91" s="4"/>
-      <c r="BA91" s="4"/>
-      <c r="BB91" s="4"/>
-      <c r="BC91" s="4"/>
-      <c r="BD91" s="4"/>
-      <c r="BE91" s="4"/>
-      <c r="BF91" s="4"/>
-      <c r="BG91" s="4"/>
-      <c r="BH91" s="4"/>
-      <c r="BI91" s="4"/>
-      <c r="BJ91" s="4"/>
-      <c r="BK91" s="4"/>
-      <c r="BL91" s="4"/>
-      <c r="BM91" s="4"/>
+      <c r="A91" s="8" t="n">
+        <v>306691</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>1772.88</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" s="12" t="n">
+        <v>1772.88</v>
+      </c>
+      <c r="P91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="13" t="n">
+        <v>0.000432</v>
+      </c>
+      <c r="R91" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="U91" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V91" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W91" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X91" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="12" t="n">
+        <v>1772.88</v>
+      </c>
+      <c r="AA91" s="12" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="AB91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW91" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX91" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG91" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI91" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ91" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="BK91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM91" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="4"/>
-      <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
-      <c r="Z92" s="4"/>
-      <c r="AA92" s="4"/>
-      <c r="AB92" s="4"/>
-      <c r="AC92" s="4"/>
-      <c r="AD92" s="4"/>
-      <c r="AE92" s="4"/>
-      <c r="AF92" s="4"/>
-      <c r="AG92" s="4"/>
-      <c r="AH92" s="4"/>
-      <c r="AI92" s="4"/>
-      <c r="AJ92" s="4"/>
-      <c r="AK92" s="4"/>
-      <c r="AL92" s="4"/>
-      <c r="AM92" s="4"/>
-      <c r="AN92" s="4"/>
-      <c r="AO92" s="4"/>
-      <c r="AP92" s="4"/>
-      <c r="AQ92" s="4"/>
-      <c r="AR92" s="4"/>
-      <c r="AS92" s="4"/>
-      <c r="AT92" s="4"/>
-      <c r="AU92" s="4"/>
-      <c r="AV92" s="4"/>
-      <c r="AW92" s="4"/>
-      <c r="AX92" s="4"/>
-      <c r="AY92" s="4"/>
-      <c r="AZ92" s="4"/>
-      <c r="BA92" s="4"/>
-      <c r="BB92" s="4"/>
-      <c r="BC92" s="4"/>
-      <c r="BD92" s="4"/>
-      <c r="BE92" s="4"/>
-      <c r="BF92" s="4"/>
-      <c r="BG92" s="4"/>
-      <c r="BH92" s="4"/>
-      <c r="BI92" s="4"/>
-      <c r="BJ92" s="4"/>
-      <c r="BK92" s="4"/>
-      <c r="BL92" s="4"/>
-      <c r="BM92" s="4"/>
+      <c r="A92" s="8" t="n">
+        <v>306698</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="K92" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <v>4467.6</v>
+      </c>
+      <c r="M92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" s="12" t="n">
+        <v>4467.6</v>
+      </c>
+      <c r="P92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="13" t="n">
+        <v>0.029904</v>
+      </c>
+      <c r="R92" s="12" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="S92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="U92" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V92" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W92" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X92" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="12" t="n">
+        <v>4467.6</v>
+      </c>
+      <c r="AA92" s="12" t="n">
+        <v>312.73</v>
+      </c>
+      <c r="AB92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW92" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX92" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF92" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG92" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI92" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ92" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="BK92" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL92" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM92" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
-      <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
-      <c r="Z93" s="4"/>
-      <c r="AA93" s="4"/>
-      <c r="AB93" s="4"/>
-      <c r="AC93" s="4"/>
-      <c r="AD93" s="4"/>
-      <c r="AE93" s="4"/>
-      <c r="AF93" s="4"/>
-      <c r="AG93" s="4"/>
-      <c r="AH93" s="4"/>
-      <c r="AI93" s="4"/>
-      <c r="AJ93" s="4"/>
-      <c r="AK93" s="4"/>
-      <c r="AL93" s="4"/>
-      <c r="AM93" s="4"/>
-      <c r="AN93" s="4"/>
-      <c r="AO93" s="4"/>
-      <c r="AP93" s="4"/>
-      <c r="AQ93" s="4"/>
-      <c r="AR93" s="4"/>
-      <c r="AS93" s="4"/>
-      <c r="AT93" s="4"/>
-      <c r="AU93" s="4"/>
-      <c r="AV93" s="4"/>
-      <c r="AW93" s="4"/>
-      <c r="AX93" s="4"/>
-      <c r="AY93" s="4"/>
-      <c r="AZ93" s="4"/>
-      <c r="BA93" s="4"/>
-      <c r="BB93" s="4"/>
-      <c r="BC93" s="4"/>
-      <c r="BD93" s="4"/>
-      <c r="BE93" s="4"/>
-      <c r="BF93" s="4"/>
-      <c r="BG93" s="4"/>
-      <c r="BH93" s="4"/>
-      <c r="BI93" s="4"/>
-      <c r="BJ93" s="4"/>
-      <c r="BK93" s="4"/>
-      <c r="BL93" s="4"/>
-      <c r="BM93" s="4"/>
+      <c r="A93" s="8" t="n">
+        <v>306700</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="K93" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L93" s="12" t="n">
+        <v>5471.63</v>
+      </c>
+      <c r="M93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" s="12" t="n">
+        <v>5471.63</v>
+      </c>
+      <c r="P93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="13" t="n">
+        <v>0.276514</v>
+      </c>
+      <c r="R93" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="S93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="U93" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V93" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="W93" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X93" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="12" t="n">
+        <v>5471.63</v>
+      </c>
+      <c r="AA93" s="12" t="n">
+        <v>656.6</v>
+      </c>
+      <c r="AB93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW93" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX93" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF93" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG93" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI93" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ93" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="BK93" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL93" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM93" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4"/>
-      <c r="W94" s="4"/>
-      <c r="X94" s="4"/>
-      <c r="Y94" s="4"/>
-      <c r="Z94" s="4"/>
-      <c r="AA94" s="4"/>
-      <c r="AB94" s="4"/>
-      <c r="AC94" s="4"/>
-      <c r="AD94" s="4"/>
-      <c r="AE94" s="4"/>
-      <c r="AF94" s="4"/>
-      <c r="AG94" s="4"/>
-      <c r="AH94" s="4"/>
-      <c r="AI94" s="4"/>
-      <c r="AJ94" s="4"/>
-      <c r="AK94" s="4"/>
-      <c r="AL94" s="4"/>
-      <c r="AM94" s="4"/>
-      <c r="AN94" s="4"/>
-      <c r="AO94" s="4"/>
-      <c r="AP94" s="4"/>
-      <c r="AQ94" s="4"/>
-      <c r="AR94" s="4"/>
-      <c r="AS94" s="4"/>
-      <c r="AT94" s="4"/>
-      <c r="AU94" s="4"/>
-      <c r="AV94" s="4"/>
-      <c r="AW94" s="4"/>
-      <c r="AX94" s="4"/>
-      <c r="AY94" s="4"/>
-      <c r="AZ94" s="4"/>
-      <c r="BA94" s="4"/>
-      <c r="BB94" s="4"/>
-      <c r="BC94" s="4"/>
-      <c r="BD94" s="4"/>
-      <c r="BE94" s="4"/>
-      <c r="BF94" s="4"/>
-      <c r="BG94" s="4"/>
-      <c r="BH94" s="4"/>
-      <c r="BI94" s="4"/>
-      <c r="BJ94" s="4"/>
-      <c r="BK94" s="4"/>
-      <c r="BL94" s="4"/>
-      <c r="BM94" s="4"/>
+      <c r="A94" s="8" t="n">
+        <v>306701</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J94" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="K94" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L94" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="M94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="P94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="13" t="n">
+        <v>0.199656</v>
+      </c>
+      <c r="R94" s="12" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="S94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="U94" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V94" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="W94" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X94" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="AA94" s="12" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="AB94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW94" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX94" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF94" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG94" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI94" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ94" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="BK94" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL94" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM94" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
-      <c r="X95" s="4"/>
-      <c r="Y95" s="4"/>
-      <c r="Z95" s="4"/>
-      <c r="AA95" s="4"/>
-      <c r="AB95" s="4"/>
-      <c r="AC95" s="4"/>
-      <c r="AD95" s="4"/>
-      <c r="AE95" s="4"/>
-      <c r="AF95" s="4"/>
-      <c r="AG95" s="4"/>
-      <c r="AH95" s="4"/>
-      <c r="AI95" s="4"/>
-      <c r="AJ95" s="4"/>
-      <c r="AK95" s="4"/>
-      <c r="AL95" s="4"/>
-      <c r="AM95" s="4"/>
-      <c r="AN95" s="4"/>
-      <c r="AO95" s="4"/>
-      <c r="AP95" s="4"/>
-      <c r="AQ95" s="4"/>
-      <c r="AR95" s="4"/>
-      <c r="AS95" s="4"/>
-      <c r="AT95" s="4"/>
-      <c r="AU95" s="4"/>
-      <c r="AV95" s="4"/>
-      <c r="AW95" s="4"/>
-      <c r="AX95" s="4"/>
-      <c r="AY95" s="4"/>
-      <c r="AZ95" s="4"/>
-      <c r="BA95" s="4"/>
-      <c r="BB95" s="4"/>
-      <c r="BC95" s="4"/>
-      <c r="BD95" s="4"/>
-      <c r="BE95" s="4"/>
-      <c r="BF95" s="4"/>
-      <c r="BG95" s="4"/>
-      <c r="BH95" s="4"/>
-      <c r="BI95" s="4"/>
-      <c r="BJ95" s="4"/>
-      <c r="BK95" s="4"/>
-      <c r="BL95" s="4"/>
-      <c r="BM95" s="4"/>
+      <c r="A95" s="8" t="n">
+        <v>306703</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="K95" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <v>22671.86</v>
+      </c>
+      <c r="M95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O95" s="12" t="n">
+        <v>21745.65</v>
+      </c>
+      <c r="P95" s="12" t="n">
+        <v>550</v>
+      </c>
+      <c r="Q95" s="13" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="R95" s="12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="S95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="U95" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V95" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="W95" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X95" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y95" s="12" t="n">
+        <v>376.21</v>
+      </c>
+      <c r="Z95" s="12" t="n">
+        <v>22295.65</v>
+      </c>
+      <c r="AA95" s="12" t="n">
+        <v>1560.7</v>
+      </c>
+      <c r="AB95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW95" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX95" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF95" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG95" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI95" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ95" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="BK95" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL95" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM95" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4"/>
-      <c r="W96" s="4"/>
-      <c r="X96" s="4"/>
-      <c r="Y96" s="4"/>
-      <c r="Z96" s="4"/>
-      <c r="AA96" s="4"/>
-      <c r="AB96" s="4"/>
-      <c r="AC96" s="4"/>
-      <c r="AD96" s="4"/>
-      <c r="AE96" s="4"/>
-      <c r="AF96" s="4"/>
-      <c r="AG96" s="4"/>
-      <c r="AH96" s="4"/>
-      <c r="AI96" s="4"/>
-      <c r="AJ96" s="4"/>
-      <c r="AK96" s="4"/>
-      <c r="AL96" s="4"/>
-      <c r="AM96" s="4"/>
-      <c r="AN96" s="4"/>
-      <c r="AO96" s="4"/>
-      <c r="AP96" s="4"/>
-      <c r="AQ96" s="4"/>
-      <c r="AR96" s="4"/>
-      <c r="AS96" s="4"/>
-      <c r="AT96" s="4"/>
-      <c r="AU96" s="4"/>
-      <c r="AV96" s="4"/>
-      <c r="AW96" s="4"/>
-      <c r="AX96" s="4"/>
-      <c r="AY96" s="4"/>
-      <c r="AZ96" s="4"/>
-      <c r="BA96" s="4"/>
-      <c r="BB96" s="4"/>
-      <c r="BC96" s="4"/>
-      <c r="BD96" s="4"/>
-      <c r="BE96" s="4"/>
-      <c r="BF96" s="4"/>
-      <c r="BG96" s="4"/>
-      <c r="BH96" s="4"/>
-      <c r="BI96" s="4"/>
-      <c r="BJ96" s="4"/>
-      <c r="BK96" s="4"/>
-      <c r="BL96" s="4"/>
-      <c r="BM96" s="4"/>
+      <c r="A96" s="8" t="n">
+        <v>306712</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L96" s="12" t="n">
+        <v>278.41</v>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" s="12" t="n">
+        <v>278.41</v>
+      </c>
+      <c r="P96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="13" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="R96" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="U96" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X96" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="12" t="n">
+        <v>278.41</v>
+      </c>
+      <c r="AA96" s="12" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="AB96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW96" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX96" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF96" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG96" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI96" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ96" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="BK96" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL96" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM96" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8" t="n">
+        <v>306714</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K97" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>567.53</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" s="12" t="n">
+        <v>567.53</v>
+      </c>
+      <c r="P97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="13" t="n">
+        <v>0.08136</v>
+      </c>
+      <c r="R97" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="S97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="U97" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X97" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="12" t="n">
+        <v>567.53</v>
+      </c>
+      <c r="AA97" s="12" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="AB97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW97" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX97" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF97" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG97" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI97" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ97" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="BK97" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL97" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM97" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="8" t="n">
+        <v>306715</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J98" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K98" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>814.81</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" s="12" t="n">
+        <v>814.81</v>
+      </c>
+      <c r="P98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="13" t="n">
+        <v>0.034656</v>
+      </c>
+      <c r="R98" s="12" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="S98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="U98" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X98" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="12" t="n">
+        <v>814.81</v>
+      </c>
+      <c r="AA98" s="12" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="AB98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW98" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX98" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF98" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG98" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI98" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ98" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="BK98" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL98" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM98" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8" t="n">
+        <v>306717</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K99" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>1070.58</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" s="12" t="n">
+        <v>1070.58</v>
+      </c>
+      <c r="P99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="13" t="n">
+        <v>0.095984</v>
+      </c>
+      <c r="R99" s="12" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="S99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="U99" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X99" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="12" t="n">
+        <v>1070.58</v>
+      </c>
+      <c r="AA99" s="12" t="n">
+        <v>74.94</v>
+      </c>
+      <c r="AB99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW99" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX99" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF99" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG99" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI99" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ99" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="BK99" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL99" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM99" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8" t="n">
+        <v>306734</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="K100" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>1773.17</v>
+      </c>
+      <c r="M100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O100" s="12" t="n">
+        <v>1664.94</v>
+      </c>
+      <c r="P100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="U100" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V100" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="W100" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X100" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y100" s="12" t="n">
+        <v>108.23</v>
+      </c>
+      <c r="Z100" s="12" t="n">
+        <v>1664.94</v>
+      </c>
+      <c r="AA100" s="12" t="n">
+        <v>116.54</v>
+      </c>
+      <c r="AB100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV100" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW100" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX100" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF100" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG100" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH100" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI100" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ100" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="BK100" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL100" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM100" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8" t="n">
+        <v>306735</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J101" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K101" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>2666.87</v>
+      </c>
+      <c r="M101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" s="12" t="n">
+        <v>2352.5</v>
+      </c>
+      <c r="P101" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q101" s="13" t="n">
+        <v>0.05513</v>
+      </c>
+      <c r="R101" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="U101" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V101" s="12" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="W101" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X101" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y101" s="12" t="n">
+        <v>229.37</v>
+      </c>
+      <c r="Z101" s="12" t="n">
+        <v>2437.5</v>
+      </c>
+      <c r="AA101" s="12" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AB101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW101" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX101" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF101" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG101" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH101" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI101" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ101" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="BK101" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL101" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM101" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B103" s="17"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="17"/>
+      <c r="G103" s="17"/>
+      <c r="H103" s="17"/>
+      <c r="I103" s="17"/>
+      <c r="J103" s="17"/>
+      <c r="K103" s="17"/>
+      <c r="L103" s="17"/>
+      <c r="M103" s="17"/>
+      <c r="N103" s="17"/>
+      <c r="O103" s="17"/>
+      <c r="P103" s="17"/>
+      <c r="Q103" s="17"/>
+      <c r="R103" s="17"/>
+      <c r="S103" s="17"/>
+      <c r="T103" s="17"/>
+      <c r="U103" s="17"/>
+      <c r="V103" s="17"/>
+    </row>
+    <row r="104" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="B104" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H104" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I104" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="J104" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K104" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L104" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M104" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="N104" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O104" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P104" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q104" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R104" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S104" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="T104" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="U104" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V104" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="19" t="n">
+        <v>97</v>
+      </c>
+      <c r="B105" s="19" t="n">
+        <v>838.8</v>
+      </c>
+      <c r="C105" s="19" t="n">
+        <v>635</v>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E105" s="19" t="n">
+        <v>7415.49</v>
+      </c>
+      <c r="F105" s="19" t="n">
+        <v>400705.34</v>
+      </c>
+      <c r="G105" s="19" t="n">
+        <v>24415.52</v>
+      </c>
+      <c r="H105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="19" t="n">
+        <v>408120.83</v>
+      </c>
+      <c r="L105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="20" t="n">
+        <v>33.024979</v>
+      </c>
+      <c r="S105" s="19" t="n">
+        <v>400809.14</v>
+      </c>
+      <c r="T105" s="19" t="n">
+        <v>408120.83</v>
+      </c>
+      <c r="U105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B106" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C106" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F106" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G106" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H106" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I106" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J106" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K106" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="L106" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="M106" s="18" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="19" t="n">
+        <v>5719.07</v>
+      </c>
+      <c r="B107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="19" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="E107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="B109" s="21"/>
+      <c r="C109" s="21"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="21"/>
+      <c r="G109" s="21"/>
+      <c r="H109" s="21"/>
+      <c r="I109" s="21"/>
+      <c r="J109" s="21"/>
+      <c r="K109" s="21"/>
+      <c r="L109" s="21"/>
+      <c r="M109" s="21"/>
+      <c r="N109" s="21"/>
+      <c r="O109" s="21"/>
+      <c r="P109" s="21"/>
+      <c r="Q109" s="21"/>
+      <c r="R109" s="21"/>
+      <c r="S109" s="21"/>
+      <c r="T109" s="21"/>
+      <c r="U109" s="21"/>
+      <c r="V109" s="21"/>
+      <c r="W109" s="21"/>
+      <c r="X109" s="21"/>
+      <c r="Y109" s="21"/>
+      <c r="Z109" s="21"/>
+      <c r="AA109" s="21"/>
+      <c r="AB109" s="21"/>
+      <c r="AC109" s="21"/>
+      <c r="AD109" s="21"/>
+      <c r="AE109" s="21"/>
+      <c r="AF109" s="21"/>
+      <c r="AG109" s="21"/>
+      <c r="AH109" s="21"/>
+      <c r="AI109" s="21"/>
+      <c r="AJ109" s="21"/>
+      <c r="AK109" s="21"/>
+      <c r="AL109" s="21"/>
+      <c r="AM109" s="21"/>
+      <c r="AN109" s="21"/>
+      <c r="AO109" s="21"/>
+      <c r="AP109" s="21"/>
+      <c r="AQ109" s="21"/>
+      <c r="AR109" s="21"/>
+      <c r="AS109" s="21"/>
+      <c r="AT109" s="21"/>
+      <c r="AU109" s="21"/>
+      <c r="AV109" s="21"/>
+      <c r="AW109" s="21"/>
+      <c r="AX109" s="21"/>
+      <c r="AY109" s="21"/>
+      <c r="AZ109" s="21"/>
+      <c r="BA109" s="21"/>
+      <c r="BB109" s="21"/>
+      <c r="BC109" s="21"/>
+      <c r="BD109" s="21"/>
+      <c r="BE109" s="21"/>
+      <c r="BF109" s="21"/>
+      <c r="BG109" s="21"/>
+      <c r="BH109" s="21"/>
+      <c r="BI109" s="21"/>
+      <c r="BJ109" s="21"/>
+      <c r="BK109" s="21"/>
+      <c r="BL109" s="21"/>
+      <c r="BM109" s="21"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4"/>
+      <c r="S110" s="4"/>
+      <c r="T110" s="4"/>
+      <c r="U110" s="4"/>
+      <c r="V110" s="4"/>
+      <c r="W110" s="4"/>
+      <c r="X110" s="4"/>
+      <c r="Y110" s="4"/>
+      <c r="Z110" s="4"/>
+      <c r="AA110" s="4"/>
+      <c r="AB110" s="4"/>
+      <c r="AC110" s="4"/>
+      <c r="AD110" s="4"/>
+      <c r="AE110" s="4"/>
+      <c r="AF110" s="4"/>
+      <c r="AG110" s="4"/>
+      <c r="AH110" s="4"/>
+      <c r="AI110" s="4"/>
+      <c r="AJ110" s="4"/>
+      <c r="AK110" s="4"/>
+      <c r="AL110" s="4"/>
+      <c r="AM110" s="4"/>
+      <c r="AN110" s="4"/>
+      <c r="AO110" s="4"/>
+      <c r="AP110" s="4"/>
+      <c r="AQ110" s="4"/>
+      <c r="AR110" s="4"/>
+      <c r="AS110" s="4"/>
+      <c r="AT110" s="4"/>
+      <c r="AU110" s="4"/>
+      <c r="AV110" s="4"/>
+      <c r="AW110" s="4"/>
+      <c r="AX110" s="4"/>
+      <c r="AY110" s="4"/>
+      <c r="AZ110" s="4"/>
+      <c r="BA110" s="4"/>
+      <c r="BB110" s="4"/>
+      <c r="BC110" s="4"/>
+      <c r="BD110" s="4"/>
+      <c r="BE110" s="4"/>
+      <c r="BF110" s="4"/>
+      <c r="BG110" s="4"/>
+      <c r="BH110" s="4"/>
+      <c r="BI110" s="4"/>
+      <c r="BJ110" s="4"/>
+      <c r="BK110" s="4"/>
+      <c r="BL110" s="4"/>
+      <c r="BM110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4"/>
+      <c r="S111" s="4"/>
+      <c r="T111" s="4"/>
+      <c r="U111" s="4"/>
+      <c r="V111" s="4"/>
+      <c r="W111" s="4"/>
+      <c r="X111" s="4"/>
+      <c r="Y111" s="4"/>
+      <c r="Z111" s="4"/>
+      <c r="AA111" s="4"/>
+      <c r="AB111" s="4"/>
+      <c r="AC111" s="4"/>
+      <c r="AD111" s="4"/>
+      <c r="AE111" s="4"/>
+      <c r="AF111" s="4"/>
+      <c r="AG111" s="4"/>
+      <c r="AH111" s="4"/>
+      <c r="AI111" s="4"/>
+      <c r="AJ111" s="4"/>
+      <c r="AK111" s="4"/>
+      <c r="AL111" s="4"/>
+      <c r="AM111" s="4"/>
+      <c r="AN111" s="4"/>
+      <c r="AO111" s="4"/>
+      <c r="AP111" s="4"/>
+      <c r="AQ111" s="4"/>
+      <c r="AR111" s="4"/>
+      <c r="AS111" s="4"/>
+      <c r="AT111" s="4"/>
+      <c r="AU111" s="4"/>
+      <c r="AV111" s="4"/>
+      <c r="AW111" s="4"/>
+      <c r="AX111" s="4"/>
+      <c r="AY111" s="4"/>
+      <c r="AZ111" s="4"/>
+      <c r="BA111" s="4"/>
+      <c r="BB111" s="4"/>
+      <c r="BC111" s="4"/>
+      <c r="BD111" s="4"/>
+      <c r="BE111" s="4"/>
+      <c r="BF111" s="4"/>
+      <c r="BG111" s="4"/>
+      <c r="BH111" s="4"/>
+      <c r="BI111" s="4"/>
+      <c r="BJ111" s="4"/>
+      <c r="BK111" s="4"/>
+      <c r="BL111" s="4"/>
+      <c r="BM111" s="4"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="4"/>
+      <c r="R112" s="4"/>
+      <c r="S112" s="4"/>
+      <c r="T112" s="4"/>
+      <c r="U112" s="4"/>
+      <c r="V112" s="4"/>
+      <c r="W112" s="4"/>
+      <c r="X112" s="4"/>
+      <c r="Y112" s="4"/>
+      <c r="Z112" s="4"/>
+      <c r="AA112" s="4"/>
+      <c r="AB112" s="4"/>
+      <c r="AC112" s="4"/>
+      <c r="AD112" s="4"/>
+      <c r="AE112" s="4"/>
+      <c r="AF112" s="4"/>
+      <c r="AG112" s="4"/>
+      <c r="AH112" s="4"/>
+      <c r="AI112" s="4"/>
+      <c r="AJ112" s="4"/>
+      <c r="AK112" s="4"/>
+      <c r="AL112" s="4"/>
+      <c r="AM112" s="4"/>
+      <c r="AN112" s="4"/>
+      <c r="AO112" s="4"/>
+      <c r="AP112" s="4"/>
+      <c r="AQ112" s="4"/>
+      <c r="AR112" s="4"/>
+      <c r="AS112" s="4"/>
+      <c r="AT112" s="4"/>
+      <c r="AU112" s="4"/>
+      <c r="AV112" s="4"/>
+      <c r="AW112" s="4"/>
+      <c r="AX112" s="4"/>
+      <c r="AY112" s="4"/>
+      <c r="AZ112" s="4"/>
+      <c r="BA112" s="4"/>
+      <c r="BB112" s="4"/>
+      <c r="BC112" s="4"/>
+      <c r="BD112" s="4"/>
+      <c r="BE112" s="4"/>
+      <c r="BF112" s="4"/>
+      <c r="BG112" s="4"/>
+      <c r="BH112" s="4"/>
+      <c r="BI112" s="4"/>
+      <c r="BJ112" s="4"/>
+      <c r="BK112" s="4"/>
+      <c r="BL112" s="4"/>
+      <c r="BM112" s="4"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="4"/>
+      <c r="S113" s="4"/>
+      <c r="T113" s="4"/>
+      <c r="U113" s="4"/>
+      <c r="V113" s="4"/>
+      <c r="W113" s="4"/>
+      <c r="X113" s="4"/>
+      <c r="Y113" s="4"/>
+      <c r="Z113" s="4"/>
+      <c r="AA113" s="4"/>
+      <c r="AB113" s="4"/>
+      <c r="AC113" s="4"/>
+      <c r="AD113" s="4"/>
+      <c r="AE113" s="4"/>
+      <c r="AF113" s="4"/>
+      <c r="AG113" s="4"/>
+      <c r="AH113" s="4"/>
+      <c r="AI113" s="4"/>
+      <c r="AJ113" s="4"/>
+      <c r="AK113" s="4"/>
+      <c r="AL113" s="4"/>
+      <c r="AM113" s="4"/>
+      <c r="AN113" s="4"/>
+      <c r="AO113" s="4"/>
+      <c r="AP113" s="4"/>
+      <c r="AQ113" s="4"/>
+      <c r="AR113" s="4"/>
+      <c r="AS113" s="4"/>
+      <c r="AT113" s="4"/>
+      <c r="AU113" s="4"/>
+      <c r="AV113" s="4"/>
+      <c r="AW113" s="4"/>
+      <c r="AX113" s="4"/>
+      <c r="AY113" s="4"/>
+      <c r="AZ113" s="4"/>
+      <c r="BA113" s="4"/>
+      <c r="BB113" s="4"/>
+      <c r="BC113" s="4"/>
+      <c r="BD113" s="4"/>
+      <c r="BE113" s="4"/>
+      <c r="BF113" s="4"/>
+      <c r="BG113" s="4"/>
+      <c r="BH113" s="4"/>
+      <c r="BI113" s="4"/>
+      <c r="BJ113" s="4"/>
+      <c r="BK113" s="4"/>
+      <c r="BL113" s="4"/>
+      <c r="BM113" s="4"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="4"/>
+      <c r="S114" s="4"/>
+      <c r="T114" s="4"/>
+      <c r="U114" s="4"/>
+      <c r="V114" s="4"/>
+      <c r="W114" s="4"/>
+      <c r="X114" s="4"/>
+      <c r="Y114" s="4"/>
+      <c r="Z114" s="4"/>
+      <c r="AA114" s="4"/>
+      <c r="AB114" s="4"/>
+      <c r="AC114" s="4"/>
+      <c r="AD114" s="4"/>
+      <c r="AE114" s="4"/>
+      <c r="AF114" s="4"/>
+      <c r="AG114" s="4"/>
+      <c r="AH114" s="4"/>
+      <c r="AI114" s="4"/>
+      <c r="AJ114" s="4"/>
+      <c r="AK114" s="4"/>
+      <c r="AL114" s="4"/>
+      <c r="AM114" s="4"/>
+      <c r="AN114" s="4"/>
+      <c r="AO114" s="4"/>
+      <c r="AP114" s="4"/>
+      <c r="AQ114" s="4"/>
+      <c r="AR114" s="4"/>
+      <c r="AS114" s="4"/>
+      <c r="AT114" s="4"/>
+      <c r="AU114" s="4"/>
+      <c r="AV114" s="4"/>
+      <c r="AW114" s="4"/>
+      <c r="AX114" s="4"/>
+      <c r="AY114" s="4"/>
+      <c r="AZ114" s="4"/>
+      <c r="BA114" s="4"/>
+      <c r="BB114" s="4"/>
+      <c r="BC114" s="4"/>
+      <c r="BD114" s="4"/>
+      <c r="BE114" s="4"/>
+      <c r="BF114" s="4"/>
+      <c r="BG114" s="4"/>
+      <c r="BH114" s="4"/>
+      <c r="BI114" s="4"/>
+      <c r="BJ114" s="4"/>
+      <c r="BK114" s="4"/>
+      <c r="BL114" s="4"/>
+      <c r="BM114" s="4"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4"/>
+      <c r="S115" s="4"/>
+      <c r="T115" s="4"/>
+      <c r="U115" s="4"/>
+      <c r="V115" s="4"/>
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="4"/>
+      <c r="Z115" s="4"/>
+      <c r="AA115" s="4"/>
+      <c r="AB115" s="4"/>
+      <c r="AC115" s="4"/>
+      <c r="AD115" s="4"/>
+      <c r="AE115" s="4"/>
+      <c r="AF115" s="4"/>
+      <c r="AG115" s="4"/>
+      <c r="AH115" s="4"/>
+      <c r="AI115" s="4"/>
+      <c r="AJ115" s="4"/>
+      <c r="AK115" s="4"/>
+      <c r="AL115" s="4"/>
+      <c r="AM115" s="4"/>
+      <c r="AN115" s="4"/>
+      <c r="AO115" s="4"/>
+      <c r="AP115" s="4"/>
+      <c r="AQ115" s="4"/>
+      <c r="AR115" s="4"/>
+      <c r="AS115" s="4"/>
+      <c r="AT115" s="4"/>
+      <c r="AU115" s="4"/>
+      <c r="AV115" s="4"/>
+      <c r="AW115" s="4"/>
+      <c r="AX115" s="4"/>
+      <c r="AY115" s="4"/>
+      <c r="AZ115" s="4"/>
+      <c r="BA115" s="4"/>
+      <c r="BB115" s="4"/>
+      <c r="BC115" s="4"/>
+      <c r="BD115" s="4"/>
+      <c r="BE115" s="4"/>
+      <c r="BF115" s="4"/>
+      <c r="BG115" s="4"/>
+      <c r="BH115" s="4"/>
+      <c r="BI115" s="4"/>
+      <c r="BJ115" s="4"/>
+      <c r="BK115" s="4"/>
+      <c r="BL115" s="4"/>
+      <c r="BM115" s="4"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="4"/>
+      <c r="S116" s="4"/>
+      <c r="T116" s="4"/>
+      <c r="U116" s="4"/>
+      <c r="V116" s="4"/>
+      <c r="W116" s="4"/>
+      <c r="X116" s="4"/>
+      <c r="Y116" s="4"/>
+      <c r="Z116" s="4"/>
+      <c r="AA116" s="4"/>
+      <c r="AB116" s="4"/>
+      <c r="AC116" s="4"/>
+      <c r="AD116" s="4"/>
+      <c r="AE116" s="4"/>
+      <c r="AF116" s="4"/>
+      <c r="AG116" s="4"/>
+      <c r="AH116" s="4"/>
+      <c r="AI116" s="4"/>
+      <c r="AJ116" s="4"/>
+      <c r="AK116" s="4"/>
+      <c r="AL116" s="4"/>
+      <c r="AM116" s="4"/>
+      <c r="AN116" s="4"/>
+      <c r="AO116" s="4"/>
+      <c r="AP116" s="4"/>
+      <c r="AQ116" s="4"/>
+      <c r="AR116" s="4"/>
+      <c r="AS116" s="4"/>
+      <c r="AT116" s="4"/>
+      <c r="AU116" s="4"/>
+      <c r="AV116" s="4"/>
+      <c r="AW116" s="4"/>
+      <c r="AX116" s="4"/>
+      <c r="AY116" s="4"/>
+      <c r="AZ116" s="4"/>
+      <c r="BA116" s="4"/>
+      <c r="BB116" s="4"/>
+      <c r="BC116" s="4"/>
+      <c r="BD116" s="4"/>
+      <c r="BE116" s="4"/>
+      <c r="BF116" s="4"/>
+      <c r="BG116" s="4"/>
+      <c r="BH116" s="4"/>
+      <c r="BI116" s="4"/>
+      <c r="BJ116" s="4"/>
+      <c r="BK116" s="4"/>
+      <c r="BL116" s="4"/>
+      <c r="BM116" s="4"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="4"/>
+      <c r="R117" s="4"/>
+      <c r="S117" s="4"/>
+      <c r="T117" s="4"/>
+      <c r="U117" s="4"/>
+      <c r="V117" s="4"/>
+      <c r="W117" s="4"/>
+      <c r="X117" s="4"/>
+      <c r="Y117" s="4"/>
+      <c r="Z117" s="4"/>
+      <c r="AA117" s="4"/>
+      <c r="AB117" s="4"/>
+      <c r="AC117" s="4"/>
+      <c r="AD117" s="4"/>
+      <c r="AE117" s="4"/>
+      <c r="AF117" s="4"/>
+      <c r="AG117" s="4"/>
+      <c r="AH117" s="4"/>
+      <c r="AI117" s="4"/>
+      <c r="AJ117" s="4"/>
+      <c r="AK117" s="4"/>
+      <c r="AL117" s="4"/>
+      <c r="AM117" s="4"/>
+      <c r="AN117" s="4"/>
+      <c r="AO117" s="4"/>
+      <c r="AP117" s="4"/>
+      <c r="AQ117" s="4"/>
+      <c r="AR117" s="4"/>
+      <c r="AS117" s="4"/>
+      <c r="AT117" s="4"/>
+      <c r="AU117" s="4"/>
+      <c r="AV117" s="4"/>
+      <c r="AW117" s="4"/>
+      <c r="AX117" s="4"/>
+      <c r="AY117" s="4"/>
+      <c r="AZ117" s="4"/>
+      <c r="BA117" s="4"/>
+      <c r="BB117" s="4"/>
+      <c r="BC117" s="4"/>
+      <c r="BD117" s="4"/>
+      <c r="BE117" s="4"/>
+      <c r="BF117" s="4"/>
+      <c r="BG117" s="4"/>
+      <c r="BH117" s="4"/>
+      <c r="BI117" s="4"/>
+      <c r="BJ117" s="4"/>
+      <c r="BK117" s="4"/>
+      <c r="BL117" s="4"/>
+      <c r="BM117" s="4"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="4"/>
+      <c r="S118" s="4"/>
+      <c r="T118" s="4"/>
+      <c r="U118" s="4"/>
+      <c r="V118" s="4"/>
+      <c r="W118" s="4"/>
+      <c r="X118" s="4"/>
+      <c r="Y118" s="4"/>
+      <c r="Z118" s="4"/>
+      <c r="AA118" s="4"/>
+      <c r="AB118" s="4"/>
+      <c r="AC118" s="4"/>
+      <c r="AD118" s="4"/>
+      <c r="AE118" s="4"/>
+      <c r="AF118" s="4"/>
+      <c r="AG118" s="4"/>
+      <c r="AH118" s="4"/>
+      <c r="AI118" s="4"/>
+      <c r="AJ118" s="4"/>
+      <c r="AK118" s="4"/>
+      <c r="AL118" s="4"/>
+      <c r="AM118" s="4"/>
+      <c r="AN118" s="4"/>
+      <c r="AO118" s="4"/>
+      <c r="AP118" s="4"/>
+      <c r="AQ118" s="4"/>
+      <c r="AR118" s="4"/>
+      <c r="AS118" s="4"/>
+      <c r="AT118" s="4"/>
+      <c r="AU118" s="4"/>
+      <c r="AV118" s="4"/>
+      <c r="AW118" s="4"/>
+      <c r="AX118" s="4"/>
+      <c r="AY118" s="4"/>
+      <c r="AZ118" s="4"/>
+      <c r="BA118" s="4"/>
+      <c r="BB118" s="4"/>
+      <c r="BC118" s="4"/>
+      <c r="BD118" s="4"/>
+      <c r="BE118" s="4"/>
+      <c r="BF118" s="4"/>
+      <c r="BG118" s="4"/>
+      <c r="BH118" s="4"/>
+      <c r="BI118" s="4"/>
+      <c r="BJ118" s="4"/>
+      <c r="BK118" s="4"/>
+      <c r="BL118" s="4"/>
+      <c r="BM118" s="4"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4"/>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="4"/>
+      <c r="S119" s="4"/>
+      <c r="T119" s="4"/>
+      <c r="U119" s="4"/>
+      <c r="V119" s="4"/>
+      <c r="W119" s="4"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="4"/>
+      <c r="AA119" s="4"/>
+      <c r="AB119" s="4"/>
+      <c r="AC119" s="4"/>
+      <c r="AD119" s="4"/>
+      <c r="AE119" s="4"/>
+      <c r="AF119" s="4"/>
+      <c r="AG119" s="4"/>
+      <c r="AH119" s="4"/>
+      <c r="AI119" s="4"/>
+      <c r="AJ119" s="4"/>
+      <c r="AK119" s="4"/>
+      <c r="AL119" s="4"/>
+      <c r="AM119" s="4"/>
+      <c r="AN119" s="4"/>
+      <c r="AO119" s="4"/>
+      <c r="AP119" s="4"/>
+      <c r="AQ119" s="4"/>
+      <c r="AR119" s="4"/>
+      <c r="AS119" s="4"/>
+      <c r="AT119" s="4"/>
+      <c r="AU119" s="4"/>
+      <c r="AV119" s="4"/>
+      <c r="AW119" s="4"/>
+      <c r="AX119" s="4"/>
+      <c r="AY119" s="4"/>
+      <c r="AZ119" s="4"/>
+      <c r="BA119" s="4"/>
+      <c r="BB119" s="4"/>
+      <c r="BC119" s="4"/>
+      <c r="BD119" s="4"/>
+      <c r="BE119" s="4"/>
+      <c r="BF119" s="4"/>
+      <c r="BG119" s="4"/>
+      <c r="BH119" s="4"/>
+      <c r="BI119" s="4"/>
+      <c r="BJ119" s="4"/>
+      <c r="BK119" s="4"/>
+      <c r="BL119" s="4"/>
+      <c r="BM119" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="90">
+  <mergeCells count="113">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -32875,18 +37511,41 @@
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B78:E78"/>
-    <mergeCell ref="A80:V80"/>
-    <mergeCell ref="A86:BM86"/>
-    <mergeCell ref="A87:BM87"/>
-    <mergeCell ref="A88:BM88"/>
-    <mergeCell ref="A89:BM89"/>
-    <mergeCell ref="A90:BM90"/>
-    <mergeCell ref="A91:BM91"/>
-    <mergeCell ref="A92:BM92"/>
-    <mergeCell ref="A93:BM93"/>
-    <mergeCell ref="A94:BM94"/>
-    <mergeCell ref="A95:BM95"/>
-    <mergeCell ref="A96:BM96"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="A103:V103"/>
+    <mergeCell ref="A109:BM109"/>
+    <mergeCell ref="A110:BM110"/>
+    <mergeCell ref="A111:BM111"/>
+    <mergeCell ref="A112:BM112"/>
+    <mergeCell ref="A113:BM113"/>
+    <mergeCell ref="A114:BM114"/>
+    <mergeCell ref="A115:BM115"/>
+    <mergeCell ref="A116:BM116"/>
+    <mergeCell ref="A117:BM117"/>
+    <mergeCell ref="A118:BM118"/>
+    <mergeCell ref="A119:BM119"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3072" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3592" uniqueCount="424">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 14/05/2026 07:28:18</t>
+    <t xml:space="preserve">Emitido em: 15/05/2026 07:59:54</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -1100,6 +1100,141 @@
   </si>
   <si>
     <t xml:space="preserve">42260535635346000140550020001121781534580370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.119,25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006394171502977260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.850 - DEXCO S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.720,43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - FILIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260597837181005378550010001623201200486876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">446,07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829781228464036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">273,43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829771206775953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.209,61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829971596208423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.083.076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050830761221787698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.727,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260524546165000393550040000981601962020810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.783,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006396901908194720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.967,67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006397081888143897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">817.980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.957,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260579416459000120550010008179801823855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">506,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007578201370188640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.023,78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006399571193331798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.206,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260510691158000370550010002932181828516528</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17345,7 +17480,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM96"/>
+  <dimension ref="A1:BM109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -31850,1016 +31985,3499 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4"/>
+      <c r="A79" s="8" t="n">
+        <v>307296</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>4119.25</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="12" t="n">
+        <v>4119.25</v>
+      </c>
+      <c r="P79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="13" t="n">
+        <v>0.55013</v>
+      </c>
+      <c r="R79" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="U79" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X79" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="12" t="n">
+        <v>4119.25</v>
+      </c>
+      <c r="AA79" s="12" t="n">
+        <v>164.77</v>
+      </c>
+      <c r="AB79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW79" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX79" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF79" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG79" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI79" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ79" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="BK79" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL79" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM79" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="80" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="17"/>
-      <c r="M80" s="17"/>
-      <c r="N80" s="17"/>
-      <c r="O80" s="17"/>
-      <c r="P80" s="17"/>
-      <c r="Q80" s="17"/>
-      <c r="R80" s="17"/>
-      <c r="S80" s="17"/>
-      <c r="T80" s="17"/>
-      <c r="U80" s="17"/>
-      <c r="V80" s="17"/>
+    <row r="80" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="n">
+        <v>307309</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L80" s="12" t="n">
+        <v>1720.43</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="12" t="n">
+        <v>1720.43</v>
+      </c>
+      <c r="P80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="12" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="S80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="U80" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="X80" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="12" t="n">
+        <v>1720.43</v>
+      </c>
+      <c r="AA80" s="12" t="n">
+        <v>120.43</v>
+      </c>
+      <c r="AB80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW80" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX80" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG80" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI80" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ80" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="BK80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM80" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="81" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="18" t="s">
+    <row r="81" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="n">
+        <v>307311</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I81" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="B81" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="E81" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F81" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I81" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="J81" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K81" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L81" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M81" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="N81" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O81" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P81" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q81" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R81" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S81" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="T81" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="U81" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V81" s="18" t="s">
-        <v>37</v>
+      <c r="J81" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L81" s="12" t="n">
+        <v>446.07</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" s="12" t="n">
+        <v>418.84</v>
+      </c>
+      <c r="P81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="13" t="n">
+        <v>0.134454</v>
+      </c>
+      <c r="R81" s="12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="S81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="U81" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V81" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W81" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X81" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y81" s="12" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="Z81" s="12" t="n">
+        <v>418.84</v>
+      </c>
+      <c r="AA81" s="12" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="AB81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW81" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX81" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG81" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI81" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ81" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="BK81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM81" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="19" t="n">
-        <v>74</v>
-      </c>
-      <c r="B82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E82" s="19" t="n">
-        <v>12910.57</v>
-      </c>
-      <c r="F82" s="19" t="n">
-        <v>280532.35</v>
-      </c>
-      <c r="G82" s="19" t="n">
-        <v>15886.61</v>
-      </c>
-      <c r="H82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="19" t="n">
-        <v>89.72</v>
-      </c>
-      <c r="K82" s="19" t="n">
-        <v>293442.92</v>
-      </c>
-      <c r="L82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="20" t="n">
-        <v>32.83966</v>
-      </c>
-      <c r="S82" s="19" t="n">
-        <v>280432.35</v>
-      </c>
-      <c r="T82" s="19" t="n">
-        <v>293442.92</v>
-      </c>
-      <c r="U82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="19" t="n">
-        <v>0</v>
+      <c r="A82" s="8" t="n">
+        <v>307312</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L82" s="12" t="n">
+        <v>273.43</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="12" t="n">
+        <v>256.74</v>
+      </c>
+      <c r="P82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="13" t="n">
+        <v>0.14364</v>
+      </c>
+      <c r="R82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="U82" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V82" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W82" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X82" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y82" s="12" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="Z82" s="12" t="n">
+        <v>256.74</v>
+      </c>
+      <c r="AA82" s="12" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="AB82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW82" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX82" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG82" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI82" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ82" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="BK82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM82" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B83" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F83" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G83" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I83" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J83" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K83" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="L83" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="M83" s="18" t="s">
-        <v>369</v>
+    <row r="83" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="8" t="n">
+        <v>307313</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <v>4209.61</v>
+      </c>
+      <c r="M83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O83" s="12" t="n">
+        <v>3952.68</v>
+      </c>
+      <c r="P83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="13" t="n">
+        <v>0.471828</v>
+      </c>
+      <c r="R83" s="12" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="S83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="U83" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X83" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y83" s="12" t="n">
+        <v>256.93</v>
+      </c>
+      <c r="Z83" s="12" t="n">
+        <v>3952.68</v>
+      </c>
+      <c r="AA83" s="12" t="n">
+        <v>158.11</v>
+      </c>
+      <c r="AB83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW83" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX83" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG83" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI83" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ83" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="BK83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM83" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="19" t="n">
-        <v>3107.36</v>
-      </c>
-      <c r="B84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="19" t="n">
-        <v>45.12</v>
-      </c>
-      <c r="E84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="19" t="n">
-        <v>0</v>
+      <c r="A84" s="8" t="n">
+        <v>307314</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>501.26</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" s="12" t="n">
+        <v>470.66</v>
+      </c>
+      <c r="P84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="13" t="n">
+        <v>0.123032</v>
+      </c>
+      <c r="R84" s="12" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="S84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="U84" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W84" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X84" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y84" s="12" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Z84" s="12" t="n">
+        <v>470.66</v>
+      </c>
+      <c r="AA84" s="12" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="AB84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW84" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX84" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG84" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI84" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ84" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="BK84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM84" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4"/>
+      <c r="A85" s="8" t="n">
+        <v>307317</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>1727.12</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <v>1573.69</v>
+      </c>
+      <c r="P85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="U85" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V85" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W85" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X85" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y85" s="12" t="n">
+        <v>153.43</v>
+      </c>
+      <c r="Z85" s="12" t="n">
+        <v>1573.69</v>
+      </c>
+      <c r="AA85" s="12" t="n">
+        <v>110.16</v>
+      </c>
+      <c r="AB85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW85" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX85" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG85" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI85" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ85" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="BK85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM85" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="86" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="B86" s="21"/>
-      <c r="C86" s="21"/>
-      <c r="D86" s="21"/>
-      <c r="E86" s="21"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21"/>
-      <c r="K86" s="21"/>
-      <c r="L86" s="21"/>
-      <c r="M86" s="21"/>
-      <c r="N86" s="21"/>
-      <c r="O86" s="21"/>
-      <c r="P86" s="21"/>
-      <c r="Q86" s="21"/>
-      <c r="R86" s="21"/>
-      <c r="S86" s="21"/>
-      <c r="T86" s="21"/>
-      <c r="U86" s="21"/>
-      <c r="V86" s="21"/>
-      <c r="W86" s="21"/>
-      <c r="X86" s="21"/>
-      <c r="Y86" s="21"/>
-      <c r="Z86" s="21"/>
-      <c r="AA86" s="21"/>
-      <c r="AB86" s="21"/>
-      <c r="AC86" s="21"/>
-      <c r="AD86" s="21"/>
-      <c r="AE86" s="21"/>
-      <c r="AF86" s="21"/>
-      <c r="AG86" s="21"/>
-      <c r="AH86" s="21"/>
-      <c r="AI86" s="21"/>
-      <c r="AJ86" s="21"/>
-      <c r="AK86" s="21"/>
-      <c r="AL86" s="21"/>
-      <c r="AM86" s="21"/>
-      <c r="AN86" s="21"/>
-      <c r="AO86" s="21"/>
-      <c r="AP86" s="21"/>
-      <c r="AQ86" s="21"/>
-      <c r="AR86" s="21"/>
-      <c r="AS86" s="21"/>
-      <c r="AT86" s="21"/>
-      <c r="AU86" s="21"/>
-      <c r="AV86" s="21"/>
-      <c r="AW86" s="21"/>
-      <c r="AX86" s="21"/>
-      <c r="AY86" s="21"/>
-      <c r="AZ86" s="21"/>
-      <c r="BA86" s="21"/>
-      <c r="BB86" s="21"/>
-      <c r="BC86" s="21"/>
-      <c r="BD86" s="21"/>
-      <c r="BE86" s="21"/>
-      <c r="BF86" s="21"/>
-      <c r="BG86" s="21"/>
-      <c r="BH86" s="21"/>
-      <c r="BI86" s="21"/>
-      <c r="BJ86" s="21"/>
-      <c r="BK86" s="21"/>
-      <c r="BL86" s="21"/>
-      <c r="BM86" s="21"/>
+    <row r="86" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="n">
+        <v>307325</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>2783.92</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" s="12" t="n">
+        <v>2783.92</v>
+      </c>
+      <c r="P86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="13" t="n">
+        <v>0.005548</v>
+      </c>
+      <c r="R86" s="12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="U86" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V86" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W86" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X86" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="12" t="n">
+        <v>2783.92</v>
+      </c>
+      <c r="AA86" s="12" t="n">
+        <v>194.87</v>
+      </c>
+      <c r="AB86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW86" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX86" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG86" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI86" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ86" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="BK86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM86" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="4"/>
-      <c r="X87" s="4"/>
-      <c r="Y87" s="4"/>
-      <c r="Z87" s="4"/>
-      <c r="AA87" s="4"/>
-      <c r="AB87" s="4"/>
-      <c r="AC87" s="4"/>
-      <c r="AD87" s="4"/>
-      <c r="AE87" s="4"/>
-      <c r="AF87" s="4"/>
-      <c r="AG87" s="4"/>
-      <c r="AH87" s="4"/>
-      <c r="AI87" s="4"/>
-      <c r="AJ87" s="4"/>
-      <c r="AK87" s="4"/>
-      <c r="AL87" s="4"/>
-      <c r="AM87" s="4"/>
-      <c r="AN87" s="4"/>
-      <c r="AO87" s="4"/>
-      <c r="AP87" s="4"/>
-      <c r="AQ87" s="4"/>
-      <c r="AR87" s="4"/>
-      <c r="AS87" s="4"/>
-      <c r="AT87" s="4"/>
-      <c r="AU87" s="4"/>
-      <c r="AV87" s="4"/>
-      <c r="AW87" s="4"/>
-      <c r="AX87" s="4"/>
-      <c r="AY87" s="4"/>
-      <c r="AZ87" s="4"/>
-      <c r="BA87" s="4"/>
-      <c r="BB87" s="4"/>
-      <c r="BC87" s="4"/>
-      <c r="BD87" s="4"/>
-      <c r="BE87" s="4"/>
-      <c r="BF87" s="4"/>
-      <c r="BG87" s="4"/>
-      <c r="BH87" s="4"/>
-      <c r="BI87" s="4"/>
-      <c r="BJ87" s="4"/>
-      <c r="BK87" s="4"/>
-      <c r="BL87" s="4"/>
-      <c r="BM87" s="4"/>
+      <c r="A87" s="8" t="n">
+        <v>307326</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>2967.67</v>
+      </c>
+      <c r="M87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="12" t="n">
+        <v>2786.54</v>
+      </c>
+      <c r="P87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="13" t="n">
+        <v>0.027908</v>
+      </c>
+      <c r="R87" s="12" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="S87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="U87" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V87" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W87" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X87" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y87" s="12" t="n">
+        <v>181.13</v>
+      </c>
+      <c r="Z87" s="12" t="n">
+        <v>2786.54</v>
+      </c>
+      <c r="AA87" s="12" t="n">
+        <v>195.06</v>
+      </c>
+      <c r="AB87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW87" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX87" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG87" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI87" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ87" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="BK87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM87" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4"/>
-      <c r="W88" s="4"/>
-      <c r="X88" s="4"/>
-      <c r="Y88" s="4"/>
-      <c r="Z88" s="4"/>
-      <c r="AA88" s="4"/>
-      <c r="AB88" s="4"/>
-      <c r="AC88" s="4"/>
-      <c r="AD88" s="4"/>
-      <c r="AE88" s="4"/>
-      <c r="AF88" s="4"/>
-      <c r="AG88" s="4"/>
-      <c r="AH88" s="4"/>
-      <c r="AI88" s="4"/>
-      <c r="AJ88" s="4"/>
-      <c r="AK88" s="4"/>
-      <c r="AL88" s="4"/>
-      <c r="AM88" s="4"/>
-      <c r="AN88" s="4"/>
-      <c r="AO88" s="4"/>
-      <c r="AP88" s="4"/>
-      <c r="AQ88" s="4"/>
-      <c r="AR88" s="4"/>
-      <c r="AS88" s="4"/>
-      <c r="AT88" s="4"/>
-      <c r="AU88" s="4"/>
-      <c r="AV88" s="4"/>
-      <c r="AW88" s="4"/>
-      <c r="AX88" s="4"/>
-      <c r="AY88" s="4"/>
-      <c r="AZ88" s="4"/>
-      <c r="BA88" s="4"/>
-      <c r="BB88" s="4"/>
-      <c r="BC88" s="4"/>
-      <c r="BD88" s="4"/>
-      <c r="BE88" s="4"/>
-      <c r="BF88" s="4"/>
-      <c r="BG88" s="4"/>
-      <c r="BH88" s="4"/>
-      <c r="BI88" s="4"/>
-      <c r="BJ88" s="4"/>
-      <c r="BK88" s="4"/>
-      <c r="BL88" s="4"/>
-      <c r="BM88" s="4"/>
+      <c r="A88" s="8" t="n">
+        <v>307328</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>2957.37</v>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" s="12" t="n">
+        <v>2694.64</v>
+      </c>
+      <c r="P88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="13" t="n">
+        <v>0.080236</v>
+      </c>
+      <c r="R88" s="12" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="S88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="U88" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V88" s="12" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="W88" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X88" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y88" s="12" t="n">
+        <v>262.73</v>
+      </c>
+      <c r="Z88" s="12" t="n">
+        <v>2694.64</v>
+      </c>
+      <c r="AA88" s="12" t="n">
+        <v>107.79</v>
+      </c>
+      <c r="AB88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW88" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX88" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG88" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI88" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ88" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="BK88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM88" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
-      <c r="X89" s="4"/>
-      <c r="Y89" s="4"/>
-      <c r="Z89" s="4"/>
-      <c r="AA89" s="4"/>
-      <c r="AB89" s="4"/>
-      <c r="AC89" s="4"/>
-      <c r="AD89" s="4"/>
-      <c r="AE89" s="4"/>
-      <c r="AF89" s="4"/>
-      <c r="AG89" s="4"/>
-      <c r="AH89" s="4"/>
-      <c r="AI89" s="4"/>
-      <c r="AJ89" s="4"/>
-      <c r="AK89" s="4"/>
-      <c r="AL89" s="4"/>
-      <c r="AM89" s="4"/>
-      <c r="AN89" s="4"/>
-      <c r="AO89" s="4"/>
-      <c r="AP89" s="4"/>
-      <c r="AQ89" s="4"/>
-      <c r="AR89" s="4"/>
-      <c r="AS89" s="4"/>
-      <c r="AT89" s="4"/>
-      <c r="AU89" s="4"/>
-      <c r="AV89" s="4"/>
-      <c r="AW89" s="4"/>
-      <c r="AX89" s="4"/>
-      <c r="AY89" s="4"/>
-      <c r="AZ89" s="4"/>
-      <c r="BA89" s="4"/>
-      <c r="BB89" s="4"/>
-      <c r="BC89" s="4"/>
-      <c r="BD89" s="4"/>
-      <c r="BE89" s="4"/>
-      <c r="BF89" s="4"/>
-      <c r="BG89" s="4"/>
-      <c r="BH89" s="4"/>
-      <c r="BI89" s="4"/>
-      <c r="BJ89" s="4"/>
-      <c r="BK89" s="4"/>
-      <c r="BL89" s="4"/>
-      <c r="BM89" s="4"/>
+      <c r="A89" s="8" t="n">
+        <v>307331</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>506.4</v>
+      </c>
+      <c r="M89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>499.2</v>
+      </c>
+      <c r="P89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="13" t="n">
+        <v>0.032832</v>
+      </c>
+      <c r="R89" s="12" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="S89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="U89" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V89" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="W89" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X89" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y89" s="12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z89" s="12" t="n">
+        <v>499.2</v>
+      </c>
+      <c r="AA89" s="12" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AB89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW89" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX89" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG89" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI89" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ89" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="BK89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM89" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-      <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
-      <c r="V90" s="4"/>
-      <c r="W90" s="4"/>
-      <c r="X90" s="4"/>
-      <c r="Y90" s="4"/>
-      <c r="Z90" s="4"/>
-      <c r="AA90" s="4"/>
-      <c r="AB90" s="4"/>
-      <c r="AC90" s="4"/>
-      <c r="AD90" s="4"/>
-      <c r="AE90" s="4"/>
-      <c r="AF90" s="4"/>
-      <c r="AG90" s="4"/>
-      <c r="AH90" s="4"/>
-      <c r="AI90" s="4"/>
-      <c r="AJ90" s="4"/>
-      <c r="AK90" s="4"/>
-      <c r="AL90" s="4"/>
-      <c r="AM90" s="4"/>
-      <c r="AN90" s="4"/>
-      <c r="AO90" s="4"/>
-      <c r="AP90" s="4"/>
-      <c r="AQ90" s="4"/>
-      <c r="AR90" s="4"/>
-      <c r="AS90" s="4"/>
-      <c r="AT90" s="4"/>
-      <c r="AU90" s="4"/>
-      <c r="AV90" s="4"/>
-      <c r="AW90" s="4"/>
-      <c r="AX90" s="4"/>
-      <c r="AY90" s="4"/>
-      <c r="AZ90" s="4"/>
-      <c r="BA90" s="4"/>
-      <c r="BB90" s="4"/>
-      <c r="BC90" s="4"/>
-      <c r="BD90" s="4"/>
-      <c r="BE90" s="4"/>
-      <c r="BF90" s="4"/>
-      <c r="BG90" s="4"/>
-      <c r="BH90" s="4"/>
-      <c r="BI90" s="4"/>
-      <c r="BJ90" s="4"/>
-      <c r="BK90" s="4"/>
-      <c r="BL90" s="4"/>
-      <c r="BM90" s="4"/>
+      <c r="A90" s="8" t="n">
+        <v>307333</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>1023.78</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="12" t="n">
+        <v>1023.78</v>
+      </c>
+      <c r="P90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="13" t="n">
+        <v>0.010272</v>
+      </c>
+      <c r="R90" s="12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="U90" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V90" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W90" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X90" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="12" t="n">
+        <v>1023.78</v>
+      </c>
+      <c r="AA90" s="12" t="n">
+        <v>71.66</v>
+      </c>
+      <c r="AB90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW90" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX90" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG90" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI90" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ90" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="BK90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM90" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
-      <c r="X91" s="4"/>
-      <c r="Y91" s="4"/>
-      <c r="Z91" s="4"/>
-      <c r="AA91" s="4"/>
-      <c r="AB91" s="4"/>
-      <c r="AC91" s="4"/>
-      <c r="AD91" s="4"/>
-      <c r="AE91" s="4"/>
-      <c r="AF91" s="4"/>
-      <c r="AG91" s="4"/>
-      <c r="AH91" s="4"/>
-      <c r="AI91" s="4"/>
-      <c r="AJ91" s="4"/>
-      <c r="AK91" s="4"/>
-      <c r="AL91" s="4"/>
-      <c r="AM91" s="4"/>
-      <c r="AN91" s="4"/>
-      <c r="AO91" s="4"/>
-      <c r="AP91" s="4"/>
-      <c r="AQ91" s="4"/>
-      <c r="AR91" s="4"/>
-      <c r="AS91" s="4"/>
-      <c r="AT91" s="4"/>
-      <c r="AU91" s="4"/>
-      <c r="AV91" s="4"/>
-      <c r="AW91" s="4"/>
-      <c r="AX91" s="4"/>
-      <c r="AY91" s="4"/>
-      <c r="AZ91" s="4"/>
-      <c r="BA91" s="4"/>
-      <c r="BB91" s="4"/>
-      <c r="BC91" s="4"/>
-      <c r="BD91" s="4"/>
-      <c r="BE91" s="4"/>
-      <c r="BF91" s="4"/>
-      <c r="BG91" s="4"/>
-      <c r="BH91" s="4"/>
-      <c r="BI91" s="4"/>
-      <c r="BJ91" s="4"/>
-      <c r="BK91" s="4"/>
-      <c r="BL91" s="4"/>
-      <c r="BM91" s="4"/>
+      <c r="A91" s="8" t="n">
+        <v>307353</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>2206.41</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O91" s="12" t="n">
+        <v>1942</v>
+      </c>
+      <c r="P91" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q91" s="13" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="R91" s="12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="S91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="U91" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V91" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W91" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X91" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y91" s="12" t="n">
+        <v>179.41</v>
+      </c>
+      <c r="Z91" s="12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="AA91" s="12" t="n">
+        <v>81.07</v>
+      </c>
+      <c r="AB91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW91" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX91" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG91" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI91" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ91" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="BK91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM91" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="4"/>
-      <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
-      <c r="Z92" s="4"/>
-      <c r="AA92" s="4"/>
-      <c r="AB92" s="4"/>
-      <c r="AC92" s="4"/>
-      <c r="AD92" s="4"/>
-      <c r="AE92" s="4"/>
-      <c r="AF92" s="4"/>
-      <c r="AG92" s="4"/>
-      <c r="AH92" s="4"/>
-      <c r="AI92" s="4"/>
-      <c r="AJ92" s="4"/>
-      <c r="AK92" s="4"/>
-      <c r="AL92" s="4"/>
-      <c r="AM92" s="4"/>
-      <c r="AN92" s="4"/>
-      <c r="AO92" s="4"/>
-      <c r="AP92" s="4"/>
-      <c r="AQ92" s="4"/>
-      <c r="AR92" s="4"/>
-      <c r="AS92" s="4"/>
-      <c r="AT92" s="4"/>
-      <c r="AU92" s="4"/>
-      <c r="AV92" s="4"/>
-      <c r="AW92" s="4"/>
-      <c r="AX92" s="4"/>
-      <c r="AY92" s="4"/>
-      <c r="AZ92" s="4"/>
-      <c r="BA92" s="4"/>
-      <c r="BB92" s="4"/>
-      <c r="BC92" s="4"/>
-      <c r="BD92" s="4"/>
-      <c r="BE92" s="4"/>
-      <c r="BF92" s="4"/>
-      <c r="BG92" s="4"/>
-      <c r="BH92" s="4"/>
-      <c r="BI92" s="4"/>
-      <c r="BJ92" s="4"/>
-      <c r="BK92" s="4"/>
-      <c r="BL92" s="4"/>
-      <c r="BM92" s="4"/>
+      <c r="A92" s="4"/>
     </row>
-    <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
-      <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
-      <c r="Z93" s="4"/>
-      <c r="AA93" s="4"/>
-      <c r="AB93" s="4"/>
-      <c r="AC93" s="4"/>
-      <c r="AD93" s="4"/>
-      <c r="AE93" s="4"/>
-      <c r="AF93" s="4"/>
-      <c r="AG93" s="4"/>
-      <c r="AH93" s="4"/>
-      <c r="AI93" s="4"/>
-      <c r="AJ93" s="4"/>
-      <c r="AK93" s="4"/>
-      <c r="AL93" s="4"/>
-      <c r="AM93" s="4"/>
-      <c r="AN93" s="4"/>
-      <c r="AO93" s="4"/>
-      <c r="AP93" s="4"/>
-      <c r="AQ93" s="4"/>
-      <c r="AR93" s="4"/>
-      <c r="AS93" s="4"/>
-      <c r="AT93" s="4"/>
-      <c r="AU93" s="4"/>
-      <c r="AV93" s="4"/>
-      <c r="AW93" s="4"/>
-      <c r="AX93" s="4"/>
-      <c r="AY93" s="4"/>
-      <c r="AZ93" s="4"/>
-      <c r="BA93" s="4"/>
-      <c r="BB93" s="4"/>
-      <c r="BC93" s="4"/>
-      <c r="BD93" s="4"/>
-      <c r="BE93" s="4"/>
-      <c r="BF93" s="4"/>
-      <c r="BG93" s="4"/>
-      <c r="BH93" s="4"/>
-      <c r="BI93" s="4"/>
-      <c r="BJ93" s="4"/>
-      <c r="BK93" s="4"/>
-      <c r="BL93" s="4"/>
-      <c r="BM93" s="4"/>
+    <row r="93" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="17"/>
+      <c r="F93" s="17"/>
+      <c r="G93" s="17"/>
+      <c r="H93" s="17"/>
+      <c r="I93" s="17"/>
+      <c r="J93" s="17"/>
+      <c r="K93" s="17"/>
+      <c r="L93" s="17"/>
+      <c r="M93" s="17"/>
+      <c r="N93" s="17"/>
+      <c r="O93" s="17"/>
+      <c r="P93" s="17"/>
+      <c r="Q93" s="17"/>
+      <c r="R93" s="17"/>
+      <c r="S93" s="17"/>
+      <c r="T93" s="17"/>
+      <c r="U93" s="17"/>
+      <c r="V93" s="17"/>
     </row>
-    <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4"/>
-      <c r="W94" s="4"/>
-      <c r="X94" s="4"/>
-      <c r="Y94" s="4"/>
-      <c r="Z94" s="4"/>
-      <c r="AA94" s="4"/>
-      <c r="AB94" s="4"/>
-      <c r="AC94" s="4"/>
-      <c r="AD94" s="4"/>
-      <c r="AE94" s="4"/>
-      <c r="AF94" s="4"/>
-      <c r="AG94" s="4"/>
-      <c r="AH94" s="4"/>
-      <c r="AI94" s="4"/>
-      <c r="AJ94" s="4"/>
-      <c r="AK94" s="4"/>
-      <c r="AL94" s="4"/>
-      <c r="AM94" s="4"/>
-      <c r="AN94" s="4"/>
-      <c r="AO94" s="4"/>
-      <c r="AP94" s="4"/>
-      <c r="AQ94" s="4"/>
-      <c r="AR94" s="4"/>
-      <c r="AS94" s="4"/>
-      <c r="AT94" s="4"/>
-      <c r="AU94" s="4"/>
-      <c r="AV94" s="4"/>
-      <c r="AW94" s="4"/>
-      <c r="AX94" s="4"/>
-      <c r="AY94" s="4"/>
-      <c r="AZ94" s="4"/>
-      <c r="BA94" s="4"/>
-      <c r="BB94" s="4"/>
-      <c r="BC94" s="4"/>
-      <c r="BD94" s="4"/>
-      <c r="BE94" s="4"/>
-      <c r="BF94" s="4"/>
-      <c r="BG94" s="4"/>
-      <c r="BH94" s="4"/>
-      <c r="BI94" s="4"/>
-      <c r="BJ94" s="4"/>
-      <c r="BK94" s="4"/>
-      <c r="BL94" s="4"/>
-      <c r="BM94" s="4"/>
+    <row r="94" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I94" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="J94" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K94" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L94" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M94" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="N94" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O94" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P94" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q94" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R94" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S94" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="T94" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="U94" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V94" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
-      <c r="X95" s="4"/>
-      <c r="Y95" s="4"/>
-      <c r="Z95" s="4"/>
-      <c r="AA95" s="4"/>
-      <c r="AB95" s="4"/>
-      <c r="AC95" s="4"/>
-      <c r="AD95" s="4"/>
-      <c r="AE95" s="4"/>
-      <c r="AF95" s="4"/>
-      <c r="AG95" s="4"/>
-      <c r="AH95" s="4"/>
-      <c r="AI95" s="4"/>
-      <c r="AJ95" s="4"/>
-      <c r="AK95" s="4"/>
-      <c r="AL95" s="4"/>
-      <c r="AM95" s="4"/>
-      <c r="AN95" s="4"/>
-      <c r="AO95" s="4"/>
-      <c r="AP95" s="4"/>
-      <c r="AQ95" s="4"/>
-      <c r="AR95" s="4"/>
-      <c r="AS95" s="4"/>
-      <c r="AT95" s="4"/>
-      <c r="AU95" s="4"/>
-      <c r="AV95" s="4"/>
-      <c r="AW95" s="4"/>
-      <c r="AX95" s="4"/>
-      <c r="AY95" s="4"/>
-      <c r="AZ95" s="4"/>
-      <c r="BA95" s="4"/>
-      <c r="BB95" s="4"/>
-      <c r="BC95" s="4"/>
-      <c r="BD95" s="4"/>
-      <c r="BE95" s="4"/>
-      <c r="BF95" s="4"/>
-      <c r="BG95" s="4"/>
-      <c r="BH95" s="4"/>
-      <c r="BI95" s="4"/>
-      <c r="BJ95" s="4"/>
-      <c r="BK95" s="4"/>
-      <c r="BL95" s="4"/>
-      <c r="BM95" s="4"/>
+      <c r="A95" s="19" t="n">
+        <v>87</v>
+      </c>
+      <c r="B95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="19" t="n">
+        <v>85</v>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>14025.92</v>
+      </c>
+      <c r="F95" s="19" t="n">
+        <v>304859.72</v>
+      </c>
+      <c r="G95" s="19" t="n">
+        <v>17171.46</v>
+      </c>
+      <c r="H95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="19" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="K95" s="19" t="n">
+        <v>318885.64</v>
+      </c>
+      <c r="L95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="20" t="n">
+        <v>34.41994</v>
+      </c>
+      <c r="S95" s="19" t="n">
+        <v>304674.72</v>
+      </c>
+      <c r="T95" s="19" t="n">
+        <v>318885.64</v>
+      </c>
+      <c r="U95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4"/>
-      <c r="W96" s="4"/>
-      <c r="X96" s="4"/>
-      <c r="Y96" s="4"/>
-      <c r="Z96" s="4"/>
-      <c r="AA96" s="4"/>
-      <c r="AB96" s="4"/>
-      <c r="AC96" s="4"/>
-      <c r="AD96" s="4"/>
-      <c r="AE96" s="4"/>
-      <c r="AF96" s="4"/>
-      <c r="AG96" s="4"/>
-      <c r="AH96" s="4"/>
-      <c r="AI96" s="4"/>
-      <c r="AJ96" s="4"/>
-      <c r="AK96" s="4"/>
-      <c r="AL96" s="4"/>
-      <c r="AM96" s="4"/>
-      <c r="AN96" s="4"/>
-      <c r="AO96" s="4"/>
-      <c r="AP96" s="4"/>
-      <c r="AQ96" s="4"/>
-      <c r="AR96" s="4"/>
-      <c r="AS96" s="4"/>
-      <c r="AT96" s="4"/>
-      <c r="AU96" s="4"/>
-      <c r="AV96" s="4"/>
-      <c r="AW96" s="4"/>
-      <c r="AX96" s="4"/>
-      <c r="AY96" s="4"/>
-      <c r="AZ96" s="4"/>
-      <c r="BA96" s="4"/>
-      <c r="BB96" s="4"/>
-      <c r="BC96" s="4"/>
-      <c r="BD96" s="4"/>
-      <c r="BE96" s="4"/>
-      <c r="BF96" s="4"/>
-      <c r="BG96" s="4"/>
-      <c r="BH96" s="4"/>
-      <c r="BI96" s="4"/>
-      <c r="BJ96" s="4"/>
-      <c r="BK96" s="4"/>
-      <c r="BL96" s="4"/>
-      <c r="BM96" s="4"/>
+    <row r="96" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H96" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I96" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J96" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K96" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="L96" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="M96" s="18" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="19" t="n">
+        <v>3423.43</v>
+      </c>
+      <c r="B97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="19" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="E97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4"/>
+    </row>
+    <row r="99" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="B99" s="21"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="21"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="21"/>
+      <c r="K99" s="21"/>
+      <c r="L99" s="21"/>
+      <c r="M99" s="21"/>
+      <c r="N99" s="21"/>
+      <c r="O99" s="21"/>
+      <c r="P99" s="21"/>
+      <c r="Q99" s="21"/>
+      <c r="R99" s="21"/>
+      <c r="S99" s="21"/>
+      <c r="T99" s="21"/>
+      <c r="U99" s="21"/>
+      <c r="V99" s="21"/>
+      <c r="W99" s="21"/>
+      <c r="X99" s="21"/>
+      <c r="Y99" s="21"/>
+      <c r="Z99" s="21"/>
+      <c r="AA99" s="21"/>
+      <c r="AB99" s="21"/>
+      <c r="AC99" s="21"/>
+      <c r="AD99" s="21"/>
+      <c r="AE99" s="21"/>
+      <c r="AF99" s="21"/>
+      <c r="AG99" s="21"/>
+      <c r="AH99" s="21"/>
+      <c r="AI99" s="21"/>
+      <c r="AJ99" s="21"/>
+      <c r="AK99" s="21"/>
+      <c r="AL99" s="21"/>
+      <c r="AM99" s="21"/>
+      <c r="AN99" s="21"/>
+      <c r="AO99" s="21"/>
+      <c r="AP99" s="21"/>
+      <c r="AQ99" s="21"/>
+      <c r="AR99" s="21"/>
+      <c r="AS99" s="21"/>
+      <c r="AT99" s="21"/>
+      <c r="AU99" s="21"/>
+      <c r="AV99" s="21"/>
+      <c r="AW99" s="21"/>
+      <c r="AX99" s="21"/>
+      <c r="AY99" s="21"/>
+      <c r="AZ99" s="21"/>
+      <c r="BA99" s="21"/>
+      <c r="BB99" s="21"/>
+      <c r="BC99" s="21"/>
+      <c r="BD99" s="21"/>
+      <c r="BE99" s="21"/>
+      <c r="BF99" s="21"/>
+      <c r="BG99" s="21"/>
+      <c r="BH99" s="21"/>
+      <c r="BI99" s="21"/>
+      <c r="BJ99" s="21"/>
+      <c r="BK99" s="21"/>
+      <c r="BL99" s="21"/>
+      <c r="BM99" s="21"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="4"/>
+      <c r="S100" s="4"/>
+      <c r="T100" s="4"/>
+      <c r="U100" s="4"/>
+      <c r="V100" s="4"/>
+      <c r="W100" s="4"/>
+      <c r="X100" s="4"/>
+      <c r="Y100" s="4"/>
+      <c r="Z100" s="4"/>
+      <c r="AA100" s="4"/>
+      <c r="AB100" s="4"/>
+      <c r="AC100" s="4"/>
+      <c r="AD100" s="4"/>
+      <c r="AE100" s="4"/>
+      <c r="AF100" s="4"/>
+      <c r="AG100" s="4"/>
+      <c r="AH100" s="4"/>
+      <c r="AI100" s="4"/>
+      <c r="AJ100" s="4"/>
+      <c r="AK100" s="4"/>
+      <c r="AL100" s="4"/>
+      <c r="AM100" s="4"/>
+      <c r="AN100" s="4"/>
+      <c r="AO100" s="4"/>
+      <c r="AP100" s="4"/>
+      <c r="AQ100" s="4"/>
+      <c r="AR100" s="4"/>
+      <c r="AS100" s="4"/>
+      <c r="AT100" s="4"/>
+      <c r="AU100" s="4"/>
+      <c r="AV100" s="4"/>
+      <c r="AW100" s="4"/>
+      <c r="AX100" s="4"/>
+      <c r="AY100" s="4"/>
+      <c r="AZ100" s="4"/>
+      <c r="BA100" s="4"/>
+      <c r="BB100" s="4"/>
+      <c r="BC100" s="4"/>
+      <c r="BD100" s="4"/>
+      <c r="BE100" s="4"/>
+      <c r="BF100" s="4"/>
+      <c r="BG100" s="4"/>
+      <c r="BH100" s="4"/>
+      <c r="BI100" s="4"/>
+      <c r="BJ100" s="4"/>
+      <c r="BK100" s="4"/>
+      <c r="BL100" s="4"/>
+      <c r="BM100" s="4"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="4"/>
+      <c r="R101" s="4"/>
+      <c r="S101" s="4"/>
+      <c r="T101" s="4"/>
+      <c r="U101" s="4"/>
+      <c r="V101" s="4"/>
+      <c r="W101" s="4"/>
+      <c r="X101" s="4"/>
+      <c r="Y101" s="4"/>
+      <c r="Z101" s="4"/>
+      <c r="AA101" s="4"/>
+      <c r="AB101" s="4"/>
+      <c r="AC101" s="4"/>
+      <c r="AD101" s="4"/>
+      <c r="AE101" s="4"/>
+      <c r="AF101" s="4"/>
+      <c r="AG101" s="4"/>
+      <c r="AH101" s="4"/>
+      <c r="AI101" s="4"/>
+      <c r="AJ101" s="4"/>
+      <c r="AK101" s="4"/>
+      <c r="AL101" s="4"/>
+      <c r="AM101" s="4"/>
+      <c r="AN101" s="4"/>
+      <c r="AO101" s="4"/>
+      <c r="AP101" s="4"/>
+      <c r="AQ101" s="4"/>
+      <c r="AR101" s="4"/>
+      <c r="AS101" s="4"/>
+      <c r="AT101" s="4"/>
+      <c r="AU101" s="4"/>
+      <c r="AV101" s="4"/>
+      <c r="AW101" s="4"/>
+      <c r="AX101" s="4"/>
+      <c r="AY101" s="4"/>
+      <c r="AZ101" s="4"/>
+      <c r="BA101" s="4"/>
+      <c r="BB101" s="4"/>
+      <c r="BC101" s="4"/>
+      <c r="BD101" s="4"/>
+      <c r="BE101" s="4"/>
+      <c r="BF101" s="4"/>
+      <c r="BG101" s="4"/>
+      <c r="BH101" s="4"/>
+      <c r="BI101" s="4"/>
+      <c r="BJ101" s="4"/>
+      <c r="BK101" s="4"/>
+      <c r="BL101" s="4"/>
+      <c r="BM101" s="4"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="4"/>
+      <c r="T102" s="4"/>
+      <c r="U102" s="4"/>
+      <c r="V102" s="4"/>
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+      <c r="AA102" s="4"/>
+      <c r="AB102" s="4"/>
+      <c r="AC102" s="4"/>
+      <c r="AD102" s="4"/>
+      <c r="AE102" s="4"/>
+      <c r="AF102" s="4"/>
+      <c r="AG102" s="4"/>
+      <c r="AH102" s="4"/>
+      <c r="AI102" s="4"/>
+      <c r="AJ102" s="4"/>
+      <c r="AK102" s="4"/>
+      <c r="AL102" s="4"/>
+      <c r="AM102" s="4"/>
+      <c r="AN102" s="4"/>
+      <c r="AO102" s="4"/>
+      <c r="AP102" s="4"/>
+      <c r="AQ102" s="4"/>
+      <c r="AR102" s="4"/>
+      <c r="AS102" s="4"/>
+      <c r="AT102" s="4"/>
+      <c r="AU102" s="4"/>
+      <c r="AV102" s="4"/>
+      <c r="AW102" s="4"/>
+      <c r="AX102" s="4"/>
+      <c r="AY102" s="4"/>
+      <c r="AZ102" s="4"/>
+      <c r="BA102" s="4"/>
+      <c r="BB102" s="4"/>
+      <c r="BC102" s="4"/>
+      <c r="BD102" s="4"/>
+      <c r="BE102" s="4"/>
+      <c r="BF102" s="4"/>
+      <c r="BG102" s="4"/>
+      <c r="BH102" s="4"/>
+      <c r="BI102" s="4"/>
+      <c r="BJ102" s="4"/>
+      <c r="BK102" s="4"/>
+      <c r="BL102" s="4"/>
+      <c r="BM102" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="4"/>
+      <c r="T103" s="4"/>
+      <c r="U103" s="4"/>
+      <c r="V103" s="4"/>
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="4"/>
+      <c r="AA103" s="4"/>
+      <c r="AB103" s="4"/>
+      <c r="AC103" s="4"/>
+      <c r="AD103" s="4"/>
+      <c r="AE103" s="4"/>
+      <c r="AF103" s="4"/>
+      <c r="AG103" s="4"/>
+      <c r="AH103" s="4"/>
+      <c r="AI103" s="4"/>
+      <c r="AJ103" s="4"/>
+      <c r="AK103" s="4"/>
+      <c r="AL103" s="4"/>
+      <c r="AM103" s="4"/>
+      <c r="AN103" s="4"/>
+      <c r="AO103" s="4"/>
+      <c r="AP103" s="4"/>
+      <c r="AQ103" s="4"/>
+      <c r="AR103" s="4"/>
+      <c r="AS103" s="4"/>
+      <c r="AT103" s="4"/>
+      <c r="AU103" s="4"/>
+      <c r="AV103" s="4"/>
+      <c r="AW103" s="4"/>
+      <c r="AX103" s="4"/>
+      <c r="AY103" s="4"/>
+      <c r="AZ103" s="4"/>
+      <c r="BA103" s="4"/>
+      <c r="BB103" s="4"/>
+      <c r="BC103" s="4"/>
+      <c r="BD103" s="4"/>
+      <c r="BE103" s="4"/>
+      <c r="BF103" s="4"/>
+      <c r="BG103" s="4"/>
+      <c r="BH103" s="4"/>
+      <c r="BI103" s="4"/>
+      <c r="BJ103" s="4"/>
+      <c r="BK103" s="4"/>
+      <c r="BL103" s="4"/>
+      <c r="BM103" s="4"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4"/>
+      <c r="S104" s="4"/>
+      <c r="T104" s="4"/>
+      <c r="U104" s="4"/>
+      <c r="V104" s="4"/>
+      <c r="W104" s="4"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="4"/>
+      <c r="AA104" s="4"/>
+      <c r="AB104" s="4"/>
+      <c r="AC104" s="4"/>
+      <c r="AD104" s="4"/>
+      <c r="AE104" s="4"/>
+      <c r="AF104" s="4"/>
+      <c r="AG104" s="4"/>
+      <c r="AH104" s="4"/>
+      <c r="AI104" s="4"/>
+      <c r="AJ104" s="4"/>
+      <c r="AK104" s="4"/>
+      <c r="AL104" s="4"/>
+      <c r="AM104" s="4"/>
+      <c r="AN104" s="4"/>
+      <c r="AO104" s="4"/>
+      <c r="AP104" s="4"/>
+      <c r="AQ104" s="4"/>
+      <c r="AR104" s="4"/>
+      <c r="AS104" s="4"/>
+      <c r="AT104" s="4"/>
+      <c r="AU104" s="4"/>
+      <c r="AV104" s="4"/>
+      <c r="AW104" s="4"/>
+      <c r="AX104" s="4"/>
+      <c r="AY104" s="4"/>
+      <c r="AZ104" s="4"/>
+      <c r="BA104" s="4"/>
+      <c r="BB104" s="4"/>
+      <c r="BC104" s="4"/>
+      <c r="BD104" s="4"/>
+      <c r="BE104" s="4"/>
+      <c r="BF104" s="4"/>
+      <c r="BG104" s="4"/>
+      <c r="BH104" s="4"/>
+      <c r="BI104" s="4"/>
+      <c r="BJ104" s="4"/>
+      <c r="BK104" s="4"/>
+      <c r="BL104" s="4"/>
+      <c r="BM104" s="4"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="4"/>
+      <c r="S105" s="4"/>
+      <c r="T105" s="4"/>
+      <c r="U105" s="4"/>
+      <c r="V105" s="4"/>
+      <c r="W105" s="4"/>
+      <c r="X105" s="4"/>
+      <c r="Y105" s="4"/>
+      <c r="Z105" s="4"/>
+      <c r="AA105" s="4"/>
+      <c r="AB105" s="4"/>
+      <c r="AC105" s="4"/>
+      <c r="AD105" s="4"/>
+      <c r="AE105" s="4"/>
+      <c r="AF105" s="4"/>
+      <c r="AG105" s="4"/>
+      <c r="AH105" s="4"/>
+      <c r="AI105" s="4"/>
+      <c r="AJ105" s="4"/>
+      <c r="AK105" s="4"/>
+      <c r="AL105" s="4"/>
+      <c r="AM105" s="4"/>
+      <c r="AN105" s="4"/>
+      <c r="AO105" s="4"/>
+      <c r="AP105" s="4"/>
+      <c r="AQ105" s="4"/>
+      <c r="AR105" s="4"/>
+      <c r="AS105" s="4"/>
+      <c r="AT105" s="4"/>
+      <c r="AU105" s="4"/>
+      <c r="AV105" s="4"/>
+      <c r="AW105" s="4"/>
+      <c r="AX105" s="4"/>
+      <c r="AY105" s="4"/>
+      <c r="AZ105" s="4"/>
+      <c r="BA105" s="4"/>
+      <c r="BB105" s="4"/>
+      <c r="BC105" s="4"/>
+      <c r="BD105" s="4"/>
+      <c r="BE105" s="4"/>
+      <c r="BF105" s="4"/>
+      <c r="BG105" s="4"/>
+      <c r="BH105" s="4"/>
+      <c r="BI105" s="4"/>
+      <c r="BJ105" s="4"/>
+      <c r="BK105" s="4"/>
+      <c r="BL105" s="4"/>
+      <c r="BM105" s="4"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+      <c r="S106" s="4"/>
+      <c r="T106" s="4"/>
+      <c r="U106" s="4"/>
+      <c r="V106" s="4"/>
+      <c r="W106" s="4"/>
+      <c r="X106" s="4"/>
+      <c r="Y106" s="4"/>
+      <c r="Z106" s="4"/>
+      <c r="AA106" s="4"/>
+      <c r="AB106" s="4"/>
+      <c r="AC106" s="4"/>
+      <c r="AD106" s="4"/>
+      <c r="AE106" s="4"/>
+      <c r="AF106" s="4"/>
+      <c r="AG106" s="4"/>
+      <c r="AH106" s="4"/>
+      <c r="AI106" s="4"/>
+      <c r="AJ106" s="4"/>
+      <c r="AK106" s="4"/>
+      <c r="AL106" s="4"/>
+      <c r="AM106" s="4"/>
+      <c r="AN106" s="4"/>
+      <c r="AO106" s="4"/>
+      <c r="AP106" s="4"/>
+      <c r="AQ106" s="4"/>
+      <c r="AR106" s="4"/>
+      <c r="AS106" s="4"/>
+      <c r="AT106" s="4"/>
+      <c r="AU106" s="4"/>
+      <c r="AV106" s="4"/>
+      <c r="AW106" s="4"/>
+      <c r="AX106" s="4"/>
+      <c r="AY106" s="4"/>
+      <c r="AZ106" s="4"/>
+      <c r="BA106" s="4"/>
+      <c r="BB106" s="4"/>
+      <c r="BC106" s="4"/>
+      <c r="BD106" s="4"/>
+      <c r="BE106" s="4"/>
+      <c r="BF106" s="4"/>
+      <c r="BG106" s="4"/>
+      <c r="BH106" s="4"/>
+      <c r="BI106" s="4"/>
+      <c r="BJ106" s="4"/>
+      <c r="BK106" s="4"/>
+      <c r="BL106" s="4"/>
+      <c r="BM106" s="4"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+      <c r="T107" s="4"/>
+      <c r="U107" s="4"/>
+      <c r="V107" s="4"/>
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
+      <c r="AA107" s="4"/>
+      <c r="AB107" s="4"/>
+      <c r="AC107" s="4"/>
+      <c r="AD107" s="4"/>
+      <c r="AE107" s="4"/>
+      <c r="AF107" s="4"/>
+      <c r="AG107" s="4"/>
+      <c r="AH107" s="4"/>
+      <c r="AI107" s="4"/>
+      <c r="AJ107" s="4"/>
+      <c r="AK107" s="4"/>
+      <c r="AL107" s="4"/>
+      <c r="AM107" s="4"/>
+      <c r="AN107" s="4"/>
+      <c r="AO107" s="4"/>
+      <c r="AP107" s="4"/>
+      <c r="AQ107" s="4"/>
+      <c r="AR107" s="4"/>
+      <c r="AS107" s="4"/>
+      <c r="AT107" s="4"/>
+      <c r="AU107" s="4"/>
+      <c r="AV107" s="4"/>
+      <c r="AW107" s="4"/>
+      <c r="AX107" s="4"/>
+      <c r="AY107" s="4"/>
+      <c r="AZ107" s="4"/>
+      <c r="BA107" s="4"/>
+      <c r="BB107" s="4"/>
+      <c r="BC107" s="4"/>
+      <c r="BD107" s="4"/>
+      <c r="BE107" s="4"/>
+      <c r="BF107" s="4"/>
+      <c r="BG107" s="4"/>
+      <c r="BH107" s="4"/>
+      <c r="BI107" s="4"/>
+      <c r="BJ107" s="4"/>
+      <c r="BK107" s="4"/>
+      <c r="BL107" s="4"/>
+      <c r="BM107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="4"/>
+      <c r="T108" s="4"/>
+      <c r="U108" s="4"/>
+      <c r="V108" s="4"/>
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="4"/>
+      <c r="Z108" s="4"/>
+      <c r="AA108" s="4"/>
+      <c r="AB108" s="4"/>
+      <c r="AC108" s="4"/>
+      <c r="AD108" s="4"/>
+      <c r="AE108" s="4"/>
+      <c r="AF108" s="4"/>
+      <c r="AG108" s="4"/>
+      <c r="AH108" s="4"/>
+      <c r="AI108" s="4"/>
+      <c r="AJ108" s="4"/>
+      <c r="AK108" s="4"/>
+      <c r="AL108" s="4"/>
+      <c r="AM108" s="4"/>
+      <c r="AN108" s="4"/>
+      <c r="AO108" s="4"/>
+      <c r="AP108" s="4"/>
+      <c r="AQ108" s="4"/>
+      <c r="AR108" s="4"/>
+      <c r="AS108" s="4"/>
+      <c r="AT108" s="4"/>
+      <c r="AU108" s="4"/>
+      <c r="AV108" s="4"/>
+      <c r="AW108" s="4"/>
+      <c r="AX108" s="4"/>
+      <c r="AY108" s="4"/>
+      <c r="AZ108" s="4"/>
+      <c r="BA108" s="4"/>
+      <c r="BB108" s="4"/>
+      <c r="BC108" s="4"/>
+      <c r="BD108" s="4"/>
+      <c r="BE108" s="4"/>
+      <c r="BF108" s="4"/>
+      <c r="BG108" s="4"/>
+      <c r="BH108" s="4"/>
+      <c r="BI108" s="4"/>
+      <c r="BJ108" s="4"/>
+      <c r="BK108" s="4"/>
+      <c r="BL108" s="4"/>
+      <c r="BM108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+      <c r="S109" s="4"/>
+      <c r="T109" s="4"/>
+      <c r="U109" s="4"/>
+      <c r="V109" s="4"/>
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="4"/>
+      <c r="AA109" s="4"/>
+      <c r="AB109" s="4"/>
+      <c r="AC109" s="4"/>
+      <c r="AD109" s="4"/>
+      <c r="AE109" s="4"/>
+      <c r="AF109" s="4"/>
+      <c r="AG109" s="4"/>
+      <c r="AH109" s="4"/>
+      <c r="AI109" s="4"/>
+      <c r="AJ109" s="4"/>
+      <c r="AK109" s="4"/>
+      <c r="AL109" s="4"/>
+      <c r="AM109" s="4"/>
+      <c r="AN109" s="4"/>
+      <c r="AO109" s="4"/>
+      <c r="AP109" s="4"/>
+      <c r="AQ109" s="4"/>
+      <c r="AR109" s="4"/>
+      <c r="AS109" s="4"/>
+      <c r="AT109" s="4"/>
+      <c r="AU109" s="4"/>
+      <c r="AV109" s="4"/>
+      <c r="AW109" s="4"/>
+      <c r="AX109" s="4"/>
+      <c r="AY109" s="4"/>
+      <c r="AZ109" s="4"/>
+      <c r="BA109" s="4"/>
+      <c r="BB109" s="4"/>
+      <c r="BC109" s="4"/>
+      <c r="BD109" s="4"/>
+      <c r="BE109" s="4"/>
+      <c r="BF109" s="4"/>
+      <c r="BG109" s="4"/>
+      <c r="BH109" s="4"/>
+      <c r="BI109" s="4"/>
+      <c r="BJ109" s="4"/>
+      <c r="BK109" s="4"/>
+      <c r="BL109" s="4"/>
+      <c r="BM109" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="90">
+  <mergeCells count="103">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -32938,18 +35556,31 @@
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B78:E78"/>
-    <mergeCell ref="A80:V80"/>
-    <mergeCell ref="A86:BM86"/>
-    <mergeCell ref="A87:BM87"/>
-    <mergeCell ref="A88:BM88"/>
-    <mergeCell ref="A89:BM89"/>
-    <mergeCell ref="A90:BM90"/>
-    <mergeCell ref="A91:BM91"/>
-    <mergeCell ref="A92:BM92"/>
-    <mergeCell ref="A93:BM93"/>
-    <mergeCell ref="A94:BM94"/>
-    <mergeCell ref="A95:BM95"/>
-    <mergeCell ref="A96:BM96"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="A93:V93"/>
+    <mergeCell ref="A99:BM99"/>
+    <mergeCell ref="A100:BM100"/>
+    <mergeCell ref="A101:BM101"/>
+    <mergeCell ref="A102:BM102"/>
+    <mergeCell ref="A103:BM103"/>
+    <mergeCell ref="A104:BM104"/>
+    <mergeCell ref="A105:BM105"/>
+    <mergeCell ref="A106:BM106"/>
+    <mergeCell ref="A107:BM107"/>
+    <mergeCell ref="A108:BM108"/>
+    <mergeCell ref="A109:BM109"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="335">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 18/05/2026 07:30:58</t>
+    <t xml:space="preserve">Emitido em: 19/05/2026 05:30:31</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -340,279 +340,267 @@
     <t xml:space="preserve">35260475801902000126550000013538461061418038</t>
   </si>
   <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">635.928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.233,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006359281745462137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260524546165000393550040000980061727013914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.413,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260524546165000393550040000980051314694727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.532,07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260509306858000153550010000709261237889907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.891 - STUDIOLUCE ILUMINACAO IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.193,88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510599342000123550020001044791920149108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260511389565000200570050003989501000852039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54,66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050803981473767772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050803991044656674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.122,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804001438231179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.768,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575821546000102550040001403101130982608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.171,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260530228132000136550010000092891773232410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260530228132000136550010000092901435141905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804101599979210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.304.072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.534,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260550949528001232550010023040721860830987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">261.170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.391,61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260558329608000144550010002611701002611716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.582 - GRUPO MARMO E HIME COMERCIO, IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.867,78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260520587017000285550010000397411851274488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.768,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829941322627923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.083.080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">461,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050830801584930623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">886,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829741533961189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.259 - IMD COMERCIO DE MOVEIS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.276,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260503961151000447550060004095291908594429</t>
+  </si>
+  <si>
     <t xml:space="preserve">90 - TRAMONTINA TEEC S.A</t>
   </si>
   <si>
-    <t xml:space="preserve">683.317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.698,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260501554846000136550010006833171531710325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">635.928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.233,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006359281745462137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260524546165000393550040000980061727013914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.413,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260524546165000393550040000980051314694727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.532,07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260509306858000153550010000709261237889907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.891 - STUDIOLUCE ILUMINACAO IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.193,88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260510599342000123550020001044791920149108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260511389565000200570050003989501000852039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54,66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050803981473767772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">264,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050803991044656674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.122,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804001438231179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.768,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575821546000102550040001403101130982608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.171,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260530228132000136550010000092891773232410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63,31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260530228132000136550010000092901435141905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804101599979210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.304.072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.534,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260550949528001232550010023040721860830987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">261.170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.391,61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260558329608000144550010002611701002611716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.582 - GRUPO MARMO E HIME COMERCIO, IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.867,78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260520587017000285550010000397411851274488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.768,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829941322627923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.083.080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">461,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050830801584930623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">886,44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829741533961189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.259 - IMD COMERCIO DE MOVEIS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409.529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.276,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260503961151000447550060004095291908594429</t>
-  </si>
-  <si>
     <t xml:space="preserve">684.266</t>
   </si>
   <si>
@@ -893,6 +881,93 @@
   </si>
   <si>
     <t xml:space="preserve">42260575821546000102550040001404991623793421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.288 - ITAMONTE ILUM EIRELI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.389,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260527160810000161550010000073791608989680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.807,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260527160810000161550010000073801321349708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.255,43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260512077181000133550030002249621339755688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.664 - STANDARD ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.416,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260556365423000160550010000120471129493398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260511389565000200570050003993491000856175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">410.501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.535,23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260503961151000447550060004105011217621653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.428,23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007589831576786810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">642.851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.351,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006428511520912936</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17138,7 +17213,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM73"/>
+  <dimension ref="A1:BM79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -18656,7 +18731,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>306825</v>
+        <v>306942</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>106</v>
@@ -18668,67 +18743,67 @@
         <v>107</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>75698.87</v>
+        <v>2233.8</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>71271.6</v>
+        <v>2233.8</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>4.400605</v>
+        <v>0.013104</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>623.56</v>
+        <v>3.36</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>4427.27</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>71271.6</v>
+        <v>2233.8</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>3720.23</v>
+        <v>156.37</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18794,7 +18869,7 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>77</v>
@@ -18833,7 +18908,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18847,10 +18922,10 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>306942</v>
+        <v>307049</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -18859,22 +18934,22 @@
         <v>113</v>
       </c>
       <c r="G12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>85</v>
-      </c>
       <c r="J12" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2233.8</v>
+        <v>174.72</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18883,22 +18958,22 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>2233.8</v>
+        <v>159.2</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.013104</v>
+        <v>0</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
@@ -18910,16 +18985,16 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>0</v>
+        <v>15.52</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>2233.8</v>
+        <v>159.2</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>156.37</v>
+        <v>11.14</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -19024,7 +19099,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19038,7 +19113,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>307049</v>
+        <v>307051</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>64</v>
@@ -19047,34 +19122,34 @@
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>174.72</v>
+        <v>7413.56</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>159.2</v>
+        <v>6754.95</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
@@ -19089,28 +19164,28 @@
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>15.52</v>
+        <v>658.61</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>159.2</v>
+        <v>6754.95</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>11.14</v>
+        <v>468.39</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19215,7 +19290,7 @@
         <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19229,79 +19304,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>307051</v>
+        <v>307055</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>7413.56</v>
+        <v>2532.07</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6754.95</v>
+        <v>2307.12</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0</v>
+        <v>0.076024</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0</v>
+        <v>11.04</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>658.61</v>
+        <v>224.95</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>6754.95</v>
+        <v>2307.12</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>468.39</v>
+        <v>161.49</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19406,7 +19481,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19420,79 +19495,79 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>307055</v>
+        <v>307083</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>83</v>
-      </c>
       <c r="H15" s="9" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>2532.07</v>
+        <v>1193.88</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>2307.12</v>
+        <v>1087.82</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.076024</v>
+        <v>0</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>11.04</v>
+        <v>0</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>224.95</v>
+        <v>106.06</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>2307.12</v>
+        <v>1087.82</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>161.49</v>
+        <v>43.51</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19501,7 +19576,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="12" t="n">
-        <v>0</v>
+        <v>89.72</v>
       </c>
       <c r="AE15" s="12" t="n">
         <v>0</v>
@@ -19582,25 +19657,25 @@
         <v>75</v>
       </c>
       <c r="BE15" s="14" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="BF15" s="9" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="BG15" s="9" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="BH15" s="14" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="BI15" s="9" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BK15" s="9" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="BL15" s="9" t="s">
         <v>75</v>
@@ -19611,34 +19686,34 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>307083</v>
+        <v>307084</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>85</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>1193.88</v>
+        <v>54.66</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19647,22 +19722,22 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>1087.82</v>
+        <v>51.32</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0</v>
+        <v>0.134276</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19674,16 +19749,16 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>106.06</v>
+        <v>3.34</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>1087.82</v>
+        <v>51.32</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>43.51</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19692,7 +19767,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="12" t="n">
-        <v>89.72</v>
+        <v>0</v>
       </c>
       <c r="AE16" s="12" t="n">
         <v>0</v>
@@ -19773,25 +19848,25 @@
         <v>75</v>
       </c>
       <c r="BE16" s="14" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="BF16" s="9" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="BG16" s="9" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="BH16" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ16" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="BI16" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ16" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="BK16" s="9" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="BL16" s="9" t="s">
         <v>75</v>
@@ -19802,16 +19877,16 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>307084</v>
+        <v>307085</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>83</v>
@@ -19820,16 +19895,16 @@
         <v>85</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>54.66</v>
+        <v>264.8</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19838,22 +19913,22 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>51.32</v>
+        <v>264.8</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.134276</v>
+        <v>0.00087</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0.43</v>
+        <v>0.93</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19865,16 +19940,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>51.32</v>
+        <v>264.8</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>2.05</v>
+        <v>18.54</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19979,7 +20054,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19993,16 +20068,16 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>307085</v>
+        <v>307086</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>83</v>
@@ -20011,16 +20086,16 @@
         <v>85</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>264.8</v>
+        <v>1122.7</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -20029,22 +20104,22 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>264.8</v>
+        <v>1122.7</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.00087</v>
+        <v>0.0036</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>0.93</v>
+        <v>4.85</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
@@ -20056,16 +20131,16 @@
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>264.8</v>
+        <v>1122.7</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>18.54</v>
+        <v>44.91</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20170,7 +20245,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20184,34 +20259,34 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>307086</v>
+        <v>307100</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>1122.7</v>
+        <v>3768.3</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20220,43 +20295,43 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>1122.7</v>
+        <v>3768.3</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.0036</v>
+        <v>0.216</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>4.85</v>
+        <v>91.2</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>1122.7</v>
+        <v>3768.3</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>44.91</v>
+        <v>263.78</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20361,7 +20436,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20375,34 +20450,34 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>307100</v>
+        <v>307121</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>85</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>3768.3</v>
+        <v>1171.26</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20411,43 +20486,43 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>3768.3</v>
+        <v>1067.21</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.216</v>
+        <v>0.056916</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>104.05</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>3768.3</v>
+        <v>1067.21</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>263.78</v>
+        <v>74.7</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20552,7 +20627,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20566,16 +20641,16 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307121</v>
+        <v>307122</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>83</v>
@@ -20584,16 +20659,16 @@
         <v>85</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1171.26</v>
+        <v>63.31</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20602,13 +20677,13 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1067.21</v>
+        <v>57.69</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.056916</v>
+        <v>0.009486</v>
       </c>
       <c r="R21" s="12" t="n">
         <v>0</v>
@@ -20617,28 +20692,28 @@
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>104.05</v>
+        <v>5.62</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>1067.21</v>
+        <v>57.69</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>74.7</v>
+        <v>4.04</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20707,7 +20782,7 @@
         <v>87</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20743,7 +20818,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20757,16 +20832,16 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307122</v>
+        <v>307170</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>83</v>
@@ -20775,7 +20850,7 @@
         <v>85</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>78</v>
@@ -20784,7 +20859,7 @@
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>63.31</v>
+        <v>404.81</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20793,22 +20868,22 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>57.69</v>
+        <v>404.81</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.009486</v>
+        <v>0.000858</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20820,16 +20895,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>57.69</v>
+        <v>404.81</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>4.04</v>
+        <v>16.19</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20898,7 +20973,7 @@
         <v>87</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20934,7 +21009,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20948,52 +21023,52 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307170</v>
+        <v>307182</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>404.81</v>
+        <v>1534.81</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>404.81</v>
+        <v>1490.26</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.108038</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>2.43</v>
+        <v>5</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
@@ -21005,22 +21080,22 @@
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0</v>
+        <v>44.55</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>404.81</v>
+        <v>1490.26</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>16.19</v>
+        <v>104.32</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21089,7 +21164,7 @@
         <v>87</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21139,7 +21214,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307182</v>
+        <v>307206</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>167</v>
@@ -21154,37 +21229,37 @@
         <v>83</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1534.81</v>
+        <v>15391.61</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>1490.26</v>
+        <v>14024.25</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.108038</v>
+        <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
@@ -21196,22 +21271,22 @@
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>63</v>
+        <v>57.33</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>44.55</v>
+        <v>1367.36</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>1490.26</v>
+        <v>14024.25</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>104.32</v>
+        <v>981.71</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21330,7 +21405,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307206</v>
+        <v>307209</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>172</v>
@@ -21345,28 +21420,28 @@
         <v>83</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="I25" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>15391.61</v>
+        <v>1867.78</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>14024.25</v>
+        <v>1685.3</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
@@ -21375,7 +21450,7 @@
         <v>0</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
@@ -21387,22 +21462,22 @@
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>57.33</v>
+        <v>45</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>1367.36</v>
+        <v>182.48</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>14024.25</v>
+        <v>1685.3</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>981.71</v>
+        <v>67.41</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21521,79 +21596,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307209</v>
+        <v>307221</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>1867.78</v>
+        <v>3768.28</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>1685.3</v>
+        <v>3598.38</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.536658</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>7.5</v>
+        <v>34.56</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>182.48</v>
+        <v>169.9</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>1685.3</v>
+        <v>3598.38</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>67.41</v>
+        <v>143.94</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21662,7 +21737,7 @@
         <v>87</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21698,7 +21773,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21712,25 +21787,25 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307221</v>
+        <v>307222</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>78</v>
@@ -21739,31 +21814,31 @@
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>3768.28</v>
+        <v>461.96</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>3598.38</v>
+        <v>461.96</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.536658</v>
+        <v>0.002057</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>34.56</v>
+        <v>2.43</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
@@ -21775,16 +21850,16 @@
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>169.9</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>3598.38</v>
+        <v>461.96</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>143.94</v>
+        <v>18.48</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21889,7 +21964,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21903,34 +21978,34 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307222</v>
+        <v>307224</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>461.96</v>
+        <v>886.44</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21939,43 +22014,43 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>461.96</v>
+        <v>886.44</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.002057</v>
+        <v>0.00154</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>2.43</v>
+        <v>0.83</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>461.96</v>
+        <v>886.44</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>18.48</v>
+        <v>62.05</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22044,7 +22119,7 @@
         <v>87</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22080,7 +22155,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22094,10 +22169,10 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>307224</v>
+        <v>307269</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -22106,40 +22181,40 @@
         <v>188</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>886.44</v>
+        <v>3276</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>886.44</v>
+        <v>3120</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.00154</v>
+        <v>0</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>0.83</v>
+        <v>18.05</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
@@ -22151,22 +22226,22 @@
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>41.33</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>886.44</v>
+        <v>3120</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>62.05</v>
+        <v>124.8</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22285,7 +22360,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>307269</v>
+        <v>307273</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>192</v>
@@ -22297,40 +22372,40 @@
         <v>193</v>
       </c>
       <c r="G30" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3276</v>
+        <v>7705.98</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>3120</v>
+        <v>6908.35</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0</v>
+        <v>0.438516</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>18.05</v>
+        <v>71.6</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
@@ -22342,22 +22417,22 @@
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>41.33</v>
+        <v>34</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>156</v>
+        <v>797.63</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>3120</v>
+        <v>6908.35</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>124.8</v>
+        <v>358.82</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22476,10 +22551,10 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>307273</v>
+        <v>307276</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -22491,64 +22566,64 @@
         <v>83</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>7705.98</v>
+        <v>522.97</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>6908.35</v>
+        <v>491.06</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.438516</v>
+        <v>0.013568</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>71.6</v>
+        <v>3.04</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>797.63</v>
+        <v>31.91</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>6908.35</v>
+        <v>491.06</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>358.82</v>
+        <v>34.38</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22653,7 +22728,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22667,58 +22742,58 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>307276</v>
+        <v>307277</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>522.97</v>
+        <v>1122.7</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>491.06</v>
+        <v>1122.7</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.013568</v>
+        <v>0.004114</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>3.04</v>
+        <v>4.85</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
@@ -22730,16 +22805,16 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>31.91</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>491.06</v>
+        <v>1122.7</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>34.38</v>
+        <v>44.91</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22844,7 +22919,7 @@
         <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22858,79 +22933,79 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>307277</v>
+        <v>307280</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1122.7</v>
+        <v>2385.63</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>1122.7</v>
+        <v>2214.84</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.004114</v>
+        <v>20.166476</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>4.85</v>
+        <v>23.3</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>28</v>
+        <v>43.93</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>0</v>
+        <v>170.79</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>1122.7</v>
+        <v>2214.84</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>44.91</v>
+        <v>88.59</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23035,7 +23110,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23049,10 +23124,10 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>307280</v>
+        <v>307281</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -23061,67 +23136,67 @@
         <v>207</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>2385.63</v>
+        <v>4762.99</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>2214.84</v>
+        <v>4546</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>20.166476</v>
+        <v>0.02738</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>23.3</v>
+        <v>21.28</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>43.93</v>
+        <v>58.63</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>170.79</v>
+        <v>216.99</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>2214.84</v>
+        <v>4546</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>88.59</v>
+        <v>181.84</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23226,7 +23301,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23240,52 +23315,52 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>307281</v>
+        <v>307296</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>206</v>
+        <v>106</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I35" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>174</v>
-      </c>
       <c r="J35" s="9" t="s">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>4762.99</v>
+        <v>4119.25</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>4546</v>
+        <v>4119.25</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.02738</v>
+        <v>0.55013</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>21.28</v>
+        <v>250</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
@@ -23297,22 +23372,22 @@
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>58.63</v>
+        <v>0</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>216.99</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>4546</v>
+        <v>4119.25</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>181.84</v>
+        <v>164.77</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23381,7 +23456,7 @@
         <v>87</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23431,25 +23506,25 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>307296</v>
+        <v>307309</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>78</v>
@@ -23458,7 +23533,7 @@
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>4119.25</v>
+        <v>1720.43</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -23467,16 +23542,16 @@
         <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>4119.25</v>
+        <v>1720.43</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.55013</v>
+        <v>0</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>250</v>
+        <v>10.21</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
@@ -23491,19 +23566,19 @@
         <v>0</v>
       </c>
       <c r="W36" s="9" t="s">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>4119.25</v>
+        <v>1720.43</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>164.77</v>
+        <v>120.43</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23608,7 +23683,7 @@
         <v>78</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23622,10 +23697,10 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>307309</v>
+        <v>307311</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>218</v>
+        <v>136</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -23637,37 +23712,37 @@
         <v>83</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>1720.43</v>
+        <v>446.07</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>1720.43</v>
+        <v>418.84</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0</v>
+        <v>0.134454</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>10.21</v>
+        <v>0.92</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
@@ -23679,22 +23754,22 @@
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W37" s="9" t="s">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>0</v>
+        <v>27.23</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>1720.43</v>
+        <v>418.84</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>120.43</v>
+        <v>23.54</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23763,7 +23838,7 @@
         <v>87</v>
       </c>
       <c r="AX37" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY37" s="14" t="s">
         <v>75</v>
@@ -23799,7 +23874,7 @@
         <v>78</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23813,58 +23888,58 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>307311</v>
+        <v>307312</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>446.07</v>
+        <v>273.43</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>418.84</v>
+        <v>256.74</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.134454</v>
+        <v>0.14364</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
@@ -23876,16 +23951,16 @@
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>27.23</v>
+        <v>16.69</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>418.84</v>
+        <v>256.74</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>23.54</v>
+        <v>10.27</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23990,7 +24065,7 @@
         <v>78</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24004,79 +24079,79 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>307312</v>
+        <v>307313</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>273.43</v>
+        <v>4209.61</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>256.74</v>
+        <v>3952.68</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.14364</v>
+        <v>0.471828</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>16.69</v>
+        <v>256.93</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>256.74</v>
+        <v>3952.68</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>10.27</v>
+        <v>158.11</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24145,7 +24220,7 @@
         <v>87</v>
       </c>
       <c r="AX39" s="10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AY39" s="14" t="s">
         <v>75</v>
@@ -24181,7 +24256,7 @@
         <v>78</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24195,79 +24270,79 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>307313</v>
+        <v>307314</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>4209.61</v>
+        <v>501.26</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>3952.68</v>
+        <v>470.66</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.471828</v>
+        <v>0.123032</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>7.22</v>
+        <v>4.49</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>256.93</v>
+        <v>30.6</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>3952.68</v>
+        <v>470.66</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>158.11</v>
+        <v>18.82</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24336,7 +24411,7 @@
         <v>87</v>
       </c>
       <c r="AX40" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY40" s="14" t="s">
         <v>75</v>
@@ -24372,7 +24447,7 @@
         <v>78</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24386,34 +24461,34 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>307314</v>
+        <v>307317</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>501.26</v>
+        <v>1727.12</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
@@ -24422,43 +24497,43 @@
         <v>2</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>470.66</v>
+        <v>1573.69</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.123032</v>
+        <v>0</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>30.6</v>
+        <v>153.43</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>470.66</v>
+        <v>1573.69</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>18.82</v>
+        <v>110.16</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24563,7 +24638,7 @@
         <v>78</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24577,79 +24652,79 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>307317</v>
+        <v>307325</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="H42" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J42" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>1727.12</v>
+        <v>2783.92</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>1573.69</v>
+        <v>2783.92</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0</v>
+        <v>0.005548</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>153.43</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>1573.69</v>
+        <v>2783.92</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>110.16</v>
+        <v>194.87</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24754,7 +24829,7 @@
         <v>78</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24768,34 +24843,34 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>307325</v>
+        <v>307326</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H43" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J43" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>2783.92</v>
+        <v>2967.67</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
@@ -24804,22 +24879,22 @@
         <v>1</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>2783.92</v>
+        <v>2786.54</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.005548</v>
+        <v>0.027908</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>0.98</v>
+        <v>3.56</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
@@ -24831,16 +24906,16 @@
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>0</v>
+        <v>181.13</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>2783.92</v>
+        <v>2786.54</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>194.87</v>
+        <v>195.06</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24945,7 +25020,7 @@
         <v>78</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -24959,10 +25034,10 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>307326</v>
+        <v>307328</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>112</v>
+        <v>240</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
@@ -24971,22 +25046,22 @@
         <v>241</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="H44" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J44" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>2967.67</v>
+        <v>2957.37</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -24995,16 +25070,16 @@
         <v>1</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>2786.54</v>
+        <v>2694.64</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.027908</v>
+        <v>0.080236</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>3.56</v>
+        <v>24.96</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
@@ -25016,22 +25091,22 @@
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>28</v>
+        <v>40.76</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>181.13</v>
+        <v>262.73</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>2786.54</v>
+        <v>2694.64</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>195.06</v>
+        <v>107.79</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25150,7 +25225,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>307328</v>
+        <v>307331</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>244</v>
@@ -25165,64 +25240,64 @@
         <v>83</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>2957.37</v>
+        <v>506.4</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>2694.64</v>
+        <v>499.2</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.080236</v>
+        <v>0.032832</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>24.96</v>
+        <v>5.78</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>40.76</v>
+        <v>61</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>262.73</v>
+        <v>7.2</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>2694.64</v>
+        <v>499.2</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>107.79</v>
+        <v>28.3</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25327,7 +25402,7 @@
         <v>78</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25341,10 +25416,10 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>307331</v>
+        <v>307333</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
@@ -25353,67 +25428,67 @@
         <v>249</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="H46" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J46" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>506.4</v>
+        <v>1023.78</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>499.2</v>
+        <v>1023.78</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.032832</v>
+        <v>0.010272</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>5.78</v>
+        <v>2.14</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>499.2</v>
+        <v>1023.78</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>28.3</v>
+        <v>71.66</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25518,7 +25593,7 @@
         <v>78</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25532,10 +25607,10 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>307333</v>
+        <v>307353</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>112</v>
+        <v>252</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
@@ -25544,40 +25619,40 @@
         <v>253</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="H47" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J47" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1023.78</v>
+        <v>2206.41</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>1023.78</v>
+        <v>1942</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.0004</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>2.14</v>
+        <v>5.8</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
@@ -25595,16 +25670,16 @@
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>0</v>
+        <v>179.41</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>1023.78</v>
+        <v>2027</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>71.66</v>
+        <v>81.07</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25723,7 +25798,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>307353</v>
+        <v>307370</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>256</v>
@@ -25738,43 +25813,43 @@
         <v>83</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>179</v>
+        <v>259</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>2206.41</v>
+        <v>683.81</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>1942</v>
+        <v>623.06</v>
       </c>
       <c r="P48" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.0004</v>
+        <v>0.006756</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
@@ -25786,16 +25861,16 @@
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>179.41</v>
+        <v>60.75</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>2027</v>
+        <v>623.06</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>81.07</v>
+        <v>43.61</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25900,7 +25975,7 @@
         <v>78</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="BK48" s="9" t="s">
         <v>75</v>
@@ -25914,79 +25989,79 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>307370</v>
+        <v>307375</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>683.81</v>
+        <v>8873.06</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>623.06</v>
+        <v>7890.92</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.006756</v>
+        <v>0.00636</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>28</v>
+        <v>44.19</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>60.75</v>
+        <v>982.14</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>623.06</v>
+        <v>7890.92</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>43.61</v>
+        <v>552.36</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26091,7 +26166,7 @@
         <v>78</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26105,34 +26180,34 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>307375</v>
+        <v>307378</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>8873.06</v>
+        <v>1369.96</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
@@ -26141,16 +26216,16 @@
         <v>5</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>7890.92</v>
+        <v>1349.3</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.00636</v>
+        <v>0.122352</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>7.8</v>
+        <v>6.73</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
@@ -26162,22 +26237,22 @@
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>44.19</v>
+        <v>61</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>982.14</v>
+        <v>20.66</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>7890.92</v>
+        <v>1349.3</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>552.36</v>
+        <v>94.45</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26296,79 +26371,79 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>307378</v>
+        <v>307391</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>1369.96</v>
+        <v>938.36</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>1349.3</v>
+        <v>855</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.122352</v>
+        <v>0</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V51" s="12" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="W51" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>20.66</v>
+        <v>83.36</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>1349.3</v>
+        <v>855</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>94.45</v>
+        <v>59.85</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26377,7 +26452,7 @@
         <v>0</v>
       </c>
       <c r="AD51" s="12" t="n">
-        <v>0</v>
+        <v>18.94</v>
       </c>
       <c r="AE51" s="12" t="n">
         <v>0</v>
@@ -26434,7 +26509,7 @@
         <v>74</v>
       </c>
       <c r="AW51" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX51" s="10" t="s">
         <v>77</v>
@@ -26458,25 +26533,25 @@
         <v>75</v>
       </c>
       <c r="BE51" s="14" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="BF51" s="9" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="BG51" s="9" t="s">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="BH51" s="14" t="s">
-        <v>75</v>
+        <v>274</v>
       </c>
       <c r="BI51" s="9" t="s">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="BK51" s="9" t="s">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="BL51" s="9" t="s">
         <v>75</v>
@@ -26487,34 +26562,34 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>307391</v>
+        <v>307392</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>938.36</v>
+        <v>375.13</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
@@ -26523,7 +26598,7 @@
         <v>1</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>855</v>
+        <v>341.8</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
@@ -26538,28 +26613,28 @@
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Y52" s="12" t="n">
-        <v>83.36</v>
+        <v>33.33</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>855</v>
+        <v>341.8</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>59.85</v>
+        <v>23.93</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26568,7 +26643,7 @@
         <v>0</v>
       </c>
       <c r="AD52" s="12" t="n">
-        <v>18.94</v>
+        <v>7.57</v>
       </c>
       <c r="AE52" s="12" t="n">
         <v>0</v>
@@ -26625,7 +26700,7 @@
         <v>74</v>
       </c>
       <c r="AW52" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX52" s="10" t="s">
         <v>77</v>
@@ -26649,25 +26724,25 @@
         <v>75</v>
       </c>
       <c r="BE52" s="14" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="BF52" s="9" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="BG52" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="BH52" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="BI52" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="BK52" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="BL52" s="9" t="s">
         <v>75</v>
@@ -26678,10 +26753,10 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>307392</v>
+        <v>307397</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>273</v>
+        <v>136</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
@@ -26690,22 +26765,22 @@
         <v>281</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>275</v>
+        <v>83</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>375.13</v>
+        <v>202.92</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
@@ -26714,16 +26789,16 @@
         <v>1</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>341.8</v>
+        <v>202.92</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0</v>
+        <v>0.00963</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
@@ -26741,16 +26816,16 @@
         <v>73</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Y53" s="12" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>341.8</v>
+        <v>202.92</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>23.93</v>
+        <v>14.2</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -26759,7 +26834,7 @@
         <v>0</v>
       </c>
       <c r="AD53" s="12" t="n">
-        <v>7.57</v>
+        <v>0</v>
       </c>
       <c r="AE53" s="12" t="n">
         <v>0</v>
@@ -26840,25 +26915,25 @@
         <v>75</v>
       </c>
       <c r="BE53" s="14" t="s">
-        <v>277</v>
+        <v>75</v>
       </c>
       <c r="BF53" s="9" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="BG53" s="9" t="s">
-        <v>262</v>
+        <v>78</v>
       </c>
       <c r="BH53" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI53" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ53" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="BI53" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="BJ53" s="9" t="s">
-        <v>284</v>
-      </c>
       <c r="BK53" s="9" t="s">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="BL53" s="9" t="s">
         <v>75</v>
@@ -26869,34 +26944,34 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>307397</v>
+        <v>307402</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>202.92</v>
+        <v>19503.54</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
@@ -26905,43 +26980,43 @@
         <v>1</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>202.92</v>
+        <v>19503.54</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0.00963</v>
+        <v>1.9872</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>1.65</v>
+        <v>5453.76</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V54" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W54" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Y54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>202.92</v>
+        <v>19503.54</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>14.2</v>
+        <v>1365.25</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27007,7 +27082,7 @@
         <v>74</v>
       </c>
       <c r="AW54" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX54" s="10" t="s">
         <v>77</v>
@@ -27046,7 +27121,7 @@
         <v>78</v>
       </c>
       <c r="BJ54" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BK54" s="9" t="s">
         <v>75</v>
@@ -27060,10 +27135,10 @@
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>307402</v>
+        <v>307425</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>152</v>
+        <v>287</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
@@ -27072,67 +27147,67 @@
         <v>288</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>262</v>
+        <v>169</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>19503.54</v>
+        <v>1389.3</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>19503.54</v>
+        <v>1389.3</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>1.9872</v>
+        <v>0</v>
       </c>
       <c r="R55" s="12" t="n">
-        <v>5453.76</v>
+        <v>2</v>
       </c>
       <c r="S55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="U55" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V55" s="12" t="n">
-        <v>56</v>
+        <v>38.5</v>
       </c>
       <c r="W55" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X55" s="9" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="Y55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>19503.54</v>
+        <v>1389.3</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>1365.25</v>
+        <v>41.12</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27198,7 +27273,7 @@
         <v>74</v>
       </c>
       <c r="AW55" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX55" s="10" t="s">
         <v>77</v>
@@ -27237,7 +27312,7 @@
         <v>78</v>
       </c>
       <c r="BJ55" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BK55" s="9" t="s">
         <v>75</v>
@@ -27250,741 +27325,1473 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4"/>
+      <c r="A56" s="8" t="n">
+        <v>307426</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>1807.1</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" s="12" t="n">
+        <v>1807.1</v>
+      </c>
+      <c r="P56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="13" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="R56" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="S56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="U56" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V56" s="12" t="n">
+        <v>46.01</v>
+      </c>
+      <c r="W56" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X56" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="12" t="n">
+        <v>1807.1</v>
+      </c>
+      <c r="AA56" s="12" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="AB56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV56" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW56" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX56" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF56" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG56" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH56" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI56" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ56" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="BK56" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL56" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM56" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="57" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
-      <c r="Q57" s="17"/>
-      <c r="R57" s="17"/>
-      <c r="S57" s="17"/>
-      <c r="T57" s="17"/>
-      <c r="U57" s="17"/>
-      <c r="V57" s="17"/>
+    <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="n">
+        <v>307463</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>1255.43</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>1163.96</v>
+      </c>
+      <c r="P57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="U57" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V57" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W57" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X57" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y57" s="12" t="n">
+        <v>91.47</v>
+      </c>
+      <c r="Z57" s="12" t="n">
+        <v>1163.96</v>
+      </c>
+      <c r="AA57" s="12" t="n">
+        <v>81.47</v>
+      </c>
+      <c r="AB57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="12" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="AE57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW57" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX57" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE57" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="BF57" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG57" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="BH57" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="BI57" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="BJ57" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="BK57" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="BL57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM57" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I58" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="J58" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K58" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L58" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M58" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="N58" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O58" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P58" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q58" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R58" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S58" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="T58" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="U58" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V58" s="18" t="s">
-        <v>37</v>
+    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="n">
+        <v>307464</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>1416.24</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O58" s="12" t="n">
+        <v>1290.43</v>
+      </c>
+      <c r="P58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="U58" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V58" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W58" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X58" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y58" s="12" t="n">
+        <v>125.81</v>
+      </c>
+      <c r="Z58" s="12" t="n">
+        <v>1290.43</v>
+      </c>
+      <c r="AA58" s="12" t="n">
+        <v>90.33</v>
+      </c>
+      <c r="AB58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="12" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="AE58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW58" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX58" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE58" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="BF58" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BG58" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="BH58" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="BI58" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="BJ58" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK58" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="BL58" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM58" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="19" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="19" t="n">
-        <v>85</v>
-      </c>
-      <c r="D59" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E59" s="19" t="n">
-        <v>11110.23</v>
-      </c>
-      <c r="F59" s="19" t="n">
-        <v>191595.98</v>
-      </c>
-      <c r="G59" s="19" t="n">
-        <v>11069.02</v>
-      </c>
-      <c r="H59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="19" t="n">
-        <v>116.23</v>
-      </c>
-      <c r="K59" s="19" t="n">
-        <v>202706.21</v>
-      </c>
-      <c r="L59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="20" t="n">
-        <v>30.38832</v>
-      </c>
-      <c r="S59" s="19" t="n">
-        <v>191410.98</v>
-      </c>
-      <c r="T59" s="19" t="n">
-        <v>202706.21</v>
-      </c>
-      <c r="U59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="19" t="n">
-        <v>0</v>
+      <c r="A59" s="8" t="n">
+        <v>307470</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L59" s="12" t="n">
+        <v>2535.23</v>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>2310</v>
+      </c>
+      <c r="P59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="R59" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="U59" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V59" s="12" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="W59" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X59" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y59" s="12" t="n">
+        <v>225.23</v>
+      </c>
+      <c r="Z59" s="12" t="n">
+        <v>2310</v>
+      </c>
+      <c r="AA59" s="12" t="n">
+        <v>92.4</v>
+      </c>
+      <c r="AB59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW59" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX59" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG59" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI59" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ59" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="BK59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM59" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F60" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G60" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I60" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J60" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K60" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="L60" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="M60" s="18" t="s">
-        <v>300</v>
+    <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="n">
+        <v>307472</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L60" s="12" t="n">
+        <v>2428.23</v>
+      </c>
+      <c r="M60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O60" s="12" t="n">
+        <v>2410.9</v>
+      </c>
+      <c r="P60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="13" t="n">
+        <v>0.244932</v>
+      </c>
+      <c r="R60" s="12" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="S60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="U60" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V60" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="W60" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X60" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y60" s="12" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="Z60" s="12" t="n">
+        <v>2410.9</v>
+      </c>
+      <c r="AA60" s="12" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="AB60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW60" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX60" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF60" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG60" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI60" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ60" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="BK60" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL60" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM60" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="19" t="n">
-        <v>6827.88</v>
-      </c>
-      <c r="B61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="19" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="E61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="19" t="n">
-        <v>0</v>
+      <c r="A61" s="8" t="n">
+        <v>307475</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>3351.6</v>
+      </c>
+      <c r="M61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="12" t="n">
+        <v>3351.6</v>
+      </c>
+      <c r="P61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="13" t="n">
+        <v>0.001236</v>
+      </c>
+      <c r="R61" s="12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="U61" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V61" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="W61" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X61" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="12" t="n">
+        <v>3351.6</v>
+      </c>
+      <c r="AA61" s="12" t="n">
+        <v>234.61</v>
+      </c>
+      <c r="AB61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV61" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW61" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX61" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF61" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG61" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI61" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ61" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="BK61" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL61" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM61" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="21"/>
-      <c r="L63" s="21"/>
-      <c r="M63" s="21"/>
-      <c r="N63" s="21"/>
-      <c r="O63" s="21"/>
-      <c r="P63" s="21"/>
-      <c r="Q63" s="21"/>
-      <c r="R63" s="21"/>
-      <c r="S63" s="21"/>
-      <c r="T63" s="21"/>
-      <c r="U63" s="21"/>
-      <c r="V63" s="21"/>
-      <c r="W63" s="21"/>
-      <c r="X63" s="21"/>
-      <c r="Y63" s="21"/>
-      <c r="Z63" s="21"/>
-      <c r="AA63" s="21"/>
-      <c r="AB63" s="21"/>
-      <c r="AC63" s="21"/>
-      <c r="AD63" s="21"/>
-      <c r="AE63" s="21"/>
-      <c r="AF63" s="21"/>
-      <c r="AG63" s="21"/>
-      <c r="AH63" s="21"/>
-      <c r="AI63" s="21"/>
-      <c r="AJ63" s="21"/>
-      <c r="AK63" s="21"/>
-      <c r="AL63" s="21"/>
-      <c r="AM63" s="21"/>
-      <c r="AN63" s="21"/>
-      <c r="AO63" s="21"/>
-      <c r="AP63" s="21"/>
-      <c r="AQ63" s="21"/>
-      <c r="AR63" s="21"/>
-      <c r="AS63" s="21"/>
-      <c r="AT63" s="21"/>
-      <c r="AU63" s="21"/>
-      <c r="AV63" s="21"/>
-      <c r="AW63" s="21"/>
-      <c r="AX63" s="21"/>
-      <c r="AY63" s="21"/>
-      <c r="AZ63" s="21"/>
-      <c r="BA63" s="21"/>
-      <c r="BB63" s="21"/>
-      <c r="BC63" s="21"/>
-      <c r="BD63" s="21"/>
-      <c r="BE63" s="21"/>
-      <c r="BF63" s="21"/>
-      <c r="BG63" s="21"/>
-      <c r="BH63" s="21"/>
-      <c r="BI63" s="21"/>
-      <c r="BJ63" s="21"/>
-      <c r="BK63" s="21"/>
-      <c r="BL63" s="21"/>
-      <c r="BM63" s="21"/>
+      <c r="A63" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="17"/>
+      <c r="O63" s="17"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="17"/>
+      <c r="V63" s="17"/>
     </row>
-    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4"/>
-      <c r="U64" s="4"/>
-      <c r="V64" s="4"/>
-      <c r="W64" s="4"/>
-      <c r="X64" s="4"/>
-      <c r="Y64" s="4"/>
-      <c r="Z64" s="4"/>
-      <c r="AA64" s="4"/>
-      <c r="AB64" s="4"/>
-      <c r="AC64" s="4"/>
-      <c r="AD64" s="4"/>
-      <c r="AE64" s="4"/>
-      <c r="AF64" s="4"/>
-      <c r="AG64" s="4"/>
-      <c r="AH64" s="4"/>
-      <c r="AI64" s="4"/>
-      <c r="AJ64" s="4"/>
-      <c r="AK64" s="4"/>
-      <c r="AL64" s="4"/>
-      <c r="AM64" s="4"/>
-      <c r="AN64" s="4"/>
-      <c r="AO64" s="4"/>
-      <c r="AP64" s="4"/>
-      <c r="AQ64" s="4"/>
-      <c r="AR64" s="4"/>
-      <c r="AS64" s="4"/>
-      <c r="AT64" s="4"/>
-      <c r="AU64" s="4"/>
-      <c r="AV64" s="4"/>
-      <c r="AW64" s="4"/>
-      <c r="AX64" s="4"/>
-      <c r="AY64" s="4"/>
-      <c r="AZ64" s="4"/>
-      <c r="BA64" s="4"/>
-      <c r="BB64" s="4"/>
-      <c r="BC64" s="4"/>
-      <c r="BD64" s="4"/>
-      <c r="BE64" s="4"/>
-      <c r="BF64" s="4"/>
-      <c r="BG64" s="4"/>
-      <c r="BH64" s="4"/>
-      <c r="BI64" s="4"/>
-      <c r="BJ64" s="4"/>
-      <c r="BK64" s="4"/>
-      <c r="BL64" s="4"/>
-      <c r="BM64" s="4"/>
+    <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="J64" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K64" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L64" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M64" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="N64" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O64" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P64" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R64" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S64" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="T64" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="U64" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V64" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
-      <c r="Z65" s="4"/>
-      <c r="AA65" s="4"/>
-      <c r="AB65" s="4"/>
-      <c r="AC65" s="4"/>
-      <c r="AD65" s="4"/>
-      <c r="AE65" s="4"/>
-      <c r="AF65" s="4"/>
-      <c r="AG65" s="4"/>
-      <c r="AH65" s="4"/>
-      <c r="AI65" s="4"/>
-      <c r="AJ65" s="4"/>
-      <c r="AK65" s="4"/>
-      <c r="AL65" s="4"/>
-      <c r="AM65" s="4"/>
-      <c r="AN65" s="4"/>
-      <c r="AO65" s="4"/>
-      <c r="AP65" s="4"/>
-      <c r="AQ65" s="4"/>
-      <c r="AR65" s="4"/>
-      <c r="AS65" s="4"/>
-      <c r="AT65" s="4"/>
-      <c r="AU65" s="4"/>
-      <c r="AV65" s="4"/>
-      <c r="AW65" s="4"/>
-      <c r="AX65" s="4"/>
-      <c r="AY65" s="4"/>
-      <c r="AZ65" s="4"/>
-      <c r="BA65" s="4"/>
-      <c r="BB65" s="4"/>
-      <c r="BC65" s="4"/>
-      <c r="BD65" s="4"/>
-      <c r="BE65" s="4"/>
-      <c r="BF65" s="4"/>
-      <c r="BG65" s="4"/>
-      <c r="BH65" s="4"/>
-      <c r="BI65" s="4"/>
-      <c r="BJ65" s="4"/>
-      <c r="BK65" s="4"/>
-      <c r="BL65" s="4"/>
-      <c r="BM65" s="4"/>
+      <c r="A65" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>85</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>7142.8</v>
+      </c>
+      <c r="F65" s="19" t="n">
+        <v>134047.67</v>
+      </c>
+      <c r="G65" s="19" t="n">
+        <v>8106.31</v>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>231.29</v>
+      </c>
+      <c r="K65" s="19" t="n">
+        <v>141190.47</v>
+      </c>
+      <c r="L65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="20" t="n">
+        <v>40.257883</v>
+      </c>
+      <c r="S65" s="19" t="n">
+        <v>133862.67</v>
+      </c>
+      <c r="T65" s="19" t="n">
+        <v>141190.47</v>
+      </c>
+      <c r="U65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
-      <c r="Z66" s="4"/>
-      <c r="AA66" s="4"/>
-      <c r="AB66" s="4"/>
-      <c r="AC66" s="4"/>
-      <c r="AD66" s="4"/>
-      <c r="AE66" s="4"/>
-      <c r="AF66" s="4"/>
-      <c r="AG66" s="4"/>
-      <c r="AH66" s="4"/>
-      <c r="AI66" s="4"/>
-      <c r="AJ66" s="4"/>
-      <c r="AK66" s="4"/>
-      <c r="AL66" s="4"/>
-      <c r="AM66" s="4"/>
-      <c r="AN66" s="4"/>
-      <c r="AO66" s="4"/>
-      <c r="AP66" s="4"/>
-      <c r="AQ66" s="4"/>
-      <c r="AR66" s="4"/>
-      <c r="AS66" s="4"/>
-      <c r="AT66" s="4"/>
-      <c r="AU66" s="4"/>
-      <c r="AV66" s="4"/>
-      <c r="AW66" s="4"/>
-      <c r="AX66" s="4"/>
-      <c r="AY66" s="4"/>
-      <c r="AZ66" s="4"/>
-      <c r="BA66" s="4"/>
-      <c r="BB66" s="4"/>
-      <c r="BC66" s="4"/>
-      <c r="BD66" s="4"/>
-      <c r="BE66" s="4"/>
-      <c r="BF66" s="4"/>
-      <c r="BG66" s="4"/>
-      <c r="BH66" s="4"/>
-      <c r="BI66" s="4"/>
-      <c r="BJ66" s="4"/>
-      <c r="BK66" s="4"/>
-      <c r="BL66" s="4"/>
-      <c r="BM66" s="4"/>
+    <row r="66" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I66" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J66" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K66" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="L66" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="M66" s="18" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="4"/>
-      <c r="AB67" s="4"/>
-      <c r="AC67" s="4"/>
-      <c r="AD67" s="4"/>
-      <c r="AE67" s="4"/>
-      <c r="AF67" s="4"/>
-      <c r="AG67" s="4"/>
-      <c r="AH67" s="4"/>
-      <c r="AI67" s="4"/>
-      <c r="AJ67" s="4"/>
-      <c r="AK67" s="4"/>
-      <c r="AL67" s="4"/>
-      <c r="AM67" s="4"/>
-      <c r="AN67" s="4"/>
-      <c r="AO67" s="4"/>
-      <c r="AP67" s="4"/>
-      <c r="AQ67" s="4"/>
-      <c r="AR67" s="4"/>
-      <c r="AS67" s="4"/>
-      <c r="AT67" s="4"/>
-      <c r="AU67" s="4"/>
-      <c r="AV67" s="4"/>
-      <c r="AW67" s="4"/>
-      <c r="AX67" s="4"/>
-      <c r="AY67" s="4"/>
-      <c r="AZ67" s="4"/>
-      <c r="BA67" s="4"/>
-      <c r="BB67" s="4"/>
-      <c r="BC67" s="4"/>
-      <c r="BD67" s="4"/>
-      <c r="BE67" s="4"/>
-      <c r="BF67" s="4"/>
-      <c r="BG67" s="4"/>
-      <c r="BH67" s="4"/>
-      <c r="BI67" s="4"/>
-      <c r="BJ67" s="4"/>
-      <c r="BK67" s="4"/>
-      <c r="BL67" s="4"/>
-      <c r="BM67" s="4"/>
+      <c r="A67" s="19" t="n">
+        <v>6239.61</v>
+      </c>
+      <c r="B67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="E67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
-      <c r="Y68" s="4"/>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="4"/>
-      <c r="AB68" s="4"/>
-      <c r="AC68" s="4"/>
-      <c r="AD68" s="4"/>
-      <c r="AE68" s="4"/>
-      <c r="AF68" s="4"/>
-      <c r="AG68" s="4"/>
-      <c r="AH68" s="4"/>
-      <c r="AI68" s="4"/>
-      <c r="AJ68" s="4"/>
-      <c r="AK68" s="4"/>
-      <c r="AL68" s="4"/>
-      <c r="AM68" s="4"/>
-      <c r="AN68" s="4"/>
-      <c r="AO68" s="4"/>
-      <c r="AP68" s="4"/>
-      <c r="AQ68" s="4"/>
-      <c r="AR68" s="4"/>
-      <c r="AS68" s="4"/>
-      <c r="AT68" s="4"/>
-      <c r="AU68" s="4"/>
-      <c r="AV68" s="4"/>
-      <c r="AW68" s="4"/>
-      <c r="AX68" s="4"/>
-      <c r="AY68" s="4"/>
-      <c r="AZ68" s="4"/>
-      <c r="BA68" s="4"/>
-      <c r="BB68" s="4"/>
-      <c r="BC68" s="4"/>
-      <c r="BD68" s="4"/>
-      <c r="BE68" s="4"/>
-      <c r="BF68" s="4"/>
-      <c r="BG68" s="4"/>
-      <c r="BH68" s="4"/>
-      <c r="BI68" s="4"/>
-      <c r="BJ68" s="4"/>
-      <c r="BK68" s="4"/>
-      <c r="BL68" s="4"/>
-      <c r="BM68" s="4"/>
+      <c r="A68" s="4"/>
     </row>
-    <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
-      <c r="Y69" s="4"/>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
-      <c r="AB69" s="4"/>
-      <c r="AC69" s="4"/>
-      <c r="AD69" s="4"/>
-      <c r="AE69" s="4"/>
-      <c r="AF69" s="4"/>
-      <c r="AG69" s="4"/>
-      <c r="AH69" s="4"/>
-      <c r="AI69" s="4"/>
-      <c r="AJ69" s="4"/>
-      <c r="AK69" s="4"/>
-      <c r="AL69" s="4"/>
-      <c r="AM69" s="4"/>
-      <c r="AN69" s="4"/>
-      <c r="AO69" s="4"/>
-      <c r="AP69" s="4"/>
-      <c r="AQ69" s="4"/>
-      <c r="AR69" s="4"/>
-      <c r="AS69" s="4"/>
-      <c r="AT69" s="4"/>
-      <c r="AU69" s="4"/>
-      <c r="AV69" s="4"/>
-      <c r="AW69" s="4"/>
-      <c r="AX69" s="4"/>
-      <c r="AY69" s="4"/>
-      <c r="AZ69" s="4"/>
-      <c r="BA69" s="4"/>
-      <c r="BB69" s="4"/>
-      <c r="BC69" s="4"/>
-      <c r="BD69" s="4"/>
-      <c r="BE69" s="4"/>
-      <c r="BF69" s="4"/>
-      <c r="BG69" s="4"/>
-      <c r="BH69" s="4"/>
-      <c r="BI69" s="4"/>
-      <c r="BJ69" s="4"/>
-      <c r="BK69" s="4"/>
-      <c r="BL69" s="4"/>
-      <c r="BM69" s="4"/>
+    <row r="69" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="21"/>
+      <c r="R69" s="21"/>
+      <c r="S69" s="21"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="21"/>
+      <c r="V69" s="21"/>
+      <c r="W69" s="21"/>
+      <c r="X69" s="21"/>
+      <c r="Y69" s="21"/>
+      <c r="Z69" s="21"/>
+      <c r="AA69" s="21"/>
+      <c r="AB69" s="21"/>
+      <c r="AC69" s="21"/>
+      <c r="AD69" s="21"/>
+      <c r="AE69" s="21"/>
+      <c r="AF69" s="21"/>
+      <c r="AG69" s="21"/>
+      <c r="AH69" s="21"/>
+      <c r="AI69" s="21"/>
+      <c r="AJ69" s="21"/>
+      <c r="AK69" s="21"/>
+      <c r="AL69" s="21"/>
+      <c r="AM69" s="21"/>
+      <c r="AN69" s="21"/>
+      <c r="AO69" s="21"/>
+      <c r="AP69" s="21"/>
+      <c r="AQ69" s="21"/>
+      <c r="AR69" s="21"/>
+      <c r="AS69" s="21"/>
+      <c r="AT69" s="21"/>
+      <c r="AU69" s="21"/>
+      <c r="AV69" s="21"/>
+      <c r="AW69" s="21"/>
+      <c r="AX69" s="21"/>
+      <c r="AY69" s="21"/>
+      <c r="AZ69" s="21"/>
+      <c r="BA69" s="21"/>
+      <c r="BB69" s="21"/>
+      <c r="BC69" s="21"/>
+      <c r="BD69" s="21"/>
+      <c r="BE69" s="21"/>
+      <c r="BF69" s="21"/>
+      <c r="BG69" s="21"/>
+      <c r="BH69" s="21"/>
+      <c r="BI69" s="21"/>
+      <c r="BJ69" s="21"/>
+      <c r="BK69" s="21"/>
+      <c r="BL69" s="21"/>
+      <c r="BM69" s="21"/>
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -28053,7 +28860,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -28122,7 +28929,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -28191,7 +28998,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -28258,8 +29065,422 @@
       <c r="BL73" s="4"/>
       <c r="BM73" s="4"/>
     </row>
+    <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+      <c r="T74" s="4"/>
+      <c r="U74" s="4"/>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="4"/>
+      <c r="AB74" s="4"/>
+      <c r="AC74" s="4"/>
+      <c r="AD74" s="4"/>
+      <c r="AE74" s="4"/>
+      <c r="AF74" s="4"/>
+      <c r="AG74" s="4"/>
+      <c r="AH74" s="4"/>
+      <c r="AI74" s="4"/>
+      <c r="AJ74" s="4"/>
+      <c r="AK74" s="4"/>
+      <c r="AL74" s="4"/>
+      <c r="AM74" s="4"/>
+      <c r="AN74" s="4"/>
+      <c r="AO74" s="4"/>
+      <c r="AP74" s="4"/>
+      <c r="AQ74" s="4"/>
+      <c r="AR74" s="4"/>
+      <c r="AS74" s="4"/>
+      <c r="AT74" s="4"/>
+      <c r="AU74" s="4"/>
+      <c r="AV74" s="4"/>
+      <c r="AW74" s="4"/>
+      <c r="AX74" s="4"/>
+      <c r="AY74" s="4"/>
+      <c r="AZ74" s="4"/>
+      <c r="BA74" s="4"/>
+      <c r="BB74" s="4"/>
+      <c r="BC74" s="4"/>
+      <c r="BD74" s="4"/>
+      <c r="BE74" s="4"/>
+      <c r="BF74" s="4"/>
+      <c r="BG74" s="4"/>
+      <c r="BH74" s="4"/>
+      <c r="BI74" s="4"/>
+      <c r="BJ74" s="4"/>
+      <c r="BK74" s="4"/>
+      <c r="BL74" s="4"/>
+      <c r="BM74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="4"/>
+      <c r="AB75" s="4"/>
+      <c r="AC75" s="4"/>
+      <c r="AD75" s="4"/>
+      <c r="AE75" s="4"/>
+      <c r="AF75" s="4"/>
+      <c r="AG75" s="4"/>
+      <c r="AH75" s="4"/>
+      <c r="AI75" s="4"/>
+      <c r="AJ75" s="4"/>
+      <c r="AK75" s="4"/>
+      <c r="AL75" s="4"/>
+      <c r="AM75" s="4"/>
+      <c r="AN75" s="4"/>
+      <c r="AO75" s="4"/>
+      <c r="AP75" s="4"/>
+      <c r="AQ75" s="4"/>
+      <c r="AR75" s="4"/>
+      <c r="AS75" s="4"/>
+      <c r="AT75" s="4"/>
+      <c r="AU75" s="4"/>
+      <c r="AV75" s="4"/>
+      <c r="AW75" s="4"/>
+      <c r="AX75" s="4"/>
+      <c r="AY75" s="4"/>
+      <c r="AZ75" s="4"/>
+      <c r="BA75" s="4"/>
+      <c r="BB75" s="4"/>
+      <c r="BC75" s="4"/>
+      <c r="BD75" s="4"/>
+      <c r="BE75" s="4"/>
+      <c r="BF75" s="4"/>
+      <c r="BG75" s="4"/>
+      <c r="BH75" s="4"/>
+      <c r="BI75" s="4"/>
+      <c r="BJ75" s="4"/>
+      <c r="BK75" s="4"/>
+      <c r="BL75" s="4"/>
+      <c r="BM75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="4"/>
+      <c r="AB76" s="4"/>
+      <c r="AC76" s="4"/>
+      <c r="AD76" s="4"/>
+      <c r="AE76" s="4"/>
+      <c r="AF76" s="4"/>
+      <c r="AG76" s="4"/>
+      <c r="AH76" s="4"/>
+      <c r="AI76" s="4"/>
+      <c r="AJ76" s="4"/>
+      <c r="AK76" s="4"/>
+      <c r="AL76" s="4"/>
+      <c r="AM76" s="4"/>
+      <c r="AN76" s="4"/>
+      <c r="AO76" s="4"/>
+      <c r="AP76" s="4"/>
+      <c r="AQ76" s="4"/>
+      <c r="AR76" s="4"/>
+      <c r="AS76" s="4"/>
+      <c r="AT76" s="4"/>
+      <c r="AU76" s="4"/>
+      <c r="AV76" s="4"/>
+      <c r="AW76" s="4"/>
+      <c r="AX76" s="4"/>
+      <c r="AY76" s="4"/>
+      <c r="AZ76" s="4"/>
+      <c r="BA76" s="4"/>
+      <c r="BB76" s="4"/>
+      <c r="BC76" s="4"/>
+      <c r="BD76" s="4"/>
+      <c r="BE76" s="4"/>
+      <c r="BF76" s="4"/>
+      <c r="BG76" s="4"/>
+      <c r="BH76" s="4"/>
+      <c r="BI76" s="4"/>
+      <c r="BJ76" s="4"/>
+      <c r="BK76" s="4"/>
+      <c r="BL76" s="4"/>
+      <c r="BM76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="4"/>
+      <c r="AB77" s="4"/>
+      <c r="AC77" s="4"/>
+      <c r="AD77" s="4"/>
+      <c r="AE77" s="4"/>
+      <c r="AF77" s="4"/>
+      <c r="AG77" s="4"/>
+      <c r="AH77" s="4"/>
+      <c r="AI77" s="4"/>
+      <c r="AJ77" s="4"/>
+      <c r="AK77" s="4"/>
+      <c r="AL77" s="4"/>
+      <c r="AM77" s="4"/>
+      <c r="AN77" s="4"/>
+      <c r="AO77" s="4"/>
+      <c r="AP77" s="4"/>
+      <c r="AQ77" s="4"/>
+      <c r="AR77" s="4"/>
+      <c r="AS77" s="4"/>
+      <c r="AT77" s="4"/>
+      <c r="AU77" s="4"/>
+      <c r="AV77" s="4"/>
+      <c r="AW77" s="4"/>
+      <c r="AX77" s="4"/>
+      <c r="AY77" s="4"/>
+      <c r="AZ77" s="4"/>
+      <c r="BA77" s="4"/>
+      <c r="BB77" s="4"/>
+      <c r="BC77" s="4"/>
+      <c r="BD77" s="4"/>
+      <c r="BE77" s="4"/>
+      <c r="BF77" s="4"/>
+      <c r="BG77" s="4"/>
+      <c r="BH77" s="4"/>
+      <c r="BI77" s="4"/>
+      <c r="BJ77" s="4"/>
+      <c r="BK77" s="4"/>
+      <c r="BL77" s="4"/>
+      <c r="BM77" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="4"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="4"/>
+      <c r="AB78" s="4"/>
+      <c r="AC78" s="4"/>
+      <c r="AD78" s="4"/>
+      <c r="AE78" s="4"/>
+      <c r="AF78" s="4"/>
+      <c r="AG78" s="4"/>
+      <c r="AH78" s="4"/>
+      <c r="AI78" s="4"/>
+      <c r="AJ78" s="4"/>
+      <c r="AK78" s="4"/>
+      <c r="AL78" s="4"/>
+      <c r="AM78" s="4"/>
+      <c r="AN78" s="4"/>
+      <c r="AO78" s="4"/>
+      <c r="AP78" s="4"/>
+      <c r="AQ78" s="4"/>
+      <c r="AR78" s="4"/>
+      <c r="AS78" s="4"/>
+      <c r="AT78" s="4"/>
+      <c r="AU78" s="4"/>
+      <c r="AV78" s="4"/>
+      <c r="AW78" s="4"/>
+      <c r="AX78" s="4"/>
+      <c r="AY78" s="4"/>
+      <c r="AZ78" s="4"/>
+      <c r="BA78" s="4"/>
+      <c r="BB78" s="4"/>
+      <c r="BC78" s="4"/>
+      <c r="BD78" s="4"/>
+      <c r="BE78" s="4"/>
+      <c r="BF78" s="4"/>
+      <c r="BG78" s="4"/>
+      <c r="BH78" s="4"/>
+      <c r="BI78" s="4"/>
+      <c r="BJ78" s="4"/>
+      <c r="BK78" s="4"/>
+      <c r="BL78" s="4"/>
+      <c r="BM78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="4"/>
+      <c r="U79" s="4"/>
+      <c r="V79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="4"/>
+      <c r="AB79" s="4"/>
+      <c r="AC79" s="4"/>
+      <c r="AD79" s="4"/>
+      <c r="AE79" s="4"/>
+      <c r="AF79" s="4"/>
+      <c r="AG79" s="4"/>
+      <c r="AH79" s="4"/>
+      <c r="AI79" s="4"/>
+      <c r="AJ79" s="4"/>
+      <c r="AK79" s="4"/>
+      <c r="AL79" s="4"/>
+      <c r="AM79" s="4"/>
+      <c r="AN79" s="4"/>
+      <c r="AO79" s="4"/>
+      <c r="AP79" s="4"/>
+      <c r="AQ79" s="4"/>
+      <c r="AR79" s="4"/>
+      <c r="AS79" s="4"/>
+      <c r="AT79" s="4"/>
+      <c r="AU79" s="4"/>
+      <c r="AV79" s="4"/>
+      <c r="AW79" s="4"/>
+      <c r="AX79" s="4"/>
+      <c r="AY79" s="4"/>
+      <c r="AZ79" s="4"/>
+      <c r="BA79" s="4"/>
+      <c r="BB79" s="4"/>
+      <c r="BC79" s="4"/>
+      <c r="BD79" s="4"/>
+      <c r="BE79" s="4"/>
+      <c r="BF79" s="4"/>
+      <c r="BG79" s="4"/>
+      <c r="BH79" s="4"/>
+      <c r="BI79" s="4"/>
+      <c r="BJ79" s="4"/>
+      <c r="BK79" s="4"/>
+      <c r="BL79" s="4"/>
+      <c r="BM79" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="73">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -28315,18 +29536,24 @@
     <mergeCell ref="B53:E53"/>
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B55:E55"/>
-    <mergeCell ref="A57:V57"/>
-    <mergeCell ref="A63:BM63"/>
-    <mergeCell ref="A64:BM64"/>
-    <mergeCell ref="A65:BM65"/>
-    <mergeCell ref="A66:BM66"/>
-    <mergeCell ref="A67:BM67"/>
-    <mergeCell ref="A68:BM68"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A63:V63"/>
     <mergeCell ref="A69:BM69"/>
     <mergeCell ref="A70:BM70"/>
     <mergeCell ref="A71:BM71"/>
     <mergeCell ref="A72:BM72"/>
     <mergeCell ref="A73:BM73"/>
+    <mergeCell ref="A74:BM74"/>
+    <mergeCell ref="A75:BM75"/>
+    <mergeCell ref="A76:BM76"/>
+    <mergeCell ref="A77:BM77"/>
+    <mergeCell ref="A78:BM78"/>
+    <mergeCell ref="A79:BM79"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="332">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 19/05/2026 05:30:31</t>
+    <t xml:space="preserve">Emitido em: 20/05/2026 05:30:32</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -214,633 +214,597 @@
     <t xml:space="preserve">Fornecedor substituto tributário</t>
   </si>
   <si>
+    <t xml:space="preserve">36.025 - FRESNOMAQ INDUSTRIA DE MAQUINAS S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.320,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ag. chegada da mercadoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - OBJETIVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">32260406337280001186550010000599891874418073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.486 - ROCA SANITARIOS BRASIL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.352.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013520891393486645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.352.088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013520881842296450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.352.087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013520871369635550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.353.846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.070,58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260475801902000126550000013538461061418038</t>
+  </si>
+  <si>
     <t xml:space="preserve">17.596 - LIGHT ENGINE ILUMINACAO</t>
   </si>
   <si>
-    <t xml:space="preserve">97.832</t>
+    <t xml:space="preserve">98.006</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.481,49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ag. chegada da mercadoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - OBJETIVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260524546165000393550040000980061727013914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.413,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260524546165000393550040000980051314694727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.532,07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260509306858000153550010000709261237889907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.891 - STUDIOLUCE ILUMINACAO IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.193,88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510599342000123550020001044791920149108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260511389565000200570050003989501000852039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54,66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050803981473767772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050803991044656674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.122,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804001438231179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.768,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575821546000102550040001403101130982608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.171,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260530228132000136550010000092891773232410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260530228132000136550010000092901435141905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804101599979210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.304.072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.534,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260550949528001232550010023040721860830987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">261.170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.391,61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260558329608000144550010002611701002611716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.768,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829941322627923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.083.080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">461,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050830801584930623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">886,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829741533961189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.259 - IMD COMERCIO DE MOVEIS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.276,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260503961151000447550060004095291908594429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 - TRAMONTINA TEEC S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">684.266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.705,98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260501554846000136550010006842661501852320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">522,97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829761067401777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829751121039328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.385,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260535635346000140550020001121771279175684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.762,99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260535635346000140550020001121781534580370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.119,25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006394171502977260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.850 - DEXCO S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.720,43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - FILIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260597837181005378550010001623201200486876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">446,07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829781228464036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">273,43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829771206775953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.209,61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829971596208423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.083.076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050830761221787698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.727,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260524546165000393550040000981601962020810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.783,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006396901908194720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.967,67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006397081888143897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.940 - BLUMENAU ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">817.980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.957,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260579416459000120550010008179801823855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">506,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007578201370188640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.023,78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006399571193331798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.206,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260510691158000370550010002932181828516528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.329 - S &amp; L SOUZA E LIMA FABRICACAO E COMERCIO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">683,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510394416000195550010000482621000254830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">261.906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.873,06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260558329608000144550010002619061002619078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.369,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007586021560856835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938,36</t>
   </si>
   <si>
     <t xml:space="preserve">S</t>
   </si>
   <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260424546165000393550040000978321120610091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.025 - FRESNOMAQ INDUSTRIA DE MAQUINAS S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.320,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32260406337280001186550010000599891874418073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.486 - ROCA SANITARIOS BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.352.089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">278,41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260475801902000126550000013520891393486645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.352.088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260475801902000126550000013520881842296450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.352.087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260475801902000126550000013520871369635550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.353.846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.070,58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260475801902000126550000013538461061418038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">635.928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.233,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006359281745462137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260524546165000393550040000980061727013914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.413,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260524546165000393550040000980051314694727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.532,07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260509306858000153550010000709261237889907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.891 - STUDIOLUCE ILUMINACAO IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.193,88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260510599342000123550020001044791920149108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260511389565000200570050003989501000852039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54,66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050803981473767772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">264,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050803991044656674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.122,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804001438231179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.768,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575821546000102550040001403101130982608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.171,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260530228132000136550010000092891773232410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63,31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260530228132000136550010000092901435141905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804101599979210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.304.072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.534,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260550949528001232550010023040721860830987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">261.170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.391,61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260558329608000144550010002611701002611716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.582 - GRUPO MARMO E HIME COMERCIO, IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.867,78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260520587017000285550010000397411851274488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.768,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829941322627923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.083.080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">461,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050830801584930623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">886,44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829741533961189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.259 - IMD COMERCIO DE MOVEIS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409.529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.276,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260503961151000447550060004095291908594429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 - TRAMONTINA TEEC S.A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">684.266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.705,98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260501554846000136550010006842661501852320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">522,97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829761067401777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829751121039328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.385,63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260535635346000140550020001121771279175684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.762,99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260535635346000140550020001121781534580370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.119,25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006394171502977260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.850 - DEXCO S.A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.720,43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - FILIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260597837181005378550010001623201200486876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">446,07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829781228464036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">273,43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829771206775953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.209,61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829971596208423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.083.076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050830761221787698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.727,12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260524546165000393550040000981601962020810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.783,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006396901908194720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.967,67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006397081888143897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.940 - BLUMENAU ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">817.980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.957,37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260579416459000120550010008179801823855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">506,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007578201370188640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.023,78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006399571193331798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.206,41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260510691158000370550010002932181828516528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.329 - S &amp; L SOUZA E LIMA FABRICACAO E COMERCIO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">683,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260510394416000195550010000482621000254830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">261.906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.873,06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260558329608000144550010002619061002619078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.369,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007586021560856835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">938,36</t>
-  </si>
-  <si>
     <t xml:space="preserve">399.348</t>
   </si>
   <si>
@@ -968,6 +932,33 @@
   </si>
   <si>
     <t xml:space="preserve">42260575339051000141550080006428511520912936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.599 - S&amp;L IMPORTS COMERCIO DE IMPORTACAO E EXPORTACAO DE PRODUTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">960,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260533765312000145550010000197501000329040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.980,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260512077181000133550030002249611055606702</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17213,7 +17204,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM79"/>
+  <dimension ref="A1:BM78"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17585,7 +17576,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>306559</v>
+        <v>306701</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17612,28 +17603,28 @@
         <v>70</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>1481.49</v>
+        <v>1320</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>1249.88</v>
+        <v>1320</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>0</v>
+        <v>0.199656</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>0</v>
+        <v>8.76</v>
       </c>
       <c r="S5" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T5" s="14" t="s">
         <v>71</v>
@@ -17642,7 +17633,7 @@
         <v>72</v>
       </c>
       <c r="V5" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="W5" s="9" t="s">
         <v>73</v>
@@ -17651,13 +17642,13 @@
         <v>68</v>
       </c>
       <c r="Y5" s="12" t="n">
-        <v>131.61</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>1349.88</v>
+        <v>1320</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>84.33</v>
+        <v>158.4</v>
       </c>
       <c r="AB5" s="12" t="n">
         <v>0</v>
@@ -17776,7 +17767,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>306701</v>
+        <v>306712</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>81</v>
@@ -17791,19 +17782,19 @@
         <v>83</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>1320</v>
+        <v>278.41</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
@@ -17812,43 +17803,43 @@
         <v>1</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>1320</v>
+        <v>278.41</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.199656</v>
+        <v>0.054</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>8.76</v>
+        <v>18.6</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="Y6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>1320</v>
+        <v>278.41</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>158.4</v>
+        <v>19.49</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17914,10 +17905,10 @@
         <v>74</v>
       </c>
       <c r="AW6" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX6" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY6" s="14" t="s">
         <v>75</v>
@@ -17953,7 +17944,7 @@
         <v>78</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="BK6" s="9" t="s">
         <v>75</v>
@@ -17967,25 +17958,25 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>306712</v>
+        <v>306714</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>78</v>
@@ -17994,7 +17985,7 @@
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>278.41</v>
+        <v>567.53</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -18003,22 +17994,22 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>278.41</v>
+        <v>567.53</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.054</v>
+        <v>0.08136</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>18.6</v>
+        <v>26.3</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
@@ -18030,16 +18021,16 @@
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="Y7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>278.41</v>
+        <v>567.53</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>19.49</v>
+        <v>39.73</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -18105,10 +18096,10 @@
         <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -18144,7 +18135,7 @@
         <v>78</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -18158,25 +18149,25 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>306714</v>
+        <v>306715</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>78</v>
@@ -18185,7 +18176,7 @@
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>567.53</v>
+        <v>814.81</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -18194,22 +18185,22 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>567.53</v>
+        <v>814.81</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.08136</v>
+        <v>0.034656</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>26.3</v>
+        <v>16.14</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
@@ -18221,16 +18212,16 @@
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="Y8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>567.53</v>
+        <v>814.81</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>39.73</v>
+        <v>57.04</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18296,10 +18287,10 @@
         <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -18335,7 +18326,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18349,25 +18340,25 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306715</v>
+        <v>306717</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>78</v>
@@ -18376,7 +18367,7 @@
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>814.81</v>
+        <v>1070.58</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -18385,22 +18376,22 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>814.81</v>
+        <v>1070.58</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.034656</v>
+        <v>0.095984</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>16.14</v>
+        <v>41.84</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
@@ -18412,16 +18403,16 @@
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>814.81</v>
+        <v>1070.58</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>57.04</v>
+        <v>74.94</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18487,10 +18478,10 @@
         <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18526,7 +18517,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18540,34 +18531,34 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>306717</v>
+        <v>307049</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="J10" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1070.58</v>
+        <v>174.72</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18576,16 +18567,16 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>1070.58</v>
+        <v>159.2</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.095984</v>
+        <v>0</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>41.84</v>
+        <v>0</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
@@ -18597,22 +18588,22 @@
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>0</v>
+        <v>15.52</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>1070.58</v>
+        <v>159.2</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>74.94</v>
+        <v>11.14</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18678,10 +18669,10 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18731,79 +18722,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>306942</v>
+        <v>307051</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>2233.8</v>
+        <v>7413.56</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>2233.8</v>
+        <v>6754.95</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.013104</v>
+        <v>0</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>658.61</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>2233.8</v>
+        <v>6754.95</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>156.37</v>
+        <v>468.39</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18869,7 +18860,7 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>77</v>
@@ -18908,7 +18899,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18922,79 +18913,79 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>307049</v>
+        <v>307055</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>174.72</v>
+        <v>2532.07</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>159.2</v>
+        <v>2307.12</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0</v>
+        <v>0.076024</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>0</v>
+        <v>11.04</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>15.52</v>
+        <v>224.95</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>159.2</v>
+        <v>2307.12</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>11.14</v>
+        <v>161.49</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -19060,7 +19051,7 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX12" s="10" t="s">
         <v>77</v>
@@ -19099,7 +19090,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19113,43 +19104,43 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>307051</v>
+        <v>307083</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>114</v>
-      </c>
       <c r="J13" s="9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>7413.56</v>
+        <v>1193.88</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>6754.95</v>
+        <v>1087.82</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
@@ -19164,28 +19155,28 @@
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>658.61</v>
+        <v>106.06</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>6754.95</v>
+        <v>1087.82</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>468.39</v>
+        <v>43.51</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19194,7 +19185,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="12" t="n">
-        <v>0</v>
+        <v>89.72</v>
       </c>
       <c r="AE13" s="12" t="n">
         <v>0</v>
@@ -19251,7 +19242,7 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX13" s="10" t="s">
         <v>77</v>
@@ -19275,25 +19266,25 @@
         <v>75</v>
       </c>
       <c r="BE13" s="14" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="BF13" s="9" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="BH13" s="14" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="BI13" s="9" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="BK13" s="9" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="BL13" s="9" t="s">
         <v>75</v>
@@ -19304,79 +19295,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>307055</v>
+        <v>307084</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>2532.07</v>
+        <v>54.66</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>2307.12</v>
+        <v>51.32</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.076024</v>
+        <v>0.134276</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>11.04</v>
+        <v>0.43</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>224.95</v>
+        <v>3.34</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>2307.12</v>
+        <v>51.32</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>161.49</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19442,7 +19433,7 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX14" s="10" t="s">
         <v>77</v>
@@ -19481,7 +19472,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19495,7 +19486,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>307083</v>
+        <v>307085</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>125</v>
@@ -19504,25 +19495,25 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>1193.88</v>
+        <v>264.8</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19531,16 +19522,16 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>1087.82</v>
+        <v>264.8</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0</v>
+        <v>0.00087</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
@@ -19558,16 +19549,16 @@
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>106.06</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>1087.82</v>
+        <v>264.8</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>43.51</v>
+        <v>18.54</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19576,7 +19567,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="12" t="n">
-        <v>89.72</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="12" t="n">
         <v>0</v>
@@ -19633,7 +19624,7 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
         <v>77</v>
@@ -19657,25 +19648,25 @@
         <v>75</v>
       </c>
       <c r="BE15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ15" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="BF15" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG15" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="BH15" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="BI15" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="BJ15" s="9" t="s">
-        <v>134</v>
-      </c>
       <c r="BK15" s="9" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="BL15" s="9" t="s">
         <v>75</v>
@@ -19686,34 +19677,34 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>307084</v>
+        <v>307086</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>54.66</v>
+        <v>1122.7</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19722,22 +19713,22 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>51.32</v>
+        <v>1122.7</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.134276</v>
+        <v>0.0036</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0.43</v>
+        <v>4.85</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19749,16 +19740,16 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>51.32</v>
+        <v>1122.7</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>2.05</v>
+        <v>44.91</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19824,7 +19815,7 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
         <v>77</v>
@@ -19863,7 +19854,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19877,34 +19868,34 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>307085</v>
+        <v>307100</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>264.8</v>
+        <v>3768.3</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19913,43 +19904,43 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>264.8</v>
+        <v>3768.3</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.00087</v>
+        <v>0.216</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>0.93</v>
+        <v>91.2</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>264.8</v>
+        <v>3768.3</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>18.54</v>
+        <v>263.78</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -20015,7 +20006,7 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX17" s="10" t="s">
         <v>77</v>
@@ -20054,7 +20045,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -20068,34 +20059,34 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>307086</v>
+        <v>307121</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1122.7</v>
+        <v>1171.26</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -20104,43 +20095,43 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>1122.7</v>
+        <v>1067.21</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.0036</v>
+        <v>0.056916</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>0</v>
+        <v>104.05</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>1122.7</v>
+        <v>1067.21</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>44.91</v>
+        <v>74.7</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20206,7 +20197,7 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
         <v>77</v>
@@ -20245,7 +20236,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20259,34 +20250,34 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>307100</v>
+        <v>307122</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>3768.3</v>
+        <v>63.31</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20295,43 +20286,43 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>3768.3</v>
+        <v>57.69</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.216</v>
+        <v>0.009486</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>3768.3</v>
+        <v>57.69</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>263.78</v>
+        <v>4.04</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20397,10 +20388,10 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20436,7 +20427,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20450,34 +20441,34 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>307121</v>
+        <v>307170</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>1171.26</v>
+        <v>404.81</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20486,43 +20477,43 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>1067.21</v>
+        <v>404.81</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.056916</v>
+        <v>0.000858</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>104.05</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>1067.21</v>
+        <v>404.81</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>74.7</v>
+        <v>16.19</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20588,10 +20579,10 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20627,7 +20618,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20641,79 +20632,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307122</v>
+        <v>307182</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>63.31</v>
+        <v>1534.81</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>57.69</v>
+        <v>1490.26</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.009486</v>
+        <v>0.108038</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>5.62</v>
+        <v>44.55</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>57.69</v>
+        <v>1490.26</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>4.04</v>
+        <v>104.32</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20779,10 +20770,10 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20818,7 +20809,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20832,79 +20823,79 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307170</v>
+        <v>307206</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>404.81</v>
+        <v>15391.61</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>404.81</v>
+        <v>14024.25</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.000858</v>
+        <v>0</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0</v>
+        <v>57.33</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>1367.36</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>404.81</v>
+        <v>14024.25</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>16.19</v>
+        <v>981.71</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20970,10 +20961,10 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -21009,7 +21000,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -21023,79 +21014,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307182</v>
+        <v>307221</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1534.81</v>
+        <v>3768.28</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>1490.26</v>
+        <v>3598.38</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.108038</v>
+        <v>0.536658</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>5</v>
+        <v>34.56</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>44.55</v>
+        <v>169.9</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>1490.26</v>
+        <v>3598.38</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>104.32</v>
+        <v>143.94</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21161,10 +21152,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21200,7 +21191,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21214,79 +21205,79 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307206</v>
+        <v>307222</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>15391.61</v>
+        <v>461.96</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>14024.25</v>
+        <v>461.96</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0</v>
+        <v>0.002057</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>57.33</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>1367.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>14024.25</v>
+        <v>461.96</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>981.71</v>
+        <v>18.48</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21352,10 +21343,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21391,7 +21382,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21405,79 +21396,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307209</v>
+        <v>307224</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1867.78</v>
+        <v>886.44</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>1685.3</v>
+        <v>886.44</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0</v>
+        <v>0.00154</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>7.5</v>
+        <v>0.83</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>182.48</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>1685.3</v>
+        <v>886.44</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>67.41</v>
+        <v>62.05</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21543,7 +21534,7 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
         <v>77</v>
@@ -21582,7 +21573,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21596,79 +21587,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307221</v>
+        <v>307269</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>3768.28</v>
+        <v>3276</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>3598.38</v>
+        <v>3120</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.536658</v>
+        <v>0</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>34.56</v>
+        <v>18.05</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>0</v>
+        <v>41.33</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>169.9</v>
+        <v>156</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>3598.38</v>
+        <v>3120</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>143.94</v>
+        <v>124.8</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21734,10 +21725,10 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21773,7 +21764,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21787,79 +21778,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307222</v>
+        <v>307273</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>461.96</v>
+        <v>7705.98</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>461.96</v>
+        <v>6908.35</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.002057</v>
+        <v>0.438516</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>2.43</v>
+        <v>71.6</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>797.63</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>461.96</v>
+        <v>6908.35</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>18.48</v>
+        <v>358.82</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21925,10 +21916,10 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21964,7 +21955,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21978,58 +21969,58 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307224</v>
+        <v>307276</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>886.44</v>
+        <v>522.97</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>886.44</v>
+        <v>491.06</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.00154</v>
+        <v>0.013568</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0.83</v>
+        <v>3.04</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
@@ -22041,16 +22032,16 @@
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>0</v>
+        <v>31.91</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>886.44</v>
+        <v>491.06</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>62.05</v>
+        <v>34.38</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22116,7 +22107,7 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX28" s="10" t="s">
         <v>77</v>
@@ -22155,7 +22146,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22169,79 +22160,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>307269</v>
+        <v>307277</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>3276</v>
+        <v>1122.7</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>3120</v>
+        <v>1122.7</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0</v>
+        <v>0.004114</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>18.05</v>
+        <v>4.85</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>41.33</v>
+        <v>28</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>3120</v>
+        <v>1122.7</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>124.8</v>
+        <v>44.91</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22307,7 +22298,7 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
         <v>77</v>
@@ -22346,7 +22337,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22360,79 +22351,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>307273</v>
+        <v>307280</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>7705.98</v>
+        <v>2385.63</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>6908.35</v>
+        <v>2214.84</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.438516</v>
+        <v>20.166476</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>71.6</v>
+        <v>23.3</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>34</v>
+        <v>43.93</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>797.63</v>
+        <v>170.79</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>6908.35</v>
+        <v>2214.84</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>358.82</v>
+        <v>88.59</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22498,7 +22489,7 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX30" s="10" t="s">
         <v>77</v>
@@ -22537,7 +22528,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22551,79 +22542,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>307276</v>
+        <v>307281</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>522.97</v>
+        <v>4762.99</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>491.06</v>
+        <v>4546</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.013568</v>
+        <v>0.02738</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>3.04</v>
+        <v>21.28</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>28</v>
+        <v>58.63</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>31.91</v>
+        <v>216.99</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>491.06</v>
+        <v>4546</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>34.38</v>
+        <v>181.84</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22689,7 +22680,7 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
         <v>77</v>
@@ -22728,7 +22719,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22742,34 +22733,34 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>307277</v>
+        <v>307296</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>1122.7</v>
+        <v>4119.25</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22778,43 +22769,43 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>1122.7</v>
+        <v>4119.25</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.004114</v>
+        <v>0.55013</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>4.85</v>
+        <v>250</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>1122.7</v>
+        <v>4119.25</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>44.91</v>
+        <v>164.77</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22880,10 +22871,10 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX32" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY32" s="14" t="s">
         <v>75</v>
@@ -22919,7 +22910,7 @@
         <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22933,79 +22924,79 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>307280</v>
+        <v>307309</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>2385.63</v>
+        <v>1720.43</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>2214.84</v>
+        <v>1720.43</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>20.166476</v>
+        <v>0</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>23.3</v>
+        <v>10.21</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>43.93</v>
+        <v>0</v>
       </c>
       <c r="W33" s="9" t="s">
-        <v>73</v>
+        <v>203</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>170.79</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>2214.84</v>
+        <v>1720.43</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>88.59</v>
+        <v>120.43</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23071,10 +23062,10 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -23110,7 +23101,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23124,79 +23115,79 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>307281</v>
+        <v>307311</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>4762.99</v>
+        <v>446.07</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>4546</v>
+        <v>418.84</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.02738</v>
+        <v>0.134454</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>21.28</v>
+        <v>0.92</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>58.63</v>
+        <v>28</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>216.99</v>
+        <v>27.23</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>4546</v>
+        <v>418.84</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>181.84</v>
+        <v>23.54</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23262,7 +23253,7 @@
         <v>74</v>
       </c>
       <c r="AW34" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX34" s="10" t="s">
         <v>77</v>
@@ -23301,7 +23292,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23315,34 +23306,34 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>307296</v>
+        <v>307312</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>4119.25</v>
+        <v>273.43</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23351,43 +23342,43 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>4119.25</v>
+        <v>256.74</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.55013</v>
+        <v>0.14364</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>0</v>
+        <v>16.69</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>4119.25</v>
+        <v>256.74</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>164.77</v>
+        <v>10.27</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23453,10 +23444,10 @@
         <v>74</v>
       </c>
       <c r="AW35" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23492,7 +23483,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23506,25 +23497,25 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>307309</v>
+        <v>307313</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>78</v>
@@ -23533,31 +23524,31 @@
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1720.43</v>
+        <v>4209.61</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>1720.43</v>
+        <v>3952.68</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0</v>
+        <v>0.471828</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>10.21</v>
+        <v>7.22</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
@@ -23566,19 +23557,19 @@
         <v>0</v>
       </c>
       <c r="W36" s="9" t="s">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>0</v>
+        <v>256.93</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>1720.43</v>
+        <v>3952.68</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>120.43</v>
+        <v>158.11</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23644,10 +23635,10 @@
         <v>74</v>
       </c>
       <c r="AW36" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX36" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY36" s="14" t="s">
         <v>75</v>
@@ -23683,7 +23674,7 @@
         <v>78</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23697,34 +23688,34 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>307311</v>
+        <v>307314</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>446.07</v>
+        <v>501.26</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -23733,22 +23724,22 @@
         <v>2</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>418.84</v>
+        <v>470.66</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.134454</v>
+        <v>0.123032</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>0.92</v>
+        <v>4.49</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
@@ -23760,16 +23751,16 @@
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>27.23</v>
+        <v>30.6</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>418.84</v>
+        <v>470.66</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>23.54</v>
+        <v>18.82</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23835,7 +23826,7 @@
         <v>74</v>
       </c>
       <c r="AW37" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX37" s="10" t="s">
         <v>77</v>
@@ -23874,7 +23865,7 @@
         <v>78</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23888,49 +23879,49 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>307312</v>
+        <v>307317</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>273.43</v>
+        <v>1727.12</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>256.74</v>
+        <v>1573.69</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.14364</v>
+        <v>0</v>
       </c>
       <c r="R38" s="12" t="n">
         <v>0</v>
@@ -23939,28 +23930,28 @@
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>16.69</v>
+        <v>153.43</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>256.74</v>
+        <v>1573.69</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>10.27</v>
+        <v>110.16</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -24026,7 +24017,7 @@
         <v>74</v>
       </c>
       <c r="AW38" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX38" s="10" t="s">
         <v>77</v>
@@ -24065,7 +24056,7 @@
         <v>78</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24079,79 +24070,79 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>307313</v>
+        <v>307325</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>4209.61</v>
+        <v>2783.92</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>3952.68</v>
+        <v>2783.92</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.471828</v>
+        <v>0.005548</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>7.22</v>
+        <v>0.98</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>256.93</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>3952.68</v>
+        <v>2783.92</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>158.11</v>
+        <v>194.87</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24217,10 +24208,10 @@
         <v>74</v>
       </c>
       <c r="AW39" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX39" s="10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AY39" s="14" t="s">
         <v>75</v>
@@ -24256,7 +24247,7 @@
         <v>78</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24270,58 +24261,58 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>307314</v>
+        <v>307326</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>501.26</v>
+        <v>2967.67</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>470.66</v>
+        <v>2786.54</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.123032</v>
+        <v>0.027908</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>4.49</v>
+        <v>3.56</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
@@ -24333,16 +24324,16 @@
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>30.6</v>
+        <v>181.13</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>470.66</v>
+        <v>2786.54</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>18.82</v>
+        <v>195.06</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24408,7 +24399,7 @@
         <v>74</v>
       </c>
       <c r="AW40" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX40" s="10" t="s">
         <v>77</v>
@@ -24447,7 +24438,7 @@
         <v>78</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24461,79 +24452,79 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>307317</v>
+        <v>307328</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>64</v>
+        <v>227</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1727.12</v>
+        <v>2957.37</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>1573.69</v>
+        <v>2694.64</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0</v>
+        <v>0.080236</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>0</v>
+        <v>24.96</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>42</v>
+        <v>40.76</v>
       </c>
       <c r="W41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>153.43</v>
+        <v>262.73</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>1573.69</v>
+        <v>2694.64</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>110.16</v>
+        <v>107.79</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24599,7 +24590,7 @@
         <v>74</v>
       </c>
       <c r="AW41" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX41" s="10" t="s">
         <v>77</v>
@@ -24638,7 +24629,7 @@
         <v>78</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24652,79 +24643,79 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>307325</v>
+        <v>307331</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>2783.92</v>
+        <v>506.4</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>2783.92</v>
+        <v>499.2</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.005548</v>
+        <v>0.032832</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>0.98</v>
+        <v>5.78</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>2783.92</v>
+        <v>499.2</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>194.87</v>
+        <v>28.3</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24790,7 +24781,7 @@
         <v>74</v>
       </c>
       <c r="AW42" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX42" s="10" t="s">
         <v>77</v>
@@ -24829,7 +24820,7 @@
         <v>78</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24843,34 +24834,34 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>307326</v>
+        <v>307333</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>2967.67</v>
+        <v>1023.78</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
@@ -24879,22 +24870,22 @@
         <v>1</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>2786.54</v>
+        <v>1023.78</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.027908</v>
+        <v>0.010272</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>3.56</v>
+        <v>2.14</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
@@ -24906,16 +24897,16 @@
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>181.13</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>2786.54</v>
+        <v>1023.78</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>195.06</v>
+        <v>71.66</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24981,7 +24972,7 @@
         <v>74</v>
       </c>
       <c r="AW43" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX43" s="10" t="s">
         <v>77</v>
@@ -25020,7 +25011,7 @@
         <v>78</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -25034,79 +25025,79 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>307328</v>
+        <v>307353</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>2957.37</v>
+        <v>2206.41</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>2694.64</v>
+        <v>1942</v>
       </c>
       <c r="P44" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.080236</v>
+        <v>0.0004</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>24.96</v>
+        <v>5.8</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>40.76</v>
+        <v>28</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>262.73</v>
+        <v>179.41</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>2694.64</v>
+        <v>2027</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>107.79</v>
+        <v>81.07</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25172,7 +25163,7 @@
         <v>74</v>
       </c>
       <c r="AW44" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX44" s="10" t="s">
         <v>77</v>
@@ -25211,7 +25202,7 @@
         <v>78</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25225,25 +25216,25 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>307331</v>
+        <v>307370</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I45" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>246</v>
@@ -25252,25 +25243,25 @@
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>506.4</v>
+        <v>683.81</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>499.2</v>
+        <v>623.06</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.032832</v>
+        <v>0.006756</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
@@ -25282,22 +25273,22 @@
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>7.2</v>
+        <v>60.75</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>499.2</v>
+        <v>623.06</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>28.3</v>
+        <v>43.61</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25363,7 +25354,7 @@
         <v>74</v>
       </c>
       <c r="AW45" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX45" s="10" t="s">
         <v>77</v>
@@ -25416,10 +25407,10 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>307333</v>
+        <v>307375</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
@@ -25428,40 +25419,40 @@
         <v>249</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>174</v>
+        <v>246</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1023.78</v>
+        <v>8873.06</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>1023.78</v>
+        <v>7890.92</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.010272</v>
+        <v>0.00636</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>2.14</v>
+        <v>7.8</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
@@ -25473,22 +25464,22 @@
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>28</v>
+        <v>44.19</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>0</v>
+        <v>982.14</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>1023.78</v>
+        <v>7890.92</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>71.66</v>
+        <v>552.36</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25554,7 +25545,7 @@
         <v>74</v>
       </c>
       <c r="AW46" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX46" s="10" t="s">
         <v>77</v>
@@ -25607,52 +25598,52 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>307353</v>
+        <v>307378</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="J47" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>2206.41</v>
+        <v>1369.96</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>1942</v>
+        <v>1349.3</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.0004</v>
+        <v>0.122352</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>5.8</v>
+        <v>6.73</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
@@ -25664,22 +25655,22 @@
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>179.41</v>
+        <v>20.66</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>2027</v>
+        <v>1349.3</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>81.07</v>
+        <v>94.45</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25745,7 +25736,7 @@
         <v>74</v>
       </c>
       <c r="AW47" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX47" s="10" t="s">
         <v>77</v>
@@ -25798,7 +25789,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>307370</v>
+        <v>307391</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>256</v>
@@ -25810,37 +25801,37 @@
         <v>257</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>683.81</v>
+        <v>938.36</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>623.06</v>
+        <v>855</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.006756</v>
+        <v>0</v>
       </c>
       <c r="R48" s="12" t="n">
         <v>0</v>
@@ -25849,28 +25840,28 @@
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>60.75</v>
+        <v>83.36</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>623.06</v>
+        <v>855</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>43.61</v>
+        <v>59.85</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25879,7 +25870,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="12" t="n">
-        <v>0</v>
+        <v>18.94</v>
       </c>
       <c r="AE48" s="12" t="n">
         <v>0</v>
@@ -25936,7 +25927,7 @@
         <v>74</v>
       </c>
       <c r="AW48" s="14" t="s">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="AX48" s="10" t="s">
         <v>77</v>
@@ -25960,25 +25951,25 @@
         <v>75</v>
       </c>
       <c r="BE48" s="14" t="s">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="BF48" s="9" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BG48" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BH48" s="14" t="s">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="BI48" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="BK48" s="9" t="s">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="BL48" s="9" t="s">
         <v>75</v>
@@ -25989,79 +25980,79 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>307375</v>
+        <v>307392</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>167</v>
+        <v>256</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>8873.06</v>
+        <v>375.13</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>7890.92</v>
+        <v>341.8</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.00636</v>
+        <v>0</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>44.19</v>
+        <v>28</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>982.14</v>
+        <v>33.33</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>7890.92</v>
+        <v>341.8</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>552.36</v>
+        <v>23.93</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26070,7 +26061,7 @@
         <v>0</v>
       </c>
       <c r="AD49" s="12" t="n">
-        <v>0</v>
+        <v>7.57</v>
       </c>
       <c r="AE49" s="12" t="n">
         <v>0</v>
@@ -26127,7 +26118,7 @@
         <v>74</v>
       </c>
       <c r="AW49" s="14" t="s">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="AX49" s="10" t="s">
         <v>77</v>
@@ -26151,25 +26142,25 @@
         <v>75</v>
       </c>
       <c r="BE49" s="14" t="s">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="BF49" s="9" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BG49" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BH49" s="14" t="s">
-        <v>75</v>
+        <v>267</v>
       </c>
       <c r="BI49" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BJ49" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="BK49" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="BK49" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="BL49" s="9" t="s">
         <v>75</v>
@@ -26180,79 +26171,79 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>307378</v>
+        <v>307397</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>244</v>
+        <v>125</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>1369.96</v>
+        <v>202.92</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>1349.3</v>
+        <v>202.92</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.122352</v>
+        <v>0.00963</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>6.73</v>
+        <v>1.65</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="U50" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>20.66</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>1349.3</v>
+        <v>202.92</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>94.45</v>
+        <v>14.2</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26318,7 +26309,7 @@
         <v>74</v>
       </c>
       <c r="AW50" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX50" s="10" t="s">
         <v>77</v>
@@ -26357,7 +26348,7 @@
         <v>78</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26371,34 +26362,34 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>307391</v>
+        <v>307402</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>938.36</v>
+        <v>19503.54</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
@@ -26407,22 +26398,22 @@
         <v>1</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>855</v>
+        <v>19503.54</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0</v>
+        <v>1.9872</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>0</v>
+        <v>5453.76</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
@@ -26434,16 +26425,16 @@
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>83.36</v>
+        <v>0</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>855</v>
+        <v>19503.54</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>59.85</v>
+        <v>1365.25</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26452,7 +26443,7 @@
         <v>0</v>
       </c>
       <c r="AD51" s="12" t="n">
-        <v>18.94</v>
+        <v>0</v>
       </c>
       <c r="AE51" s="12" t="n">
         <v>0</v>
@@ -26509,7 +26500,7 @@
         <v>74</v>
       </c>
       <c r="AW51" s="14" t="s">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="AX51" s="10" t="s">
         <v>77</v>
@@ -26533,25 +26524,25 @@
         <v>75</v>
       </c>
       <c r="BE51" s="14" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
       <c r="BF51" s="9" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="BG51" s="9" t="s">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="BH51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI51" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ51" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="BI51" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="BJ51" s="9" t="s">
-        <v>275</v>
-      </c>
       <c r="BK51" s="9" t="s">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="BL51" s="9" t="s">
         <v>75</v>
@@ -26562,43 +26553,43 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>307392</v>
+        <v>307425</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="I52" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="G52" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>258</v>
-      </c>
       <c r="J52" s="9" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>375.13</v>
+        <v>1389.3</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>341.8</v>
+        <v>1389.3</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
@@ -26607,7 +26598,7 @@
         <v>0</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
@@ -26619,22 +26610,22 @@
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>28</v>
+        <v>38.5</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="Y52" s="12" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>341.8</v>
+        <v>1389.3</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>23.93</v>
+        <v>41.12</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26643,7 +26634,7 @@
         <v>0</v>
       </c>
       <c r="AD52" s="12" t="n">
-        <v>7.57</v>
+        <v>0</v>
       </c>
       <c r="AE52" s="12" t="n">
         <v>0</v>
@@ -26700,7 +26691,7 @@
         <v>74</v>
       </c>
       <c r="AW52" s="14" t="s">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="AX52" s="10" t="s">
         <v>77</v>
@@ -26724,25 +26715,25 @@
         <v>75</v>
       </c>
       <c r="BE52" s="14" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
       <c r="BF52" s="9" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="BG52" s="9" t="s">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="BH52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI52" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ52" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="BI52" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="BJ52" s="9" t="s">
-        <v>280</v>
-      </c>
       <c r="BK52" s="9" t="s">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="BL52" s="9" t="s">
         <v>75</v>
@@ -26753,79 +26744,79 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>307397</v>
+        <v>307426</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>136</v>
+        <v>275</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>202.92</v>
+        <v>1807.1</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>202.92</v>
+        <v>1807.1</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0.00963</v>
+        <v>0.024</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="U53" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V53" s="12" t="n">
-        <v>28</v>
+        <v>46.01</v>
       </c>
       <c r="W53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="Y53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>202.92</v>
+        <v>1807.1</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>14.2</v>
+        <v>53.49</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -26891,7 +26882,7 @@
         <v>74</v>
       </c>
       <c r="AW53" s="14" t="s">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="AX53" s="10" t="s">
         <v>77</v>
@@ -26930,7 +26921,7 @@
         <v>78</v>
       </c>
       <c r="BJ53" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="BK53" s="9" t="s">
         <v>75</v>
@@ -26944,79 +26935,79 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>307402</v>
+        <v>307463</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>146</v>
+        <v>256</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>19503.54</v>
+        <v>1255.43</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>19503.54</v>
+        <v>1163.96</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>1.9872</v>
+        <v>0</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>5453.76</v>
+        <v>0</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V54" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W54" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="Y54" s="12" t="n">
-        <v>0</v>
+        <v>91.47</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>19503.54</v>
+        <v>1163.96</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>1365.25</v>
+        <v>81.47</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27025,7 +27016,7 @@
         <v>0</v>
       </c>
       <c r="AD54" s="12" t="n">
-        <v>0</v>
+        <v>25.34</v>
       </c>
       <c r="AE54" s="12" t="n">
         <v>0</v>
@@ -27106,25 +27097,25 @@
         <v>75</v>
       </c>
       <c r="BE54" s="14" t="s">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="BF54" s="9" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BG54" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BH54" s="14" t="s">
-        <v>75</v>
+        <v>285</v>
       </c>
       <c r="BI54" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BJ54" s="9" t="s">
         <v>286</v>
       </c>
       <c r="BK54" s="9" t="s">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="BL54" s="9" t="s">
         <v>75</v>
@@ -27135,7 +27126,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>307425</v>
+        <v>307464</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>287</v>
@@ -27147,31 +27138,31 @@
         <v>288</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>1389.3</v>
+        <v>1416.24</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>1389.3</v>
+        <v>1290.43</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
@@ -27180,34 +27171,34 @@
         <v>0</v>
       </c>
       <c r="R55" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="U55" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V55" s="12" t="n">
-        <v>38.5</v>
+        <v>28</v>
       </c>
       <c r="W55" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X55" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="Y55" s="12" t="n">
-        <v>0</v>
+        <v>125.81</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>1389.3</v>
+        <v>1290.43</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>41.12</v>
+        <v>90.33</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27216,7 +27207,7 @@
         <v>0</v>
       </c>
       <c r="AD55" s="12" t="n">
-        <v>0</v>
+        <v>89.72</v>
       </c>
       <c r="AE55" s="12" t="n">
         <v>0</v>
@@ -27297,25 +27288,25 @@
         <v>75</v>
       </c>
       <c r="BE55" s="14" t="s">
-        <v>75</v>
+        <v>290</v>
       </c>
       <c r="BF55" s="9" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BG55" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BH55" s="14" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="BI55" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BJ55" s="9" t="s">
         <v>291</v>
       </c>
       <c r="BK55" s="9" t="s">
-        <v>75</v>
+        <v>292</v>
       </c>
       <c r="BL55" s="9" t="s">
         <v>75</v>
@@ -27326,34 +27317,34 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>307426</v>
+        <v>307470</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>169</v>
+        <v>245</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>1807.1</v>
+        <v>2535.23</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
@@ -27362,43 +27353,43 @@
         <v>2</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>1807.1</v>
+        <v>2310</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>0.024</v>
+        <v>14</v>
       </c>
       <c r="R56" s="12" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="S56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T56" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="U56" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V56" s="12" t="n">
-        <v>46.01</v>
+        <v>40.76</v>
       </c>
       <c r="W56" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X56" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="Y56" s="12" t="n">
-        <v>0</v>
+        <v>225.23</v>
       </c>
       <c r="Z56" s="12" t="n">
-        <v>1807.1</v>
+        <v>2310</v>
       </c>
       <c r="AA56" s="12" t="n">
-        <v>53.49</v>
+        <v>92.4</v>
       </c>
       <c r="AB56" s="12" t="n">
         <v>0</v>
@@ -27464,7 +27455,7 @@
         <v>74</v>
       </c>
       <c r="AW56" s="14" t="s">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="AX56" s="10" t="s">
         <v>77</v>
@@ -27503,7 +27494,7 @@
         <v>78</v>
       </c>
       <c r="BJ56" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BK56" s="9" t="s">
         <v>75</v>
@@ -27517,79 +27508,79 @@
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
-        <v>307463</v>
+        <v>307472</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>271</v>
+        <v>66</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>1255.43</v>
+        <v>2428.23</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>1163.96</v>
+        <v>2410.9</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="13" t="n">
-        <v>0</v>
+        <v>0.244932</v>
       </c>
       <c r="R57" s="12" t="n">
-        <v>0</v>
+        <v>21.65</v>
       </c>
       <c r="S57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="U57" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V57" s="12" t="n">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="W57" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X57" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="Y57" s="12" t="n">
-        <v>91.47</v>
+        <v>17.33</v>
       </c>
       <c r="Z57" s="12" t="n">
-        <v>1163.96</v>
+        <v>2410.9</v>
       </c>
       <c r="AA57" s="12" t="n">
-        <v>81.47</v>
+        <v>164.1</v>
       </c>
       <c r="AB57" s="12" t="n">
         <v>0</v>
@@ -27598,7 +27589,7 @@
         <v>0</v>
       </c>
       <c r="AD57" s="12" t="n">
-        <v>25.34</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="12" t="n">
         <v>0</v>
@@ -27655,7 +27646,7 @@
         <v>74</v>
       </c>
       <c r="AW57" s="14" t="s">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="AX57" s="10" t="s">
         <v>77</v>
@@ -27679,25 +27670,25 @@
         <v>75</v>
       </c>
       <c r="BE57" s="14" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
       <c r="BF57" s="9" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="BG57" s="9" t="s">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="BH57" s="14" t="s">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="BI57" s="9" t="s">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="BJ57" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="BK57" s="9" t="s">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="BL57" s="9" t="s">
         <v>75</v>
@@ -27708,10 +27699,10 @@
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
-        <v>307464</v>
+        <v>307475</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>299</v>
+        <v>194</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -27720,67 +27711,67 @@
         <v>300</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>1416.24</v>
+        <v>3351.6</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O58" s="12" t="n">
-        <v>1290.43</v>
+        <v>3351.6</v>
       </c>
       <c r="P58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="13" t="n">
-        <v>0</v>
+        <v>0.001236</v>
       </c>
       <c r="R58" s="12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="U58" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V58" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W58" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X58" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="Y58" s="12" t="n">
-        <v>125.81</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="12" t="n">
-        <v>1290.43</v>
+        <v>3351.6</v>
       </c>
       <c r="AA58" s="12" t="n">
-        <v>90.33</v>
+        <v>234.61</v>
       </c>
       <c r="AB58" s="12" t="n">
         <v>0</v>
@@ -27789,7 +27780,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="12" t="n">
-        <v>89.72</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="12" t="n">
         <v>0</v>
@@ -27846,7 +27837,7 @@
         <v>74</v>
       </c>
       <c r="AW58" s="14" t="s">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="AX58" s="10" t="s">
         <v>77</v>
@@ -27870,25 +27861,25 @@
         <v>75</v>
       </c>
       <c r="BE58" s="14" t="s">
-        <v>302</v>
+        <v>75</v>
       </c>
       <c r="BF58" s="9" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="BG58" s="9" t="s">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="BH58" s="14" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="BI58" s="9" t="s">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="BJ58" s="9" t="s">
         <v>303</v>
       </c>
       <c r="BK58" s="9" t="s">
-        <v>304</v>
+        <v>75</v>
       </c>
       <c r="BL58" s="9" t="s">
         <v>75</v>
@@ -27899,10 +27890,10 @@
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
-        <v>307470</v>
+        <v>307501</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>187</v>
+        <v>304</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
@@ -27911,67 +27902,67 @@
         <v>305</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>2535.23</v>
+        <v>960.64</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>2310</v>
+        <v>875.3</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="13" t="n">
-        <v>14</v>
+        <v>0.00556</v>
       </c>
       <c r="R59" s="12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T59" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="U59" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V59" s="12" t="n">
-        <v>40.76</v>
+        <v>28</v>
       </c>
       <c r="W59" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X59" s="9" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="Y59" s="12" t="n">
-        <v>225.23</v>
+        <v>85.34</v>
       </c>
       <c r="Z59" s="12" t="n">
-        <v>2310</v>
+        <v>875.3</v>
       </c>
       <c r="AA59" s="12" t="n">
-        <v>92.4</v>
+        <v>35.01</v>
       </c>
       <c r="AB59" s="12" t="n">
         <v>0</v>
@@ -28037,7 +28028,7 @@
         <v>74</v>
       </c>
       <c r="AW59" s="14" t="s">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="AX59" s="10" t="s">
         <v>77</v>
@@ -28076,7 +28067,7 @@
         <v>78</v>
       </c>
       <c r="BJ59" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BK59" s="9" t="s">
         <v>75</v>
@@ -28090,52 +28081,52 @@
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
-        <v>307472</v>
+        <v>307506</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
       <c r="F60" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>2428.23</v>
+        <v>5980.14</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O60" s="12" t="n">
-        <v>2410.9</v>
+        <v>5541.97</v>
       </c>
       <c r="P60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="13" t="n">
-        <v>0.244932</v>
+        <v>0</v>
       </c>
       <c r="R60" s="12" t="n">
-        <v>21.65</v>
+        <v>3.6</v>
       </c>
       <c r="S60" s="12" t="n">
         <v>0</v>
@@ -28147,22 +28138,22 @@
         <v>72</v>
       </c>
       <c r="V60" s="12" t="n">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="W60" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X60" s="9" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="Y60" s="12" t="n">
-        <v>17.33</v>
+        <v>438.17</v>
       </c>
       <c r="Z60" s="12" t="n">
-        <v>2410.9</v>
+        <v>5541.97</v>
       </c>
       <c r="AA60" s="12" t="n">
-        <v>164.1</v>
+        <v>387.94</v>
       </c>
       <c r="AB60" s="12" t="n">
         <v>0</v>
@@ -28171,7 +28162,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="12" t="n">
-        <v>0</v>
+        <v>120.72</v>
       </c>
       <c r="AE60" s="12" t="n">
         <v>0</v>
@@ -28228,7 +28219,7 @@
         <v>74</v>
       </c>
       <c r="AW60" s="14" t="s">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="AX60" s="10" t="s">
         <v>77</v>
@@ -28252,25 +28243,25 @@
         <v>75</v>
       </c>
       <c r="BE60" s="14" t="s">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="BF60" s="9" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BG60" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BH60" s="14" t="s">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="BI60" s="9" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="BJ60" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="BK60" s="9" t="s">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="BL60" s="9" t="s">
         <v>75</v>
@@ -28280,518 +28271,396 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="n">
-        <v>307475</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I61" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="J61" s="9" t="s">
+      <c r="A61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="K61" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>3351.6</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>3351.6</v>
-      </c>
-      <c r="P61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="13" t="n">
-        <v>0.001236</v>
-      </c>
-      <c r="R61" s="12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="U61" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V61" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W61" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X61" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="Y61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="12" t="n">
-        <v>3351.6</v>
-      </c>
-      <c r="AA61" s="12" t="n">
-        <v>234.61</v>
-      </c>
-      <c r="AB61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV61" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW61" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AX61" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG61" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH61" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI61" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ61" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="BK61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM61" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="17"/>
+      <c r="V62" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="17"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
-      <c r="S63" s="17"/>
-      <c r="T63" s="17"/>
-      <c r="U63" s="17"/>
-      <c r="V63" s="17"/>
+      <c r="J63" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L63" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M63" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="N63" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O63" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P63" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q63" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R63" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S63" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="T63" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="U63" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V63" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="B64" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F64" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I64" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="J64" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K64" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L64" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M64" s="18" t="s">
+    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="19" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="19" t="n">
+        <v>85</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>7352.22</v>
+      </c>
+      <c r="F64" s="19" t="n">
+        <v>135195.96</v>
+      </c>
+      <c r="G64" s="19" t="n">
+        <v>8221.15</v>
+      </c>
+      <c r="H64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="19" t="n">
+        <v>352.01</v>
+      </c>
+      <c r="K64" s="19" t="n">
+        <v>142548.18</v>
+      </c>
+      <c r="L64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="20" t="n">
+        <v>40.250339</v>
+      </c>
+      <c r="S64" s="19" t="n">
+        <v>135110.96</v>
+      </c>
+      <c r="T64" s="19" t="n">
+        <v>142548.18</v>
+      </c>
+      <c r="U64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I65" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J65" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K65" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="N64" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O64" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P64" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q64" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R64" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S64" s="18" t="s">
+      <c r="L65" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="T64" s="18" t="s">
+      <c r="M65" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="U64" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V64" s="18" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="19" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" s="19" t="n">
-        <v>85</v>
-      </c>
-      <c r="D65" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E65" s="19" t="n">
-        <v>7142.8</v>
-      </c>
-      <c r="F65" s="19" t="n">
-        <v>134047.67</v>
-      </c>
-      <c r="G65" s="19" t="n">
-        <v>8106.31</v>
-      </c>
-      <c r="H65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="19" t="n">
-        <v>231.29</v>
-      </c>
-      <c r="K65" s="19" t="n">
-        <v>141190.47</v>
-      </c>
-      <c r="L65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="20" t="n">
-        <v>40.257883</v>
-      </c>
-      <c r="S65" s="19" t="n">
-        <v>133862.67</v>
-      </c>
-      <c r="T65" s="19" t="n">
-        <v>141190.47</v>
-      </c>
-      <c r="U65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B66" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I66" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J66" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K66" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="L66" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="M66" s="18" t="s">
-        <v>325</v>
+    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="19" t="n">
+        <v>6232.35</v>
+      </c>
+      <c r="B66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="19" t="n">
-        <v>6239.61</v>
-      </c>
-      <c r="B67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="19" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="E67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A67" s="4"/>
     </row>
-    <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4"/>
+    <row r="68" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
+      <c r="V68" s="21"/>
+      <c r="W68" s="21"/>
+      <c r="X68" s="21"/>
+      <c r="Y68" s="21"/>
+      <c r="Z68" s="21"/>
+      <c r="AA68" s="21"/>
+      <c r="AB68" s="21"/>
+      <c r="AC68" s="21"/>
+      <c r="AD68" s="21"/>
+      <c r="AE68" s="21"/>
+      <c r="AF68" s="21"/>
+      <c r="AG68" s="21"/>
+      <c r="AH68" s="21"/>
+      <c r="AI68" s="21"/>
+      <c r="AJ68" s="21"/>
+      <c r="AK68" s="21"/>
+      <c r="AL68" s="21"/>
+      <c r="AM68" s="21"/>
+      <c r="AN68" s="21"/>
+      <c r="AO68" s="21"/>
+      <c r="AP68" s="21"/>
+      <c r="AQ68" s="21"/>
+      <c r="AR68" s="21"/>
+      <c r="AS68" s="21"/>
+      <c r="AT68" s="21"/>
+      <c r="AU68" s="21"/>
+      <c r="AV68" s="21"/>
+      <c r="AW68" s="21"/>
+      <c r="AX68" s="21"/>
+      <c r="AY68" s="21"/>
+      <c r="AZ68" s="21"/>
+      <c r="BA68" s="21"/>
+      <c r="BB68" s="21"/>
+      <c r="BC68" s="21"/>
+      <c r="BD68" s="21"/>
+      <c r="BE68" s="21"/>
+      <c r="BF68" s="21"/>
+      <c r="BG68" s="21"/>
+      <c r="BH68" s="21"/>
+      <c r="BI68" s="21"/>
+      <c r="BJ68" s="21"/>
+      <c r="BK68" s="21"/>
+      <c r="BL68" s="21"/>
+      <c r="BM68" s="21"/>
     </row>
-    <row r="69" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
-      <c r="P69" s="21"/>
-      <c r="Q69" s="21"/>
-      <c r="R69" s="21"/>
-      <c r="S69" s="21"/>
-      <c r="T69" s="21"/>
-      <c r="U69" s="21"/>
-      <c r="V69" s="21"/>
-      <c r="W69" s="21"/>
-      <c r="X69" s="21"/>
-      <c r="Y69" s="21"/>
-      <c r="Z69" s="21"/>
-      <c r="AA69" s="21"/>
-      <c r="AB69" s="21"/>
-      <c r="AC69" s="21"/>
-      <c r="AD69" s="21"/>
-      <c r="AE69" s="21"/>
-      <c r="AF69" s="21"/>
-      <c r="AG69" s="21"/>
-      <c r="AH69" s="21"/>
-      <c r="AI69" s="21"/>
-      <c r="AJ69" s="21"/>
-      <c r="AK69" s="21"/>
-      <c r="AL69" s="21"/>
-      <c r="AM69" s="21"/>
-      <c r="AN69" s="21"/>
-      <c r="AO69" s="21"/>
-      <c r="AP69" s="21"/>
-      <c r="AQ69" s="21"/>
-      <c r="AR69" s="21"/>
-      <c r="AS69" s="21"/>
-      <c r="AT69" s="21"/>
-      <c r="AU69" s="21"/>
-      <c r="AV69" s="21"/>
-      <c r="AW69" s="21"/>
-      <c r="AX69" s="21"/>
-      <c r="AY69" s="21"/>
-      <c r="AZ69" s="21"/>
-      <c r="BA69" s="21"/>
-      <c r="BB69" s="21"/>
-      <c r="BC69" s="21"/>
-      <c r="BD69" s="21"/>
-      <c r="BE69" s="21"/>
-      <c r="BF69" s="21"/>
-      <c r="BG69" s="21"/>
-      <c r="BH69" s="21"/>
-      <c r="BI69" s="21"/>
-      <c r="BJ69" s="21"/>
-      <c r="BK69" s="21"/>
-      <c r="BL69" s="21"/>
-      <c r="BM69" s="21"/>
+    <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
+      <c r="AB69" s="4"/>
+      <c r="AC69" s="4"/>
+      <c r="AD69" s="4"/>
+      <c r="AE69" s="4"/>
+      <c r="AF69" s="4"/>
+      <c r="AG69" s="4"/>
+      <c r="AH69" s="4"/>
+      <c r="AI69" s="4"/>
+      <c r="AJ69" s="4"/>
+      <c r="AK69" s="4"/>
+      <c r="AL69" s="4"/>
+      <c r="AM69" s="4"/>
+      <c r="AN69" s="4"/>
+      <c r="AO69" s="4"/>
+      <c r="AP69" s="4"/>
+      <c r="AQ69" s="4"/>
+      <c r="AR69" s="4"/>
+      <c r="AS69" s="4"/>
+      <c r="AT69" s="4"/>
+      <c r="AU69" s="4"/>
+      <c r="AV69" s="4"/>
+      <c r="AW69" s="4"/>
+      <c r="AX69" s="4"/>
+      <c r="AY69" s="4"/>
+      <c r="AZ69" s="4"/>
+      <c r="BA69" s="4"/>
+      <c r="BB69" s="4"/>
+      <c r="BC69" s="4"/>
+      <c r="BD69" s="4"/>
+      <c r="BE69" s="4"/>
+      <c r="BF69" s="4"/>
+      <c r="BG69" s="4"/>
+      <c r="BH69" s="4"/>
+      <c r="BI69" s="4"/>
+      <c r="BJ69" s="4"/>
+      <c r="BK69" s="4"/>
+      <c r="BL69" s="4"/>
+      <c r="BM69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>75</v>
+        <v>324</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -28860,7 +28729,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -28929,7 +28798,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -28998,7 +28867,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>329</v>
+        <v>22</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -29067,7 +28936,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>22</v>
+        <v>327</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -29136,7 +29005,7 @@
     </row>
     <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -29205,7 +29074,7 @@
     </row>
     <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -29274,7 +29143,7 @@
     </row>
     <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -29343,7 +29212,7 @@
     </row>
     <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -29410,77 +29279,8 @@
       <c r="BL78" s="4"/>
       <c r="BM78" s="4"/>
     </row>
-    <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="4"/>
-      <c r="U79" s="4"/>
-      <c r="V79" s="4"/>
-      <c r="W79" s="4"/>
-      <c r="X79" s="4"/>
-      <c r="Y79" s="4"/>
-      <c r="Z79" s="4"/>
-      <c r="AA79" s="4"/>
-      <c r="AB79" s="4"/>
-      <c r="AC79" s="4"/>
-      <c r="AD79" s="4"/>
-      <c r="AE79" s="4"/>
-      <c r="AF79" s="4"/>
-      <c r="AG79" s="4"/>
-      <c r="AH79" s="4"/>
-      <c r="AI79" s="4"/>
-      <c r="AJ79" s="4"/>
-      <c r="AK79" s="4"/>
-      <c r="AL79" s="4"/>
-      <c r="AM79" s="4"/>
-      <c r="AN79" s="4"/>
-      <c r="AO79" s="4"/>
-      <c r="AP79" s="4"/>
-      <c r="AQ79" s="4"/>
-      <c r="AR79" s="4"/>
-      <c r="AS79" s="4"/>
-      <c r="AT79" s="4"/>
-      <c r="AU79" s="4"/>
-      <c r="AV79" s="4"/>
-      <c r="AW79" s="4"/>
-      <c r="AX79" s="4"/>
-      <c r="AY79" s="4"/>
-      <c r="AZ79" s="4"/>
-      <c r="BA79" s="4"/>
-      <c r="BB79" s="4"/>
-      <c r="BC79" s="4"/>
-      <c r="BD79" s="4"/>
-      <c r="BE79" s="4"/>
-      <c r="BF79" s="4"/>
-      <c r="BG79" s="4"/>
-      <c r="BH79" s="4"/>
-      <c r="BI79" s="4"/>
-      <c r="BJ79" s="4"/>
-      <c r="BK79" s="4"/>
-      <c r="BL79" s="4"/>
-      <c r="BM79" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="72">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -29541,8 +29341,8 @@
     <mergeCell ref="B58:E58"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="A63:V63"/>
+    <mergeCell ref="A62:V62"/>
+    <mergeCell ref="A68:BM68"/>
     <mergeCell ref="A69:BM69"/>
     <mergeCell ref="A70:BM70"/>
     <mergeCell ref="A71:BM71"/>
@@ -29553,7 +29353,6 @@
     <mergeCell ref="A76:BM76"/>
     <mergeCell ref="A77:BM77"/>
     <mergeCell ref="A78:BM78"/>
-    <mergeCell ref="A79:BM79"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
+++ b/tratando_tabelas/sr_acabamentos/entradas_sr_acabamentos.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="309">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 20/05/2026 05:30:32</t>
+    <t xml:space="preserve">Emitido em: 21/05/2026 05:30:34</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -286,15 +286,6 @@
     <t xml:space="preserve">35260475801902000126550000013520891393486645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.352.088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260475801902000126550000013520881842296450</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.352.087</t>
   </si>
   <si>
@@ -349,561 +340,453 @@
     <t xml:space="preserve">42260524546165000393550040000980051314694727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.893 - REVOLUZ INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.532,07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260509306858000153550010000709261237889907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.891 - STUDIOLUCE ILUMINACAO IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.479</t>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54,66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050803981473767772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050803991044656674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.122,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804001438231179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.171,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260530228132000136550010000092891773232410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260530228132000136550010000092901435141905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804101599979210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.304.072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.534,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260550949528001232550010023040721860830987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.768,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829941322627923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.083.080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">461,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050830801584930623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">886,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829741533961189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 - TRAMONTINA TEEC S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">684.266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.705,98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260501554846000136550010006842661501852320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">522,97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829761067401777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829751121039328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.177</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.193,88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.950</t>
+    <t xml:space="preserve">12/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.385,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260535635346000140550020001121771279175684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.762,99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260535635346000140550020001121781534580370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.119,25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006394171502977260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">446,07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829781228464036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">273,43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829771206775953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.209,61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829971596208423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.083.076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050830761221787698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.727,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260524546165000393550040000981601962020810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.783,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006396901908194720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.967,67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006397081888143897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">506,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007578201370188640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.023,78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006399571193331798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.206,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260510691158000370550010002932181828516528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.329 - S &amp; L SOUZA E LIMA FABRICACAO E COMERCIO DE LUMINARIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">683,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510394416000195550010000482621000254830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">261.906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.873,06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260558329608000144550010002619061002619078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.369,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007586021560856835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938,36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.348</t>
   </si>
   <si>
     <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
   </si>
   <si>
-    <t xml:space="preserve">89,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260510599342000123550020001044791920149108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260511389565000200570050003989501000852039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54,66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050803981473767772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">264,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050803991044656674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.122,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804001438231179</t>
+    <t xml:space="preserve">18,94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260512077181000133550030002249851510571498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260511389565000200570050003993481000856160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260512077181000133550030002249861111696979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050856481644529258</t>
   </si>
   <si>
     <t xml:space="preserve">3.101 - INDUSTRIA E COMERCIO DE MOLDURAS SANTA LUZIA LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">140.310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.768,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575821546000102550040001403101130982608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.145 - TKS ILUMINACAO E VENTILADORES LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.171,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260530228132000136550010000092891773232410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63,31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260530228132000136550010000092901435141905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804101599979210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.304.072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.534,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260550949528001232550010023040721860830987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">261.170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.391,61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260558329608000144550010002611701002611716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.768,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829941322627923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.083.080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">461,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050830801584930623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">886,44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829741533961189</t>
+    <t xml:space="preserve">140.499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.503,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575821546000102550040001404991623793421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.288 - ITAMONTE ILUM EIRELI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.389,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260527160810000161550010000073791608989680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.807,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260527160810000161550010000073801321349708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.255,43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260512077181000133550030002249621339755688</t>
   </si>
   <si>
     <t xml:space="preserve">28.259 - IMD COMERCIO DE MOVEIS LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">409.529</t>
+    <t xml:space="preserve">410.501</t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">3.276,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260503961151000447550060004095291908594429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 - TRAMONTINA TEEC S.A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">684.266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.705,98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260501554846000136550010006842661501852320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">522,97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829761067401777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829751121039328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.385,63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260535635346000140550020001121771279175684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.762,99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260535635346000140550020001121781534580370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.119,25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006394171502977260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.850 - DEXCO S.A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.720,43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - FILIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260597837181005378550010001623201200486876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">446,07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829781228464036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">273,43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829771206775953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.209,61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829971596208423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.083.076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050830761221787698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.727,12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260524546165000393550040000981601962020810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.783,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006396901908194720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.967,67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006397081888143897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.940 - BLUMENAU ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">817.980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.957,37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260579416459000120550010008179801823855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">506,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007578201370188640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.023,78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006399571193331798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.206,41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260510691158000370550010002932181828516528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.329 - S &amp; L SOUZA E LIMA FABRICACAO E COMERCIO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">683,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260510394416000195550010000482621000254830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">261.906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.873,06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260558329608000144550010002619061002619078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.369,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007586021560856835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.923 - NEW LINE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">938,36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260512077181000133550030002249851510571498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260511389565000200570050003993481000856160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375,13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260512077181000133550030002249861111696979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050856481644529258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.503,54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575821546000102550040001404991623793421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.288 - ITAMONTE ILUM EIRELI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.389,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260527160810000161550010000073791608989680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.807,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260527160810000161550010000073801321349708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.255,43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25,34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260512077181000133550030002249621339755688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.664 - STANDARD ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.416,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260556365423000160550010000120471129493398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260511389565000200570050003993491000856175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">410.501</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.535,23</t>
   </si>
   <si>
@@ -959,6 +842,54 @@
   </si>
   <si>
     <t xml:space="preserve">35260512077181000133550030002249611055606702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.628 - VFL IMPORTADORA E DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.412,66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260505104359000122550010000046901793546356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855721283787591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855731188671996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.491,07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855711577662802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050856521165316109</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17204,7 +17135,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM78"/>
+  <dimension ref="A1:BM74"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17958,7 +17889,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>306714</v>
+        <v>306715</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>81</v>
@@ -17985,7 +17916,7 @@
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>567.53</v>
+        <v>814.81</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17994,16 +17925,16 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>567.53</v>
+        <v>814.81</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.08136</v>
+        <v>0.034656</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>26.3</v>
+        <v>16.14</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
@@ -18027,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>567.53</v>
+        <v>814.81</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>39.73</v>
+        <v>57.04</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -18149,7 +18080,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>306715</v>
+        <v>306717</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>81</v>
@@ -18164,7 +18095,7 @@
         <v>83</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>68</v>
@@ -18176,7 +18107,7 @@
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>814.81</v>
+        <v>1070.58</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -18185,22 +18116,22 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>814.81</v>
+        <v>1070.58</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.034656</v>
+        <v>0.095984</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>16.14</v>
+        <v>41.84</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
@@ -18218,10 +18149,10 @@
         <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>814.81</v>
+        <v>1070.58</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>57.04</v>
+        <v>74.94</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18326,7 +18257,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18340,34 +18271,34 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306717</v>
+        <v>307049</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>1070.58</v>
+        <v>174.72</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -18376,43 +18307,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>1070.58</v>
+        <v>159.2</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.095984</v>
+        <v>0</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>41.84</v>
+        <v>0</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>0</v>
+        <v>15.52</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>1070.58</v>
+        <v>159.2</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>74.94</v>
+        <v>11.14</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18481,7 +18412,7 @@
         <v>76</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18517,7 +18448,7 @@
         <v>78</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18531,43 +18462,43 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>307049</v>
+        <v>307051</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="J10" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>174.72</v>
+        <v>7413.56</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>159.2</v>
+        <v>6754.95</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
@@ -18588,22 +18519,22 @@
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>15.52</v>
+        <v>658.61</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>159.2</v>
+        <v>6754.95</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>11.14</v>
+        <v>468.39</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18722,79 +18653,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>307051</v>
+        <v>307084</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>7413.56</v>
+        <v>54.66</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>6754.95</v>
+        <v>51.32</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0</v>
+        <v>0.134276</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>658.61</v>
+        <v>3.34</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>6754.95</v>
+        <v>51.32</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>468.39</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18899,7 +18830,7 @@
         <v>78</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18913,79 +18844,79 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>307055</v>
+        <v>307085</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2532.07</v>
+        <v>264.8</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>2307.12</v>
+        <v>264.8</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.076024</v>
+        <v>0.00087</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>11.04</v>
+        <v>0.93</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>224.95</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>2307.12</v>
+        <v>264.8</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>161.49</v>
+        <v>18.54</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -19090,7 +19021,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19104,10 +19035,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>307083</v>
+        <v>307086</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -19116,22 +19047,22 @@
         <v>115</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>69</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>1193.88</v>
+        <v>1122.7</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -19140,22 +19071,22 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>1087.82</v>
+        <v>1122.7</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
@@ -19167,16 +19098,16 @@
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>106.06</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>1087.82</v>
+        <v>1122.7</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>43.51</v>
+        <v>44.91</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19185,7 +19116,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="12" t="n">
-        <v>89.72</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="12" t="n">
         <v>0</v>
@@ -19266,25 +19197,25 @@
         <v>75</v>
       </c>
       <c r="BE13" s="14" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="BF13" s="9" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="BH13" s="14" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="BI13" s="9" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="BK13" s="9" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="BL13" s="9" t="s">
         <v>75</v>
@@ -19295,16 +19226,16 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>307084</v>
+        <v>307121</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>66</v>
@@ -19313,16 +19244,16 @@
         <v>69</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>54.66</v>
+        <v>1171.26</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
@@ -19331,43 +19262,43 @@
         <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>51.32</v>
+        <v>1067.21</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.134276</v>
+        <v>0.056916</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>3.34</v>
+        <v>104.05</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>51.32</v>
+        <v>1067.21</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>2.05</v>
+        <v>74.7</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19472,7 +19403,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19486,16 +19417,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>307085</v>
+        <v>307122</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>66</v>
@@ -19504,16 +19435,16 @@
         <v>69</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>264.8</v>
+        <v>63.31</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19522,43 +19453,43 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>264.8</v>
+        <v>57.69</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.00087</v>
+        <v>0.009486</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>264.8</v>
+        <v>57.69</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>18.54</v>
+        <v>4.04</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19627,7 +19558,7 @@
         <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19663,7 +19594,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19677,16 +19608,16 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>307086</v>
+        <v>307170</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>66</v>
@@ -19695,16 +19626,16 @@
         <v>69</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>1122.7</v>
+        <v>404.81</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19713,43 +19644,43 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>1122.7</v>
+        <v>404.81</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.0036</v>
+        <v>0.000858</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>4.85</v>
+        <v>2.43</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="Y16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>1122.7</v>
+        <v>404.81</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>44.91</v>
+        <v>16.19</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19818,7 +19749,7 @@
         <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19854,7 +19785,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19868,79 +19799,79 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>307100</v>
+        <v>307182</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>3768.3</v>
+        <v>1534.81</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>3768.3</v>
+        <v>1490.26</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.216</v>
+        <v>0.108038</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>91.2</v>
+        <v>5</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>0</v>
+        <v>44.55</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>3768.3</v>
+        <v>1490.26</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>263.78</v>
+        <v>104.32</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -20045,7 +19976,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -20059,79 +19990,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>307121</v>
+        <v>307221</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1171.26</v>
+        <v>3768.28</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>1067.21</v>
+        <v>3598.38</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.056916</v>
+        <v>0.536658</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>0</v>
+        <v>34.56</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>104.05</v>
+        <v>169.9</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>1067.21</v>
+        <v>3598.38</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>74.7</v>
+        <v>143.94</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20200,7 +20131,7 @@
         <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20236,7 +20167,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20250,25 +20181,25 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>307122</v>
+        <v>307222</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>78</v>
@@ -20277,7 +20208,7 @@
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>63.31</v>
+        <v>461.96</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20286,22 +20217,22 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>57.69</v>
+        <v>461.96</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.009486</v>
+        <v>0.002057</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -20313,16 +20244,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>57.69</v>
+        <v>461.96</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>4.04</v>
+        <v>18.48</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20391,7 +20322,7 @@
         <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20427,7 +20358,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20441,34 +20372,34 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>307170</v>
+        <v>307224</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>404.81</v>
+        <v>886.44</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20477,43 +20408,43 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>404.81</v>
+        <v>886.44</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.00154</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>2.43</v>
+        <v>0.83</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="Y20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>404.81</v>
+        <v>886.44</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>16.19</v>
+        <v>62.05</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20582,7 +20513,7 @@
         <v>76</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20618,7 +20549,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20632,79 +20563,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307182</v>
+        <v>307273</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1534.81</v>
+        <v>7705.98</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1490.26</v>
+        <v>6908.35</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.108038</v>
+        <v>0.438516</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>5</v>
+        <v>71.6</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>44.55</v>
+        <v>797.63</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>1490.26</v>
+        <v>6908.35</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>104.32</v>
+        <v>358.82</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20809,7 +20740,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20823,79 +20754,79 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307206</v>
+        <v>307276</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>15391.61</v>
+        <v>522.97</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>14024.25</v>
+        <v>491.06</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0</v>
+        <v>0.013568</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>57.33</v>
+        <v>28</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>1367.36</v>
+        <v>31.91</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>14024.25</v>
+        <v>491.06</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>981.71</v>
+        <v>34.38</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -21000,7 +20931,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -21014,79 +20945,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307221</v>
+        <v>307277</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>3768.28</v>
+        <v>1122.7</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>3598.38</v>
+        <v>1122.7</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.536658</v>
+        <v>0.004114</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>34.56</v>
+        <v>4.85</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>169.9</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>3598.38</v>
+        <v>1122.7</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>143.94</v>
+        <v>44.91</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21155,7 +21086,7 @@
         <v>76</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21191,7 +21122,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21205,79 +21136,79 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307222</v>
+        <v>307280</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>461.96</v>
+        <v>2385.63</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>461.96</v>
+        <v>2214.84</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.002057</v>
+        <v>20.166476</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>2.43</v>
+        <v>23.3</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>0</v>
+        <v>43.93</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>0</v>
+        <v>170.79</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>461.96</v>
+        <v>2214.84</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>18.48</v>
+        <v>88.59</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21346,7 +21277,7 @@
         <v>76</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21382,7 +21313,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21396,79 +21327,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307224</v>
+        <v>307281</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>886.44</v>
+        <v>4762.99</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>886.44</v>
+        <v>4546</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.00154</v>
+        <v>0.02738</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>0.83</v>
+        <v>21.28</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>28</v>
+        <v>58.63</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>0</v>
+        <v>216.99</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>886.44</v>
+        <v>4546</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>62.05</v>
+        <v>181.84</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21573,7 +21504,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21587,79 +21518,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307269</v>
+        <v>307296</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>3276</v>
+        <v>4119.25</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>3120</v>
+        <v>4119.25</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.55013</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>18.05</v>
+        <v>250</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>41.33</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>3120</v>
+        <v>4119.25</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>124.8</v>
+        <v>164.77</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21728,7 +21659,7 @@
         <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21764,7 +21695,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21778,79 +21709,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307273</v>
+        <v>307311</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>176</v>
+        <v>106</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>7705.98</v>
+        <v>446.07</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6908.35</v>
+        <v>418.84</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.438516</v>
+        <v>0.134454</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>71.6</v>
+        <v>0.92</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>797.63</v>
+        <v>27.23</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>6908.35</v>
+        <v>418.84</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>358.82</v>
+        <v>23.54</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21955,7 +21886,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21969,58 +21900,58 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307276</v>
+        <v>307312</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>522.97</v>
+        <v>273.43</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>491.06</v>
+        <v>256.74</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.013568</v>
+        <v>0.14364</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
@@ -22032,16 +21963,16 @@
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>31.91</v>
+        <v>16.69</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>491.06</v>
+        <v>256.74</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>34.38</v>
+        <v>10.27</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22146,7 +22077,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22160,79 +22091,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>307277</v>
+        <v>307313</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1122.7</v>
+        <v>4209.61</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>1122.7</v>
+        <v>3952.68</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.004114</v>
+        <v>0.471828</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>4.85</v>
+        <v>7.22</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>256.93</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>1122.7</v>
+        <v>3952.68</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>44.91</v>
+        <v>158.11</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22301,7 +22232,7 @@
         <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22337,7 +22268,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22351,79 +22282,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>307280</v>
+        <v>307314</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2385.63</v>
+        <v>501.26</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>2214.84</v>
+        <v>470.66</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>20.166476</v>
+        <v>0.123032</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>23.3</v>
+        <v>4.49</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>43.93</v>
+        <v>28</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>170.79</v>
+        <v>30.6</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>2214.84</v>
+        <v>470.66</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>88.59</v>
+        <v>18.82</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22528,7 +22459,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22542,79 +22473,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>307281</v>
+        <v>307317</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>4762.99</v>
+        <v>1727.12</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>4546</v>
+        <v>1573.69</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.02738</v>
+        <v>0</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>21.28</v>
+        <v>0</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>58.63</v>
+        <v>42</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>216.99</v>
+        <v>153.43</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>4546</v>
+        <v>1573.69</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>181.84</v>
+        <v>110.16</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22719,7 +22650,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22733,34 +22664,34 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>307296</v>
+        <v>307325</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>4119.25</v>
+        <v>2783.92</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22769,43 +22700,43 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>4119.25</v>
+        <v>2783.92</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.55013</v>
+        <v>0.005548</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>250</v>
+        <v>0.98</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>4119.25</v>
+        <v>2783.92</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>164.77</v>
+        <v>194.87</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22874,7 +22805,7 @@
         <v>76</v>
       </c>
       <c r="AX32" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY32" s="14" t="s">
         <v>75</v>
@@ -22910,7 +22841,7 @@
         <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22924,34 +22855,34 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>307309</v>
+        <v>307326</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1720.43</v>
+        <v>2967.67</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -22960,43 +22891,43 @@
         <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>1720.43</v>
+        <v>2786.54</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0</v>
+        <v>0.027908</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>10.21</v>
+        <v>3.56</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W33" s="9" t="s">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>0</v>
+        <v>181.13</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>1720.43</v>
+        <v>2786.54</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>120.43</v>
+        <v>195.06</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23065,7 +22996,7 @@
         <v>76</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -23101,7 +23032,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23115,79 +23046,79 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>307311</v>
+        <v>307331</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>446.07</v>
+        <v>506.4</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>418.84</v>
+        <v>499.2</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.134454</v>
+        <v>0.032832</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>0.92</v>
+        <v>5.78</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>27.23</v>
+        <v>7.2</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>418.84</v>
+        <v>499.2</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>23.54</v>
+        <v>28.3</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23292,7 +23223,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23306,34 +23237,34 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>307312</v>
+        <v>307333</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>273.43</v>
+        <v>1023.78</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23342,22 +23273,22 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>256.74</v>
+        <v>1023.78</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.14364</v>
+        <v>0.010272</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
@@ -23369,16 +23300,16 @@
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>16.69</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>256.74</v>
+        <v>1023.78</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>10.27</v>
+        <v>71.66</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23483,7 +23414,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23497,79 +23428,79 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>307313</v>
+        <v>307353</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>4209.61</v>
+        <v>2206.41</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>3952.68</v>
+        <v>1942</v>
       </c>
       <c r="P36" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.471828</v>
+        <v>0.0004</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>7.22</v>
+        <v>5.8</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>256.93</v>
+        <v>179.41</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>3952.68</v>
+        <v>2027</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>158.11</v>
+        <v>81.07</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23638,7 +23569,7 @@
         <v>76</v>
       </c>
       <c r="AX36" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY36" s="14" t="s">
         <v>75</v>
@@ -23674,7 +23605,7 @@
         <v>78</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23688,34 +23619,34 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>307314</v>
+        <v>307370</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>501.26</v>
+        <v>683.81</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -23724,22 +23655,22 @@
         <v>2</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>470.66</v>
+        <v>623.06</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.123032</v>
+        <v>0.006756</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
@@ -23751,16 +23682,16 @@
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>30.6</v>
+        <v>60.75</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>470.66</v>
+        <v>623.06</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>18.82</v>
+        <v>43.61</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23865,7 +23796,7 @@
         <v>78</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23879,79 +23810,79 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>307317</v>
+        <v>307375</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>1727.12</v>
+        <v>8873.06</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>1573.69</v>
+        <v>7890.92</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0</v>
+        <v>0.00636</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>42</v>
+        <v>44.19</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>153.43</v>
+        <v>982.14</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>1573.69</v>
+        <v>7890.92</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>110.16</v>
+        <v>552.36</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -24056,7 +23987,7 @@
         <v>78</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24070,79 +24001,79 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>307325</v>
+        <v>307378</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>196</v>
+        <v>66</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>2783.92</v>
+        <v>1369.96</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>2783.92</v>
+        <v>1349.3</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.005548</v>
+        <v>0.122352</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>0.98</v>
+        <v>6.73</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>0</v>
+        <v>20.66</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>2783.92</v>
+        <v>1349.3</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>194.87</v>
+        <v>94.45</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24247,7 +24178,7 @@
         <v>78</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24261,34 +24192,34 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>307326</v>
+        <v>307391</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>2967.67</v>
+        <v>938.36</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
@@ -24297,43 +24228,43 @@
         <v>1</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>2786.54</v>
+        <v>855</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.027908</v>
+        <v>0</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>181.13</v>
+        <v>83.36</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>2786.54</v>
+        <v>855</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>195.06</v>
+        <v>59.85</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24342,7 +24273,7 @@
         <v>0</v>
       </c>
       <c r="AD40" s="12" t="n">
-        <v>0</v>
+        <v>18.94</v>
       </c>
       <c r="AE40" s="12" t="n">
         <v>0</v>
@@ -24399,7 +24330,7 @@
         <v>74</v>
       </c>
       <c r="AW40" s="14" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="AX40" s="10" t="s">
         <v>77</v>
@@ -24423,25 +24354,25 @@
         <v>75</v>
       </c>
       <c r="BE40" s="14" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="BF40" s="9" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="BG40" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="BH40" s="14" t="s">
-        <v>75</v>
+        <v>226</v>
       </c>
       <c r="BI40" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="BK40" s="9" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="BL40" s="9" t="s">
         <v>75</v>
@@ -24452,34 +24383,34 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>307328</v>
+        <v>307392</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>66</v>
+        <v>221</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>2957.37</v>
+        <v>375.13</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
@@ -24488,43 +24419,43 @@
         <v>1</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>2694.64</v>
+        <v>341.8</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.080236</v>
+        <v>0</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>24.96</v>
+        <v>0</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>40.76</v>
+        <v>28</v>
       </c>
       <c r="W41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>262.73</v>
+        <v>33.33</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>2694.64</v>
+        <v>341.8</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>107.79</v>
+        <v>23.93</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24533,7 +24464,7 @@
         <v>0</v>
       </c>
       <c r="AD41" s="12" t="n">
-        <v>0</v>
+        <v>7.57</v>
       </c>
       <c r="AE41" s="12" t="n">
         <v>0</v>
@@ -24590,7 +24521,7 @@
         <v>74</v>
       </c>
       <c r="AW41" s="14" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="AX41" s="10" t="s">
         <v>77</v>
@@ -24614,25 +24545,25 @@
         <v>75</v>
       </c>
       <c r="BE41" s="14" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="BF41" s="9" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="BG41" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="BH41" s="14" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="BI41" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BK41" s="9" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="BL41" s="9" t="s">
         <v>75</v>
@@ -24643,52 +24574,52 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>307331</v>
+        <v>307397</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>231</v>
+        <v>106</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>233</v>
+        <v>159</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>506.4</v>
+        <v>202.92</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>499.2</v>
+        <v>202.92</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.032832</v>
+        <v>0.00963</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>5.78</v>
+        <v>1.65</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
@@ -24700,22 +24631,22 @@
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>499.2</v>
+        <v>202.92</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>28.3</v>
+        <v>14.2</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24834,34 +24765,34 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>307333</v>
+        <v>307402</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>196</v>
+        <v>97</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>218</v>
+        <v>159</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1023.78</v>
+        <v>19503.54</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
@@ -24870,43 +24801,43 @@
         <v>1</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>1023.78</v>
+        <v>19503.54</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.010272</v>
+        <v>1.9872</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>2.14</v>
+        <v>5453.76</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="Y43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>1023.78</v>
+        <v>19503.54</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>71.66</v>
+        <v>1365.25</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24972,7 +24903,7 @@
         <v>74</v>
       </c>
       <c r="AW43" s="14" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="AX43" s="10" t="s">
         <v>77</v>
@@ -25011,7 +24942,7 @@
         <v>78</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -25025,79 +24956,79 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>307353</v>
+        <v>307425</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>218</v>
+        <v>159</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>2206.41</v>
+        <v>1389.3</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>1942</v>
+        <v>1389.3</v>
       </c>
       <c r="P44" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>28</v>
+        <v>38.5</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>179.41</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>2027</v>
+        <v>1389.3</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>81.07</v>
+        <v>41.12</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25163,7 +25094,7 @@
         <v>74</v>
       </c>
       <c r="AW44" s="14" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="AX44" s="10" t="s">
         <v>77</v>
@@ -25202,7 +25133,7 @@
         <v>78</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25216,34 +25147,34 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>307370</v>
+        <v>307426</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>197</v>
+        <v>136</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>246</v>
+        <v>159</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>683.81</v>
+        <v>1807.1</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
@@ -25252,43 +25183,43 @@
         <v>2</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>623.06</v>
+        <v>1807.1</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.006756</v>
+        <v>0.024</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>28</v>
+        <v>46.01</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>60.75</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>623.06</v>
+        <v>1807.1</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>43.61</v>
+        <v>53.49</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25354,7 +25285,7 @@
         <v>74</v>
       </c>
       <c r="AW45" s="14" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="AX45" s="10" t="s">
         <v>77</v>
@@ -25393,7 +25324,7 @@
         <v>78</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25407,34 +25338,34 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>307375</v>
+        <v>307463</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>66</v>
+        <v>221</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>8873.06</v>
+        <v>1255.43</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -25443,43 +25374,43 @@
         <v>5</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>7890.92</v>
+        <v>1163.96</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.00636</v>
+        <v>0</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>44.19</v>
+        <v>28</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>982.14</v>
+        <v>91.47</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>7890.92</v>
+        <v>1163.96</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>552.36</v>
+        <v>81.47</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25488,7 +25419,7 @@
         <v>0</v>
       </c>
       <c r="AD46" s="12" t="n">
-        <v>0</v>
+        <v>25.34</v>
       </c>
       <c r="AE46" s="12" t="n">
         <v>0</v>
@@ -25569,25 +25500,25 @@
         <v>75</v>
       </c>
       <c r="BE46" s="14" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="BF46" s="9" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="BG46" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="BH46" s="14" t="s">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="BI46" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="BJ46" s="9" t="s">
         <v>251</v>
       </c>
       <c r="BK46" s="9" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="BL46" s="9" t="s">
         <v>75</v>
@@ -25598,79 +25529,79 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>307378</v>
+        <v>307470</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>66</v>
+        <v>254</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>253</v>
+        <v>159</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1369.96</v>
+        <v>2535.23</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>1349.3</v>
+        <v>2310</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.122352</v>
+        <v>14</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>6.73</v>
+        <v>3.5</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>61</v>
+        <v>40.76</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>20.66</v>
+        <v>225.23</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>1349.3</v>
+        <v>2310</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>94.45</v>
+        <v>92.4</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25736,7 +25667,7 @@
         <v>74</v>
       </c>
       <c r="AW47" s="14" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="AX47" s="10" t="s">
         <v>77</v>
@@ -25775,7 +25706,7 @@
         <v>78</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25789,10 +25720,10 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>307391</v>
+        <v>307472</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>256</v>
+        <v>193</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -25801,40 +25732,40 @@
         <v>257</v>
       </c>
       <c r="G48" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="J48" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>938.36</v>
+        <v>2428.23</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>855</v>
+        <v>2410.9</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0</v>
+        <v>0.244932</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>0</v>
+        <v>21.65</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
@@ -25846,22 +25777,22 @@
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>83.36</v>
+        <v>17.33</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>855</v>
+        <v>2410.9</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>59.85</v>
+        <v>164.1</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25870,7 +25801,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="12" t="n">
-        <v>18.94</v>
+        <v>0</v>
       </c>
       <c r="AE48" s="12" t="n">
         <v>0</v>
@@ -25927,7 +25858,7 @@
         <v>74</v>
       </c>
       <c r="AW48" s="14" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="AX48" s="10" t="s">
         <v>77</v>
@@ -25951,25 +25882,25 @@
         <v>75</v>
       </c>
       <c r="BE48" s="14" t="s">
-        <v>261</v>
+        <v>75</v>
       </c>
       <c r="BF48" s="9" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="BG48" s="9" t="s">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="BH48" s="14" t="s">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="BI48" s="9" t="s">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BK48" s="9" t="s">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="BL48" s="9" t="s">
         <v>75</v>
@@ -25980,34 +25911,34 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>307392</v>
+        <v>307475</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>375.13</v>
+        <v>3351.6</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
@@ -26016,43 +25947,43 @@
         <v>1</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>341.8</v>
+        <v>3351.6</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0</v>
+        <v>0.001236</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>341.8</v>
+        <v>3351.6</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>23.93</v>
+        <v>234.61</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26061,7 +25992,7 @@
         <v>0</v>
       </c>
       <c r="AD49" s="12" t="n">
-        <v>7.57</v>
+        <v>0</v>
       </c>
       <c r="AE49" s="12" t="n">
         <v>0</v>
@@ -26118,7 +26049,7 @@
         <v>74</v>
       </c>
       <c r="AW49" s="14" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="AX49" s="10" t="s">
         <v>77</v>
@@ -26142,25 +26073,25 @@
         <v>75</v>
       </c>
       <c r="BE49" s="14" t="s">
-        <v>261</v>
+        <v>75</v>
       </c>
       <c r="BF49" s="9" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="BG49" s="9" t="s">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="BH49" s="14" t="s">
-        <v>267</v>
+        <v>75</v>
       </c>
       <c r="BI49" s="9" t="s">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="BK49" s="9" t="s">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="BL49" s="9" t="s">
         <v>75</v>
@@ -26171,34 +26102,34 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>307397</v>
+        <v>307501</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>125</v>
+        <v>265</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>188</v>
+        <v>132</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>202.92</v>
+        <v>960.64</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
@@ -26207,22 +26138,22 @@
         <v>1</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>202.92</v>
+        <v>875.3</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.00963</v>
+        <v>0.00556</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="U50" s="15" t="s">
         <v>72</v>
@@ -26234,16 +26165,16 @@
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>0</v>
+        <v>85.34</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>202.92</v>
+        <v>875.3</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>14.2</v>
+        <v>35.01</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26309,7 +26240,7 @@
         <v>74</v>
       </c>
       <c r="AW50" s="14" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="AX50" s="10" t="s">
         <v>77</v>
@@ -26348,7 +26279,7 @@
         <v>78</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26362,58 +26293,58 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>307402</v>
+        <v>307506</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>100</v>
+        <v>221</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>245</v>
+        <v>168</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>19503.54</v>
+        <v>5980.14</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>19503.54</v>
+        <v>5541.97</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>1.9872</v>
+        <v>0</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>5453.76</v>
+        <v>3.6</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
@@ -26425,16 +26356,16 @@
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>0</v>
+        <v>438.17</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>19503.54</v>
+        <v>5541.97</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>1365.25</v>
+        <v>387.94</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26443,7 +26374,7 @@
         <v>0</v>
       </c>
       <c r="AD51" s="12" t="n">
-        <v>0</v>
+        <v>120.72</v>
       </c>
       <c r="AE51" s="12" t="n">
         <v>0</v>
@@ -26500,7 +26431,7 @@
         <v>74</v>
       </c>
       <c r="AW51" s="14" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="AX51" s="10" t="s">
         <v>77</v>
@@ -26524,25 +26455,25 @@
         <v>75</v>
       </c>
       <c r="BE51" s="14" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="BF51" s="9" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="BG51" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="BH51" s="14" t="s">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="BI51" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="BK51" s="9" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="BL51" s="9" t="s">
         <v>75</v>
@@ -26553,52 +26484,52 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>307425</v>
+        <v>307540</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="I52" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="J52" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>1389.3</v>
+        <v>4412.66</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>1389.3</v>
+        <v>4412.66</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0</v>
+        <v>0.005301</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>2</v>
+        <v>5.95</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
@@ -26610,22 +26541,22 @@
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>38.5</v>
+        <v>61.33</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>1389.3</v>
+        <v>4412.66</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>41.12</v>
+        <v>176.5</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26691,7 +26622,7 @@
         <v>74</v>
       </c>
       <c r="AW52" s="14" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="AX52" s="10" t="s">
         <v>77</v>
@@ -26744,10 +26675,10 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>307426</v>
+        <v>307570</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>275</v>
+        <v>106</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
@@ -26759,37 +26690,37 @@
         <v>66</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>1807.1</v>
+        <v>355.13</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>1807.1</v>
+        <v>355.13</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0.024</v>
+        <v>0.00819</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>6</v>
+        <v>2.17</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
@@ -26801,22 +26732,22 @@
         <v>72</v>
       </c>
       <c r="V53" s="12" t="n">
-        <v>46.01</v>
+        <v>0</v>
       </c>
       <c r="W53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>1807.1</v>
+        <v>355.13</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>53.49</v>
+        <v>14.21</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -26882,10 +26813,10 @@
         <v>74</v>
       </c>
       <c r="AW53" s="14" t="s">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="AX53" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY53" s="14" t="s">
         <v>75</v>
@@ -26935,10 +26866,10 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>307463</v>
+        <v>307571</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>256</v>
+        <v>106</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -26947,67 +26878,67 @@
         <v>283</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>258</v>
+        <v>66</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>1255.43</v>
+        <v>355.13</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>1163.96</v>
+        <v>355.13</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0</v>
+        <v>0.00819</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V54" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W54" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y54" s="12" t="n">
-        <v>91.47</v>
+        <v>0</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>1163.96</v>
+        <v>355.13</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>81.47</v>
+        <v>14.21</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27016,7 +26947,7 @@
         <v>0</v>
       </c>
       <c r="AD54" s="12" t="n">
-        <v>25.34</v>
+        <v>0</v>
       </c>
       <c r="AE54" s="12" t="n">
         <v>0</v>
@@ -27076,7 +27007,7 @@
         <v>76</v>
       </c>
       <c r="AX54" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY54" s="14" t="s">
         <v>75</v>
@@ -27097,25 +27028,25 @@
         <v>75</v>
       </c>
       <c r="BE54" s="14" t="s">
-        <v>261</v>
+        <v>75</v>
       </c>
       <c r="BF54" s="9" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="BG54" s="9" t="s">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="BH54" s="14" t="s">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="BI54" s="9" t="s">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="BJ54" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="BK54" s="9" t="s">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="BL54" s="9" t="s">
         <v>75</v>
@@ -27126,79 +27057,79 @@
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>307464</v>
+        <v>307573</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>287</v>
+        <v>106</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>1416.24</v>
+        <v>1491.07</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>1290.43</v>
+        <v>1400.07</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>0</v>
+        <v>0.022383</v>
       </c>
       <c r="R55" s="12" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="S55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="14" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="U55" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V55" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W55" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X55" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y55" s="12" t="n">
-        <v>125.81</v>
+        <v>91</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>1290.43</v>
+        <v>1400.07</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>90.33</v>
+        <v>56</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27207,7 +27138,7 @@
         <v>0</v>
       </c>
       <c r="AD55" s="12" t="n">
-        <v>89.72</v>
+        <v>0</v>
       </c>
       <c r="AE55" s="12" t="n">
         <v>0</v>
@@ -27267,7 +27198,7 @@
         <v>76</v>
       </c>
       <c r="AX55" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY55" s="14" t="s">
         <v>75</v>
@@ -27288,25 +27219,25 @@
         <v>75</v>
       </c>
       <c r="BE55" s="14" t="s">
-        <v>290</v>
+        <v>75</v>
       </c>
       <c r="BF55" s="9" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="BG55" s="9" t="s">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="BH55" s="14" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="BI55" s="9" t="s">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="BJ55" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="BK55" s="9" t="s">
-        <v>292</v>
+        <v>75</v>
       </c>
       <c r="BL55" s="9" t="s">
         <v>75</v>
@@ -27317,79 +27248,79 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>307470</v>
+        <v>307577</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2535.23</v>
+        <v>355.13</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>2310</v>
+        <v>355.13</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>14</v>
+        <v>0.00819</v>
       </c>
       <c r="R56" s="12" t="n">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="S56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T56" s="14" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="U56" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V56" s="12" t="n">
-        <v>40.76</v>
+        <v>0</v>
       </c>
       <c r="W56" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X56" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y56" s="12" t="n">
-        <v>225.23</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="12" t="n">
-        <v>2310</v>
+        <v>355.13</v>
       </c>
       <c r="AA56" s="12" t="n">
-        <v>92.4</v>
+        <v>14.21</v>
       </c>
       <c r="AB56" s="12" t="n">
         <v>0</v>
@@ -27455,10 +27386,10 @@
         <v>74</v>
       </c>
       <c r="AW56" s="14" t="s">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="AX56" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY56" s="14" t="s">
         <v>75</v>
@@ -27494,7 +27425,7 @@
         <v>78</v>
       </c>
       <c r="BJ56" s="9" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="BK56" s="9" t="s">
         <v>75</v>
@@ -27507,1091 +27438,603 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="n">
-        <v>307472</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9" t="s">
+      <c r="A57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M59" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="N59" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O59" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P59" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q59" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S59" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="T59" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>2428.23</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>2410.9</v>
-      </c>
-      <c r="P57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="13" t="n">
-        <v>0.244932</v>
-      </c>
-      <c r="R57" s="12" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="S57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="U57" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V57" s="12" t="n">
-        <v>123</v>
-      </c>
-      <c r="W57" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X57" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y57" s="12" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="Z57" s="12" t="n">
-        <v>2410.9</v>
-      </c>
-      <c r="AA57" s="12" t="n">
-        <v>164.1</v>
-      </c>
-      <c r="AB57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW57" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX57" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG57" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI57" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ57" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="BK57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM57" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="n">
-        <v>307475</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L58" s="12" t="n">
-        <v>3351.6</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" s="12" t="n">
-        <v>3351.6</v>
-      </c>
-      <c r="P58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="13" t="n">
-        <v>0.001236</v>
-      </c>
-      <c r="R58" s="12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="U58" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V58" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W58" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X58" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="12" t="n">
-        <v>3351.6</v>
-      </c>
-      <c r="AA58" s="12" t="n">
-        <v>234.61</v>
-      </c>
-      <c r="AB58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW58" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX58" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG58" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI58" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ58" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="BK58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM58" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="n">
-        <v>307501</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>960.64</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" s="12" t="n">
-        <v>875.3</v>
-      </c>
-      <c r="P59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="13" t="n">
-        <v>0.00556</v>
-      </c>
-      <c r="R59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="U59" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V59" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W59" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X59" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="Y59" s="12" t="n">
-        <v>85.34</v>
-      </c>
-      <c r="Z59" s="12" t="n">
-        <v>875.3</v>
-      </c>
-      <c r="AA59" s="12" t="n">
-        <v>35.01</v>
-      </c>
-      <c r="AB59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW59" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX59" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG59" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI59" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ59" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="BK59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM59" s="16" t="s">
-        <v>80</v>
+      <c r="U59" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V59" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="n">
-        <v>307506</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="K60" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L60" s="12" t="n">
-        <v>5980.14</v>
-      </c>
-      <c r="M60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O60" s="12" t="n">
-        <v>5541.97</v>
-      </c>
-      <c r="P60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="U60" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V60" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="W60" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X60" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="Y60" s="12" t="n">
-        <v>438.17</v>
-      </c>
-      <c r="Z60" s="12" t="n">
-        <v>5541.97</v>
-      </c>
-      <c r="AA60" s="12" t="n">
-        <v>387.94</v>
-      </c>
-      <c r="AB60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="12" t="n">
-        <v>120.72</v>
-      </c>
-      <c r="AE60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW60" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX60" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE60" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="BF60" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="BG60" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="BH60" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="BI60" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="BJ60" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="BK60" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL60" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM60" s="16" t="s">
-        <v>80</v>
+      <c r="A60" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>85</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>5200.31</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>111493.56</v>
+      </c>
+      <c r="G60" s="19" t="n">
+        <v>6562.71</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v>172.57</v>
+      </c>
+      <c r="K60" s="19" t="n">
+        <v>116693.87</v>
+      </c>
+      <c r="L60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="20" t="n">
+        <v>39.848973</v>
+      </c>
+      <c r="S60" s="19" t="n">
+        <v>111408.56</v>
+      </c>
+      <c r="T60" s="19" t="n">
+        <v>116693.87</v>
+      </c>
+      <c r="U60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4"/>
+    <row r="61" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I61" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K61" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="L61" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="M61" s="18" t="s">
+        <v>299</v>
+      </c>
     </row>
-    <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
-      <c r="S62" s="17"/>
-      <c r="T62" s="17"/>
-      <c r="U62" s="17"/>
-      <c r="V62" s="17"/>
+    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="19" t="n">
+        <v>6075.66</v>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I63" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="J63" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K63" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L63" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M63" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="N63" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O63" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P63" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R63" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S63" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="T63" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="U63" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V63" s="18" t="s">
-        <v>37</v>
-      </c>
+    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="19" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="19" t="n">
-        <v>85</v>
-      </c>
-      <c r="D64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="19" t="n">
-        <v>7352.22</v>
-      </c>
-      <c r="F64" s="19" t="n">
-        <v>135195.96</v>
-      </c>
-      <c r="G64" s="19" t="n">
-        <v>8221.15</v>
-      </c>
-      <c r="H64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="19" t="n">
-        <v>352.01</v>
-      </c>
-      <c r="K64" s="19" t="n">
-        <v>142548.18</v>
-      </c>
-      <c r="L64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="20" t="n">
-        <v>40.250339</v>
-      </c>
-      <c r="S64" s="19" t="n">
-        <v>135110.96</v>
-      </c>
-      <c r="T64" s="19" t="n">
-        <v>142548.18</v>
-      </c>
-      <c r="U64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="19" t="n">
-        <v>0</v>
-      </c>
+    <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="21"/>
+      <c r="M64" s="21"/>
+      <c r="N64" s="21"/>
+      <c r="O64" s="21"/>
+      <c r="P64" s="21"/>
+      <c r="Q64" s="21"/>
+      <c r="R64" s="21"/>
+      <c r="S64" s="21"/>
+      <c r="T64" s="21"/>
+      <c r="U64" s="21"/>
+      <c r="V64" s="21"/>
+      <c r="W64" s="21"/>
+      <c r="X64" s="21"/>
+      <c r="Y64" s="21"/>
+      <c r="Z64" s="21"/>
+      <c r="AA64" s="21"/>
+      <c r="AB64" s="21"/>
+      <c r="AC64" s="21"/>
+      <c r="AD64" s="21"/>
+      <c r="AE64" s="21"/>
+      <c r="AF64" s="21"/>
+      <c r="AG64" s="21"/>
+      <c r="AH64" s="21"/>
+      <c r="AI64" s="21"/>
+      <c r="AJ64" s="21"/>
+      <c r="AK64" s="21"/>
+      <c r="AL64" s="21"/>
+      <c r="AM64" s="21"/>
+      <c r="AN64" s="21"/>
+      <c r="AO64" s="21"/>
+      <c r="AP64" s="21"/>
+      <c r="AQ64" s="21"/>
+      <c r="AR64" s="21"/>
+      <c r="AS64" s="21"/>
+      <c r="AT64" s="21"/>
+      <c r="AU64" s="21"/>
+      <c r="AV64" s="21"/>
+      <c r="AW64" s="21"/>
+      <c r="AX64" s="21"/>
+      <c r="AY64" s="21"/>
+      <c r="AZ64" s="21"/>
+      <c r="BA64" s="21"/>
+      <c r="BB64" s="21"/>
+      <c r="BC64" s="21"/>
+      <c r="BD64" s="21"/>
+      <c r="BE64" s="21"/>
+      <c r="BF64" s="21"/>
+      <c r="BG64" s="21"/>
+      <c r="BH64" s="21"/>
+      <c r="BI64" s="21"/>
+      <c r="BJ64" s="21"/>
+      <c r="BK64" s="21"/>
+      <c r="BL64" s="21"/>
+      <c r="BM64" s="21"/>
     </row>
-    <row r="65" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B65" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F65" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G65" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I65" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J65" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K65" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="L65" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="M65" s="18" t="s">
-        <v>322</v>
-      </c>
+    <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4"/>
+      <c r="AD65" s="4"/>
+      <c r="AE65" s="4"/>
+      <c r="AF65" s="4"/>
+      <c r="AG65" s="4"/>
+      <c r="AH65" s="4"/>
+      <c r="AI65" s="4"/>
+      <c r="AJ65" s="4"/>
+      <c r="AK65" s="4"/>
+      <c r="AL65" s="4"/>
+      <c r="AM65" s="4"/>
+      <c r="AN65" s="4"/>
+      <c r="AO65" s="4"/>
+      <c r="AP65" s="4"/>
+      <c r="AQ65" s="4"/>
+      <c r="AR65" s="4"/>
+      <c r="AS65" s="4"/>
+      <c r="AT65" s="4"/>
+      <c r="AU65" s="4"/>
+      <c r="AV65" s="4"/>
+      <c r="AW65" s="4"/>
+      <c r="AX65" s="4"/>
+      <c r="AY65" s="4"/>
+      <c r="AZ65" s="4"/>
+      <c r="BA65" s="4"/>
+      <c r="BB65" s="4"/>
+      <c r="BC65" s="4"/>
+      <c r="BD65" s="4"/>
+      <c r="BE65" s="4"/>
+      <c r="BF65" s="4"/>
+      <c r="BG65" s="4"/>
+      <c r="BH65" s="4"/>
+      <c r="BI65" s="4"/>
+      <c r="BJ65" s="4"/>
+      <c r="BK65" s="4"/>
+      <c r="BL65" s="4"/>
+      <c r="BM65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="19" t="n">
-        <v>6232.35</v>
-      </c>
-      <c r="B66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="19" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="E66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A66" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="4"/>
+      <c r="AD66" s="4"/>
+      <c r="AE66" s="4"/>
+      <c r="AF66" s="4"/>
+      <c r="AG66" s="4"/>
+      <c r="AH66" s="4"/>
+      <c r="AI66" s="4"/>
+      <c r="AJ66" s="4"/>
+      <c r="AK66" s="4"/>
+      <c r="AL66" s="4"/>
+      <c r="AM66" s="4"/>
+      <c r="AN66" s="4"/>
+      <c r="AO66" s="4"/>
+      <c r="AP66" s="4"/>
+      <c r="AQ66" s="4"/>
+      <c r="AR66" s="4"/>
+      <c r="AS66" s="4"/>
+      <c r="AT66" s="4"/>
+      <c r="AU66" s="4"/>
+      <c r="AV66" s="4"/>
+      <c r="AW66" s="4"/>
+      <c r="AX66" s="4"/>
+      <c r="AY66" s="4"/>
+      <c r="AZ66" s="4"/>
+      <c r="BA66" s="4"/>
+      <c r="BB66" s="4"/>
+      <c r="BC66" s="4"/>
+      <c r="BD66" s="4"/>
+      <c r="BE66" s="4"/>
+      <c r="BF66" s="4"/>
+      <c r="BG66" s="4"/>
+      <c r="BH66" s="4"/>
+      <c r="BI66" s="4"/>
+      <c r="BJ66" s="4"/>
+      <c r="BK66" s="4"/>
+      <c r="BL66" s="4"/>
+      <c r="BM66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4"/>
+      <c r="A67" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4"/>
+      <c r="AD67" s="4"/>
+      <c r="AE67" s="4"/>
+      <c r="AF67" s="4"/>
+      <c r="AG67" s="4"/>
+      <c r="AH67" s="4"/>
+      <c r="AI67" s="4"/>
+      <c r="AJ67" s="4"/>
+      <c r="AK67" s="4"/>
+      <c r="AL67" s="4"/>
+      <c r="AM67" s="4"/>
+      <c r="AN67" s="4"/>
+      <c r="AO67" s="4"/>
+      <c r="AP67" s="4"/>
+      <c r="AQ67" s="4"/>
+      <c r="AR67" s="4"/>
+      <c r="AS67" s="4"/>
+      <c r="AT67" s="4"/>
+      <c r="AU67" s="4"/>
+      <c r="AV67" s="4"/>
+      <c r="AW67" s="4"/>
+      <c r="AX67" s="4"/>
+      <c r="AY67" s="4"/>
+      <c r="AZ67" s="4"/>
+      <c r="BA67" s="4"/>
+      <c r="BB67" s="4"/>
+      <c r="BC67" s="4"/>
+      <c r="BD67" s="4"/>
+      <c r="BE67" s="4"/>
+      <c r="BF67" s="4"/>
+      <c r="BG67" s="4"/>
+      <c r="BH67" s="4"/>
+      <c r="BI67" s="4"/>
+      <c r="BJ67" s="4"/>
+      <c r="BK67" s="4"/>
+      <c r="BL67" s="4"/>
+      <c r="BM67" s="4"/>
     </row>
-    <row r="68" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
-      <c r="P68" s="21"/>
-      <c r="Q68" s="21"/>
-      <c r="R68" s="21"/>
-      <c r="S68" s="21"/>
-      <c r="T68" s="21"/>
-      <c r="U68" s="21"/>
-      <c r="V68" s="21"/>
-      <c r="W68" s="21"/>
-      <c r="X68" s="21"/>
-      <c r="Y68" s="21"/>
-      <c r="Z68" s="21"/>
-      <c r="AA68" s="21"/>
-      <c r="AB68" s="21"/>
-      <c r="AC68" s="21"/>
-      <c r="AD68" s="21"/>
-      <c r="AE68" s="21"/>
-      <c r="AF68" s="21"/>
-      <c r="AG68" s="21"/>
-      <c r="AH68" s="21"/>
-      <c r="AI68" s="21"/>
-      <c r="AJ68" s="21"/>
-      <c r="AK68" s="21"/>
-      <c r="AL68" s="21"/>
-  